--- a/wwwroot/template/TemPlateQuote.xlsx
+++ b/wwwroot/template/TemPlateQuote.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\khanhmf\Cost Managerment\wwwroot\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE926360-FC8C-43B8-AFA5-A6B87905164F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{763D4767-76BC-4C8C-A850-AC2FD00ACA1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F4BD22E2-5202-4BAA-B608-770E176E4E09}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F4BD22E2-5202-4BAA-B608-770E176E4E09}"/>
   </bookViews>
   <sheets>
     <sheet name="Form blank" sheetId="2" r:id="rId1"/>
@@ -714,7 +714,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="641">
   <si>
     <t>No</t>
   </si>
@@ -762,336 +762,66 @@
     <t>Ngày 日付(*)</t>
   </si>
   <si>
-    <t>1110</t>
-  </si>
-  <si>
-    <t>GA-GA-CANTEEN</t>
-  </si>
-  <si>
-    <t>1130</t>
-  </si>
-  <si>
-    <t>GA-GA-DORMITORY</t>
-  </si>
-  <si>
-    <t>1210</t>
-  </si>
-  <si>
-    <t>GA-GA</t>
-  </si>
-  <si>
-    <t>1211</t>
-  </si>
-  <si>
-    <t>ADM-PER</t>
-  </si>
-  <si>
-    <t>1212</t>
-  </si>
-  <si>
     <t>GA-SFE</t>
   </si>
   <si>
-    <t>1220</t>
-  </si>
-  <si>
     <t>GA-FAC</t>
   </si>
   <si>
-    <t>1221</t>
-  </si>
-  <si>
     <t>TT Factory GA COMMON</t>
   </si>
   <si>
-    <t>1310</t>
-  </si>
-  <si>
-    <t>ADM-ACC</t>
-  </si>
-  <si>
-    <t>1410</t>
-  </si>
-  <si>
     <t>ADM-MP</t>
   </si>
   <si>
-    <t>2210</t>
-  </si>
-  <si>
-    <t>PR2-PR2 COMMON</t>
-  </si>
-  <si>
-    <t>2310</t>
-  </si>
-  <si>
-    <t>R&amp;D-PE</t>
-  </si>
-  <si>
-    <t>2311</t>
-  </si>
-  <si>
     <t>R&amp;D-EE</t>
   </si>
   <si>
-    <t>2312</t>
-  </si>
-  <si>
-    <t>R&amp;D-DE</t>
-  </si>
-  <si>
-    <t>2421</t>
-  </si>
-  <si>
-    <t>PR1-PR3-SP</t>
-  </si>
-  <si>
-    <t>2490</t>
-  </si>
-  <si>
-    <t>PR1-PR3 COMMON</t>
-  </si>
-  <si>
-    <t>2510</t>
-  </si>
-  <si>
-    <t>PR1-MC</t>
-  </si>
-  <si>
-    <t>2610</t>
-  </si>
-  <si>
-    <t>PR2-PR4 COMMON</t>
-  </si>
-  <si>
-    <t>2710</t>
-  </si>
-  <si>
     <t>PR2-PR5 COMMON</t>
   </si>
   <si>
-    <t>3110</t>
-  </si>
-  <si>
-    <t>PUR-PUR</t>
-  </si>
-  <si>
-    <t>3111</t>
-  </si>
-  <si>
     <t>PUR-PRO</t>
   </si>
   <si>
-    <t>3210</t>
-  </si>
-  <si>
-    <t>PC-SHIP</t>
-  </si>
-  <si>
-    <t>PC-SHIP-OF</t>
-  </si>
-  <si>
-    <t>3211</t>
-  </si>
-  <si>
     <t>PC-SHIP-WH</t>
   </si>
   <si>
-    <t>3212</t>
-  </si>
-  <si>
     <t>TT Factory - PC-SHIP WH</t>
   </si>
   <si>
-    <t>3310</t>
-  </si>
-  <si>
-    <t>PC-PC</t>
-  </si>
-  <si>
-    <t>3320</t>
-  </si>
-  <si>
-    <t>PC-MC</t>
-  </si>
-  <si>
-    <t>3321</t>
-  </si>
-  <si>
     <t>TT Factory - PC-MC</t>
   </si>
   <si>
-    <t>3410</t>
-  </si>
-  <si>
-    <t>SQM-SEM</t>
-  </si>
-  <si>
-    <t>3510</t>
-  </si>
-  <si>
-    <t>ADM-IT</t>
-  </si>
-  <si>
-    <t>R&amp;D-IT</t>
-  </si>
-  <si>
-    <t>4110</t>
-  </si>
-  <si>
-    <t>QA-QA</t>
-  </si>
-  <si>
-    <t>4111</t>
-  </si>
-  <si>
     <t>TT Factory - QA-QA</t>
   </si>
   <si>
-    <t>4140</t>
-  </si>
-  <si>
     <t>QA-QM</t>
   </si>
   <si>
-    <t>4210</t>
-  </si>
-  <si>
-    <t>SQM-IQC</t>
-  </si>
-  <si>
-    <t>4211</t>
-  </si>
-  <si>
     <t>TT Factory - SQM-IQC</t>
   </si>
   <si>
-    <t>4230</t>
-  </si>
-  <si>
-    <t>SQM-SQC</t>
-  </si>
-  <si>
-    <t>4240</t>
-  </si>
-  <si>
     <t>SQM-PSU</t>
   </si>
   <si>
-    <t>5110</t>
-  </si>
-  <si>
-    <t>MPE-MP1 (F1)</t>
-  </si>
-  <si>
-    <t>PP-MP1-F1</t>
-  </si>
-  <si>
-    <t>5120</t>
-  </si>
-  <si>
-    <t>MPE-MP1 (M301)</t>
-  </si>
-  <si>
-    <t>MPE-MP2-M301</t>
-  </si>
-  <si>
-    <t>PP-MP4-M301</t>
-  </si>
-  <si>
-    <t>5130</t>
-  </si>
-  <si>
-    <t>MPE-MP1 (F4)</t>
-  </si>
-  <si>
-    <t>MPE-MP3-F4</t>
-  </si>
-  <si>
-    <t>PP-MP2-F4</t>
-  </si>
-  <si>
-    <t>5150</t>
-  </si>
-  <si>
-    <t>MPE-MP1 (COMMON)</t>
-  </si>
-  <si>
-    <t>MPE-MP-MM</t>
-  </si>
-  <si>
-    <t>5170</t>
-  </si>
-  <si>
-    <t>MPE-PE</t>
-  </si>
-  <si>
-    <t>5210</t>
-  </si>
-  <si>
-    <t>MPE-MP2 (PLASTIC)</t>
-  </si>
-  <si>
     <t>MPE-MP-TTF</t>
   </si>
   <si>
-    <t>6110</t>
-  </si>
-  <si>
-    <t>R&amp;D-BPS</t>
-  </si>
-  <si>
-    <t>STR-BPS</t>
-  </si>
-  <si>
-    <t>7110</t>
-  </si>
-  <si>
     <t>EPE-PCB COMMON</t>
   </si>
   <si>
-    <t>7111</t>
-  </si>
-  <si>
     <t>EPE-PCB SUB-PS PCB</t>
   </si>
   <si>
-    <t>7112</t>
-  </si>
-  <si>
     <t>EPE-PCB MAIN PCB</t>
   </si>
   <si>
-    <t>7120</t>
-  </si>
-  <si>
     <t>EPE-EE</t>
   </si>
   <si>
-    <t>8110</t>
-  </si>
-  <si>
     <t>Strategy Promotion section</t>
   </si>
   <si>
-    <t>A004</t>
-  </si>
-  <si>
-    <t>PR1-PR1-DSL SCANNER</t>
-  </si>
-  <si>
-    <t>A005</t>
-  </si>
-  <si>
-    <t>PR1-PR1-DLL SCANNER</t>
-  </si>
-  <si>
-    <t>A006</t>
-  </si>
-  <si>
-    <t>PR1-PR1-DL SCANNER</t>
-  </si>
-  <si>
     <t>A007</t>
   </si>
   <si>
@@ -1101,9 +831,6 @@
     <t>A008</t>
   </si>
   <si>
-    <t>PR1-PR1-EL SCANNER</t>
-  </si>
-  <si>
     <t>A009</t>
   </si>
   <si>
@@ -1113,24 +840,12 @@
     <t>B005</t>
   </si>
   <si>
-    <t>PR2-PR2-DSL</t>
-  </si>
-  <si>
-    <t>PROD2 - PROD4 - DSL</t>
-  </si>
-  <si>
     <t>B006</t>
   </si>
   <si>
-    <t>PR2-PR5-DLL</t>
-  </si>
-  <si>
     <t>B007</t>
   </si>
   <si>
-    <t>DLProject Main body</t>
-  </si>
-  <si>
     <t>B008</t>
   </si>
   <si>
@@ -1170,12 +885,6 @@
     <t>B016</t>
   </si>
   <si>
-    <t>PR2-PR2-ESL</t>
-  </si>
-  <si>
-    <t>PR2-PR4-ESL</t>
-  </si>
-  <si>
     <t>B017</t>
   </si>
   <si>
@@ -1200,78 +909,36 @@
     <t>C003</t>
   </si>
   <si>
-    <t>PR2-PR5-BL DRTN</t>
-  </si>
-  <si>
     <t>C004</t>
   </si>
   <si>
-    <t>PR2-PR2-DSL DRTN</t>
-  </si>
-  <si>
-    <t>PR2-PR4-DSL DRTN</t>
-  </si>
-  <si>
     <t>C005</t>
   </si>
   <si>
-    <t>PR2-PR5-DLL DRTN</t>
-  </si>
-  <si>
-    <t>C006</t>
-  </si>
-  <si>
-    <t>PR1-PR3-DL DRTN</t>
-  </si>
-  <si>
-    <t>PR2-PR2-DL DRTN</t>
-  </si>
-  <si>
-    <t>C007</t>
-  </si>
-  <si>
-    <t>PR2-PR5-DCL DRTN</t>
-  </si>
-  <si>
     <t>C008</t>
   </si>
   <si>
     <t>PR1-PR1-ELL DRTN</t>
   </si>
   <si>
-    <t>PR2-PR2-ELL DRTN</t>
-  </si>
-  <si>
     <t>C009</t>
   </si>
   <si>
     <t>PR2-PR2-ECL DR TN</t>
   </si>
   <si>
-    <t>PR2-PR4-ECL DRTN</t>
-  </si>
-  <si>
     <t>C010</t>
   </si>
   <si>
     <t>PR1-PR1-EL DRTN</t>
   </si>
   <si>
-    <t>PR1-PR3-EL DRTN</t>
-  </si>
-  <si>
-    <t>PR2-PR2-EL DRTN</t>
-  </si>
-  <si>
     <t>C011</t>
   </si>
   <si>
     <t>PR2-PR2-FCL DRTN</t>
   </si>
   <si>
-    <t>PR2-PR4-FCL DRTN</t>
-  </si>
-  <si>
     <t>C014</t>
   </si>
   <si>
@@ -1281,12 +948,6 @@
     <t>C015</t>
   </si>
   <si>
-    <t>PR2-PR2-ESL DRTN</t>
-  </si>
-  <si>
-    <t>PR2-PR4-ESL DRTN</t>
-  </si>
-  <si>
     <t>C016</t>
   </si>
   <si>
@@ -1353,15 +1014,9 @@
     <t>TT Factory - GA</t>
   </si>
   <si>
-    <t>TT Factory Stage 2 - GA</t>
-  </si>
-  <si>
     <t>Y0202311</t>
   </si>
   <si>
-    <t>TT Project - R&amp;D-EE</t>
-  </si>
-  <si>
     <t>Y0202312</t>
   </si>
   <si>
@@ -1533,9 +1188,6 @@
     <t>Y0244210</t>
   </si>
   <si>
-    <t>ESL Project - SQM-IQC</t>
-  </si>
-  <si>
     <t>Y024B016</t>
   </si>
   <si>
@@ -1638,9 +1290,6 @@
     <t>PM Project - MPE-MP</t>
   </si>
   <si>
-    <t>PM Project - MPE-MP2</t>
-  </si>
-  <si>
     <t>Y0282110</t>
   </si>
   <si>
@@ -1674,9 +1323,6 @@
     <t>Y0292300</t>
   </si>
   <si>
-    <t>DOMINO-R&amp;D</t>
-  </si>
-  <si>
     <t>Y0292510</t>
   </si>
   <si>
@@ -1687,12 +1333,6 @@
   </si>
   <si>
     <t>DOMINO-QA</t>
-  </si>
-  <si>
-    <t>(blank)</t>
-  </si>
-  <si>
-    <t>Grand Total</t>
   </si>
   <si>
     <t>Số đơn</t>
@@ -2152,6 +1792,1119 @@
 (chưa nhập về BIVN bao giờ)
 新設部品</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">A001 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A002 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A003 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A004 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A005 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A006 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B001 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B003 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B004 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B007 </t>
+  </si>
+  <si>
+    <t>B018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C001 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C003 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C005 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C006 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C007 </t>
+  </si>
+  <si>
+    <t>ECLDR</t>
+  </si>
+  <si>
+    <t>ECLTN</t>
+  </si>
+  <si>
+    <t>ELLDR</t>
+  </si>
+  <si>
+    <t>ELLLT</t>
+  </si>
+  <si>
+    <t>ELLTB</t>
+  </si>
+  <si>
+    <t>ELLTN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M013 </t>
+  </si>
+  <si>
+    <t>O0001</t>
+  </si>
+  <si>
+    <t>O0002</t>
+  </si>
+  <si>
+    <t>O0003</t>
+  </si>
+  <si>
+    <t>O0004</t>
+  </si>
+  <si>
+    <t>O0005</t>
+  </si>
+  <si>
+    <t>O0006</t>
+  </si>
+  <si>
+    <t>O0007</t>
+  </si>
+  <si>
+    <t>O0008</t>
+  </si>
+  <si>
+    <t>O0009</t>
+  </si>
+  <si>
+    <t>O0010</t>
+  </si>
+  <si>
+    <t>O0011</t>
+  </si>
+  <si>
+    <t>O0012</t>
+  </si>
+  <si>
+    <t>O0013</t>
+  </si>
+  <si>
+    <t>O0014</t>
+  </si>
+  <si>
+    <t>O0015</t>
+  </si>
+  <si>
+    <t>O0016</t>
+  </si>
+  <si>
+    <t>O0018</t>
+  </si>
+  <si>
+    <t>O0019</t>
+  </si>
+  <si>
+    <t>O0020</t>
+  </si>
+  <si>
+    <t>O0021</t>
+  </si>
+  <si>
+    <t>O0022</t>
+  </si>
+  <si>
+    <t>O0023</t>
+  </si>
+  <si>
+    <t>O0024</t>
+  </si>
+  <si>
+    <t>O0025</t>
+  </si>
+  <si>
+    <t>O0026</t>
+  </si>
+  <si>
+    <t>O0027</t>
+  </si>
+  <si>
+    <t>O0028</t>
+  </si>
+  <si>
+    <t>O0029</t>
+  </si>
+  <si>
+    <t>O0030</t>
+  </si>
+  <si>
+    <t>O0031</t>
+  </si>
+  <si>
+    <t>O0032</t>
+  </si>
+  <si>
+    <t>O0033</t>
+  </si>
+  <si>
+    <t>O0034</t>
+  </si>
+  <si>
+    <t>O0035</t>
+  </si>
+  <si>
+    <t>O0036</t>
+  </si>
+  <si>
+    <t>P1001</t>
+  </si>
+  <si>
+    <t>P1002</t>
+  </si>
+  <si>
+    <t>P1003</t>
+  </si>
+  <si>
+    <t>P1004</t>
+  </si>
+  <si>
+    <t>P10CO</t>
+  </si>
+  <si>
+    <t>P10SC</t>
+  </si>
+  <si>
+    <t>P1BFB</t>
+  </si>
+  <si>
+    <t>P1BLP</t>
+  </si>
+  <si>
+    <t>P1BLT</t>
+  </si>
+  <si>
+    <t>P1BPR</t>
+  </si>
+  <si>
+    <t>P1DLF</t>
+  </si>
+  <si>
+    <t>P1DLL</t>
+  </si>
+  <si>
+    <t>P1DLP</t>
+  </si>
+  <si>
+    <t>P1SC3</t>
+  </si>
+  <si>
+    <t>P1SC4</t>
+  </si>
+  <si>
+    <t>P1SC5</t>
+  </si>
+  <si>
+    <t>P1SC6</t>
+  </si>
+  <si>
+    <t>P1SC7</t>
+  </si>
+  <si>
+    <t>P20CO</t>
+  </si>
+  <si>
+    <t>P2BLD</t>
+  </si>
+  <si>
+    <t>P2BLT</t>
+  </si>
+  <si>
+    <t>P2CO4</t>
+  </si>
+  <si>
+    <t>P2D01</t>
+  </si>
+  <si>
+    <t>P2D02</t>
+  </si>
+  <si>
+    <t>P2D03</t>
+  </si>
+  <si>
+    <t>P2D04</t>
+  </si>
+  <si>
+    <t>P2DCL</t>
+  </si>
+  <si>
+    <t>P2DDR</t>
+  </si>
+  <si>
+    <t>P2DLD</t>
+  </si>
+  <si>
+    <t>P2DLN</t>
+  </si>
+  <si>
+    <t>P2DLR</t>
+  </si>
+  <si>
+    <t>P2DLT</t>
+  </si>
+  <si>
+    <t>P2DTN</t>
+  </si>
+  <si>
+    <t>P2T01</t>
+  </si>
+  <si>
+    <t>P2T02</t>
+  </si>
+  <si>
+    <t>P2T03</t>
+  </si>
+  <si>
+    <t>P2T04</t>
+  </si>
+  <si>
+    <t>P3001</t>
+  </si>
+  <si>
+    <t>P3004</t>
+  </si>
+  <si>
+    <t>P30CO</t>
+  </si>
+  <si>
+    <t>P30RB</t>
+  </si>
+  <si>
+    <t>P30SP</t>
+  </si>
+  <si>
+    <t>P3BLP</t>
+  </si>
+  <si>
+    <t>P3BLT</t>
+  </si>
+  <si>
+    <t>P3DLF</t>
+  </si>
+  <si>
+    <t>P3DLP</t>
+  </si>
+  <si>
+    <t>P3DLT</t>
+  </si>
+  <si>
+    <t>P3DMX</t>
+  </si>
+  <si>
+    <t>P3DTT</t>
+  </si>
+  <si>
+    <t>P40SC</t>
+  </si>
+  <si>
+    <t>P4DCO</t>
+  </si>
+  <si>
+    <t>P4DDR</t>
+  </si>
+  <si>
+    <t>P4DSF</t>
+  </si>
+  <si>
+    <t>P4DSP</t>
+  </si>
+  <si>
+    <t>P4DTN</t>
+  </si>
+  <si>
+    <t>Q0001</t>
+  </si>
+  <si>
+    <t>Q0002</t>
+  </si>
+  <si>
+    <t>Q0003</t>
+  </si>
+  <si>
+    <t>Q0004</t>
+  </si>
+  <si>
+    <t>Q0005</t>
+  </si>
+  <si>
+    <t>Q0006</t>
+  </si>
+  <si>
+    <t>Q0007</t>
+  </si>
+  <si>
+    <t>Q00K1</t>
+  </si>
+  <si>
+    <t>Q00K2</t>
+  </si>
+  <si>
+    <t>Q00K3</t>
+  </si>
+  <si>
+    <t>Q00K4</t>
+  </si>
+  <si>
+    <t>Q00K5</t>
+  </si>
+  <si>
+    <t>Q00K6</t>
+  </si>
+  <si>
+    <t>Q00K7</t>
+  </si>
+  <si>
+    <t>Q00RB</t>
+  </si>
+  <si>
+    <t>Q00SP</t>
+  </si>
+  <si>
+    <t>QD001</t>
+  </si>
+  <si>
+    <t>QD002</t>
+  </si>
+  <si>
+    <t>QDT0K</t>
+  </si>
+  <si>
+    <t>QDT0L</t>
+  </si>
+  <si>
+    <t>QT001</t>
+  </si>
+  <si>
+    <t>QT002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X001 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">X002 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y001 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y003 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y004 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y005 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y006 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y010 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y011 </t>
+  </si>
+  <si>
+    <t>Y014</t>
+  </si>
+  <si>
+    <t>Y015</t>
+  </si>
+  <si>
+    <t>Y016</t>
+  </si>
+  <si>
+    <t>Y0162312</t>
+  </si>
+  <si>
+    <t>Y0163410</t>
+  </si>
+  <si>
+    <t>Y0164140</t>
+  </si>
+  <si>
+    <t>Y0164230</t>
+  </si>
+  <si>
+    <t>Y0165160</t>
+  </si>
+  <si>
+    <t>Y0165170</t>
+  </si>
+  <si>
+    <t>Y0167120</t>
+  </si>
+  <si>
+    <t>Y016C011</t>
+  </si>
+  <si>
+    <t>Y017</t>
+  </si>
+  <si>
+    <t>Y0172312</t>
+  </si>
+  <si>
+    <t>Y0173410</t>
+  </si>
+  <si>
+    <t>Y0174230</t>
+  </si>
+  <si>
+    <t>Y0175160</t>
+  </si>
+  <si>
+    <t>Y0175170</t>
+  </si>
+  <si>
+    <t>Y0177120</t>
+  </si>
+  <si>
+    <t>Y017A008</t>
+  </si>
+  <si>
+    <t>Y017C010</t>
+  </si>
+  <si>
+    <t>Y018</t>
+  </si>
+  <si>
+    <t>Y0183100</t>
+  </si>
+  <si>
+    <t>Y0183410</t>
+  </si>
+  <si>
+    <t>Y0184140</t>
+  </si>
+  <si>
+    <t>Y0184210</t>
+  </si>
+  <si>
+    <t>Y0184230</t>
+  </si>
+  <si>
+    <t>Y0185100</t>
+  </si>
+  <si>
+    <t>Y0185160</t>
+  </si>
+  <si>
+    <t>Y0185170</t>
+  </si>
+  <si>
+    <t>Y0187110</t>
+  </si>
+  <si>
+    <t>Y0187120</t>
+  </si>
+  <si>
+    <t>Y018B012</t>
+  </si>
+  <si>
+    <t>Y018C012</t>
+  </si>
+  <si>
+    <t>Y0284240</t>
+  </si>
+  <si>
+    <t>Y029</t>
+  </si>
+  <si>
+    <t>Y0294240</t>
+  </si>
+  <si>
+    <t>Z0096</t>
+  </si>
+  <si>
+    <t>GA-Canteen</t>
+  </si>
+  <si>
+    <t>GA-Dormitory</t>
+  </si>
+  <si>
+    <t>F4 project</t>
+  </si>
+  <si>
+    <t>General Affairs</t>
+  </si>
+  <si>
+    <t>Personnel</t>
+  </si>
+  <si>
+    <t>Accounting</t>
+  </si>
+  <si>
+    <t>Office Common IM</t>
+  </si>
+  <si>
+    <t>Prod 1 Common</t>
+  </si>
+  <si>
+    <t>PR2-PR2-Common</t>
+  </si>
+  <si>
+    <t>R&amp;D Office</t>
+  </si>
+  <si>
+    <t>Equipment eng</t>
+  </si>
+  <si>
+    <t>Development eng</t>
+  </si>
+  <si>
+    <t>Manufacturing eng</t>
+  </si>
+  <si>
+    <t>Prod 3-RB</t>
+  </si>
+  <si>
+    <t>Prod 3-SP</t>
+  </si>
+  <si>
+    <t>Pro3 Common</t>
+  </si>
+  <si>
+    <t>Manufacturing control</t>
+  </si>
+  <si>
+    <t>Prod 4 Common</t>
+  </si>
+  <si>
+    <t>Purchasing</t>
+  </si>
+  <si>
+    <t>Shipping</t>
+  </si>
+  <si>
+    <t>Production Control</t>
+  </si>
+  <si>
+    <t>Material Control</t>
+  </si>
+  <si>
+    <t>SEM</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>Incoming Quality Control</t>
+  </si>
+  <si>
+    <t>Source Quality Control</t>
+  </si>
+  <si>
+    <t>Molding</t>
+  </si>
+  <si>
+    <t>Molding-M301</t>
+  </si>
+  <si>
+    <t>F4 Molding</t>
+  </si>
+  <si>
+    <t>F5 Molding</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Molding manufacturing </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Molding engineering </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Molding PP-ME </t>
+  </si>
+  <si>
+    <t>Kiban</t>
+  </si>
+  <si>
+    <t>MPE-MP-PM</t>
+  </si>
+  <si>
+    <t>BPS</t>
+  </si>
+  <si>
+    <t>Prod 1- ALL/ALL2 Scanner</t>
+  </si>
+  <si>
+    <t>Prod 1- BLL Scanner</t>
+  </si>
+  <si>
+    <t>Prod 1- BL Scanner</t>
+  </si>
+  <si>
+    <t>Prod 1-DSL Scanner</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Prod1-DLL Scanner </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Prod1-DL Scanner </t>
+  </si>
+  <si>
+    <t>PR1-PR１-EL SCANNER</t>
+  </si>
+  <si>
+    <t>Prod 3-ALL</t>
+  </si>
+  <si>
+    <t>Prod 1-BLL</t>
+  </si>
+  <si>
+    <t>Prod 3-BL</t>
+  </si>
+  <si>
+    <t>PR2-PR2 -DSL</t>
+  </si>
+  <si>
+    <t>Prod1-DLL</t>
+  </si>
+  <si>
+    <t>Y07B007</t>
+  </si>
+  <si>
+    <t>PR2-PR2 -ESL</t>
+  </si>
+  <si>
+    <t>PR1-PR1-PJ</t>
+  </si>
+  <si>
+    <t>Prod2-ALL/ALL2 DRTN</t>
+  </si>
+  <si>
+    <t>Prod2-BL DRTN</t>
+  </si>
+  <si>
+    <t>PR2-PR2 -DSL DRTN</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Prod2-DLL DRTN </t>
+  </si>
+  <si>
+    <t>Y07-DLproject</t>
+  </si>
+  <si>
+    <t>DCL</t>
+  </si>
+  <si>
+    <t>PR2-PR2 -ESL DRTN</t>
+  </si>
+  <si>
+    <t>ECL TN</t>
+  </si>
+  <si>
+    <t>ELL Hontai</t>
+  </si>
+  <si>
+    <t>ELL TN</t>
+  </si>
+  <si>
+    <t>Liquid</t>
+  </si>
+  <si>
+    <t>Other_ENG</t>
+  </si>
+  <si>
+    <t>Other_BVPS</t>
+  </si>
+  <si>
+    <t>Other_SQM</t>
+  </si>
+  <si>
+    <t>Other_BPS</t>
+  </si>
+  <si>
+    <t>Other_MC-F1</t>
+  </si>
+  <si>
+    <t>Other_Mold F1</t>
+  </si>
+  <si>
+    <t>GA</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>Mold F4</t>
+  </si>
+  <si>
+    <t>Mold F5</t>
+  </si>
+  <si>
+    <t>Other_R&amp;D</t>
+  </si>
+  <si>
+    <t>Other_MP</t>
+  </si>
+  <si>
+    <t>Other_ACC</t>
+  </si>
+  <si>
+    <t>Prod 4-Label</t>
+  </si>
+  <si>
+    <t>Equipment engineering</t>
+  </si>
+  <si>
+    <t>Development engineering</t>
+  </si>
+  <si>
+    <t>Manufacturing engineering</t>
+  </si>
+  <si>
+    <t>Prod1-DLL Scanner</t>
+  </si>
+  <si>
+    <t>Prod2-DLL DRTN</t>
+  </si>
+  <si>
+    <t>DLL Project</t>
+  </si>
+  <si>
+    <t>Mold Manufacture</t>
+  </si>
+  <si>
+    <t>Mold Engineer</t>
+  </si>
+  <si>
+    <t>Shipping - F4</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Development eng </t>
+  </si>
+  <si>
+    <t>Prod 2 common_other</t>
+  </si>
+  <si>
+    <t>MC-F4</t>
+  </si>
+  <si>
+    <t>KIBAN PJ</t>
+  </si>
+  <si>
+    <t>EPE-PCB</t>
+  </si>
+  <si>
+    <t>Pro1-ALL</t>
+  </si>
+  <si>
+    <t>Pro1-ALL2</t>
+  </si>
+  <si>
+    <t>Prod1 common</t>
+  </si>
+  <si>
+    <t>Prod1-BL- FB-A</t>
+  </si>
+  <si>
+    <t>Pro1_Common</t>
+  </si>
+  <si>
+    <t>DSL_Scanner</t>
+  </si>
+  <si>
+    <t>Dầu cồn F123</t>
+  </si>
+  <si>
+    <t>Prod1-BL- PR-A</t>
+  </si>
+  <si>
+    <t>Prod1-BL- LT-A</t>
+  </si>
+  <si>
+    <t>Dầu cồn F4</t>
+  </si>
+  <si>
+    <t>Other Prod 1 DLL</t>
+  </si>
+  <si>
+    <t>Prod 1-DLL-PR</t>
+  </si>
+  <si>
+    <t>Prod4_ECL hontai</t>
+  </si>
+  <si>
+    <t>Prod1-ELL-Scanner</t>
+  </si>
+  <si>
+    <t>Prod1-DLL-Scanner</t>
+  </si>
+  <si>
+    <t>Prod1-DL-Scanner</t>
+  </si>
+  <si>
+    <t>Pro2_DR-BL</t>
+  </si>
+  <si>
+    <t>Pro2_DR-ALL</t>
+  </si>
+  <si>
+    <t>Pro2_DR-ALL2</t>
+  </si>
+  <si>
+    <t>DL-DR-P2</t>
+  </si>
+  <si>
+    <t>DCL-TN-P2</t>
+  </si>
+  <si>
+    <t>DL-TN-P2</t>
+  </si>
+  <si>
+    <t>Prod 2-DLL-TN</t>
+  </si>
+  <si>
+    <t>F4-DSL-TN</t>
+  </si>
+  <si>
+    <t>Pro2_TN-ALL</t>
+  </si>
+  <si>
+    <t>Pro2_TN-ALL2</t>
+  </si>
+  <si>
+    <t>Pro3 ALL</t>
+  </si>
+  <si>
+    <t>Dầu cồn F6</t>
+  </si>
+  <si>
+    <t>Pro3-RB</t>
+  </si>
+  <si>
+    <t>Pro3-SP</t>
+  </si>
+  <si>
+    <t>Prod 3-DL-MX</t>
+  </si>
+  <si>
+    <t>Prod 3-DL-TT</t>
+  </si>
+  <si>
+    <t>Prod4-DSL-Scanner</t>
+  </si>
+  <si>
+    <t>Prod4-DSL-Common</t>
+  </si>
+  <si>
+    <t>F4-DSL-DR</t>
+  </si>
+  <si>
+    <t>Prod4-DSL- PR</t>
+  </si>
+  <si>
+    <t>QA-ALL</t>
+  </si>
+  <si>
+    <t>QA-ALL2</t>
+  </si>
+  <si>
+    <t>FCL FG</t>
+  </si>
+  <si>
+    <t>EL hontai</t>
+  </si>
+  <si>
+    <t>EL TN</t>
+  </si>
+  <si>
+    <t>C008 ELLe</t>
+  </si>
+  <si>
+    <t>QA-ALL (KTLM)</t>
+  </si>
+  <si>
+    <t>QA-ALL2 (KTLM)</t>
+  </si>
+  <si>
+    <t>FCL TN</t>
+  </si>
+  <si>
+    <t>EL scan</t>
+  </si>
+  <si>
+    <t>EL DR</t>
+  </si>
+  <si>
+    <t>2510 Dầu cồn F5</t>
+  </si>
+  <si>
+    <t>B016 ESL FG</t>
+  </si>
+  <si>
+    <t>QA_DR-ALL</t>
+  </si>
+  <si>
+    <t>QA_DR-ALL2</t>
+  </si>
+  <si>
+    <t>QA_TN-ALL</t>
+  </si>
+  <si>
+    <t>QA_TN-ALL2</t>
+  </si>
+  <si>
+    <t>Management(Indirect)</t>
+  </si>
+  <si>
+    <t>Management(SGA)</t>
+  </si>
+  <si>
+    <t>BLL Project</t>
+  </si>
+  <si>
+    <t>DSL Project</t>
+  </si>
+  <si>
+    <t>S Project(Indirect)</t>
+  </si>
+  <si>
+    <t>S Project(SGA)</t>
+  </si>
+  <si>
+    <t>Film PJ</t>
+  </si>
+  <si>
+    <t>DCLproject</t>
+  </si>
+  <si>
+    <t>New F5-Admin</t>
+  </si>
+  <si>
+    <t>F5</t>
+  </si>
+  <si>
+    <t>FCL</t>
+  </si>
+  <si>
+    <t>FCL Project - R&amp;D-DE</t>
+  </si>
+  <si>
+    <t>FCL Project - SQM-SEM</t>
+  </si>
+  <si>
+    <t>FCL Project - QA-QM</t>
+  </si>
+  <si>
+    <t>FCL Project - SQM-SQC</t>
+  </si>
+  <si>
+    <t>FCL Project - MPE-ME</t>
+  </si>
+  <si>
+    <t>FCL Project - MPE-PE</t>
+  </si>
+  <si>
+    <t>FCL Project - EPE-EE</t>
+  </si>
+  <si>
+    <t>FCL Project DRTN</t>
+  </si>
+  <si>
+    <t>EL</t>
+  </si>
+  <si>
+    <t>EL Project - R&amp;D-DE</t>
+  </si>
+  <si>
+    <t>EL Project - SQM-SEM</t>
+  </si>
+  <si>
+    <t>EL Project - SQM-SQC</t>
+  </si>
+  <si>
+    <t>EL Project - MPE-ME</t>
+  </si>
+  <si>
+    <t>EL Project - MPE-PE</t>
+  </si>
+  <si>
+    <t>EL Project - EPE-EE</t>
+  </si>
+  <si>
+    <t>EL Project Scanner</t>
+  </si>
+  <si>
+    <t>EL Project DRTN</t>
+  </si>
+  <si>
+    <t>ELLe Project</t>
+  </si>
+  <si>
+    <t>ELLe Project - PPC</t>
+  </si>
+  <si>
+    <t>ELLe Project - SQM-SEM</t>
+  </si>
+  <si>
+    <t>ELLe Project - QA-QM</t>
+  </si>
+  <si>
+    <t>ELLe Project - SQM-IQC</t>
+  </si>
+  <si>
+    <t>ELLe Project - SQM-SQC</t>
+  </si>
+  <si>
+    <t>ELLe Project - MPE-MP</t>
+  </si>
+  <si>
+    <t>ELLe Project - MPE-ME</t>
+  </si>
+  <si>
+    <t>ELLe Project - MPE-PE</t>
+  </si>
+  <si>
+    <t>ELLe Project - EPE-PCB</t>
+  </si>
+  <si>
+    <t>ELLe Project - EPE-EE</t>
+  </si>
+  <si>
+    <t>ELLe Project Main body</t>
+  </si>
+  <si>
+    <t>ELLe Project DRTN</t>
+  </si>
+  <si>
+    <t>ESL Project- SQM-IQC</t>
+  </si>
+  <si>
+    <t>PJ-PSU</t>
+  </si>
+  <si>
+    <t>DOMINO PROJECT</t>
+  </si>
+  <si>
+    <t>DOMIN-R&amp;D</t>
+  </si>
+  <si>
+    <t>DOMINO-PSU</t>
   </si>
 </sst>
 </file>
@@ -2370,7 +3123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2463,34 +3216,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2512,6 +3244,36 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2523,17 +3285,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2907,7 +3663,7 @@
   <sheetData>
     <row r="1" spans="1:32" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>330</v>
+        <v>210</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -2941,7 +3697,7 @@
     </row>
     <row r="2" spans="1:32" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>332</v>
+        <v>212</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -3007,18 +3763,18 @@
     </row>
     <row r="4" spans="1:32" ht="11.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9"/>
-      <c r="B4" s="34" t="s">
-        <v>333</v>
-      </c>
-      <c r="C4" s="34"/>
-      <c r="D4" s="35"/>
+      <c r="B4" s="45" t="s">
+        <v>213</v>
+      </c>
+      <c r="C4" s="45"/>
+      <c r="D4" s="46"/>
       <c r="E4" s="25"/>
       <c r="F4" s="25"/>
       <c r="G4" s="25"/>
-      <c r="H4" s="34" t="s">
-        <v>334</v>
-      </c>
-      <c r="I4" s="36"/>
+      <c r="H4" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="I4" s="47"/>
       <c r="J4" s="9"/>
       <c r="K4" s="25"/>
       <c r="M4" s="9"/>
@@ -3040,14 +3796,14 @@
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="9"/>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="35"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="46"/>
       <c r="E5" s="25"/>
       <c r="F5" s="25"/>
       <c r="G5" s="25"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="36"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="47"/>
       <c r="J5" s="25"/>
       <c r="K5" s="25"/>
       <c r="L5" s="18"/>
@@ -3071,17 +3827,17 @@
       <c r="AD5" s="9"/>
     </row>
     <row r="6" spans="1:32" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="39" t="s">
-        <v>384</v>
-      </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
+      <c r="A6" s="48" t="s">
+        <v>264</v>
+      </c>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
       <c r="J6" s="18"/>
       <c r="K6" s="18"/>
       <c r="L6" s="18"/>
@@ -3141,15 +3897,15 @@
       <c r="L7" s="26">
         <v>12</v>
       </c>
-      <c r="M7" s="44">
+      <c r="M7" s="37">
         <f>L7+1</f>
         <v>13</v>
       </c>
-      <c r="N7" s="45"/>
-      <c r="O7" s="45"/>
-      <c r="P7" s="45"/>
-      <c r="Q7" s="45"/>
-      <c r="R7" s="46"/>
+      <c r="N7" s="38"/>
+      <c r="O7" s="38"/>
+      <c r="P7" s="38"/>
+      <c r="Q7" s="38"/>
+      <c r="R7" s="39"/>
       <c r="S7" s="24">
         <v>14</v>
       </c>
@@ -3207,138 +3963,138 @@
       </c>
     </row>
     <row r="8" spans="1:32" s="7" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="41" t="s">
+      <c r="A8" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="37" t="s">
-        <v>335</v>
-      </c>
-      <c r="C8" s="37" t="s">
-        <v>336</v>
-      </c>
-      <c r="D8" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="E8" s="37" t="s">
-        <v>338</v>
-      </c>
-      <c r="F8" s="37" t="s">
-        <v>339</v>
-      </c>
-      <c r="G8" s="37" t="s">
-        <v>340</v>
-      </c>
-      <c r="H8" s="37" t="s">
-        <v>342</v>
-      </c>
-      <c r="I8" s="37" t="s">
-        <v>343</v>
-      </c>
-      <c r="J8" s="37" t="s">
-        <v>341</v>
-      </c>
-      <c r="K8" s="37" t="s">
-        <v>344</v>
-      </c>
-      <c r="L8" s="37" t="s">
-        <v>345</v>
-      </c>
-      <c r="M8" s="47" t="s">
-        <v>351</v>
-      </c>
-      <c r="N8" s="48"/>
-      <c r="O8" s="48"/>
-      <c r="P8" s="48"/>
-      <c r="Q8" s="48"/>
-      <c r="R8" s="49"/>
-      <c r="S8" s="37" t="s">
-        <v>355</v>
-      </c>
-      <c r="T8" s="37" t="s">
-        <v>356</v>
-      </c>
-      <c r="U8" s="37" t="s">
-        <v>352</v>
-      </c>
-      <c r="V8" s="37" t="s">
-        <v>353</v>
-      </c>
-      <c r="W8" s="37" t="s">
-        <v>357</v>
-      </c>
-      <c r="X8" s="37" t="s">
-        <v>358</v>
-      </c>
-      <c r="Y8" s="37" t="s">
-        <v>359</v>
-      </c>
-      <c r="Z8" s="37" t="s">
-        <v>360</v>
-      </c>
-      <c r="AA8" s="37" t="s">
-        <v>361</v>
-      </c>
-      <c r="AB8" s="37" t="s">
-        <v>362</v>
-      </c>
-      <c r="AC8" s="37" t="s">
-        <v>363</v>
-      </c>
-      <c r="AD8" s="37" t="s">
-        <v>364</v>
-      </c>
-      <c r="AE8" s="43" t="s">
-        <v>365</v>
-      </c>
-      <c r="AF8" s="43" t="s">
-        <v>366</v>
+      <c r="B8" s="35" t="s">
+        <v>215</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>216</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>217</v>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>218</v>
+      </c>
+      <c r="F8" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="G8" s="35" t="s">
+        <v>220</v>
+      </c>
+      <c r="H8" s="35" t="s">
+        <v>222</v>
+      </c>
+      <c r="I8" s="35" t="s">
+        <v>223</v>
+      </c>
+      <c r="J8" s="35" t="s">
+        <v>221</v>
+      </c>
+      <c r="K8" s="35" t="s">
+        <v>224</v>
+      </c>
+      <c r="L8" s="35" t="s">
+        <v>225</v>
+      </c>
+      <c r="M8" s="40" t="s">
+        <v>231</v>
+      </c>
+      <c r="N8" s="41"/>
+      <c r="O8" s="41"/>
+      <c r="P8" s="41"/>
+      <c r="Q8" s="41"/>
+      <c r="R8" s="42"/>
+      <c r="S8" s="35" t="s">
+        <v>235</v>
+      </c>
+      <c r="T8" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="U8" s="35" t="s">
+        <v>232</v>
+      </c>
+      <c r="V8" s="35" t="s">
+        <v>233</v>
+      </c>
+      <c r="W8" s="35" t="s">
+        <v>237</v>
+      </c>
+      <c r="X8" s="35" t="s">
+        <v>238</v>
+      </c>
+      <c r="Y8" s="35" t="s">
+        <v>239</v>
+      </c>
+      <c r="Z8" s="35" t="s">
+        <v>240</v>
+      </c>
+      <c r="AA8" s="35" t="s">
+        <v>241</v>
+      </c>
+      <c r="AB8" s="35" t="s">
+        <v>242</v>
+      </c>
+      <c r="AC8" s="35" t="s">
+        <v>243</v>
+      </c>
+      <c r="AD8" s="35" t="s">
+        <v>244</v>
+      </c>
+      <c r="AE8" s="34" t="s">
+        <v>245</v>
+      </c>
+      <c r="AF8" s="34" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="9" spans="1:32" s="7" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A9" s="42"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="L9" s="38"/>
+      <c r="A9" s="44"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="36"/>
       <c r="M9" s="19" t="s">
-        <v>346</v>
+        <v>226</v>
       </c>
       <c r="N9" s="19" t="s">
-        <v>347</v>
+        <v>227</v>
       </c>
       <c r="O9" s="19" t="s">
-        <v>348</v>
+        <v>228</v>
       </c>
       <c r="P9" s="19" t="s">
-        <v>349</v>
+        <v>229</v>
       </c>
       <c r="Q9" s="19" t="s">
-        <v>350</v>
+        <v>230</v>
       </c>
       <c r="R9" s="19" t="s">
-        <v>354</v>
-      </c>
-      <c r="S9" s="38"/>
-      <c r="T9" s="38"/>
-      <c r="U9" s="38"/>
-      <c r="V9" s="38"/>
-      <c r="W9" s="38"/>
-      <c r="X9" s="38"/>
-      <c r="Y9" s="38"/>
-      <c r="Z9" s="38"/>
-      <c r="AA9" s="38"/>
-      <c r="AB9" s="38"/>
-      <c r="AC9" s="38"/>
-      <c r="AD9" s="38"/>
-      <c r="AE9" s="43"/>
-      <c r="AF9" s="43"/>
+        <v>234</v>
+      </c>
+      <c r="S9" s="36"/>
+      <c r="T9" s="36"/>
+      <c r="U9" s="36"/>
+      <c r="V9" s="36"/>
+      <c r="W9" s="36"/>
+      <c r="X9" s="36"/>
+      <c r="Y9" s="36"/>
+      <c r="Z9" s="36"/>
+      <c r="AA9" s="36"/>
+      <c r="AB9" s="36"/>
+      <c r="AC9" s="36"/>
+      <c r="AD9" s="36"/>
+      <c r="AE9" s="34"/>
+      <c r="AF9" s="34"/>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
@@ -27982,6 +28738,23 @@
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="B4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="X8:X9"/>
     <mergeCell ref="AE8:AE9"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="AF8:AF9"/>
@@ -27998,23 +28771,6 @@
     <mergeCell ref="Z8:Z9"/>
     <mergeCell ref="AA8:AA9"/>
     <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="B4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="A6:I6"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA10:AA569" xr:uid="{A48AEAD6-16A7-419C-9ADE-A3A1D0E68BC1}">
@@ -28038,9 +28794,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DE5615F0-C9E7-4064-89AD-774F26CFBD30}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{29FC2697-C7F8-49F5-A92C-C62D205E7736}">
           <x14:formula1>
-            <xm:f>Master!$A$2:$A$169</xm:f>
+            <xm:f>Master!$A$2:$A$327</xm:f>
           </x14:formula1>
           <xm:sqref>B10:B569</xm:sqref>
         </x14:dataValidation>
@@ -28064,55 +28820,55 @@
   <sheetData>
     <row r="1" spans="2:7" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E1" s="28" t="s">
-        <v>388</v>
+        <v>268</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>389</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
       <c r="E2" s="20" t="s">
-        <v>329</v>
+        <v>209</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>329</v>
+        <v>209</v>
       </c>
       <c r="G2" s="21"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="52" t="s">
-        <v>321</v>
-      </c>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
+      <c r="B3" s="55" t="s">
+        <v>201</v>
+      </c>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
       <c r="E3" s="20" t="s">
-        <v>329</v>
+        <v>209</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>329</v>
+        <v>209</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>367</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="29">
         <v>1</v>
       </c>
-      <c r="C4" s="55" t="s">
+      <c r="C4" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="56"/>
+      <c r="D4" s="52"/>
       <c r="E4" s="20" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="G4" s="21"/>
     </row>
@@ -28120,138 +28876,138 @@
       <c r="B5" s="29">
         <v>2</v>
       </c>
-      <c r="C5" s="50" t="s">
-        <v>335</v>
-      </c>
-      <c r="D5" s="51"/>
+      <c r="C5" s="53" t="s">
+        <v>215</v>
+      </c>
+      <c r="D5" s="54"/>
       <c r="E5" s="20" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="29">
         <v>3</v>
       </c>
-      <c r="C6" s="50" t="s">
-        <v>336</v>
-      </c>
-      <c r="D6" s="51"/>
+      <c r="C6" s="53" t="s">
+        <v>216</v>
+      </c>
+      <c r="D6" s="54"/>
       <c r="E6" s="20" t="s">
-        <v>329</v>
+        <v>209</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>329</v>
+        <v>209</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>368</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7" spans="2:7" ht="63.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="29">
         <v>4</v>
       </c>
-      <c r="C7" s="50" t="s">
-        <v>337</v>
-      </c>
-      <c r="D7" s="51"/>
+      <c r="C7" s="53" t="s">
+        <v>217</v>
+      </c>
+      <c r="D7" s="54"/>
       <c r="E7" s="20" t="s">
-        <v>329</v>
+        <v>209</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>369</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" spans="2:7" ht="96" x14ac:dyDescent="0.25">
       <c r="B8" s="29">
         <v>5</v>
       </c>
-      <c r="C8" s="50" t="s">
-        <v>338</v>
-      </c>
-      <c r="D8" s="51"/>
+      <c r="C8" s="53" t="s">
+        <v>218</v>
+      </c>
+      <c r="D8" s="54"/>
       <c r="E8" s="20" t="s">
-        <v>326</v>
+        <v>206</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>326</v>
+        <v>206</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>325</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="29">
         <v>6</v>
       </c>
-      <c r="C9" s="50" t="s">
-        <v>339</v>
-      </c>
-      <c r="D9" s="51"/>
+      <c r="C9" s="53" t="s">
+        <v>219</v>
+      </c>
+      <c r="D9" s="54"/>
       <c r="E9" s="20" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>326</v>
+        <v>206</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>327</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" spans="2:7" ht="60" x14ac:dyDescent="0.25">
       <c r="B10" s="29">
         <v>7</v>
       </c>
-      <c r="C10" s="50" t="s">
-        <v>340</v>
-      </c>
-      <c r="D10" s="51"/>
+      <c r="C10" s="53" t="s">
+        <v>220</v>
+      </c>
+      <c r="D10" s="54"/>
       <c r="E10" s="20" t="s">
-        <v>329</v>
+        <v>209</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>328</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="83.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="29">
         <v>8</v>
       </c>
-      <c r="C11" s="50" t="s">
-        <v>342</v>
-      </c>
-      <c r="D11" s="51"/>
+      <c r="C11" s="53" t="s">
+        <v>222</v>
+      </c>
+      <c r="D11" s="54"/>
       <c r="E11" s="20" t="s">
-        <v>329</v>
+        <v>209</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>386</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="29">
         <v>9</v>
       </c>
-      <c r="C12" s="50" t="s">
-        <v>343</v>
-      </c>
-      <c r="D12" s="51"/>
+      <c r="C12" s="53" t="s">
+        <v>223</v>
+      </c>
+      <c r="D12" s="54"/>
       <c r="E12" s="20" t="s">
-        <v>329</v>
+        <v>209</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="G12" s="32"/>
     </row>
@@ -28259,15 +29015,15 @@
       <c r="B13" s="29">
         <v>10</v>
       </c>
-      <c r="C13" s="50" t="s">
-        <v>341</v>
-      </c>
-      <c r="D13" s="51"/>
+      <c r="C13" s="53" t="s">
+        <v>221</v>
+      </c>
+      <c r="D13" s="54"/>
       <c r="E13" s="20" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="G13" s="32"/>
     </row>
@@ -28275,15 +29031,15 @@
       <c r="B14" s="29">
         <v>11</v>
       </c>
-      <c r="C14" s="50" t="s">
-        <v>344</v>
-      </c>
-      <c r="D14" s="51"/>
+      <c r="C14" s="53" t="s">
+        <v>224</v>
+      </c>
+      <c r="D14" s="54"/>
       <c r="E14" s="20" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="G14" s="32"/>
     </row>
@@ -28291,137 +29047,137 @@
       <c r="B15" s="29">
         <v>12</v>
       </c>
-      <c r="C15" s="50" t="s">
-        <v>345</v>
-      </c>
-      <c r="D15" s="51"/>
+      <c r="C15" s="53" t="s">
+        <v>225</v>
+      </c>
+      <c r="D15" s="54"/>
       <c r="E15" s="20" t="s">
-        <v>329</v>
+        <v>209</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>370</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="72" x14ac:dyDescent="0.25">
-      <c r="B16" s="53">
+      <c r="B16" s="56">
         <f>B15+1</f>
         <v>13</v>
       </c>
-      <c r="C16" s="54" t="s">
-        <v>351</v>
+      <c r="C16" s="50" t="s">
+        <v>231</v>
       </c>
       <c r="D16" s="30" t="s">
-        <v>346</v>
+        <v>226</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>329</v>
+        <v>209</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>371</v>
+        <v>251</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="53"/>
-      <c r="C17" s="54"/>
+      <c r="B17" s="56"/>
+      <c r="C17" s="50"/>
       <c r="D17" s="30" t="s">
-        <v>347</v>
+        <v>227</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>326</v>
+        <v>206</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>372</v>
+        <v>252</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="72" x14ac:dyDescent="0.25">
-      <c r="B18" s="53"/>
-      <c r="C18" s="54"/>
+      <c r="B18" s="56"/>
+      <c r="C18" s="50"/>
       <c r="D18" s="30" t="s">
-        <v>348</v>
+        <v>228</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>326</v>
+        <v>206</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="G18" s="23" t="s">
-        <v>375</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="2:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="B19" s="53"/>
-      <c r="C19" s="54"/>
+      <c r="B19" s="56"/>
+      <c r="C19" s="50"/>
       <c r="D19" s="30" t="s">
-        <v>349</v>
+        <v>229</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>326</v>
+        <v>206</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="G19" s="23" t="s">
-        <v>373</v>
+        <v>253</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="B20" s="53"/>
-      <c r="C20" s="54"/>
+      <c r="B20" s="56"/>
+      <c r="C20" s="50"/>
       <c r="D20" s="30" t="s">
-        <v>350</v>
+        <v>230</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>331</v>
+        <v>211</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="G20" s="23" t="s">
-        <v>374</v>
+        <v>254</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="48" x14ac:dyDescent="0.25">
-      <c r="B21" s="53"/>
-      <c r="C21" s="54"/>
+      <c r="B21" s="56"/>
+      <c r="C21" s="50"/>
       <c r="D21" s="30" t="s">
-        <v>354</v>
+        <v>234</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>331</v>
+        <v>211</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="G21" s="23" t="s">
-        <v>376</v>
+        <v>256</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="31">
         <v>14</v>
       </c>
-      <c r="C22" s="50" t="s">
-        <v>355</v>
-      </c>
-      <c r="D22" s="51"/>
+      <c r="C22" s="53" t="s">
+        <v>235</v>
+      </c>
+      <c r="D22" s="54"/>
       <c r="E22" s="20" t="s">
-        <v>326</v>
+        <v>206</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>326</v>
+        <v>206</v>
       </c>
       <c r="G22" s="23" t="s">
-        <v>385</v>
+        <v>265</v>
       </c>
     </row>
     <row r="23" spans="2:7" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -28429,18 +29185,18 @@
         <f t="shared" ref="B23:B35" si="0">B22+1</f>
         <v>15</v>
       </c>
-      <c r="C23" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="D23" s="51"/>
+      <c r="C23" s="53" t="s">
+        <v>236</v>
+      </c>
+      <c r="D23" s="54"/>
       <c r="E23" s="20" t="s">
-        <v>326</v>
+        <v>206</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>326</v>
+        <v>206</v>
       </c>
       <c r="G23" s="23" t="s">
-        <v>385</v>
+        <v>265</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -28448,18 +29204,18 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C24" s="50" t="s">
-        <v>352</v>
-      </c>
-      <c r="D24" s="51"/>
+      <c r="C24" s="53" t="s">
+        <v>232</v>
+      </c>
+      <c r="D24" s="54"/>
       <c r="E24" s="20" t="s">
-        <v>326</v>
+        <v>206</v>
       </c>
       <c r="F24" s="20" t="s">
-        <v>326</v>
+        <v>206</v>
       </c>
       <c r="G24" s="23" t="s">
-        <v>385</v>
+        <v>265</v>
       </c>
     </row>
     <row r="25" spans="2:7" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -28467,18 +29223,18 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C25" s="50" t="s">
-        <v>353</v>
-      </c>
-      <c r="D25" s="51"/>
+      <c r="C25" s="53" t="s">
+        <v>233</v>
+      </c>
+      <c r="D25" s="54"/>
       <c r="E25" s="20" t="s">
-        <v>326</v>
+        <v>206</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>326</v>
+        <v>206</v>
       </c>
       <c r="G25" s="23" t="s">
-        <v>385</v>
+        <v>265</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="60.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -28486,18 +29242,18 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C26" s="50" t="s">
-        <v>357</v>
-      </c>
-      <c r="D26" s="51"/>
+      <c r="C26" s="53" t="s">
+        <v>237</v>
+      </c>
+      <c r="D26" s="54"/>
       <c r="E26" s="20" t="s">
-        <v>331</v>
+        <v>211</v>
       </c>
       <c r="F26" s="20" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="G26" s="21" t="s">
-        <v>387</v>
+        <v>267</v>
       </c>
     </row>
     <row r="27" spans="2:7" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -28505,18 +29261,18 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C27" s="50" t="s">
-        <v>358</v>
-      </c>
-      <c r="D27" s="51"/>
+      <c r="C27" s="53" t="s">
+        <v>238</v>
+      </c>
+      <c r="D27" s="54"/>
       <c r="E27" s="20" t="s">
-        <v>329</v>
+        <v>209</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="G27" s="21" t="s">
-        <v>377</v>
+        <v>257</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -28524,18 +29280,18 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C28" s="50" t="s">
-        <v>359</v>
-      </c>
-      <c r="D28" s="51"/>
+      <c r="C28" s="53" t="s">
+        <v>239</v>
+      </c>
+      <c r="D28" s="54"/>
       <c r="E28" s="20" t="s">
-        <v>329</v>
+        <v>209</v>
       </c>
       <c r="F28" s="20" t="s">
-        <v>329</v>
+        <v>209</v>
       </c>
       <c r="G28" s="21" t="s">
-        <v>378</v>
+        <v>258</v>
       </c>
     </row>
     <row r="29" spans="2:7" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -28543,18 +29299,18 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C29" s="50" t="s">
-        <v>360</v>
-      </c>
-      <c r="D29" s="51"/>
+      <c r="C29" s="53" t="s">
+        <v>240</v>
+      </c>
+      <c r="D29" s="54"/>
       <c r="E29" s="20" t="s">
-        <v>329</v>
+        <v>209</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>329</v>
+        <v>209</v>
       </c>
       <c r="G29" s="21" t="s">
-        <v>378</v>
+        <v>258</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="84.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -28562,18 +29318,18 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C30" s="50" t="s">
-        <v>361</v>
-      </c>
-      <c r="D30" s="51"/>
+      <c r="C30" s="53" t="s">
+        <v>241</v>
+      </c>
+      <c r="D30" s="54"/>
       <c r="E30" s="20" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="G30" s="21" t="s">
-        <v>379</v>
+        <v>259</v>
       </c>
     </row>
     <row r="31" spans="2:7" ht="57.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -28581,18 +29337,18 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C31" s="50" t="s">
-        <v>362</v>
-      </c>
-      <c r="D31" s="51"/>
+      <c r="C31" s="53" t="s">
+        <v>242</v>
+      </c>
+      <c r="D31" s="54"/>
       <c r="E31" s="20" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="G31" s="21" t="s">
-        <v>380</v>
+        <v>260</v>
       </c>
     </row>
     <row r="32" spans="2:7" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -28600,15 +29356,15 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C32" s="50" t="s">
-        <v>363</v>
-      </c>
-      <c r="D32" s="51"/>
+      <c r="C32" s="53" t="s">
+        <v>243</v>
+      </c>
+      <c r="D32" s="54"/>
       <c r="E32" s="20" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="G32" s="20"/>
     </row>
@@ -28617,18 +29373,18 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C33" s="50" t="s">
-        <v>364</v>
-      </c>
-      <c r="D33" s="51"/>
+      <c r="C33" s="53" t="s">
+        <v>244</v>
+      </c>
+      <c r="D33" s="54"/>
       <c r="E33" s="20" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="G33" s="21" t="s">
-        <v>381</v>
+        <v>261</v>
       </c>
     </row>
     <row r="34" spans="2:7" ht="51.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -28636,18 +29392,18 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C34" s="54" t="s">
-        <v>365</v>
-      </c>
-      <c r="D34" s="54"/>
+      <c r="C34" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="D34" s="50"/>
       <c r="E34" s="20" t="s">
-        <v>326</v>
+        <v>206</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>326</v>
+        <v>206</v>
       </c>
       <c r="G34" s="21" t="s">
-        <v>382</v>
+        <v>262</v>
       </c>
     </row>
     <row r="35" spans="2:7" ht="41.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -28655,23 +29411,37 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C35" s="54" t="s">
-        <v>366</v>
-      </c>
-      <c r="D35" s="54"/>
+      <c r="C35" s="50" t="s">
+        <v>246</v>
+      </c>
+      <c r="D35" s="50"/>
       <c r="E35" s="20" t="s">
-        <v>326</v>
+        <v>206</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>326</v>
+        <v>206</v>
       </c>
       <c r="G35" s="27" t="s">
-        <v>383</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B1:H35" xr:uid="{9A62EE61-DA4A-4471-B605-47242F0A4DEA}"/>
   <mergeCells count="30">
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B16:B21"/>
+    <mergeCell ref="C16:C21"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="C4:D4"/>
@@ -28688,20 +29458,6 @@
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="B16:B21"/>
-    <mergeCell ref="C16:C21"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -28710,1374 +29466,2628 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EDAC048-C2F1-4ABA-B2C8-6CB3150A85B7}">
-  <dimension ref="A1:B171"/>
+  <dimension ref="A1:B327"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" style="58" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" style="17" bestFit="1" customWidth="1"/>
     <col min="3" max="16384" width="8.7109375" style="17"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="58" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="58">
+        <v>1110</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="58">
+        <v>1130</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="58">
+        <v>1140</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="58">
+        <v>1210</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="58">
+        <v>1211</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="58">
+        <v>1212</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="58">
+        <v>1220</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="58">
+        <v>1221</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="58">
+        <v>1310</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="58">
+        <v>1410</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="58">
+        <v>1910</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="58">
+        <v>2110</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="58">
+        <v>2210</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="58">
+        <v>2310</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="58">
+        <v>2311</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="58">
+        <v>2312</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="58">
+        <v>2313</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="58">
+        <v>2410</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="58">
+        <v>2421</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="58">
+        <v>2490</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="58">
+        <v>2510</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="58">
+        <v>2610</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="58">
+        <v>2710</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="58">
+        <v>3110</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="58">
+        <v>3111</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="58">
+        <v>3210</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="58">
+        <v>3211</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="58">
+        <v>3212</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="58">
+        <v>3310</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="58">
+        <v>3320</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="58">
+        <v>3321</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="58">
+        <v>3410</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="58">
+        <v>3510</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="58">
+        <v>4110</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="58">
+        <v>4111</v>
+      </c>
+      <c r="B36" s="17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="58">
+        <v>4140</v>
+      </c>
+      <c r="B37" s="17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" s="58">
+        <v>4210</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="58">
+        <v>4211</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="58">
+        <v>4230</v>
+      </c>
+      <c r="B40" s="17" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="58">
+        <v>4240</v>
+      </c>
+      <c r="B41" s="17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="58">
+        <v>5110</v>
+      </c>
+      <c r="B42" s="17" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="58">
+        <v>5120</v>
+      </c>
+      <c r="B43" s="17" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" s="58">
+        <v>5130</v>
+      </c>
+      <c r="B44" s="17" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="58">
+        <v>5140</v>
+      </c>
+      <c r="B45" s="17" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" s="58">
+        <v>5150</v>
+      </c>
+      <c r="B46" s="17" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="58">
+        <v>5160</v>
+      </c>
+      <c r="B47" s="17" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="58">
+        <v>5170</v>
+      </c>
+      <c r="B48" s="17" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="58">
+        <v>5180</v>
+      </c>
+      <c r="B49" s="17" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="58">
+        <v>5210</v>
+      </c>
+      <c r="B50" s="17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" s="58">
+        <v>5220</v>
+      </c>
+      <c r="B51" s="17" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" s="58">
+        <v>6110</v>
+      </c>
+      <c r="B52" s="17" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" s="58">
+        <v>7110</v>
+      </c>
+      <c r="B53" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" s="58">
+        <v>7111</v>
+      </c>
+      <c r="B54" s="17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" s="58">
+        <v>7112</v>
+      </c>
+      <c r="B55" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" s="58">
+        <v>7120</v>
+      </c>
+      <c r="B56" s="17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57" s="58">
+        <v>8110</v>
+      </c>
+      <c r="B57" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" s="58" t="s">
+        <v>270</v>
+      </c>
+      <c r="B58" s="17" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59" s="58" t="s">
+        <v>271</v>
+      </c>
+      <c r="B59" s="17" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60" s="58" t="s">
+        <v>272</v>
+      </c>
+      <c r="B60" s="17" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61" s="58" t="s">
+        <v>273</v>
+      </c>
+      <c r="B61" s="17" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62" s="58" t="s">
+        <v>274</v>
+      </c>
+      <c r="B62" s="17" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63" s="58" t="s">
+        <v>275</v>
+      </c>
+      <c r="B63" s="17" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64" s="58" t="s">
+        <v>30</v>
+      </c>
+      <c r="B64" s="17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="B65" s="17" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66" s="58" t="s">
+        <v>33</v>
+      </c>
+      <c r="B66" s="17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="B67" s="17" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68" s="58" t="s">
+        <v>277</v>
+      </c>
+      <c r="B68" s="17" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69" s="58" t="s">
+        <v>278</v>
+      </c>
+      <c r="B69" s="17" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70" s="58" t="s">
+        <v>35</v>
+      </c>
+      <c r="B70" s="17" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="B71" s="17" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72" s="58" t="s">
+        <v>279</v>
+      </c>
+      <c r="B72" s="17" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="B73" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74" s="58" t="s">
+        <v>40</v>
+      </c>
+      <c r="B74" s="17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A75" s="58" t="s">
+        <v>42</v>
+      </c>
+      <c r="B75" s="17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A76" s="58" t="s">
+        <v>44</v>
+      </c>
+      <c r="B76" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A77" s="58" t="s">
+        <v>46</v>
+      </c>
+      <c r="B77" s="17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A78" s="58" t="s">
+        <v>48</v>
+      </c>
+      <c r="B78" s="17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A79" s="58" t="s">
+        <v>50</v>
+      </c>
+      <c r="B79" s="17" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A80" s="58" t="s">
+        <v>51</v>
+      </c>
+      <c r="B80" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A81" s="58" t="s">
+        <v>280</v>
+      </c>
+      <c r="B81" s="17" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A82" s="58" t="s">
+        <v>53</v>
+      </c>
+      <c r="B82" s="17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A83" s="58" t="s">
+        <v>55</v>
+      </c>
+      <c r="B83" s="17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A84" s="58" t="s">
+        <v>281</v>
+      </c>
+      <c r="B84" s="17" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A85" s="58" t="s">
+        <v>56</v>
+      </c>
+      <c r="B85" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A86" s="58" t="s">
+        <v>282</v>
+      </c>
+      <c r="B86" s="17" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A87" s="58" t="s">
+        <v>59</v>
+      </c>
+      <c r="B87" s="17" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A88" s="58" t="s">
+        <v>283</v>
+      </c>
+      <c r="B88" s="17" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A89" s="58" t="s">
+        <v>284</v>
+      </c>
+      <c r="B89" s="17" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A90" s="58" t="s">
+        <v>285</v>
+      </c>
+      <c r="B90" s="17" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A91" s="58" t="s">
+        <v>61</v>
+      </c>
+      <c r="B91" s="17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A92" s="58" t="s">
+        <v>63</v>
+      </c>
+      <c r="B92" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A93" s="58" t="s">
+        <v>65</v>
+      </c>
+      <c r="B93" s="17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A94" s="58" t="s">
+        <v>67</v>
+      </c>
+      <c r="B94" s="17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A95" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="B95" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A96" s="58" t="s">
+        <v>71</v>
+      </c>
+      <c r="B96" s="17" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97" s="58" t="s">
+        <v>72</v>
+      </c>
+      <c r="B97" s="17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98" s="58" t="s">
+        <v>286</v>
+      </c>
+      <c r="B98" s="17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99" s="58" t="s">
+        <v>287</v>
+      </c>
+      <c r="B99" s="17" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100" s="58" t="s">
+        <v>288</v>
+      </c>
+      <c r="B100" s="17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A101" s="58" t="s">
+        <v>289</v>
+      </c>
+      <c r="B101" s="17" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A102" s="58" t="s">
+        <v>290</v>
+      </c>
+      <c r="B102" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A103" s="58" t="s">
+        <v>291</v>
+      </c>
+      <c r="B103" s="17" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A104" s="58" t="s">
+        <v>292</v>
+      </c>
+      <c r="B104" s="17" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A105" s="58" t="s">
+        <v>293</v>
+      </c>
+      <c r="B105" s="17" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A106" s="58" t="s">
+        <v>294</v>
+      </c>
+      <c r="B106" s="17" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A107" s="58" t="s">
+        <v>295</v>
+      </c>
+      <c r="B107" s="17" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A108" s="58" t="s">
+        <v>296</v>
+      </c>
+      <c r="B108" s="17" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A109" s="58" t="s">
+        <v>297</v>
+      </c>
+      <c r="B109" s="17" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A110" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="B110" s="17" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A111" s="58" t="s">
+        <v>299</v>
+      </c>
+      <c r="B111" s="17" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A112" s="58" t="s">
+        <v>300</v>
+      </c>
+      <c r="B112" s="17" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A113" s="58" t="s">
+        <v>301</v>
+      </c>
+      <c r="B113" s="17" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A114" s="58" t="s">
+        <v>302</v>
+      </c>
+      <c r="B114" s="17" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A115" s="58" t="s">
+        <v>303</v>
+      </c>
+      <c r="B115" s="17" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A116" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="B116" s="17" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A117" s="58" t="s">
+        <v>305</v>
+      </c>
+      <c r="B117" s="17" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A118" s="58" t="s">
+        <v>306</v>
+      </c>
+      <c r="B118" s="17" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A119" s="58" t="s">
+        <v>307</v>
+      </c>
+      <c r="B119" s="17" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A120" s="58" t="s">
+        <v>308</v>
+      </c>
+      <c r="B120" s="17" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A121" s="58" t="s">
+        <v>309</v>
+      </c>
+      <c r="B121" s="17" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A122" s="58" t="s">
+        <v>310</v>
+      </c>
+      <c r="B122" s="17" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A123" s="58" t="s">
+        <v>311</v>
+      </c>
+      <c r="B123" s="17" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A124" s="58" t="s">
+        <v>312</v>
+      </c>
+      <c r="B124" s="17" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A125" s="58" t="s">
+        <v>313</v>
+      </c>
+      <c r="B125" s="17" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A126" s="58" t="s">
+        <v>314</v>
+      </c>
+      <c r="B126" s="17" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A127" s="58" t="s">
+        <v>315</v>
+      </c>
+      <c r="B127" s="17" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A128" s="58" t="s">
+        <v>316</v>
+      </c>
+      <c r="B128" s="17" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A129" s="58" t="s">
+        <v>317</v>
+      </c>
+      <c r="B129" s="17" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A130" s="58" t="s">
+        <v>318</v>
+      </c>
+      <c r="B130" s="17" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A131" s="58" t="s">
+        <v>319</v>
+      </c>
+      <c r="B131" s="17" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A132" s="58" t="s">
+        <v>320</v>
+      </c>
+      <c r="B132" s="17" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A133" s="58" t="s">
+        <v>321</v>
+      </c>
+      <c r="B133" s="17" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A134" s="58" t="s">
         <v>322</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B134" s="17" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A135" s="58" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="17" t="s">
+      <c r="B135" s="17" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A136" s="58" t="s">
+        <v>324</v>
+      </c>
+      <c r="B136" s="17" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A137" s="58" t="s">
+        <v>325</v>
+      </c>
+      <c r="B137" s="17" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A138" s="58" t="s">
+        <v>326</v>
+      </c>
+      <c r="B138" s="17" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A139" s="58" t="s">
+        <v>327</v>
+      </c>
+      <c r="B139" s="17" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A140" s="58" t="s">
+        <v>328</v>
+      </c>
+      <c r="B140" s="17" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A141" s="58" t="s">
+        <v>329</v>
+      </c>
+      <c r="B141" s="17" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A142" s="58" t="s">
+        <v>330</v>
+      </c>
+      <c r="B142" s="17" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A143" s="58" t="s">
+        <v>331</v>
+      </c>
+      <c r="B143" s="17" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A144" s="58" t="s">
+        <v>332</v>
+      </c>
+      <c r="B144" s="17" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A145" s="58" t="s">
+        <v>333</v>
+      </c>
+      <c r="B145" s="17" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A146" s="58" t="s">
+        <v>334</v>
+      </c>
+      <c r="B146" s="17" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A147" s="58" t="s">
+        <v>335</v>
+      </c>
+      <c r="B147" s="17" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A148" s="58" t="s">
+        <v>336</v>
+      </c>
+      <c r="B148" s="17" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A149" s="58" t="s">
+        <v>337</v>
+      </c>
+      <c r="B149" s="17" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A150" s="58" t="s">
+        <v>338</v>
+      </c>
+      <c r="B150" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A151" s="58" t="s">
+        <v>339</v>
+      </c>
+      <c r="B151" s="17" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A152" s="58" t="s">
+        <v>340</v>
+      </c>
+      <c r="B152" s="17" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A153" s="58" t="s">
+        <v>341</v>
+      </c>
+      <c r="B153" s="17" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A154" s="58" t="s">
+        <v>342</v>
+      </c>
+      <c r="B154" s="17" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A155" s="58" t="s">
+        <v>343</v>
+      </c>
+      <c r="B155" s="17" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A156" s="58" t="s">
+        <v>344</v>
+      </c>
+      <c r="B156" s="17" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A157" s="58" t="s">
+        <v>345</v>
+      </c>
+      <c r="B157" s="17" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A158" s="58" t="s">
+        <v>346</v>
+      </c>
+      <c r="B158" s="17">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A159" s="58" t="s">
+        <v>347</v>
+      </c>
+      <c r="B159" s="17" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A160" s="58" t="s">
+        <v>348</v>
+      </c>
+      <c r="B160" s="17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A161" s="58" t="s">
+        <v>349</v>
+      </c>
+      <c r="B161" s="17">
+        <v>2610</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A162" s="58" t="s">
+        <v>350</v>
+      </c>
+      <c r="B162" s="17" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A163" s="58" t="s">
+        <v>351</v>
+      </c>
+      <c r="B163" s="17" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A164" s="58" t="s">
+        <v>352</v>
+      </c>
+      <c r="B164" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A165" s="58" t="s">
+        <v>353</v>
+      </c>
+      <c r="B165" s="17" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A166" s="58" t="s">
+        <v>354</v>
+      </c>
+      <c r="B166" s="17" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A167" s="58" t="s">
+        <v>355</v>
+      </c>
+      <c r="B167" s="17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A168" s="58" t="s">
+        <v>356</v>
+      </c>
+      <c r="B168" s="17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A169" s="58" t="s">
+        <v>357</v>
+      </c>
+      <c r="B169" s="17" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A170" s="58" t="s">
+        <v>358</v>
+      </c>
+      <c r="B170" s="17" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A171" s="58" t="s">
+        <v>359</v>
+      </c>
+      <c r="B171" s="17" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A172" s="58" t="s">
+        <v>360</v>
+      </c>
+      <c r="B172" s="17" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A173" s="58" t="s">
+        <v>361</v>
+      </c>
+      <c r="B173" s="17" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A174" s="58" t="s">
+        <v>362</v>
+      </c>
+      <c r="B174" s="17" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A175" s="58" t="s">
+        <v>363</v>
+      </c>
+      <c r="B175" s="17" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A176" s="58" t="s">
+        <v>364</v>
+      </c>
+      <c r="B176" s="17" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A177" s="58" t="s">
+        <v>365</v>
+      </c>
+      <c r="B177" s="17" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A178" s="58" t="s">
+        <v>366</v>
+      </c>
+      <c r="B178" s="17" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A179" s="58" t="s">
+        <v>367</v>
+      </c>
+      <c r="B179" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A180" s="58" t="s">
+        <v>368</v>
+      </c>
+      <c r="B180" s="17" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A181" s="58" t="s">
+        <v>369</v>
+      </c>
+      <c r="B181" s="17" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A182" s="58" t="s">
+        <v>370</v>
+      </c>
+      <c r="B182" s="17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A183" s="58" t="s">
+        <v>371</v>
+      </c>
+      <c r="B183" s="17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A184" s="58" t="s">
+        <v>372</v>
+      </c>
+      <c r="B184" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A185" s="58" t="s">
+        <v>373</v>
+      </c>
+      <c r="B185" s="17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A186" s="58" t="s">
+        <v>374</v>
+      </c>
+      <c r="B186" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A187" s="58" t="s">
+        <v>375</v>
+      </c>
+      <c r="B187" s="17" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A188" s="58" t="s">
+        <v>376</v>
+      </c>
+      <c r="B188" s="17" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A189" s="58" t="s">
+        <v>377</v>
+      </c>
+      <c r="B189" s="17" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A190" s="58" t="s">
+        <v>378</v>
+      </c>
+      <c r="B190" s="17" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A191" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="B191" s="17" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A192" s="58" t="s">
+        <v>380</v>
+      </c>
+      <c r="B192" s="17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A193" s="58" t="s">
+        <v>381</v>
+      </c>
+      <c r="B193" s="17" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A194" s="58" t="s">
+        <v>382</v>
+      </c>
+      <c r="B194" s="17" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A195" s="58" t="s">
+        <v>383</v>
+      </c>
+      <c r="B195" s="17" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A196" s="58" t="s">
+        <v>384</v>
+      </c>
+      <c r="B196" s="17" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A197" s="58" t="s">
+        <v>385</v>
+      </c>
+      <c r="B197" s="17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A198" s="58" t="s">
+        <v>386</v>
+      </c>
+      <c r="B198" s="17" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A199" s="58" t="s">
+        <v>387</v>
+      </c>
+      <c r="B199" s="17" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A200" s="58" t="s">
+        <v>388</v>
+      </c>
+      <c r="B200" s="17" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A201" s="58" t="s">
+        <v>389</v>
+      </c>
+      <c r="B201" s="17" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A202" s="58" t="s">
+        <v>390</v>
+      </c>
+      <c r="B202" s="17" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A203" s="58" t="s">
+        <v>391</v>
+      </c>
+      <c r="B203" s="17" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A204" s="58" t="s">
+        <v>392</v>
+      </c>
+      <c r="B204" s="17" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A205" s="58" t="s">
+        <v>393</v>
+      </c>
+      <c r="B205" s="17" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A206" s="58" t="s">
+        <v>394</v>
+      </c>
+      <c r="B206" s="17" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A207" s="58" t="s">
+        <v>395</v>
+      </c>
+      <c r="B207" s="17" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A208" s="58" t="s">
+        <v>396</v>
+      </c>
+      <c r="B208" s="17" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A209" s="58" t="s">
+        <v>397</v>
+      </c>
+      <c r="B209" s="17" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A210" s="58" t="s">
+        <v>398</v>
+      </c>
+      <c r="B210" s="17" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A211" s="58" t="s">
+        <v>399</v>
+      </c>
+      <c r="B211" s="17" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A212" s="58" t="s">
+        <v>400</v>
+      </c>
+      <c r="B212" s="17" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A213" s="58" t="s">
+        <v>401</v>
+      </c>
+      <c r="B213" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A214" s="58" t="s">
+        <v>402</v>
+      </c>
+      <c r="B214" s="17" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A215" s="58" t="s">
+        <v>403</v>
+      </c>
+      <c r="B215" s="17" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A216" s="58" t="s">
+        <v>404</v>
+      </c>
+      <c r="B216" s="17" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A217" s="58" t="s">
+        <v>405</v>
+      </c>
+      <c r="B217" s="17" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A218" s="58" t="s">
+        <v>406</v>
+      </c>
+      <c r="B218" s="17" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A219" s="58" t="s">
+        <v>407</v>
+      </c>
+      <c r="B219" s="17" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A220" s="58" t="s">
+        <v>408</v>
+      </c>
+      <c r="B220" s="17" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A221" s="58" t="s">
+        <v>409</v>
+      </c>
+      <c r="B221" s="17" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A222" s="58" t="s">
+        <v>410</v>
+      </c>
+      <c r="B222" s="17" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A223" s="58" t="s">
+        <v>411</v>
+      </c>
+      <c r="B223" s="17" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A224" s="58" t="s">
+        <v>412</v>
+      </c>
+      <c r="B224" s="17" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A225" s="58" t="s">
+        <v>413</v>
+      </c>
+      <c r="B225" s="17" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A226" s="58" t="s">
+        <v>414</v>
+      </c>
+      <c r="B226" s="17" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A227" s="58" t="s">
+        <v>415</v>
+      </c>
+      <c r="B227" s="17" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A228" s="58" t="s">
+        <v>416</v>
+      </c>
+      <c r="B228" s="17" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A229" s="58" t="s">
+        <v>74</v>
+      </c>
+      <c r="B229" s="17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A230" s="58" t="s">
+        <v>76</v>
+      </c>
+      <c r="B230" s="17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A231" s="58" t="s">
+        <v>417</v>
+      </c>
+      <c r="B231" s="17" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A232" s="58" t="s">
+        <v>418</v>
+      </c>
+      <c r="B232" s="17" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A233" s="58" t="s">
+        <v>419</v>
+      </c>
+      <c r="B233" s="17" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A234" s="58" t="s">
+        <v>420</v>
+      </c>
+      <c r="B234" s="17" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A235" s="58" t="s">
+        <v>421</v>
+      </c>
+      <c r="B235" s="17" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A236" s="58" t="s">
+        <v>422</v>
+      </c>
+      <c r="B236" s="17" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A237" s="58" t="s">
+        <v>423</v>
+      </c>
+      <c r="B237" s="17" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A238" s="58" t="s">
+        <v>424</v>
+      </c>
+      <c r="B238" s="17" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A239" s="58" t="s">
+        <v>425</v>
+      </c>
+      <c r="B239" s="17" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A240" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="B240" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A241" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="B241" s="17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A242" s="58" t="s">
+        <v>426</v>
+      </c>
+      <c r="B242" s="17" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A243" s="58" t="s">
+        <v>427</v>
+      </c>
+      <c r="B243" s="17" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A244" s="58" t="s">
+        <v>428</v>
+      </c>
+      <c r="B244" s="17" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A245" s="58" t="s">
+        <v>429</v>
+      </c>
+      <c r="B245" s="17" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A246" s="58" t="s">
+        <v>430</v>
+      </c>
+      <c r="B246" s="17" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A247" s="58" t="s">
+        <v>431</v>
+      </c>
+      <c r="B247" s="17" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A248" s="58" t="s">
+        <v>432</v>
+      </c>
+      <c r="B248" s="17" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A249" s="58" t="s">
+        <v>433</v>
+      </c>
+      <c r="B249" s="17" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A250" s="58" t="s">
+        <v>434</v>
+      </c>
+      <c r="B250" s="17" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A251" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="B251" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A252" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="B252" s="17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A253" s="58" t="s">
+        <v>86</v>
+      </c>
+      <c r="B253" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A254" s="58" t="s">
+        <v>88</v>
+      </c>
+      <c r="B254" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A255" s="58" t="s">
+        <v>435</v>
+      </c>
+      <c r="B255" s="17" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A256" s="58" t="s">
+        <v>436</v>
+      </c>
+      <c r="B256" s="17" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A257" s="58" t="s">
+        <v>90</v>
+      </c>
+      <c r="B257" s="17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A258" s="58" t="s">
+        <v>437</v>
+      </c>
+      <c r="B258" s="17" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A259" s="58" t="s">
+        <v>438</v>
+      </c>
+      <c r="B259" s="17" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A260" s="58" t="s">
+        <v>439</v>
+      </c>
+      <c r="B260" s="17" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A261" s="58" t="s">
+        <v>440</v>
+      </c>
+      <c r="B261" s="17" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A262" s="58" t="s">
+        <v>441</v>
+      </c>
+      <c r="B262" s="17" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A263" s="58" t="s">
+        <v>442</v>
+      </c>
+      <c r="B263" s="17" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A264" s="58" t="s">
+        <v>443</v>
+      </c>
+      <c r="B264" s="17" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A265" s="58" t="s">
+        <v>444</v>
+      </c>
+      <c r="B265" s="17" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A266" s="58" t="s">
+        <v>445</v>
+      </c>
+      <c r="B266" s="17" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A267" s="58" t="s">
+        <v>446</v>
+      </c>
+      <c r="B267" s="17" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A268" s="58" t="s">
+        <v>92</v>
+      </c>
+      <c r="B268" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A269" s="58" t="s">
+        <v>94</v>
+      </c>
+      <c r="B269" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="B26" s="17" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="B30" s="17" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="B31" s="17" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B32" s="17" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="B33" s="17" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="B34" s="17" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="B35" s="17" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="B36" s="17" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="B37" s="17" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="B38" s="17" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="B39" s="17" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="B40" s="17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="B41" s="17" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="B42" s="17" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="B43" s="17" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="B44" s="17" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="B45" s="17" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="B46" s="17" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A47" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="B47" s="17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A48" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="B48" s="17" t="s">
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A270" s="58" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49" s="17" t="s">
+      <c r="B270" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="B49" s="17" t="s">
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A271" s="58" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50" s="17" t="s">
+      <c r="B271" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="B50" s="17" t="s">
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A272" s="58" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A51" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="B51" s="17" t="s">
+      <c r="B272" s="17" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A52" s="17" t="s">
+    <row r="273" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A273" s="58" t="s">
         <v>101</v>
       </c>
-      <c r="B52" s="17" t="s">
+      <c r="B273" s="17" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A53" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="B53" s="17" t="s">
+    <row r="274" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A274" s="58" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A54" s="17" t="s">
+      <c r="B274" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="B54" s="17" t="s">
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A275" s="58" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A55" s="17" t="s">
+      <c r="B275" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="B55" s="17" t="s">
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A276" s="58" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A56" s="17" t="s">
+      <c r="B276" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="B56" s="17" t="s">
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A277" s="58" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A57" s="17" t="s">
+      <c r="B277" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="B57" s="17" t="s">
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A278" s="58" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A58" s="17" t="s">
+      <c r="B278" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="B58" s="17" t="s">
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A279" s="58" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A59" s="17" t="s">
+      <c r="B279" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="B59" s="17" t="s">
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A280" s="58" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A60" s="17" t="s">
+      <c r="B280" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="B60" s="17" t="s">
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A281" s="58" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A61" s="17" t="s">
+      <c r="B281" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="B61" s="17" t="s">
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A282" s="58" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A62" s="17" t="s">
+      <c r="B282" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="B62" s="17" t="s">
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A283" s="58" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A63" s="17" t="s">
+      <c r="B283" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B63" s="17" t="s">
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A284" s="58" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A64" s="17" t="s">
+      <c r="B284" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="B64" s="17" t="s">
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A285" s="58" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A65" s="17" t="s">
+      <c r="B285" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="B65" s="17" t="s">
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A286" s="58" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A66" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="B66" s="17" t="s">
+      <c r="B286" s="17" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A67" s="17" t="s">
+    <row r="287" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A287" s="58" t="s">
         <v>129</v>
       </c>
-      <c r="B67" s="17" t="s">
+      <c r="B287" s="17" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A68" s="17" t="s">
+    <row r="288" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A288" s="58" t="s">
         <v>131</v>
       </c>
-      <c r="B68" s="17" t="s">
+      <c r="B288" s="17" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A69" s="17" t="s">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A289" s="58" t="s">
         <v>133</v>
       </c>
-      <c r="B69" s="17" t="s">
+      <c r="B289" s="17" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A70" s="17" t="s">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A290" s="58" t="s">
         <v>135</v>
       </c>
-      <c r="B70" s="17" t="s">
+      <c r="B290" s="17" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A71" s="17" t="s">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A291" s="58" t="s">
         <v>137</v>
       </c>
-      <c r="B71" s="17" t="s">
+      <c r="B291" s="17" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A72" s="17" t="s">
+    <row r="292" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A292" s="58" t="s">
         <v>139</v>
       </c>
-      <c r="B72" s="17" t="s">
+      <c r="B292" s="17" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A73" s="17" t="s">
+    <row r="293" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A293" s="58" t="s">
         <v>141</v>
       </c>
-      <c r="B73" s="17" t="s">
+      <c r="B293" s="17" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A74" s="17" t="s">
+    <row r="294" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A294" s="58" t="s">
         <v>143</v>
       </c>
-      <c r="B74" s="17" t="s">
+      <c r="B294" s="17" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A75" s="17" t="s">
+    <row r="295" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A295" s="58" t="s">
         <v>145</v>
       </c>
-      <c r="B75" s="17" t="s">
+      <c r="B295" s="17" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A76" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="B76" s="17" t="s">
+    <row r="296" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A296" s="58" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A77" s="17" t="s">
+      <c r="B296" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="B77" s="17" t="s">
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A297" s="58" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A78" s="17" t="s">
+      <c r="B297" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="B78" s="17" t="s">
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A298" s="58" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A79" s="17" t="s">
+      <c r="B298" s="17" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A299" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="B79" s="17" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A80" s="17" t="s">
+      <c r="B299" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="B80" s="17" t="s">
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A300" s="58" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A81" s="17" t="s">
+      <c r="B300" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="B81" s="17" t="s">
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A301" s="58" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A82" s="17" t="s">
+      <c r="B301" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="B82" s="17" t="s">
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A302" s="58" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A83" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="B83" s="17" t="s">
+      <c r="B302" s="17" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A84" s="17" t="s">
+    <row r="303" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A303" s="58" t="s">
         <v>160</v>
       </c>
-      <c r="B84" s="17" t="s">
+      <c r="B303" s="17" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A85" s="17" t="s">
+    <row r="304" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A304" s="58" t="s">
         <v>162</v>
       </c>
-      <c r="B85" s="17" t="s">
+      <c r="B304" s="17" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A86" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="B86" s="17" t="s">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A305" s="58" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A87" s="17" t="s">
+      <c r="B305" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="B87" s="17" t="s">
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A306" s="58" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A88" s="17" t="s">
+      <c r="B306" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="B88" s="17" t="s">
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A307" s="58" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A89" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="B89" s="17" t="s">
+      <c r="B307" s="17" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A90" s="17" t="s">
+    <row r="308" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A308" s="58" t="s">
         <v>170</v>
       </c>
-      <c r="B90" s="17" t="s">
+      <c r="B308" s="17" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A91" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="B91" s="17" t="s">
+    <row r="309" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A309" s="58" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A92" s="17" t="s">
+      <c r="B309" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="B92" s="17" t="s">
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A310" s="58" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A93" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="B93" s="17" t="s">
+      <c r="B310" s="17" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A94" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="B94" s="17" t="s">
+    <row r="311" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A311" s="58" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A95" s="17" t="s">
+      <c r="B311" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="B95" s="17" t="s">
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A312" s="58" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A96" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="B96" s="17" t="s">
+      <c r="B312" s="17" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A97" s="17" t="s">
+    <row r="313" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A313" s="58" t="s">
         <v>180</v>
       </c>
-      <c r="B97" s="17" t="s">
+      <c r="B313" s="17" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A98" s="17" t="s">
+    <row r="314" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A314" s="58" t="s">
         <v>182</v>
       </c>
-      <c r="B98" s="17" t="s">
+      <c r="B314" s="17" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A99" s="17" t="s">
-        <v>182</v>
-      </c>
-      <c r="B99" s="17" t="s">
+    <row r="315" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A315" s="58" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A100" s="17" t="s">
+      <c r="B315" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="B100" s="17" t="s">
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A316" s="58" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A101" s="17" t="s">
+      <c r="B316" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B101" s="17" t="s">
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A317" s="58" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A102" s="17" t="s">
+      <c r="B317" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="B102" s="17" t="s">
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A318" s="58" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A103" s="17" t="s">
+      <c r="B318" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="B103" s="17" t="s">
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A319" s="58" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A104" s="17" t="s">
+      <c r="B319" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="B104" s="17" t="s">
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A320" s="58" t="s">
+        <v>447</v>
+      </c>
+      <c r="B320" s="17" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A321" s="58" t="s">
+        <v>448</v>
+      </c>
+      <c r="B321" s="17" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A322" s="58" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A105" s="17" t="s">
+      <c r="B322" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="B105" s="17" t="s">
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A323" s="58" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A106" s="17" t="s">
+      <c r="B323" s="17" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A324" s="58" t="s">
         <v>197</v>
       </c>
-      <c r="B106" s="17" t="s">
+      <c r="B324" s="17" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A107" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="B107" s="17" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A108" s="17" t="s">
+    <row r="325" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A325" s="58" t="s">
         <v>199</v>
       </c>
-      <c r="B108" s="17" t="s">
+      <c r="B325" s="17" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A109" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="B109" s="17" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A110" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="B110" s="17" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A111" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="B111" s="17" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A112" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="B112" s="17" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A113" s="17" t="s">
-        <v>208</v>
-      </c>
-      <c r="B113" s="17" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A114" s="17" t="s">
-        <v>208</v>
-      </c>
-      <c r="B114" s="17" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A115" s="17" t="s">
-        <v>210</v>
-      </c>
-      <c r="B115" s="17" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A116" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="B116" s="17" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A117" s="17" t="s">
-        <v>214</v>
-      </c>
-      <c r="B117" s="17" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A118" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="B118" s="17" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A119" s="17" t="s">
-        <v>218</v>
-      </c>
-      <c r="B119" s="17" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A120" s="17" t="s">
-        <v>220</v>
-      </c>
-      <c r="B120" s="17" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A121" s="17" t="s">
-        <v>222</v>
-      </c>
-      <c r="B121" s="17" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A122" s="17" t="s">
-        <v>224</v>
-      </c>
-      <c r="B122" s="17" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A123" s="17" t="s">
-        <v>226</v>
-      </c>
-      <c r="B123" s="17" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A124" s="17" t="s">
-        <v>228</v>
-      </c>
-      <c r="B124" s="17" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A125" s="17" t="s">
-        <v>230</v>
-      </c>
-      <c r="B125" s="17" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A126" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="B126" s="17" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A127" s="17" t="s">
-        <v>234</v>
-      </c>
-      <c r="B127" s="17" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A128" s="17" t="s">
-        <v>236</v>
-      </c>
-      <c r="B128" s="17" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A129" s="17" t="s">
-        <v>238</v>
-      </c>
-      <c r="B129" s="17" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A130" s="17" t="s">
-        <v>240</v>
-      </c>
-      <c r="B130" s="17" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A131" s="17" t="s">
-        <v>242</v>
-      </c>
-      <c r="B131" s="17" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A132" s="17" t="s">
-        <v>244</v>
-      </c>
-      <c r="B132" s="17" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A133" s="17" t="s">
-        <v>246</v>
-      </c>
-      <c r="B133" s="17" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A134" s="17" t="s">
-        <v>248</v>
-      </c>
-      <c r="B134" s="17" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A135" s="17" t="s">
-        <v>250</v>
-      </c>
-      <c r="B135" s="17" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A136" s="17" t="s">
-        <v>252</v>
-      </c>
-      <c r="B136" s="17" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A137" s="17" t="s">
-        <v>254</v>
-      </c>
-      <c r="B137" s="17" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A138" s="17" t="s">
-        <v>256</v>
-      </c>
-      <c r="B138" s="17" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A139" s="17" t="s">
-        <v>258</v>
-      </c>
-      <c r="B139" s="17" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A140" s="17" t="s">
-        <v>260</v>
-      </c>
-      <c r="B140" s="17" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A141" s="17" t="s">
-        <v>262</v>
-      </c>
-      <c r="B141" s="17" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A142" s="17" t="s">
-        <v>264</v>
-      </c>
-      <c r="B142" s="17" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A143" s="17" t="s">
-        <v>266</v>
-      </c>
-      <c r="B143" s="17" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A144" s="17" t="s">
-        <v>268</v>
-      </c>
-      <c r="B144" s="17" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A145" s="17" t="s">
-        <v>270</v>
-      </c>
-      <c r="B145" s="17" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A146" s="17" t="s">
-        <v>272</v>
-      </c>
-      <c r="B146" s="17" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A147" s="17" t="s">
-        <v>274</v>
-      </c>
-      <c r="B147" s="17" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A148" s="17" t="s">
-        <v>276</v>
-      </c>
-      <c r="B148" s="17" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A149" s="17" t="s">
-        <v>278</v>
-      </c>
-      <c r="B149" s="17" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A150" s="17" t="s">
-        <v>280</v>
-      </c>
-      <c r="B150" s="17" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A151" s="17" t="s">
-        <v>282</v>
-      </c>
-      <c r="B151" s="17" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A152" s="17" t="s">
-        <v>284</v>
-      </c>
-      <c r="B152" s="17" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A153" s="17" t="s">
-        <v>286</v>
-      </c>
-      <c r="B153" s="17" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A154" s="17" t="s">
-        <v>288</v>
-      </c>
-      <c r="B154" s="17" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A155" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="B155" s="17" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A156" s="17" t="s">
-        <v>292</v>
-      </c>
-      <c r="B156" s="17" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A157" s="17" t="s">
-        <v>294</v>
-      </c>
-      <c r="B157" s="17" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A158" s="17" t="s">
-        <v>296</v>
-      </c>
-      <c r="B158" s="17" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A159" s="17" t="s">
-        <v>298</v>
-      </c>
-      <c r="B159" s="17" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A160" s="17" t="s">
-        <v>300</v>
-      </c>
-      <c r="B160" s="17" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A161" s="17" t="s">
-        <v>300</v>
-      </c>
-      <c r="B161" s="17" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A162" s="17" t="s">
-        <v>303</v>
-      </c>
-      <c r="B162" s="17" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A163" s="17" t="s">
-        <v>305</v>
-      </c>
-      <c r="B163" s="17" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A164" s="17" t="s">
-        <v>307</v>
-      </c>
-      <c r="B164" s="17" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A165" s="17" t="s">
-        <v>309</v>
-      </c>
-      <c r="B165" s="17" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A166" s="17" t="s">
-        <v>311</v>
-      </c>
-      <c r="B166" s="17" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A167" s="17" t="s">
-        <v>313</v>
-      </c>
-      <c r="B167" s="17" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A168" s="17" t="s">
-        <v>315</v>
-      </c>
-      <c r="B168" s="17" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A169" s="17" t="s">
-        <v>317</v>
-      </c>
-      <c r="B169" s="17" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B170" s="17" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A171" s="17" t="s">
-        <v>320</v>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A326" s="58" t="s">
+        <v>449</v>
+      </c>
+      <c r="B326" s="17" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A327" s="58" t="s">
+        <v>450</v>
+      </c>
+      <c r="B327" s="17" t="s">
+        <v>385</v>
       </c>
     </row>
   </sheetData>

--- a/wwwroot/template/TemPlateQuote.xlsx
+++ b/wwwroot/template/TemPlateQuote.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\khanhmf\Cost Managerment\wwwroot\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{763D4767-76BC-4C8C-A850-AC2FD00ACA1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C203ED8D-E19D-4507-833C-881DE0C61FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F4BD22E2-5202-4BAA-B608-770E176E4E09}"/>
   </bookViews>
@@ -714,7 +714,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1333" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="753">
   <si>
     <t>No</t>
   </si>
@@ -2906,6 +2906,342 @@
   <si>
     <t>DOMINO-PSU</t>
   </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ao/xơ </t>
+  </si>
+  <si>
+    <t>Ao/xơ (gồm bao bì)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ao/xơ (gồm cont.) </t>
+  </si>
+  <si>
+    <t>Ao/xơ (hàm lượng KL)</t>
+  </si>
+  <si>
+    <t>Ao/xơ (trọng lg khô)</t>
+  </si>
+  <si>
+    <t>Ao/xơ đong</t>
+  </si>
+  <si>
+    <t>Bản</t>
+  </si>
+  <si>
+    <t>Bảng</t>
+  </si>
+  <si>
+    <t>Barrel</t>
+  </si>
+  <si>
+    <t>Bịch</t>
+  </si>
+  <si>
+    <t>Bộ</t>
+  </si>
+  <si>
+    <t>Cái/Chiếc</t>
+  </si>
+  <si>
+    <t>Cành</t>
+  </si>
+  <si>
+    <t>Cara</t>
+  </si>
+  <si>
+    <t>Cây</t>
+  </si>
+  <si>
+    <t>Cen ti mét</t>
+  </si>
+  <si>
+    <t>Chai/ Lọ/ Tuýp</t>
+  </si>
+  <si>
+    <t>CHI</t>
+  </si>
+  <si>
+    <t>cm2</t>
+  </si>
+  <si>
+    <t>cm3</t>
+  </si>
+  <si>
+    <t>Con</t>
+  </si>
+  <si>
+    <t>CONTAINER</t>
+  </si>
+  <si>
+    <t>Củ</t>
+  </si>
+  <si>
+    <t>Cục</t>
+  </si>
+  <si>
+    <t>Cụm</t>
+  </si>
+  <si>
+    <t>Cuốn</t>
+  </si>
+  <si>
+    <t>Cuộn</t>
+  </si>
+  <si>
+    <t>dm</t>
+  </si>
+  <si>
+    <t>dm2</t>
+  </si>
+  <si>
+    <t>Đôi/Cặp</t>
+  </si>
+  <si>
+    <t>Galông ruợu</t>
+  </si>
+  <si>
+    <t>Gam</t>
+  </si>
+  <si>
+    <t>Gam (gồm bao bì)</t>
+  </si>
+  <si>
+    <t>Gam (gồm container)</t>
+  </si>
+  <si>
+    <t>Gam (hàm lượng KL)</t>
+  </si>
+  <si>
+    <t>Gam (trọng lg khô)</t>
+  </si>
+  <si>
+    <t>Gói</t>
+  </si>
+  <si>
+    <t>Hàm luợng lactoza</t>
+  </si>
+  <si>
+    <t>Hectolit</t>
+  </si>
+  <si>
+    <t>I/át</t>
+  </si>
+  <si>
+    <t>I/át khối</t>
+  </si>
+  <si>
+    <t>I/át vuông</t>
+  </si>
+  <si>
+    <t>Inch</t>
+  </si>
+  <si>
+    <t>Kiện/Hộp/Bao/Gói</t>
+  </si>
+  <si>
+    <t>Kilo lít</t>
+  </si>
+  <si>
+    <t>Kilo mét (1000 mét)</t>
+  </si>
+  <si>
+    <t>Kilô/oắt giờ</t>
+  </si>
+  <si>
+    <t>Kilogam</t>
+  </si>
+  <si>
+    <t>Kilogam (gồm bao bì)</t>
+  </si>
+  <si>
+    <t>Kilogam (gồm cont.)</t>
+  </si>
+  <si>
+    <t>Kilogam (hàm lg KL)</t>
+  </si>
+  <si>
+    <t>Kilogam (tr.lg khô)</t>
+  </si>
+  <si>
+    <t>KIT</t>
+  </si>
+  <si>
+    <t>KVA</t>
+  </si>
+  <si>
+    <t>Liều</t>
+  </si>
+  <si>
+    <t>Lít</t>
+  </si>
+  <si>
+    <t>Lít Anh</t>
+  </si>
+  <si>
+    <t>Lô (nhiều cái)</t>
+  </si>
+  <si>
+    <t>Lon/Can</t>
+  </si>
+  <si>
+    <t>Mét</t>
+  </si>
+  <si>
+    <t>Mét khối</t>
+  </si>
+  <si>
+    <t>Mét vuông</t>
+  </si>
+  <si>
+    <t>Mili gram</t>
+  </si>
+  <si>
+    <t>Mili lít</t>
+  </si>
+  <si>
+    <t>Mili mét</t>
+  </si>
+  <si>
+    <t>mm2</t>
+  </si>
+  <si>
+    <t>mm3</t>
+  </si>
+  <si>
+    <t>Nghìn</t>
+  </si>
+  <si>
+    <t>Ống</t>
+  </si>
+  <si>
+    <t>Panh</t>
+  </si>
+  <si>
+    <t>Pao</t>
+  </si>
+  <si>
+    <t>Pao (gồm bao bì)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pao (gồm container) </t>
+  </si>
+  <si>
+    <t>Pao (hàm lượng KL)</t>
+  </si>
+  <si>
+    <t>Pao (trọng lg khô)</t>
+  </si>
+  <si>
+    <t>Phút</t>
+  </si>
+  <si>
+    <t>Phút khối</t>
+  </si>
+  <si>
+    <t>Phút vuông</t>
+  </si>
+  <si>
+    <t>Quả</t>
+  </si>
+  <si>
+    <t>Quyển/Tập</t>
+  </si>
+  <si>
+    <t>RAM</t>
+  </si>
+  <si>
+    <t>Sợi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ster </t>
+  </si>
+  <si>
+    <t>Tá</t>
+  </si>
+  <si>
+    <t>Tạ (100kg)</t>
+  </si>
+  <si>
+    <t>Tấm</t>
+  </si>
+  <si>
+    <t>Tấn</t>
+  </si>
+  <si>
+    <t>Tấn (gồm bao bì)</t>
+  </si>
+  <si>
+    <t>Tấn (gồm container)</t>
+  </si>
+  <si>
+    <t>Tấn (hàm lượng KL)</t>
+  </si>
+  <si>
+    <t>Tấn (trọng lg khô)</t>
+  </si>
+  <si>
+    <t>Tấn dài</t>
+  </si>
+  <si>
+    <t>Tấn ngắn</t>
+  </si>
+  <si>
+    <t>Thanh/Mảnh/Miếng</t>
+  </si>
+  <si>
+    <t>Tờ</t>
+  </si>
+  <si>
+    <t>Tổng trọng lượng</t>
+  </si>
+  <si>
+    <t>Tổng trọng tải</t>
+  </si>
+  <si>
+    <t>Troi ao/xơ</t>
+  </si>
+  <si>
+    <t>Trọng tải</t>
+  </si>
+  <si>
+    <t>Túi</t>
+  </si>
+  <si>
+    <t>Tút</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>Viên/Hạt</t>
+  </si>
+  <si>
+    <t>UNIT</t>
+  </si>
+  <si>
+    <t>LBS</t>
+  </si>
+  <si>
+    <t>Vỉ</t>
+  </si>
+  <si>
+    <t>Inch2</t>
+  </si>
+  <si>
+    <t>Air Dry Met Ton</t>
+  </si>
+  <si>
+    <t>Sản phẩm</t>
+  </si>
+  <si>
+    <t>Thùng</t>
+  </si>
+  <si>
+    <t>Pallet</t>
+  </si>
 </sst>
 </file>
 
@@ -2914,7 +3250,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]dd\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2996,6 +3332,23 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -3123,7 +3476,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3216,13 +3569,37 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3244,24 +3621,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3273,23 +3641,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3763,18 +4123,18 @@
     </row>
     <row r="4" spans="1:32" ht="11.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9"/>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="35" t="s">
         <v>213</v>
       </c>
-      <c r="C4" s="45"/>
-      <c r="D4" s="46"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="36"/>
       <c r="E4" s="25"/>
       <c r="F4" s="25"/>
       <c r="G4" s="25"/>
-      <c r="H4" s="45" t="s">
+      <c r="H4" s="35" t="s">
         <v>214</v>
       </c>
-      <c r="I4" s="47"/>
+      <c r="I4" s="37"/>
       <c r="J4" s="9"/>
       <c r="K4" s="25"/>
       <c r="M4" s="9"/>
@@ -3796,14 +4156,14 @@
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="9"/>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="46"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="36"/>
       <c r="E5" s="25"/>
       <c r="F5" s="25"/>
       <c r="G5" s="25"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="47"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="37"/>
       <c r="J5" s="25"/>
       <c r="K5" s="25"/>
       <c r="L5" s="18"/>
@@ -3827,17 +4187,17 @@
       <c r="AD5" s="9"/>
     </row>
     <row r="6" spans="1:32" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="40" t="s">
         <v>264</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
       <c r="J6" s="18"/>
       <c r="K6" s="18"/>
       <c r="L6" s="18"/>
@@ -3897,15 +4257,15 @@
       <c r="L7" s="26">
         <v>12</v>
       </c>
-      <c r="M7" s="37">
+      <c r="M7" s="45">
         <f>L7+1</f>
         <v>13</v>
       </c>
-      <c r="N7" s="38"/>
-      <c r="O7" s="38"/>
-      <c r="P7" s="38"/>
-      <c r="Q7" s="38"/>
-      <c r="R7" s="39"/>
+      <c r="N7" s="46"/>
+      <c r="O7" s="46"/>
+      <c r="P7" s="46"/>
+      <c r="Q7" s="46"/>
+      <c r="R7" s="47"/>
       <c r="S7" s="24">
         <v>14</v>
       </c>
@@ -3963,106 +4323,106 @@
       </c>
     </row>
     <row r="8" spans="1:32" s="7" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="43" t="s">
+      <c r="A8" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="38" t="s">
         <v>215</v>
       </c>
-      <c r="C8" s="35" t="s">
+      <c r="C8" s="38" t="s">
         <v>216</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="D8" s="38" t="s">
         <v>217</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="E8" s="38" t="s">
         <v>218</v>
       </c>
-      <c r="F8" s="35" t="s">
+      <c r="F8" s="38" t="s">
         <v>219</v>
       </c>
-      <c r="G8" s="35" t="s">
+      <c r="G8" s="38" t="s">
         <v>220</v>
       </c>
-      <c r="H8" s="35" t="s">
+      <c r="H8" s="38" t="s">
         <v>222</v>
       </c>
-      <c r="I8" s="35" t="s">
+      <c r="I8" s="38" t="s">
         <v>223</v>
       </c>
-      <c r="J8" s="35" t="s">
+      <c r="J8" s="38" t="s">
         <v>221</v>
       </c>
-      <c r="K8" s="35" t="s">
+      <c r="K8" s="38" t="s">
         <v>224</v>
       </c>
-      <c r="L8" s="35" t="s">
+      <c r="L8" s="38" t="s">
         <v>225</v>
       </c>
-      <c r="M8" s="40" t="s">
+      <c r="M8" s="48" t="s">
         <v>231</v>
       </c>
-      <c r="N8" s="41"/>
-      <c r="O8" s="41"/>
-      <c r="P8" s="41"/>
-      <c r="Q8" s="41"/>
-      <c r="R8" s="42"/>
-      <c r="S8" s="35" t="s">
+      <c r="N8" s="49"/>
+      <c r="O8" s="49"/>
+      <c r="P8" s="49"/>
+      <c r="Q8" s="49"/>
+      <c r="R8" s="50"/>
+      <c r="S8" s="38" t="s">
         <v>235</v>
       </c>
-      <c r="T8" s="35" t="s">
+      <c r="T8" s="38" t="s">
         <v>236</v>
       </c>
-      <c r="U8" s="35" t="s">
+      <c r="U8" s="38" t="s">
         <v>232</v>
       </c>
-      <c r="V8" s="35" t="s">
+      <c r="V8" s="38" t="s">
         <v>233</v>
       </c>
-      <c r="W8" s="35" t="s">
+      <c r="W8" s="38" t="s">
         <v>237</v>
       </c>
-      <c r="X8" s="35" t="s">
+      <c r="X8" s="38" t="s">
         <v>238</v>
       </c>
-      <c r="Y8" s="35" t="s">
+      <c r="Y8" s="38" t="s">
         <v>239</v>
       </c>
-      <c r="Z8" s="35" t="s">
+      <c r="Z8" s="38" t="s">
         <v>240</v>
       </c>
-      <c r="AA8" s="35" t="s">
+      <c r="AA8" s="38" t="s">
         <v>241</v>
       </c>
-      <c r="AB8" s="35" t="s">
+      <c r="AB8" s="38" t="s">
         <v>242</v>
       </c>
-      <c r="AC8" s="35" t="s">
+      <c r="AC8" s="38" t="s">
         <v>243</v>
       </c>
-      <c r="AD8" s="35" t="s">
+      <c r="AD8" s="38" t="s">
         <v>244</v>
       </c>
-      <c r="AE8" s="34" t="s">
+      <c r="AE8" s="44" t="s">
         <v>245</v>
       </c>
-      <c r="AF8" s="34" t="s">
+      <c r="AF8" s="44" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="9" spans="1:32" s="7" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A9" s="44"/>
-      <c r="B9" s="36"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="36"/>
+      <c r="A9" s="43"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="39"/>
+      <c r="K9" s="39"/>
+      <c r="L9" s="39"/>
       <c r="M9" s="19" t="s">
         <v>226</v>
       </c>
@@ -4081,20 +4441,20 @@
       <c r="R9" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="S9" s="36"/>
-      <c r="T9" s="36"/>
-      <c r="U9" s="36"/>
-      <c r="V9" s="36"/>
-      <c r="W9" s="36"/>
-      <c r="X9" s="36"/>
-      <c r="Y9" s="36"/>
-      <c r="Z9" s="36"/>
-      <c r="AA9" s="36"/>
-      <c r="AB9" s="36"/>
-      <c r="AC9" s="36"/>
-      <c r="AD9" s="36"/>
-      <c r="AE9" s="34"/>
-      <c r="AF9" s="34"/>
+      <c r="S9" s="39"/>
+      <c r="T9" s="39"/>
+      <c r="U9" s="39"/>
+      <c r="V9" s="39"/>
+      <c r="W9" s="39"/>
+      <c r="X9" s="39"/>
+      <c r="Y9" s="39"/>
+      <c r="Z9" s="39"/>
+      <c r="AA9" s="39"/>
+      <c r="AB9" s="39"/>
+      <c r="AC9" s="39"/>
+      <c r="AD9" s="39"/>
+      <c r="AE9" s="44"/>
+      <c r="AF9" s="44"/>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
@@ -28738,23 +29098,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="B4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="A6:I6"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="X8:X9"/>
     <mergeCell ref="AE8:AE9"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="AF8:AF9"/>
@@ -28771,6 +29114,23 @@
     <mergeCell ref="Z8:Z9"/>
     <mergeCell ref="AA8:AA9"/>
     <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="B4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="A6:I6"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA10:AA569" xr:uid="{A48AEAD6-16A7-419C-9ADE-A3A1D0E68BC1}">
@@ -28793,12 +29153,18 @@
   <legacyDrawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{29FC2697-C7F8-49F5-A92C-C62D205E7736}">
           <x14:formula1>
             <xm:f>Master!$A$2:$A$327</xm:f>
           </x14:formula1>
           <xm:sqref>B10:B569</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E48893AE-C2D3-42E3-99FD-4C9A612FB28C}">
+          <x14:formula1>
+            <xm:f>Master!$D$2:$D$112</xm:f>
+          </x14:formula1>
+          <xm:sqref>K10:K569</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -28827,11 +29193,11 @@
       </c>
     </row>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
       <c r="E2" s="20" t="s">
         <v>209</v>
       </c>
@@ -28841,11 +29207,11 @@
       <c r="G2" s="21"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="53" t="s">
         <v>201</v>
       </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
       <c r="E3" s="20" t="s">
         <v>209</v>
       </c>
@@ -28860,10 +29226,10 @@
       <c r="B4" s="29">
         <v>1</v>
       </c>
-      <c r="C4" s="51" t="s">
+      <c r="C4" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="52"/>
+      <c r="D4" s="57"/>
       <c r="E4" s="20" t="s">
         <v>204</v>
       </c>
@@ -28876,10 +29242,10 @@
       <c r="B5" s="29">
         <v>2</v>
       </c>
-      <c r="C5" s="53" t="s">
+      <c r="C5" s="51" t="s">
         <v>215</v>
       </c>
-      <c r="D5" s="54"/>
+      <c r="D5" s="52"/>
       <c r="E5" s="20" t="s">
         <v>204</v>
       </c>
@@ -28891,10 +29257,10 @@
       <c r="B6" s="29">
         <v>3</v>
       </c>
-      <c r="C6" s="53" t="s">
+      <c r="C6" s="51" t="s">
         <v>216</v>
       </c>
-      <c r="D6" s="54"/>
+      <c r="D6" s="52"/>
       <c r="E6" s="20" t="s">
         <v>209</v>
       </c>
@@ -28909,10 +29275,10 @@
       <c r="B7" s="29">
         <v>4</v>
       </c>
-      <c r="C7" s="53" t="s">
+      <c r="C7" s="51" t="s">
         <v>217</v>
       </c>
-      <c r="D7" s="54"/>
+      <c r="D7" s="52"/>
       <c r="E7" s="20" t="s">
         <v>209</v>
       </c>
@@ -28927,10 +29293,10 @@
       <c r="B8" s="29">
         <v>5</v>
       </c>
-      <c r="C8" s="53" t="s">
+      <c r="C8" s="51" t="s">
         <v>218</v>
       </c>
-      <c r="D8" s="54"/>
+      <c r="D8" s="52"/>
       <c r="E8" s="20" t="s">
         <v>206</v>
       </c>
@@ -28945,10 +29311,10 @@
       <c r="B9" s="29">
         <v>6</v>
       </c>
-      <c r="C9" s="53" t="s">
+      <c r="C9" s="51" t="s">
         <v>219</v>
       </c>
-      <c r="D9" s="54"/>
+      <c r="D9" s="52"/>
       <c r="E9" s="20" t="s">
         <v>204</v>
       </c>
@@ -28963,10 +29329,10 @@
       <c r="B10" s="29">
         <v>7</v>
       </c>
-      <c r="C10" s="53" t="s">
+      <c r="C10" s="51" t="s">
         <v>220</v>
       </c>
-      <c r="D10" s="54"/>
+      <c r="D10" s="52"/>
       <c r="E10" s="20" t="s">
         <v>209</v>
       </c>
@@ -28981,10 +29347,10 @@
       <c r="B11" s="29">
         <v>8</v>
       </c>
-      <c r="C11" s="53" t="s">
+      <c r="C11" s="51" t="s">
         <v>222</v>
       </c>
-      <c r="D11" s="54"/>
+      <c r="D11" s="52"/>
       <c r="E11" s="20" t="s">
         <v>209</v>
       </c>
@@ -28999,10 +29365,10 @@
       <c r="B12" s="29">
         <v>9</v>
       </c>
-      <c r="C12" s="53" t="s">
+      <c r="C12" s="51" t="s">
         <v>223</v>
       </c>
-      <c r="D12" s="54"/>
+      <c r="D12" s="52"/>
       <c r="E12" s="20" t="s">
         <v>209</v>
       </c>
@@ -29015,10 +29381,10 @@
       <c r="B13" s="29">
         <v>10</v>
       </c>
-      <c r="C13" s="53" t="s">
+      <c r="C13" s="51" t="s">
         <v>221</v>
       </c>
-      <c r="D13" s="54"/>
+      <c r="D13" s="52"/>
       <c r="E13" s="20" t="s">
         <v>204</v>
       </c>
@@ -29031,10 +29397,10 @@
       <c r="B14" s="29">
         <v>11</v>
       </c>
-      <c r="C14" s="53" t="s">
+      <c r="C14" s="51" t="s">
         <v>224</v>
       </c>
-      <c r="D14" s="54"/>
+      <c r="D14" s="52"/>
       <c r="E14" s="20" t="s">
         <v>204</v>
       </c>
@@ -29047,10 +29413,10 @@
       <c r="B15" s="29">
         <v>12</v>
       </c>
-      <c r="C15" s="53" t="s">
+      <c r="C15" s="51" t="s">
         <v>225</v>
       </c>
-      <c r="D15" s="54"/>
+      <c r="D15" s="52"/>
       <c r="E15" s="20" t="s">
         <v>209</v>
       </c>
@@ -29062,11 +29428,11 @@
       </c>
     </row>
     <row r="16" spans="2:7" ht="72" x14ac:dyDescent="0.25">
-      <c r="B16" s="56">
+      <c r="B16" s="54">
         <f>B15+1</f>
         <v>13</v>
       </c>
-      <c r="C16" s="50" t="s">
+      <c r="C16" s="55" t="s">
         <v>231</v>
       </c>
       <c r="D16" s="30" t="s">
@@ -29083,8 +29449,8 @@
       </c>
     </row>
     <row r="17" spans="2:7" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="56"/>
-      <c r="C17" s="50"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="55"/>
       <c r="D17" s="30" t="s">
         <v>227</v>
       </c>
@@ -29099,8 +29465,8 @@
       </c>
     </row>
     <row r="18" spans="2:7" ht="72" x14ac:dyDescent="0.25">
-      <c r="B18" s="56"/>
-      <c r="C18" s="50"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="55"/>
       <c r="D18" s="30" t="s">
         <v>228</v>
       </c>
@@ -29115,8 +29481,8 @@
       </c>
     </row>
     <row r="19" spans="2:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="B19" s="56"/>
-      <c r="C19" s="50"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="55"/>
       <c r="D19" s="30" t="s">
         <v>229</v>
       </c>
@@ -29131,8 +29497,8 @@
       </c>
     </row>
     <row r="20" spans="2:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="B20" s="56"/>
-      <c r="C20" s="50"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="55"/>
       <c r="D20" s="30" t="s">
         <v>230</v>
       </c>
@@ -29147,8 +29513,8 @@
       </c>
     </row>
     <row r="21" spans="2:7" ht="48" x14ac:dyDescent="0.25">
-      <c r="B21" s="56"/>
-      <c r="C21" s="50"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="55"/>
       <c r="D21" s="30" t="s">
         <v>234</v>
       </c>
@@ -29166,10 +29532,10 @@
       <c r="B22" s="31">
         <v>14</v>
       </c>
-      <c r="C22" s="53" t="s">
+      <c r="C22" s="51" t="s">
         <v>235</v>
       </c>
-      <c r="D22" s="54"/>
+      <c r="D22" s="52"/>
       <c r="E22" s="20" t="s">
         <v>206</v>
       </c>
@@ -29185,10 +29551,10 @@
         <f t="shared" ref="B23:B35" si="0">B22+1</f>
         <v>15</v>
       </c>
-      <c r="C23" s="53" t="s">
+      <c r="C23" s="51" t="s">
         <v>236</v>
       </c>
-      <c r="D23" s="54"/>
+      <c r="D23" s="52"/>
       <c r="E23" s="20" t="s">
         <v>206</v>
       </c>
@@ -29204,10 +29570,10 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C24" s="53" t="s">
+      <c r="C24" s="51" t="s">
         <v>232</v>
       </c>
-      <c r="D24" s="54"/>
+      <c r="D24" s="52"/>
       <c r="E24" s="20" t="s">
         <v>206</v>
       </c>
@@ -29223,10 +29589,10 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C25" s="53" t="s">
+      <c r="C25" s="51" t="s">
         <v>233</v>
       </c>
-      <c r="D25" s="54"/>
+      <c r="D25" s="52"/>
       <c r="E25" s="20" t="s">
         <v>206</v>
       </c>
@@ -29242,10 +29608,10 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C26" s="53" t="s">
+      <c r="C26" s="51" t="s">
         <v>237</v>
       </c>
-      <c r="D26" s="54"/>
+      <c r="D26" s="52"/>
       <c r="E26" s="20" t="s">
         <v>211</v>
       </c>
@@ -29261,10 +29627,10 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C27" s="53" t="s">
+      <c r="C27" s="51" t="s">
         <v>238</v>
       </c>
-      <c r="D27" s="54"/>
+      <c r="D27" s="52"/>
       <c r="E27" s="20" t="s">
         <v>209</v>
       </c>
@@ -29280,10 +29646,10 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C28" s="53" t="s">
+      <c r="C28" s="51" t="s">
         <v>239</v>
       </c>
-      <c r="D28" s="54"/>
+      <c r="D28" s="52"/>
       <c r="E28" s="20" t="s">
         <v>209</v>
       </c>
@@ -29299,10 +29665,10 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C29" s="53" t="s">
+      <c r="C29" s="51" t="s">
         <v>240</v>
       </c>
-      <c r="D29" s="54"/>
+      <c r="D29" s="52"/>
       <c r="E29" s="20" t="s">
         <v>209</v>
       </c>
@@ -29318,10 +29684,10 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C30" s="53" t="s">
+      <c r="C30" s="51" t="s">
         <v>241</v>
       </c>
-      <c r="D30" s="54"/>
+      <c r="D30" s="52"/>
       <c r="E30" s="20" t="s">
         <v>204</v>
       </c>
@@ -29337,10 +29703,10 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C31" s="53" t="s">
+      <c r="C31" s="51" t="s">
         <v>242</v>
       </c>
-      <c r="D31" s="54"/>
+      <c r="D31" s="52"/>
       <c r="E31" s="20" t="s">
         <v>204</v>
       </c>
@@ -29356,10 +29722,10 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C32" s="53" t="s">
+      <c r="C32" s="51" t="s">
         <v>243</v>
       </c>
-      <c r="D32" s="54"/>
+      <c r="D32" s="52"/>
       <c r="E32" s="20" t="s">
         <v>204</v>
       </c>
@@ -29373,10 +29739,10 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C33" s="53" t="s">
+      <c r="C33" s="51" t="s">
         <v>244</v>
       </c>
-      <c r="D33" s="54"/>
+      <c r="D33" s="52"/>
       <c r="E33" s="20" t="s">
         <v>204</v>
       </c>
@@ -29392,10 +29758,10 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C34" s="50" t="s">
+      <c r="C34" s="55" t="s">
         <v>245</v>
       </c>
-      <c r="D34" s="50"/>
+      <c r="D34" s="55"/>
       <c r="E34" s="20" t="s">
         <v>206</v>
       </c>
@@ -29411,10 +29777,10 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C35" s="50" t="s">
+      <c r="C35" s="55" t="s">
         <v>246</v>
       </c>
-      <c r="D35" s="50"/>
+      <c r="D35" s="55"/>
       <c r="E35" s="20" t="s">
         <v>206</v>
       </c>
@@ -29428,20 +29794,6 @@
   </sheetData>
   <autoFilter ref="B1:H35" xr:uid="{9A62EE61-DA4A-4471-B605-47242F0A4DEA}"/>
   <mergeCells count="30">
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="B16:B21"/>
-    <mergeCell ref="C16:C21"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="C4:D4"/>
@@ -29458,6 +29810,20 @@
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B16:B21"/>
+    <mergeCell ref="C16:C21"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -29466,912 +29832,1248 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EDAC048-C2F1-4ABA-B2C8-6CB3150A85B7}">
-  <dimension ref="A1:B327"/>
+  <dimension ref="A1:D327"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" style="58" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" style="34" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.5703125" style="17" bestFit="1" customWidth="1"/>
     <col min="3" max="16384" width="8.7109375" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="58" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="34" t="s">
         <v>202</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="58">
+      <c r="D1" s="17" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="34">
         <v>1110</v>
       </c>
       <c r="B2" s="17" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="58">
+      <c r="D2" s="59" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="34">
         <v>1130</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="58">
+      <c r="D3" s="59" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="34">
         <v>1140</v>
       </c>
       <c r="B4" s="17" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="58">
+      <c r="D4" s="59" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="34">
         <v>1210</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="58">
+      <c r="D5" s="59" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="34">
         <v>1211</v>
       </c>
       <c r="B6" s="17" t="s">
         <v>455</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="58">
+      <c r="D6" s="59" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="34">
         <v>1212</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="58">
+      <c r="D7" s="59" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="34">
         <v>1220</v>
       </c>
       <c r="B8" s="17" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="58">
+      <c r="D8" s="60" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="34">
         <v>1221</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="58">
+      <c r="D9" s="60" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="34">
         <v>1310</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="58">
+      <c r="D10" s="59" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="34">
         <v>1410</v>
       </c>
       <c r="B11" s="17" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="58">
+      <c r="D11" s="60" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="34">
         <v>1910</v>
       </c>
       <c r="B12" s="17" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="58">
+      <c r="D12" s="59" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="34">
         <v>2110</v>
       </c>
       <c r="B13" s="17" t="s">
         <v>458</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="58">
+      <c r="D13" s="59" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="34">
         <v>2210</v>
       </c>
       <c r="B14" s="17" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="58">
+      <c r="D14" s="59" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="34">
         <v>2310</v>
       </c>
       <c r="B15" s="17" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="58">
+      <c r="D15" s="59" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="34">
         <v>2311</v>
       </c>
       <c r="B16" s="17" t="s">
         <v>461</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="58">
+      <c r="D16" s="59" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="34">
         <v>2312</v>
       </c>
       <c r="B17" s="17" t="s">
         <v>462</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="58">
+      <c r="D17" s="59" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="34">
         <v>2313</v>
       </c>
       <c r="B18" s="17" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="58">
+      <c r="D18" s="59" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A19" s="34">
         <v>2410</v>
       </c>
       <c r="B19" s="17" t="s">
         <v>464</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="58">
+      <c r="D19" s="60" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A20" s="34">
         <v>2421</v>
       </c>
       <c r="B20" s="17" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" s="58">
+      <c r="D20" s="60" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A21" s="34">
         <v>2490</v>
       </c>
       <c r="B21" s="17" t="s">
         <v>466</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="58">
+      <c r="D21" s="60" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="34">
         <v>2510</v>
       </c>
       <c r="B22" s="17" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="58">
+      <c r="D22" s="59" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A23" s="34">
         <v>2610</v>
       </c>
       <c r="B23" s="17" t="s">
         <v>468</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" s="58">
+      <c r="D23" s="60" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="34">
         <v>2710</v>
       </c>
       <c r="B24" s="17" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="58">
+      <c r="D24" s="59" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A25" s="34">
         <v>3110</v>
       </c>
       <c r="B25" s="17" t="s">
         <v>469</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" s="58">
+      <c r="D25" s="60" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A26" s="34">
         <v>3111</v>
       </c>
       <c r="B26" s="17" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="58">
+      <c r="D26" s="60" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="34">
         <v>3210</v>
       </c>
       <c r="B27" s="17" t="s">
         <v>470</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" s="58">
+      <c r="D27" s="59" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="34">
         <v>3211</v>
       </c>
       <c r="B28" s="17" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" s="58">
+      <c r="D28" s="59" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A29" s="34">
         <v>3212</v>
       </c>
       <c r="B29" s="17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" s="58">
+      <c r="D29" s="60" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A30" s="34">
         <v>3310</v>
       </c>
       <c r="B30" s="17" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" s="58">
+      <c r="D30" s="60" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="34">
         <v>3320</v>
       </c>
       <c r="B31" s="17" t="s">
         <v>472</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" s="58">
+      <c r="D31" s="59" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="34">
         <v>3321</v>
       </c>
       <c r="B32" s="17" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" s="58">
+      <c r="D32" s="59" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="34">
         <v>3410</v>
       </c>
       <c r="B33" s="17" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" s="58">
+      <c r="D33" s="59" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="34">
         <v>3510</v>
       </c>
       <c r="B34" s="17" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" s="58">
+      <c r="D34" s="59" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="34">
         <v>4110</v>
       </c>
       <c r="B35" s="17" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" s="58">
+      <c r="D35" s="59" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="34">
         <v>4111</v>
       </c>
       <c r="B36" s="17" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" s="58">
+      <c r="D36" s="59" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="34">
         <v>4140</v>
       </c>
       <c r="B37" s="17" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" s="58">
+      <c r="D37" s="59" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A38" s="34">
         <v>4210</v>
       </c>
       <c r="B38" s="17" t="s">
         <v>476</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" s="58">
+      <c r="D38" s="60" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="34">
         <v>4211</v>
       </c>
       <c r="B39" s="17" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" s="58">
+      <c r="D39" s="59" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="34">
         <v>4230</v>
       </c>
       <c r="B40" s="17" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" s="58">
+      <c r="D40" s="59" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="34">
         <v>4240</v>
       </c>
       <c r="B41" s="17" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" s="58">
+      <c r="D41" s="59" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="34">
         <v>5110</v>
       </c>
       <c r="B42" s="17" t="s">
         <v>478</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43" s="58">
+      <c r="D42" s="59" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="34">
         <v>5120</v>
       </c>
       <c r="B43" s="17" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44" s="58">
+      <c r="D43" s="59" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="34">
         <v>5130</v>
       </c>
       <c r="B44" s="17" t="s">
         <v>480</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45" s="58">
+      <c r="D44" s="59" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="34">
         <v>5140</v>
       </c>
       <c r="B45" s="17" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" s="58">
+      <c r="D45" s="59" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="34">
         <v>5150</v>
       </c>
       <c r="B46" s="17" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A47" s="58">
+      <c r="D46" s="59" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A47" s="34">
         <v>5160</v>
       </c>
       <c r="B47" s="17" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A48" s="58">
+      <c r="D47" s="59" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="34">
         <v>5170</v>
       </c>
       <c r="B48" s="17" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49" s="58">
+      <c r="D48" s="59" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A49" s="34">
         <v>5180</v>
       </c>
       <c r="B49" s="17" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50" s="58">
+      <c r="D49" s="59" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A50" s="34">
         <v>5210</v>
       </c>
       <c r="B50" s="17" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A51" s="58">
+      <c r="D50" s="59" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A51" s="34">
         <v>5220</v>
       </c>
       <c r="B51" s="17" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A52" s="58">
+      <c r="D51" s="59" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="34">
         <v>6110</v>
       </c>
       <c r="B52" s="17" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A53" s="58">
+      <c r="D52" s="59" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="34">
         <v>7110</v>
       </c>
       <c r="B53" s="17" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A54" s="58">
+      <c r="D53" s="59" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A54" s="34">
         <v>7111</v>
       </c>
       <c r="B54" s="17" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A55" s="58">
+      <c r="D54" s="60" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A55" s="34">
         <v>7112</v>
       </c>
       <c r="B55" s="17" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A56" s="58">
+      <c r="D55" s="60" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A56" s="34">
         <v>7120</v>
       </c>
       <c r="B56" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A57" s="58">
+      <c r="D56" s="60" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A57" s="34">
         <v>8110</v>
       </c>
       <c r="B57" s="17" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A58" s="58" t="s">
+      <c r="D57" s="59" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A58" s="34" t="s">
         <v>270</v>
       </c>
       <c r="B58" s="17" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A59" s="58" t="s">
+      <c r="D58" s="59" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A59" s="34" t="s">
         <v>271</v>
       </c>
       <c r="B59" s="17" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A60" s="58" t="s">
+      <c r="D59" s="60" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A60" s="34" t="s">
         <v>272</v>
       </c>
       <c r="B60" s="17" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A61" s="58" t="s">
+      <c r="D60" s="59" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A61" s="34" t="s">
         <v>273</v>
       </c>
       <c r="B61" s="17" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A62" s="58" t="s">
+      <c r="D61" s="59" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A62" s="34" t="s">
         <v>274</v>
       </c>
       <c r="B62" s="17" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A63" s="58" t="s">
+      <c r="D62" s="59" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A63" s="34" t="s">
         <v>275</v>
       </c>
       <c r="B63" s="17" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A64" s="58" t="s">
+      <c r="D63" s="59" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A64" s="34" t="s">
         <v>30</v>
       </c>
       <c r="B64" s="17" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A65" s="58" t="s">
+      <c r="D64" s="59" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A65" s="34" t="s">
         <v>32</v>
       </c>
       <c r="B65" s="17" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A66" s="58" t="s">
+      <c r="D65" s="59" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A66" s="34" t="s">
         <v>33</v>
       </c>
       <c r="B66" s="17" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A67" s="58" t="s">
+      <c r="D66" s="59" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A67" s="34" t="s">
         <v>276</v>
       </c>
       <c r="B67" s="17" t="s">
         <v>495</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A68" s="58" t="s">
+      <c r="D67" s="60" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A68" s="34" t="s">
         <v>277</v>
       </c>
       <c r="B68" s="17" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A69" s="58" t="s">
+      <c r="D68" s="60" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A69" s="34" t="s">
         <v>278</v>
       </c>
       <c r="B69" s="17" t="s">
         <v>497</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A70" s="58" t="s">
+      <c r="D69" s="59" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A70" s="34" t="s">
         <v>35</v>
       </c>
       <c r="B70" s="17" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A71" s="58" t="s">
+      <c r="D70" s="60" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A71" s="34" t="s">
         <v>36</v>
       </c>
       <c r="B71" s="17" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A72" s="58" t="s">
+      <c r="D71" s="59" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A72" s="34" t="s">
         <v>279</v>
       </c>
       <c r="B72" s="17" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A73" s="58" t="s">
+      <c r="D72" s="59" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A73" s="34" t="s">
         <v>38</v>
       </c>
       <c r="B73" s="17" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A74" s="58" t="s">
+      <c r="D73" s="59" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A74" s="34" t="s">
         <v>40</v>
       </c>
       <c r="B74" s="17" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A75" s="58" t="s">
+      <c r="D74" s="59" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A75" s="34" t="s">
         <v>42</v>
       </c>
       <c r="B75" s="17" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A76" s="58" t="s">
+      <c r="D75" s="59" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A76" s="34" t="s">
         <v>44</v>
       </c>
       <c r="B76" s="17" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A77" s="58" t="s">
+      <c r="D76" s="59" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A77" s="34" t="s">
         <v>46</v>
       </c>
       <c r="B77" s="17" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A78" s="58" t="s">
+      <c r="D77" s="59" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A78" s="34" t="s">
         <v>48</v>
       </c>
       <c r="B78" s="17" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A79" s="58" t="s">
+      <c r="D78" s="59" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A79" s="34" t="s">
         <v>50</v>
       </c>
       <c r="B79" s="17" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A80" s="58" t="s">
+      <c r="D79" s="59" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A80" s="34" t="s">
         <v>51</v>
       </c>
       <c r="B80" s="17" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A81" s="58" t="s">
+      <c r="D80" s="59" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A81" s="34" t="s">
         <v>280</v>
       </c>
       <c r="B81" s="17" t="s">
         <v>502</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A82" s="58" t="s">
+      <c r="D81" s="59" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A82" s="34" t="s">
         <v>53</v>
       </c>
       <c r="B82" s="17" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A83" s="58" t="s">
+      <c r="D82" s="60" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A83" s="34" t="s">
         <v>55</v>
       </c>
       <c r="B83" s="17" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A84" s="58" t="s">
+      <c r="D83" s="59" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A84" s="34" t="s">
         <v>281</v>
       </c>
       <c r="B84" s="17" t="s">
         <v>503</v>
       </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A85" s="58" t="s">
+      <c r="D84" s="59" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A85" s="34" t="s">
         <v>56</v>
       </c>
       <c r="B85" s="17" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A86" s="58" t="s">
+      <c r="D85" s="59" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A86" s="34" t="s">
         <v>282</v>
       </c>
       <c r="B86" s="17" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A87" s="58" t="s">
+      <c r="D86" s="60" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A87" s="34" t="s">
         <v>59</v>
       </c>
       <c r="B87" s="17" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A88" s="58" t="s">
+      <c r="D87" s="59" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A88" s="34" t="s">
         <v>283</v>
       </c>
       <c r="B88" s="17" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A89" s="58" t="s">
+      <c r="D88" s="59" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A89" s="34" t="s">
         <v>284</v>
       </c>
       <c r="B89" s="17" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A90" s="58" t="s">
+      <c r="D89" s="59" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A90" s="34" t="s">
         <v>285</v>
       </c>
       <c r="B90" s="17" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A91" s="58" t="s">
+      <c r="D90" s="59" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A91" s="34" t="s">
         <v>61</v>
       </c>
       <c r="B91" s="17" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A92" s="58" t="s">
+      <c r="D91" s="59" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A92" s="34" t="s">
         <v>63</v>
       </c>
       <c r="B92" s="17" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A93" s="58" t="s">
+      <c r="D92" s="59" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A93" s="34" t="s">
         <v>65</v>
       </c>
       <c r="B93" s="17" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A94" s="58" t="s">
+      <c r="D93" s="59" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A94" s="34" t="s">
         <v>67</v>
       </c>
       <c r="B94" s="17" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A95" s="58" t="s">
+      <c r="D94" s="59" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A95" s="34" t="s">
         <v>69</v>
       </c>
       <c r="B95" s="17" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A96" s="58" t="s">
+      <c r="D95" s="59" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A96" s="34" t="s">
         <v>71</v>
       </c>
       <c r="B96" s="17" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A97" s="58" t="s">
+      <c r="D96" s="60" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A97" s="34" t="s">
         <v>72</v>
       </c>
       <c r="B97" s="17" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A98" s="58" t="s">
+      <c r="D97" s="59" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A98" s="34" t="s">
         <v>286</v>
       </c>
       <c r="B98" s="17" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A99" s="58" t="s">
+      <c r="D98" s="59" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A99" s="34" t="s">
         <v>287</v>
       </c>
       <c r="B99" s="17" t="s">
         <v>510</v>
       </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A100" s="58" t="s">
+      <c r="D99" s="59" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A100" s="34" t="s">
         <v>288</v>
       </c>
       <c r="B100" s="17" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A101" s="58" t="s">
+      <c r="D100" s="59" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A101" s="34" t="s">
         <v>289</v>
       </c>
       <c r="B101" s="17" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A102" s="58" t="s">
+      <c r="D101" s="59" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A102" s="34" t="s">
         <v>290</v>
       </c>
       <c r="B102" s="17" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A103" s="58" t="s">
+      <c r="D102" s="59" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A103" s="34" t="s">
         <v>291</v>
       </c>
       <c r="B103" s="17" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A104" s="58" t="s">
+      <c r="D103" s="59" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A104" s="34" t="s">
         <v>292</v>
       </c>
       <c r="B104" s="17" t="s">
         <v>513</v>
       </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A105" s="58" t="s">
+      <c r="D104" s="59" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A105" s="34" t="s">
         <v>293</v>
       </c>
       <c r="B105" s="17" t="s">
         <v>514</v>
       </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A106" s="58" t="s">
+      <c r="D105" s="60" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A106" s="34" t="s">
         <v>294</v>
       </c>
       <c r="B106" s="17" t="s">
         <v>515</v>
       </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A107" s="58" t="s">
+      <c r="D106" s="60" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A107" s="34" t="s">
         <v>295</v>
       </c>
       <c r="B107" s="17" t="s">
         <v>516</v>
       </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A108" s="58" t="s">
+      <c r="D107" s="59" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A108" s="34" t="s">
         <v>296</v>
       </c>
       <c r="B108" s="17" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A109" s="58" t="s">
+      <c r="D108" s="32" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A109" s="34" t="s">
         <v>297</v>
       </c>
       <c r="B109" s="17" t="s">
         <v>516</v>
       </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A110" s="58" t="s">
+      <c r="D109" s="61" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A110" s="34" t="s">
         <v>298</v>
       </c>
       <c r="B110" s="17" t="s">
         <v>518</v>
       </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A111" s="58" t="s">
+      <c r="D110" s="32" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="A111" s="34" t="s">
         <v>299</v>
       </c>
       <c r="B111" s="17" t="s">
         <v>519</v>
       </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A112" s="58" t="s">
+      <c r="D111" s="32" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A112" s="34" t="s">
         <v>300</v>
       </c>
       <c r="B112" s="17" t="s">
         <v>520</v>
       </c>
+      <c r="D112" s="59" t="s">
+        <v>752</v>
+      </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A113" s="58" t="s">
+      <c r="A113" s="34" t="s">
         <v>301</v>
       </c>
       <c r="B113" s="17" t="s">
@@ -30379,7 +31081,7 @@
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A114" s="58" t="s">
+      <c r="A114" s="34" t="s">
         <v>302</v>
       </c>
       <c r="B114" s="17" t="s">
@@ -30387,7 +31089,7 @@
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A115" s="58" t="s">
+      <c r="A115" s="34" t="s">
         <v>303</v>
       </c>
       <c r="B115" s="17" t="s">
@@ -30395,7 +31097,7 @@
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A116" s="58" t="s">
+      <c r="A116" s="34" t="s">
         <v>304</v>
       </c>
       <c r="B116" s="17" t="s">
@@ -30403,7 +31105,7 @@
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A117" s="58" t="s">
+      <c r="A117" s="34" t="s">
         <v>305</v>
       </c>
       <c r="B117" s="17" t="s">
@@ -30411,7 +31113,7 @@
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A118" s="58" t="s">
+      <c r="A118" s="34" t="s">
         <v>306</v>
       </c>
       <c r="B118" s="17" t="s">
@@ -30419,7 +31121,7 @@
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A119" s="58" t="s">
+      <c r="A119" s="34" t="s">
         <v>307</v>
       </c>
       <c r="B119" s="17" t="s">
@@ -30427,7 +31129,7 @@
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A120" s="58" t="s">
+      <c r="A120" s="34" t="s">
         <v>308</v>
       </c>
       <c r="B120" s="17" t="s">
@@ -30435,7 +31137,7 @@
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A121" s="58" t="s">
+      <c r="A121" s="34" t="s">
         <v>309</v>
       </c>
       <c r="B121" s="17" t="s">
@@ -30443,7 +31145,7 @@
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A122" s="58" t="s">
+      <c r="A122" s="34" t="s">
         <v>310</v>
       </c>
       <c r="B122" s="17" t="s">
@@ -30451,7 +31153,7 @@
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A123" s="58" t="s">
+      <c r="A123" s="34" t="s">
         <v>311</v>
       </c>
       <c r="B123" s="17" t="s">
@@ -30459,7 +31161,7 @@
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A124" s="58" t="s">
+      <c r="A124" s="34" t="s">
         <v>312</v>
       </c>
       <c r="B124" s="17" t="s">
@@ -30467,7 +31169,7 @@
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A125" s="58" t="s">
+      <c r="A125" s="34" t="s">
         <v>313</v>
       </c>
       <c r="B125" s="17" t="s">
@@ -30475,7 +31177,7 @@
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A126" s="58" t="s">
+      <c r="A126" s="34" t="s">
         <v>314</v>
       </c>
       <c r="B126" s="17" t="s">
@@ -30483,7 +31185,7 @@
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A127" s="58" t="s">
+      <c r="A127" s="34" t="s">
         <v>315</v>
       </c>
       <c r="B127" s="17" t="s">
@@ -30491,7 +31193,7 @@
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A128" s="58" t="s">
+      <c r="A128" s="34" t="s">
         <v>316</v>
       </c>
       <c r="B128" s="17" t="s">
@@ -30499,7 +31201,7 @@
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A129" s="58" t="s">
+      <c r="A129" s="34" t="s">
         <v>317</v>
       </c>
       <c r="B129" s="17" t="s">
@@ -30507,7 +31209,7 @@
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A130" s="58" t="s">
+      <c r="A130" s="34" t="s">
         <v>318</v>
       </c>
       <c r="B130" s="17" t="s">
@@ -30515,7 +31217,7 @@
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A131" s="58" t="s">
+      <c r="A131" s="34" t="s">
         <v>319</v>
       </c>
       <c r="B131" s="17" t="s">
@@ -30523,7 +31225,7 @@
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A132" s="58" t="s">
+      <c r="A132" s="34" t="s">
         <v>320</v>
       </c>
       <c r="B132" s="17" t="s">
@@ -30531,7 +31233,7 @@
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A133" s="58" t="s">
+      <c r="A133" s="34" t="s">
         <v>321</v>
       </c>
       <c r="B133" s="17" t="s">
@@ -30539,7 +31241,7 @@
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A134" s="58" t="s">
+      <c r="A134" s="34" t="s">
         <v>322</v>
       </c>
       <c r="B134" s="17" t="s">
@@ -30547,7 +31249,7 @@
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A135" s="58" t="s">
+      <c r="A135" s="34" t="s">
         <v>323</v>
       </c>
       <c r="B135" s="17" t="s">
@@ -30555,7 +31257,7 @@
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A136" s="58" t="s">
+      <c r="A136" s="34" t="s">
         <v>324</v>
       </c>
       <c r="B136" s="17" t="s">
@@ -30563,7 +31265,7 @@
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A137" s="58" t="s">
+      <c r="A137" s="34" t="s">
         <v>325</v>
       </c>
       <c r="B137" s="17" t="s">
@@ -30571,7 +31273,7 @@
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A138" s="58" t="s">
+      <c r="A138" s="34" t="s">
         <v>326</v>
       </c>
       <c r="B138" s="17" t="s">
@@ -30579,7 +31281,7 @@
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A139" s="58" t="s">
+      <c r="A139" s="34" t="s">
         <v>327</v>
       </c>
       <c r="B139" s="17" t="s">
@@ -30587,7 +31289,7 @@
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A140" s="58" t="s">
+      <c r="A140" s="34" t="s">
         <v>328</v>
       </c>
       <c r="B140" s="17" t="s">
@@ -30595,7 +31297,7 @@
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A141" s="58" t="s">
+      <c r="A141" s="34" t="s">
         <v>329</v>
       </c>
       <c r="B141" s="17" t="s">
@@ -30603,7 +31305,7 @@
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A142" s="58" t="s">
+      <c r="A142" s="34" t="s">
         <v>330</v>
       </c>
       <c r="B142" s="17" t="s">
@@ -30611,7 +31313,7 @@
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A143" s="58" t="s">
+      <c r="A143" s="34" t="s">
         <v>331</v>
       </c>
       <c r="B143" s="17" t="s">
@@ -30619,7 +31321,7 @@
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A144" s="58" t="s">
+      <c r="A144" s="34" t="s">
         <v>332</v>
       </c>
       <c r="B144" s="17" t="s">
@@ -30627,7 +31329,7 @@
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A145" s="58" t="s">
+      <c r="A145" s="34" t="s">
         <v>333</v>
       </c>
       <c r="B145" s="17" t="s">
@@ -30635,7 +31337,7 @@
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A146" s="58" t="s">
+      <c r="A146" s="34" t="s">
         <v>334</v>
       </c>
       <c r="B146" s="17" t="s">
@@ -30643,7 +31345,7 @@
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A147" s="58" t="s">
+      <c r="A147" s="34" t="s">
         <v>335</v>
       </c>
       <c r="B147" s="17" t="s">
@@ -30651,7 +31353,7 @@
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A148" s="58" t="s">
+      <c r="A148" s="34" t="s">
         <v>336</v>
       </c>
       <c r="B148" s="17" t="s">
@@ -30659,7 +31361,7 @@
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A149" s="58" t="s">
+      <c r="A149" s="34" t="s">
         <v>337</v>
       </c>
       <c r="B149" s="17" t="s">
@@ -30667,7 +31369,7 @@
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A150" s="58" t="s">
+      <c r="A150" s="34" t="s">
         <v>338</v>
       </c>
       <c r="B150" s="17" t="s">
@@ -30675,7 +31377,7 @@
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A151" s="58" t="s">
+      <c r="A151" s="34" t="s">
         <v>339</v>
       </c>
       <c r="B151" s="17" t="s">
@@ -30683,7 +31385,7 @@
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A152" s="58" t="s">
+      <c r="A152" s="34" t="s">
         <v>340</v>
       </c>
       <c r="B152" s="17" t="s">
@@ -30691,7 +31393,7 @@
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A153" s="58" t="s">
+      <c r="A153" s="34" t="s">
         <v>341</v>
       </c>
       <c r="B153" s="17" t="s">
@@ -30699,7 +31401,7 @@
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A154" s="58" t="s">
+      <c r="A154" s="34" t="s">
         <v>342</v>
       </c>
       <c r="B154" s="17" t="s">
@@ -30707,7 +31409,7 @@
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A155" s="58" t="s">
+      <c r="A155" s="34" t="s">
         <v>343</v>
       </c>
       <c r="B155" s="17" t="s">
@@ -30715,7 +31417,7 @@
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A156" s="58" t="s">
+      <c r="A156" s="34" t="s">
         <v>344</v>
       </c>
       <c r="B156" s="17" t="s">
@@ -30723,7 +31425,7 @@
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A157" s="58" t="s">
+      <c r="A157" s="34" t="s">
         <v>345</v>
       </c>
       <c r="B157" s="17" t="s">
@@ -30731,7 +31433,7 @@
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A158" s="58" t="s">
+      <c r="A158" s="34" t="s">
         <v>346</v>
       </c>
       <c r="B158" s="17">
@@ -30739,7 +31441,7 @@
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A159" s="58" t="s">
+      <c r="A159" s="34" t="s">
         <v>347</v>
       </c>
       <c r="B159" s="17" t="s">
@@ -30747,7 +31449,7 @@
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A160" s="58" t="s">
+      <c r="A160" s="34" t="s">
         <v>348</v>
       </c>
       <c r="B160" s="17" t="s">
@@ -30755,7 +31457,7 @@
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A161" s="58" t="s">
+      <c r="A161" s="34" t="s">
         <v>349</v>
       </c>
       <c r="B161" s="17">
@@ -30763,7 +31465,7 @@
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A162" s="58" t="s">
+      <c r="A162" s="34" t="s">
         <v>350</v>
       </c>
       <c r="B162" s="17" t="s">
@@ -30771,7 +31473,7 @@
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A163" s="58" t="s">
+      <c r="A163" s="34" t="s">
         <v>351</v>
       </c>
       <c r="B163" s="17" t="s">
@@ -30779,7 +31481,7 @@
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A164" s="58" t="s">
+      <c r="A164" s="34" t="s">
         <v>352</v>
       </c>
       <c r="B164" s="17" t="s">
@@ -30787,7 +31489,7 @@
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A165" s="58" t="s">
+      <c r="A165" s="34" t="s">
         <v>353</v>
       </c>
       <c r="B165" s="17" t="s">
@@ -30795,7 +31497,7 @@
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A166" s="58" t="s">
+      <c r="A166" s="34" t="s">
         <v>354</v>
       </c>
       <c r="B166" s="17" t="s">
@@ -30803,7 +31505,7 @@
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A167" s="58" t="s">
+      <c r="A167" s="34" t="s">
         <v>355</v>
       </c>
       <c r="B167" s="17" t="s">
@@ -30811,7 +31513,7 @@
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A168" s="58" t="s">
+      <c r="A168" s="34" t="s">
         <v>356</v>
       </c>
       <c r="B168" s="17" t="s">
@@ -30819,7 +31521,7 @@
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A169" s="58" t="s">
+      <c r="A169" s="34" t="s">
         <v>357</v>
       </c>
       <c r="B169" s="17" t="s">
@@ -30827,7 +31529,7 @@
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A170" s="58" t="s">
+      <c r="A170" s="34" t="s">
         <v>358</v>
       </c>
       <c r="B170" s="17" t="s">
@@ -30835,7 +31537,7 @@
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A171" s="58" t="s">
+      <c r="A171" s="34" t="s">
         <v>359</v>
       </c>
       <c r="B171" s="17" t="s">
@@ -30843,7 +31545,7 @@
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A172" s="58" t="s">
+      <c r="A172" s="34" t="s">
         <v>360</v>
       </c>
       <c r="B172" s="17" t="s">
@@ -30851,7 +31553,7 @@
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A173" s="58" t="s">
+      <c r="A173" s="34" t="s">
         <v>361</v>
       </c>
       <c r="B173" s="17" t="s">
@@ -30859,7 +31561,7 @@
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A174" s="58" t="s">
+      <c r="A174" s="34" t="s">
         <v>362</v>
       </c>
       <c r="B174" s="17" t="s">
@@ -30867,7 +31569,7 @@
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A175" s="58" t="s">
+      <c r="A175" s="34" t="s">
         <v>363</v>
       </c>
       <c r="B175" s="17" t="s">
@@ -30875,7 +31577,7 @@
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A176" s="58" t="s">
+      <c r="A176" s="34" t="s">
         <v>364</v>
       </c>
       <c r="B176" s="17" t="s">
@@ -30883,7 +31585,7 @@
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A177" s="58" t="s">
+      <c r="A177" s="34" t="s">
         <v>365</v>
       </c>
       <c r="B177" s="17" t="s">
@@ -30891,7 +31593,7 @@
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A178" s="58" t="s">
+      <c r="A178" s="34" t="s">
         <v>366</v>
       </c>
       <c r="B178" s="17" t="s">
@@ -30899,7 +31601,7 @@
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A179" s="58" t="s">
+      <c r="A179" s="34" t="s">
         <v>367</v>
       </c>
       <c r="B179" s="17" t="s">
@@ -30907,7 +31609,7 @@
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A180" s="58" t="s">
+      <c r="A180" s="34" t="s">
         <v>368</v>
       </c>
       <c r="B180" s="17" t="s">
@@ -30915,7 +31617,7 @@
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A181" s="58" t="s">
+      <c r="A181" s="34" t="s">
         <v>369</v>
       </c>
       <c r="B181" s="17" t="s">
@@ -30923,7 +31625,7 @@
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A182" s="58" t="s">
+      <c r="A182" s="34" t="s">
         <v>370</v>
       </c>
       <c r="B182" s="17" t="s">
@@ -30931,7 +31633,7 @@
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A183" s="58" t="s">
+      <c r="A183" s="34" t="s">
         <v>371</v>
       </c>
       <c r="B183" s="17" t="s">
@@ -30939,7 +31641,7 @@
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A184" s="58" t="s">
+      <c r="A184" s="34" t="s">
         <v>372</v>
       </c>
       <c r="B184" s="17" t="s">
@@ -30947,7 +31649,7 @@
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A185" s="58" t="s">
+      <c r="A185" s="34" t="s">
         <v>373</v>
       </c>
       <c r="B185" s="17" t="s">
@@ -30955,7 +31657,7 @@
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A186" s="58" t="s">
+      <c r="A186" s="34" t="s">
         <v>374</v>
       </c>
       <c r="B186" s="17" t="s">
@@ -30963,7 +31665,7 @@
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A187" s="58" t="s">
+      <c r="A187" s="34" t="s">
         <v>375</v>
       </c>
       <c r="B187" s="17" t="s">
@@ -30971,7 +31673,7 @@
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A188" s="58" t="s">
+      <c r="A188" s="34" t="s">
         <v>376</v>
       </c>
       <c r="B188" s="17" t="s">
@@ -30979,7 +31681,7 @@
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A189" s="58" t="s">
+      <c r="A189" s="34" t="s">
         <v>377</v>
       </c>
       <c r="B189" s="17" t="s">
@@ -30987,7 +31689,7 @@
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A190" s="58" t="s">
+      <c r="A190" s="34" t="s">
         <v>378</v>
       </c>
       <c r="B190" s="17" t="s">
@@ -30995,7 +31697,7 @@
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A191" s="58" t="s">
+      <c r="A191" s="34" t="s">
         <v>379</v>
       </c>
       <c r="B191" s="17" t="s">
@@ -31003,7 +31705,7 @@
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A192" s="58" t="s">
+      <c r="A192" s="34" t="s">
         <v>380</v>
       </c>
       <c r="B192" s="17" t="s">
@@ -31011,7 +31713,7 @@
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A193" s="58" t="s">
+      <c r="A193" s="34" t="s">
         <v>381</v>
       </c>
       <c r="B193" s="17" t="s">
@@ -31019,7 +31721,7 @@
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A194" s="58" t="s">
+      <c r="A194" s="34" t="s">
         <v>382</v>
       </c>
       <c r="B194" s="17" t="s">
@@ -31027,7 +31729,7 @@
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A195" s="58" t="s">
+      <c r="A195" s="34" t="s">
         <v>383</v>
       </c>
       <c r="B195" s="17" t="s">
@@ -31035,7 +31737,7 @@
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A196" s="58" t="s">
+      <c r="A196" s="34" t="s">
         <v>384</v>
       </c>
       <c r="B196" s="17" t="s">
@@ -31043,7 +31745,7 @@
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A197" s="58" t="s">
+      <c r="A197" s="34" t="s">
         <v>385</v>
       </c>
       <c r="B197" s="17" t="s">
@@ -31051,7 +31753,7 @@
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A198" s="58" t="s">
+      <c r="A198" s="34" t="s">
         <v>386</v>
       </c>
       <c r="B198" s="17" t="s">
@@ -31059,7 +31761,7 @@
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A199" s="58" t="s">
+      <c r="A199" s="34" t="s">
         <v>387</v>
       </c>
       <c r="B199" s="17" t="s">
@@ -31067,7 +31769,7 @@
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A200" s="58" t="s">
+      <c r="A200" s="34" t="s">
         <v>388</v>
       </c>
       <c r="B200" s="17" t="s">
@@ -31075,7 +31777,7 @@
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A201" s="58" t="s">
+      <c r="A201" s="34" t="s">
         <v>389</v>
       </c>
       <c r="B201" s="17" t="s">
@@ -31083,7 +31785,7 @@
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A202" s="58" t="s">
+      <c r="A202" s="34" t="s">
         <v>390</v>
       </c>
       <c r="B202" s="17" t="s">
@@ -31091,7 +31793,7 @@
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A203" s="58" t="s">
+      <c r="A203" s="34" t="s">
         <v>391</v>
       </c>
       <c r="B203" s="17" t="s">
@@ -31099,7 +31801,7 @@
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A204" s="58" t="s">
+      <c r="A204" s="34" t="s">
         <v>392</v>
       </c>
       <c r="B204" s="17" t="s">
@@ -31107,7 +31809,7 @@
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A205" s="58" t="s">
+      <c r="A205" s="34" t="s">
         <v>393</v>
       </c>
       <c r="B205" s="17" t="s">
@@ -31115,7 +31817,7 @@
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A206" s="58" t="s">
+      <c r="A206" s="34" t="s">
         <v>394</v>
       </c>
       <c r="B206" s="17" t="s">
@@ -31123,7 +31825,7 @@
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A207" s="58" t="s">
+      <c r="A207" s="34" t="s">
         <v>395</v>
       </c>
       <c r="B207" s="17" t="s">
@@ -31131,7 +31833,7 @@
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A208" s="58" t="s">
+      <c r="A208" s="34" t="s">
         <v>396</v>
       </c>
       <c r="B208" s="17" t="s">
@@ -31139,7 +31841,7 @@
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A209" s="58" t="s">
+      <c r="A209" s="34" t="s">
         <v>397</v>
       </c>
       <c r="B209" s="17" t="s">
@@ -31147,7 +31849,7 @@
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A210" s="58" t="s">
+      <c r="A210" s="34" t="s">
         <v>398</v>
       </c>
       <c r="B210" s="17" t="s">
@@ -31155,7 +31857,7 @@
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A211" s="58" t="s">
+      <c r="A211" s="34" t="s">
         <v>399</v>
       </c>
       <c r="B211" s="17" t="s">
@@ -31163,7 +31865,7 @@
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A212" s="58" t="s">
+      <c r="A212" s="34" t="s">
         <v>400</v>
       </c>
       <c r="B212" s="17" t="s">
@@ -31171,7 +31873,7 @@
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A213" s="58" t="s">
+      <c r="A213" s="34" t="s">
         <v>401</v>
       </c>
       <c r="B213" s="17" t="s">
@@ -31179,7 +31881,7 @@
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A214" s="58" t="s">
+      <c r="A214" s="34" t="s">
         <v>402</v>
       </c>
       <c r="B214" s="17" t="s">
@@ -31187,7 +31889,7 @@
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A215" s="58" t="s">
+      <c r="A215" s="34" t="s">
         <v>403</v>
       </c>
       <c r="B215" s="17" t="s">
@@ -31195,7 +31897,7 @@
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A216" s="58" t="s">
+      <c r="A216" s="34" t="s">
         <v>404</v>
       </c>
       <c r="B216" s="17" t="s">
@@ -31203,7 +31905,7 @@
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A217" s="58" t="s">
+      <c r="A217" s="34" t="s">
         <v>405</v>
       </c>
       <c r="B217" s="17" t="s">
@@ -31211,7 +31913,7 @@
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A218" s="58" t="s">
+      <c r="A218" s="34" t="s">
         <v>406</v>
       </c>
       <c r="B218" s="17" t="s">
@@ -31219,7 +31921,7 @@
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A219" s="58" t="s">
+      <c r="A219" s="34" t="s">
         <v>407</v>
       </c>
       <c r="B219" s="17" t="s">
@@ -31227,7 +31929,7 @@
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A220" s="58" t="s">
+      <c r="A220" s="34" t="s">
         <v>408</v>
       </c>
       <c r="B220" s="17" t="s">
@@ -31235,7 +31937,7 @@
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A221" s="58" t="s">
+      <c r="A221" s="34" t="s">
         <v>409</v>
       </c>
       <c r="B221" s="17" t="s">
@@ -31243,7 +31945,7 @@
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A222" s="58" t="s">
+      <c r="A222" s="34" t="s">
         <v>410</v>
       </c>
       <c r="B222" s="17" t="s">
@@ -31251,7 +31953,7 @@
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A223" s="58" t="s">
+      <c r="A223" s="34" t="s">
         <v>411</v>
       </c>
       <c r="B223" s="17" t="s">
@@ -31259,7 +31961,7 @@
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A224" s="58" t="s">
+      <c r="A224" s="34" t="s">
         <v>412</v>
       </c>
       <c r="B224" s="17" t="s">
@@ -31267,7 +31969,7 @@
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A225" s="58" t="s">
+      <c r="A225" s="34" t="s">
         <v>413</v>
       </c>
       <c r="B225" s="17" t="s">
@@ -31275,7 +31977,7 @@
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A226" s="58" t="s">
+      <c r="A226" s="34" t="s">
         <v>414</v>
       </c>
       <c r="B226" s="17" t="s">
@@ -31283,7 +31985,7 @@
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A227" s="58" t="s">
+      <c r="A227" s="34" t="s">
         <v>415</v>
       </c>
       <c r="B227" s="17" t="s">
@@ -31291,7 +31993,7 @@
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A228" s="58" t="s">
+      <c r="A228" s="34" t="s">
         <v>416</v>
       </c>
       <c r="B228" s="17" t="s">
@@ -31299,7 +32001,7 @@
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A229" s="58" t="s">
+      <c r="A229" s="34" t="s">
         <v>74</v>
       </c>
       <c r="B229" s="17" t="s">
@@ -31307,7 +32009,7 @@
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A230" s="58" t="s">
+      <c r="A230" s="34" t="s">
         <v>76</v>
       </c>
       <c r="B230" s="17" t="s">
@@ -31315,7 +32017,7 @@
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A231" s="58" t="s">
+      <c r="A231" s="34" t="s">
         <v>417</v>
       </c>
       <c r="B231" s="17" t="s">
@@ -31323,7 +32025,7 @@
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A232" s="58" t="s">
+      <c r="A232" s="34" t="s">
         <v>418</v>
       </c>
       <c r="B232" s="17" t="s">
@@ -31331,7 +32033,7 @@
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A233" s="58" t="s">
+      <c r="A233" s="34" t="s">
         <v>419</v>
       </c>
       <c r="B233" s="17" t="s">
@@ -31339,7 +32041,7 @@
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A234" s="58" t="s">
+      <c r="A234" s="34" t="s">
         <v>420</v>
       </c>
       <c r="B234" s="17" t="s">
@@ -31347,7 +32049,7 @@
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A235" s="58" t="s">
+      <c r="A235" s="34" t="s">
         <v>421</v>
       </c>
       <c r="B235" s="17" t="s">
@@ -31355,7 +32057,7 @@
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A236" s="58" t="s">
+      <c r="A236" s="34" t="s">
         <v>422</v>
       </c>
       <c r="B236" s="17" t="s">
@@ -31363,7 +32065,7 @@
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A237" s="58" t="s">
+      <c r="A237" s="34" t="s">
         <v>423</v>
       </c>
       <c r="B237" s="17" t="s">
@@ -31371,7 +32073,7 @@
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A238" s="58" t="s">
+      <c r="A238" s="34" t="s">
         <v>424</v>
       </c>
       <c r="B238" s="17" t="s">
@@ -31379,7 +32081,7 @@
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A239" s="58" t="s">
+      <c r="A239" s="34" t="s">
         <v>425</v>
       </c>
       <c r="B239" s="17" t="s">
@@ -31387,7 +32089,7 @@
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A240" s="58" t="s">
+      <c r="A240" s="34" t="s">
         <v>78</v>
       </c>
       <c r="B240" s="17" t="s">
@@ -31395,7 +32097,7 @@
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A241" s="58" t="s">
+      <c r="A241" s="34" t="s">
         <v>80</v>
       </c>
       <c r="B241" s="17" t="s">
@@ -31403,7 +32105,7 @@
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A242" s="58" t="s">
+      <c r="A242" s="34" t="s">
         <v>426</v>
       </c>
       <c r="B242" s="17" t="s">
@@ -31411,7 +32113,7 @@
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A243" s="58" t="s">
+      <c r="A243" s="34" t="s">
         <v>427</v>
       </c>
       <c r="B243" s="17" t="s">
@@ -31419,7 +32121,7 @@
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A244" s="58" t="s">
+      <c r="A244" s="34" t="s">
         <v>428</v>
       </c>
       <c r="B244" s="17" t="s">
@@ -31427,7 +32129,7 @@
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A245" s="58" t="s">
+      <c r="A245" s="34" t="s">
         <v>429</v>
       </c>
       <c r="B245" s="17" t="s">
@@ -31435,7 +32137,7 @@
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A246" s="58" t="s">
+      <c r="A246" s="34" t="s">
         <v>430</v>
       </c>
       <c r="B246" s="17" t="s">
@@ -31443,7 +32145,7 @@
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A247" s="58" t="s">
+      <c r="A247" s="34" t="s">
         <v>431</v>
       </c>
       <c r="B247" s="17" t="s">
@@ -31451,7 +32153,7 @@
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A248" s="58" t="s">
+      <c r="A248" s="34" t="s">
         <v>432</v>
       </c>
       <c r="B248" s="17" t="s">
@@ -31459,7 +32161,7 @@
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A249" s="58" t="s">
+      <c r="A249" s="34" t="s">
         <v>433</v>
       </c>
       <c r="B249" s="17" t="s">
@@ -31467,7 +32169,7 @@
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A250" s="58" t="s">
+      <c r="A250" s="34" t="s">
         <v>434</v>
       </c>
       <c r="B250" s="17" t="s">
@@ -31475,7 +32177,7 @@
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A251" s="58" t="s">
+      <c r="A251" s="34" t="s">
         <v>82</v>
       </c>
       <c r="B251" s="17" t="s">
@@ -31483,7 +32185,7 @@
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A252" s="58" t="s">
+      <c r="A252" s="34" t="s">
         <v>84</v>
       </c>
       <c r="B252" s="17" t="s">
@@ -31491,7 +32193,7 @@
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A253" s="58" t="s">
+      <c r="A253" s="34" t="s">
         <v>86</v>
       </c>
       <c r="B253" s="17" t="s">
@@ -31499,7 +32201,7 @@
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A254" s="58" t="s">
+      <c r="A254" s="34" t="s">
         <v>88</v>
       </c>
       <c r="B254" s="17" t="s">
@@ -31507,7 +32209,7 @@
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A255" s="58" t="s">
+      <c r="A255" s="34" t="s">
         <v>435</v>
       </c>
       <c r="B255" s="17" t="s">
@@ -31515,7 +32217,7 @@
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A256" s="58" t="s">
+      <c r="A256" s="34" t="s">
         <v>436</v>
       </c>
       <c r="B256" s="17" t="s">
@@ -31523,7 +32225,7 @@
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A257" s="58" t="s">
+      <c r="A257" s="34" t="s">
         <v>90</v>
       </c>
       <c r="B257" s="17" t="s">
@@ -31531,7 +32233,7 @@
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A258" s="58" t="s">
+      <c r="A258" s="34" t="s">
         <v>437</v>
       </c>
       <c r="B258" s="17" t="s">
@@ -31539,7 +32241,7 @@
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A259" s="58" t="s">
+      <c r="A259" s="34" t="s">
         <v>438</v>
       </c>
       <c r="B259" s="17" t="s">
@@ -31547,7 +32249,7 @@
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A260" s="58" t="s">
+      <c r="A260" s="34" t="s">
         <v>439</v>
       </c>
       <c r="B260" s="17" t="s">
@@ -31555,7 +32257,7 @@
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A261" s="58" t="s">
+      <c r="A261" s="34" t="s">
         <v>440</v>
       </c>
       <c r="B261" s="17" t="s">
@@ -31563,7 +32265,7 @@
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A262" s="58" t="s">
+      <c r="A262" s="34" t="s">
         <v>441</v>
       </c>
       <c r="B262" s="17" t="s">
@@ -31571,7 +32273,7 @@
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A263" s="58" t="s">
+      <c r="A263" s="34" t="s">
         <v>442</v>
       </c>
       <c r="B263" s="17" t="s">
@@ -31579,7 +32281,7 @@
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A264" s="58" t="s">
+      <c r="A264" s="34" t="s">
         <v>443</v>
       </c>
       <c r="B264" s="17" t="s">
@@ -31587,7 +32289,7 @@
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A265" s="58" t="s">
+      <c r="A265" s="34" t="s">
         <v>444</v>
       </c>
       <c r="B265" s="17" t="s">
@@ -31595,7 +32297,7 @@
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A266" s="58" t="s">
+      <c r="A266" s="34" t="s">
         <v>445</v>
       </c>
       <c r="B266" s="17" t="s">
@@ -31603,7 +32305,7 @@
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A267" s="58" t="s">
+      <c r="A267" s="34" t="s">
         <v>446</v>
       </c>
       <c r="B267" s="17" t="s">
@@ -31611,7 +32313,7 @@
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A268" s="58" t="s">
+      <c r="A268" s="34" t="s">
         <v>92</v>
       </c>
       <c r="B268" s="17" t="s">
@@ -31619,7 +32321,7 @@
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A269" s="58" t="s">
+      <c r="A269" s="34" t="s">
         <v>94</v>
       </c>
       <c r="B269" s="17" t="s">
@@ -31627,7 +32329,7 @@
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A270" s="58" t="s">
+      <c r="A270" s="34" t="s">
         <v>95</v>
       </c>
       <c r="B270" s="17" t="s">
@@ -31635,7 +32337,7 @@
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A271" s="58" t="s">
+      <c r="A271" s="34" t="s">
         <v>97</v>
       </c>
       <c r="B271" s="17" t="s">
@@ -31643,7 +32345,7 @@
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A272" s="58" t="s">
+      <c r="A272" s="34" t="s">
         <v>99</v>
       </c>
       <c r="B272" s="17" t="s">
@@ -31651,7 +32353,7 @@
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A273" s="58" t="s">
+      <c r="A273" s="34" t="s">
         <v>101</v>
       </c>
       <c r="B273" s="17" t="s">
@@ -31659,7 +32361,7 @@
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A274" s="58" t="s">
+      <c r="A274" s="34" t="s">
         <v>103</v>
       </c>
       <c r="B274" s="17" t="s">
@@ -31667,7 +32369,7 @@
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A275" s="58" t="s">
+      <c r="A275" s="34" t="s">
         <v>105</v>
       </c>
       <c r="B275" s="17" t="s">
@@ -31675,7 +32377,7 @@
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A276" s="58" t="s">
+      <c r="A276" s="34" t="s">
         <v>107</v>
       </c>
       <c r="B276" s="17" t="s">
@@ -31683,7 +32385,7 @@
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A277" s="58" t="s">
+      <c r="A277" s="34" t="s">
         <v>109</v>
       </c>
       <c r="B277" s="17" t="s">
@@ -31691,7 +32393,7 @@
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A278" s="58" t="s">
+      <c r="A278" s="34" t="s">
         <v>111</v>
       </c>
       <c r="B278" s="17" t="s">
@@ -31699,7 +32401,7 @@
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A279" s="58" t="s">
+      <c r="A279" s="34" t="s">
         <v>113</v>
       </c>
       <c r="B279" s="17" t="s">
@@ -31707,7 +32409,7 @@
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A280" s="58" t="s">
+      <c r="A280" s="34" t="s">
         <v>115</v>
       </c>
       <c r="B280" s="17" t="s">
@@ -31715,7 +32417,7 @@
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A281" s="58" t="s">
+      <c r="A281" s="34" t="s">
         <v>117</v>
       </c>
       <c r="B281" s="17" t="s">
@@ -31723,7 +32425,7 @@
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A282" s="58" t="s">
+      <c r="A282" s="34" t="s">
         <v>119</v>
       </c>
       <c r="B282" s="17" t="s">
@@ -31731,7 +32433,7 @@
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A283" s="58" t="s">
+      <c r="A283" s="34" t="s">
         <v>121</v>
       </c>
       <c r="B283" s="17" t="s">
@@ -31739,7 +32441,7 @@
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A284" s="58" t="s">
+      <c r="A284" s="34" t="s">
         <v>123</v>
       </c>
       <c r="B284" s="17" t="s">
@@ -31747,7 +32449,7 @@
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A285" s="58" t="s">
+      <c r="A285" s="34" t="s">
         <v>125</v>
       </c>
       <c r="B285" s="17" t="s">
@@ -31755,7 +32457,7 @@
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A286" s="58" t="s">
+      <c r="A286" s="34" t="s">
         <v>127</v>
       </c>
       <c r="B286" s="17" t="s">
@@ -31763,7 +32465,7 @@
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A287" s="58" t="s">
+      <c r="A287" s="34" t="s">
         <v>129</v>
       </c>
       <c r="B287" s="17" t="s">
@@ -31771,7 +32473,7 @@
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A288" s="58" t="s">
+      <c r="A288" s="34" t="s">
         <v>131</v>
       </c>
       <c r="B288" s="17" t="s">
@@ -31779,7 +32481,7 @@
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A289" s="58" t="s">
+      <c r="A289" s="34" t="s">
         <v>133</v>
       </c>
       <c r="B289" s="17" t="s">
@@ -31787,7 +32489,7 @@
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A290" s="58" t="s">
+      <c r="A290" s="34" t="s">
         <v>135</v>
       </c>
       <c r="B290" s="17" t="s">
@@ -31795,7 +32497,7 @@
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A291" s="58" t="s">
+      <c r="A291" s="34" t="s">
         <v>137</v>
       </c>
       <c r="B291" s="17" t="s">
@@ -31803,7 +32505,7 @@
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A292" s="58" t="s">
+      <c r="A292" s="34" t="s">
         <v>139</v>
       </c>
       <c r="B292" s="17" t="s">
@@ -31811,7 +32513,7 @@
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A293" s="58" t="s">
+      <c r="A293" s="34" t="s">
         <v>141</v>
       </c>
       <c r="B293" s="17" t="s">
@@ -31819,7 +32521,7 @@
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A294" s="58" t="s">
+      <c r="A294" s="34" t="s">
         <v>143</v>
       </c>
       <c r="B294" s="17" t="s">
@@ -31827,7 +32529,7 @@
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A295" s="58" t="s">
+      <c r="A295" s="34" t="s">
         <v>145</v>
       </c>
       <c r="B295" s="17" t="s">
@@ -31835,7 +32537,7 @@
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A296" s="58" t="s">
+      <c r="A296" s="34" t="s">
         <v>147</v>
       </c>
       <c r="B296" s="17" t="s">
@@ -31843,7 +32545,7 @@
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A297" s="58" t="s">
+      <c r="A297" s="34" t="s">
         <v>149</v>
       </c>
       <c r="B297" s="17" t="s">
@@ -31851,7 +32553,7 @@
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A298" s="58" t="s">
+      <c r="A298" s="34" t="s">
         <v>151</v>
       </c>
       <c r="B298" s="17" t="s">
@@ -31859,7 +32561,7 @@
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A299" s="58" t="s">
+      <c r="A299" s="34" t="s">
         <v>152</v>
       </c>
       <c r="B299" s="17" t="s">
@@ -31867,7 +32569,7 @@
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A300" s="58" t="s">
+      <c r="A300" s="34" t="s">
         <v>154</v>
       </c>
       <c r="B300" s="17" t="s">
@@ -31875,7 +32577,7 @@
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A301" s="58" t="s">
+      <c r="A301" s="34" t="s">
         <v>156</v>
       </c>
       <c r="B301" s="17" t="s">
@@ -31883,7 +32585,7 @@
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A302" s="58" t="s">
+      <c r="A302" s="34" t="s">
         <v>158</v>
       </c>
       <c r="B302" s="17" t="s">
@@ -31891,7 +32593,7 @@
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A303" s="58" t="s">
+      <c r="A303" s="34" t="s">
         <v>160</v>
       </c>
       <c r="B303" s="17" t="s">
@@ -31899,7 +32601,7 @@
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A304" s="58" t="s">
+      <c r="A304" s="34" t="s">
         <v>162</v>
       </c>
       <c r="B304" s="17" t="s">
@@ -31907,7 +32609,7 @@
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A305" s="58" t="s">
+      <c r="A305" s="34" t="s">
         <v>164</v>
       </c>
       <c r="B305" s="17" t="s">
@@ -31915,7 +32617,7 @@
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A306" s="58" t="s">
+      <c r="A306" s="34" t="s">
         <v>166</v>
       </c>
       <c r="B306" s="17" t="s">
@@ -31923,7 +32625,7 @@
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A307" s="58" t="s">
+      <c r="A307" s="34" t="s">
         <v>168</v>
       </c>
       <c r="B307" s="17" t="s">
@@ -31931,7 +32633,7 @@
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A308" s="58" t="s">
+      <c r="A308" s="34" t="s">
         <v>170</v>
       </c>
       <c r="B308" s="17" t="s">
@@ -31939,7 +32641,7 @@
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A309" s="58" t="s">
+      <c r="A309" s="34" t="s">
         <v>172</v>
       </c>
       <c r="B309" s="17" t="s">
@@ -31947,7 +32649,7 @@
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A310" s="58" t="s">
+      <c r="A310" s="34" t="s">
         <v>174</v>
       </c>
       <c r="B310" s="17" t="s">
@@ -31955,7 +32657,7 @@
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A311" s="58" t="s">
+      <c r="A311" s="34" t="s">
         <v>176</v>
       </c>
       <c r="B311" s="17" t="s">
@@ -31963,7 +32665,7 @@
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A312" s="58" t="s">
+      <c r="A312" s="34" t="s">
         <v>178</v>
       </c>
       <c r="B312" s="17" t="s">
@@ -31971,7 +32673,7 @@
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A313" s="58" t="s">
+      <c r="A313" s="34" t="s">
         <v>180</v>
       </c>
       <c r="B313" s="17" t="s">
@@ -31979,7 +32681,7 @@
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A314" s="58" t="s">
+      <c r="A314" s="34" t="s">
         <v>182</v>
       </c>
       <c r="B314" s="17" t="s">
@@ -31987,7 +32689,7 @@
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A315" s="58" t="s">
+      <c r="A315" s="34" t="s">
         <v>184</v>
       </c>
       <c r="B315" s="17" t="s">
@@ -31995,7 +32697,7 @@
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A316" s="58" t="s">
+      <c r="A316" s="34" t="s">
         <v>186</v>
       </c>
       <c r="B316" s="17" t="s">
@@ -32003,7 +32705,7 @@
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A317" s="58" t="s">
+      <c r="A317" s="34" t="s">
         <v>188</v>
       </c>
       <c r="B317" s="17" t="s">
@@ -32011,7 +32713,7 @@
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A318" s="58" t="s">
+      <c r="A318" s="34" t="s">
         <v>190</v>
       </c>
       <c r="B318" s="17" t="s">
@@ -32019,7 +32721,7 @@
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A319" s="58" t="s">
+      <c r="A319" s="34" t="s">
         <v>192</v>
       </c>
       <c r="B319" s="17" t="s">
@@ -32027,7 +32729,7 @@
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A320" s="58" t="s">
+      <c r="A320" s="34" t="s">
         <v>447</v>
       </c>
       <c r="B320" s="17" t="s">
@@ -32035,7 +32737,7 @@
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A321" s="58" t="s">
+      <c r="A321" s="34" t="s">
         <v>448</v>
       </c>
       <c r="B321" s="17" t="s">
@@ -32043,7 +32745,7 @@
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A322" s="58" t="s">
+      <c r="A322" s="34" t="s">
         <v>194</v>
       </c>
       <c r="B322" s="17" t="s">
@@ -32051,7 +32753,7 @@
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A323" s="58" t="s">
+      <c r="A323" s="34" t="s">
         <v>196</v>
       </c>
       <c r="B323" s="17" t="s">
@@ -32059,7 +32761,7 @@
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A324" s="58" t="s">
+      <c r="A324" s="34" t="s">
         <v>197</v>
       </c>
       <c r="B324" s="17" t="s">
@@ -32067,7 +32769,7 @@
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A325" s="58" t="s">
+      <c r="A325" s="34" t="s">
         <v>199</v>
       </c>
       <c r="B325" s="17" t="s">
@@ -32075,7 +32777,7 @@
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A326" s="58" t="s">
+      <c r="A326" s="34" t="s">
         <v>449</v>
       </c>
       <c r="B326" s="17" t="s">
@@ -32083,7 +32785,7 @@
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A327" s="58" t="s">
+      <c r="A327" s="34" t="s">
         <v>450</v>
       </c>
       <c r="B327" s="17" t="s">
@@ -32116,12 +32818,12 @@
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="57" t="s">
+      <c r="C2" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
       <c r="G2" s="4" t="s">
         <v>1</v>
       </c>

--- a/wwwroot/template/TemPlateQuote.xlsx
+++ b/wwwroot/template/TemPlateQuote.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\khanhmf\Cost Managerment\wwwroot\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C203ED8D-E19D-4507-833C-881DE0C61FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89289C90-24B2-4FE4-AB08-F35F0C2D49E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F4BD22E2-5202-4BAA-B608-770E176E4E09}"/>
   </bookViews>
@@ -3572,34 +3572,20 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3621,6 +3607,36 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3632,24 +3648,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4123,18 +4123,18 @@
     </row>
     <row r="4" spans="1:32" ht="11.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9"/>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="49" t="s">
         <v>213</v>
       </c>
-      <c r="C4" s="35"/>
-      <c r="D4" s="36"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="50"/>
       <c r="E4" s="25"/>
       <c r="F4" s="25"/>
       <c r="G4" s="25"/>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="49" t="s">
         <v>214</v>
       </c>
-      <c r="I4" s="37"/>
+      <c r="I4" s="51"/>
       <c r="J4" s="9"/>
       <c r="K4" s="25"/>
       <c r="M4" s="9"/>
@@ -4156,14 +4156,14 @@
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="9"/>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="36"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="50"/>
       <c r="E5" s="25"/>
       <c r="F5" s="25"/>
       <c r="G5" s="25"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="37"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="51"/>
       <c r="J5" s="25"/>
       <c r="K5" s="25"/>
       <c r="L5" s="18"/>
@@ -4187,17 +4187,17 @@
       <c r="AD5" s="9"/>
     </row>
     <row r="6" spans="1:32" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="40" t="s">
+      <c r="A6" s="52" t="s">
         <v>264</v>
       </c>
-      <c r="B6" s="41"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="41"/>
-      <c r="I6" s="41"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
       <c r="J6" s="18"/>
       <c r="K6" s="18"/>
       <c r="L6" s="18"/>
@@ -4257,15 +4257,15 @@
       <c r="L7" s="26">
         <v>12</v>
       </c>
-      <c r="M7" s="45">
+      <c r="M7" s="41">
         <f>L7+1</f>
         <v>13</v>
       </c>
-      <c r="N7" s="46"/>
-      <c r="O7" s="46"/>
-      <c r="P7" s="46"/>
-      <c r="Q7" s="46"/>
-      <c r="R7" s="47"/>
+      <c r="N7" s="42"/>
+      <c r="O7" s="42"/>
+      <c r="P7" s="42"/>
+      <c r="Q7" s="42"/>
+      <c r="R7" s="43"/>
       <c r="S7" s="24">
         <v>14</v>
       </c>
@@ -4323,106 +4323,106 @@
       </c>
     </row>
     <row r="8" spans="1:32" s="7" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="42" t="s">
+      <c r="A8" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="39" t="s">
         <v>215</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="39" t="s">
         <v>216</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="D8" s="39" t="s">
         <v>217</v>
       </c>
-      <c r="E8" s="38" t="s">
+      <c r="E8" s="39" t="s">
         <v>218</v>
       </c>
-      <c r="F8" s="38" t="s">
+      <c r="F8" s="39" t="s">
         <v>219</v>
       </c>
-      <c r="G8" s="38" t="s">
+      <c r="G8" s="39" t="s">
         <v>220</v>
       </c>
-      <c r="H8" s="38" t="s">
+      <c r="H8" s="39" t="s">
         <v>222</v>
       </c>
-      <c r="I8" s="38" t="s">
+      <c r="I8" s="39" t="s">
         <v>223</v>
       </c>
-      <c r="J8" s="38" t="s">
+      <c r="J8" s="39" t="s">
         <v>221</v>
       </c>
-      <c r="K8" s="38" t="s">
+      <c r="K8" s="39" t="s">
         <v>224</v>
       </c>
-      <c r="L8" s="38" t="s">
+      <c r="L8" s="39" t="s">
         <v>225</v>
       </c>
-      <c r="M8" s="48" t="s">
+      <c r="M8" s="44" t="s">
         <v>231</v>
       </c>
-      <c r="N8" s="49"/>
-      <c r="O8" s="49"/>
-      <c r="P8" s="49"/>
-      <c r="Q8" s="49"/>
-      <c r="R8" s="50"/>
-      <c r="S8" s="38" t="s">
+      <c r="N8" s="45"/>
+      <c r="O8" s="45"/>
+      <c r="P8" s="45"/>
+      <c r="Q8" s="45"/>
+      <c r="R8" s="46"/>
+      <c r="S8" s="39" t="s">
         <v>235</v>
       </c>
-      <c r="T8" s="38" t="s">
+      <c r="T8" s="39" t="s">
         <v>236</v>
       </c>
-      <c r="U8" s="38" t="s">
+      <c r="U8" s="39" t="s">
         <v>232</v>
       </c>
-      <c r="V8" s="38" t="s">
+      <c r="V8" s="39" t="s">
         <v>233</v>
       </c>
-      <c r="W8" s="38" t="s">
+      <c r="W8" s="39" t="s">
         <v>237</v>
       </c>
-      <c r="X8" s="38" t="s">
+      <c r="X8" s="39" t="s">
         <v>238</v>
       </c>
-      <c r="Y8" s="38" t="s">
+      <c r="Y8" s="39" t="s">
         <v>239</v>
       </c>
-      <c r="Z8" s="38" t="s">
+      <c r="Z8" s="39" t="s">
         <v>240</v>
       </c>
-      <c r="AA8" s="38" t="s">
+      <c r="AA8" s="39" t="s">
         <v>241</v>
       </c>
-      <c r="AB8" s="38" t="s">
+      <c r="AB8" s="39" t="s">
         <v>242</v>
       </c>
-      <c r="AC8" s="38" t="s">
+      <c r="AC8" s="39" t="s">
         <v>243</v>
       </c>
-      <c r="AD8" s="38" t="s">
+      <c r="AD8" s="39" t="s">
         <v>244</v>
       </c>
-      <c r="AE8" s="44" t="s">
+      <c r="AE8" s="38" t="s">
         <v>245</v>
       </c>
-      <c r="AF8" s="44" t="s">
+      <c r="AF8" s="38" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="9" spans="1:32" s="7" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A9" s="43"/>
-      <c r="B9" s="39"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="39"/>
-      <c r="K9" s="39"/>
-      <c r="L9" s="39"/>
+      <c r="A9" s="48"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="40"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="40"/>
       <c r="M9" s="19" t="s">
         <v>226</v>
       </c>
@@ -4441,20 +4441,20 @@
       <c r="R9" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="S9" s="39"/>
-      <c r="T9" s="39"/>
-      <c r="U9" s="39"/>
-      <c r="V9" s="39"/>
-      <c r="W9" s="39"/>
-      <c r="X9" s="39"/>
-      <c r="Y9" s="39"/>
-      <c r="Z9" s="39"/>
-      <c r="AA9" s="39"/>
-      <c r="AB9" s="39"/>
-      <c r="AC9" s="39"/>
-      <c r="AD9" s="39"/>
-      <c r="AE9" s="44"/>
-      <c r="AF9" s="44"/>
+      <c r="S9" s="40"/>
+      <c r="T9" s="40"/>
+      <c r="U9" s="40"/>
+      <c r="V9" s="40"/>
+      <c r="W9" s="40"/>
+      <c r="X9" s="40"/>
+      <c r="Y9" s="40"/>
+      <c r="Z9" s="40"/>
+      <c r="AA9" s="40"/>
+      <c r="AB9" s="40"/>
+      <c r="AC9" s="40"/>
+      <c r="AD9" s="40"/>
+      <c r="AE9" s="38"/>
+      <c r="AF9" s="38"/>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
@@ -4470,8 +4470,8 @@
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
       <c r="H10" s="12" t="str">
-        <f>M10&amp;" "&amp;N10&amp;" "&amp;O10&amp;""&amp;P10&amp;" "&amp;Q10&amp;" "&amp;R10</f>
-        <v xml:space="preserve">    </v>
+        <f>L10&amp;"có hình dáng dạng "&amp;M10&amp;" chất liệu "&amp;N10&amp;" thành phần hóa chất: "&amp;O10&amp;" có kích thước "&amp;P10&amp;" dùng để "&amp;R10&amp;" cho "&amp;Q10</f>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I10" s="13"/>
       <c r="J10" s="13"/>
@@ -4514,8 +4514,8 @@
       <c r="F11" s="13"/>
       <c r="G11" s="13"/>
       <c r="H11" s="12" t="str">
-        <f t="shared" ref="H11:H29" si="1">M11&amp;" "&amp;N11&amp;" "&amp;O11&amp;""&amp;P11&amp;" "&amp;Q11&amp;" "&amp;R11</f>
-        <v xml:space="preserve">    </v>
+        <f t="shared" ref="H11:H74" si="1">L11&amp;"có hình dáng dạng "&amp;M11&amp;" chất liệu "&amp;N11&amp;" thành phần hóa chất: "&amp;O11&amp;" có kích thước "&amp;P11&amp;" dùng để "&amp;R11&amp;" cho "&amp;Q11</f>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I11" s="13"/>
       <c r="J11" s="13"/>
@@ -4559,7 +4559,7 @@
       <c r="G12" s="13"/>
       <c r="H12" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I12" s="13"/>
       <c r="J12" s="13"/>
@@ -4603,7 +4603,7 @@
       <c r="G13" s="13"/>
       <c r="H13" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I13" s="13"/>
       <c r="J13" s="13"/>
@@ -4647,7 +4647,7 @@
       <c r="G14" s="13"/>
       <c r="H14" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I14" s="13"/>
       <c r="J14" s="13"/>
@@ -4691,7 +4691,7 @@
       <c r="G15" s="13"/>
       <c r="H15" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I15" s="13"/>
       <c r="J15" s="13"/>
@@ -4735,7 +4735,7 @@
       <c r="G16" s="13"/>
       <c r="H16" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I16" s="13"/>
       <c r="J16" s="13"/>
@@ -4779,7 +4779,7 @@
       <c r="G17" s="13"/>
       <c r="H17" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I17" s="13"/>
       <c r="J17" s="13"/>
@@ -4823,7 +4823,7 @@
       <c r="G18" s="13"/>
       <c r="H18" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I18" s="13"/>
       <c r="J18" s="13"/>
@@ -4867,7 +4867,7 @@
       <c r="G19" s="13"/>
       <c r="H19" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I19" s="13"/>
       <c r="J19" s="13"/>
@@ -4911,7 +4911,7 @@
       <c r="G20" s="13"/>
       <c r="H20" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I20" s="13"/>
       <c r="J20" s="13"/>
@@ -4955,7 +4955,7 @@
       <c r="G21" s="13"/>
       <c r="H21" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I21" s="13"/>
       <c r="J21" s="13"/>
@@ -4999,7 +4999,7 @@
       <c r="G22" s="13"/>
       <c r="H22" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I22" s="13"/>
       <c r="J22" s="13"/>
@@ -5043,7 +5043,7 @@
       <c r="G23" s="13"/>
       <c r="H23" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I23" s="13"/>
       <c r="J23" s="13"/>
@@ -5087,7 +5087,7 @@
       <c r="G24" s="13"/>
       <c r="H24" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I24" s="13"/>
       <c r="J24" s="13"/>
@@ -5131,7 +5131,7 @@
       <c r="G25" s="13"/>
       <c r="H25" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I25" s="13"/>
       <c r="J25" s="13"/>
@@ -5175,7 +5175,7 @@
       <c r="G26" s="13"/>
       <c r="H26" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I26" s="13"/>
       <c r="J26" s="13"/>
@@ -5219,7 +5219,7 @@
       <c r="G27" s="13"/>
       <c r="H27" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I27" s="13"/>
       <c r="J27" s="13"/>
@@ -5263,7 +5263,7 @@
       <c r="G28" s="13"/>
       <c r="H28" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I28" s="13"/>
       <c r="J28" s="13"/>
@@ -5307,7 +5307,7 @@
       <c r="G29" s="13"/>
       <c r="H29" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I29" s="13"/>
       <c r="J29" s="13"/>
@@ -5350,8 +5350,8 @@
       <c r="F30" s="13"/>
       <c r="G30" s="13"/>
       <c r="H30" s="12" t="str">
-        <f t="shared" ref="H30:H93" si="2">M30&amp;" "&amp;N30&amp;" "&amp;O30&amp;""&amp;P30&amp;" "&amp;Q30&amp;" "&amp;R30</f>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I30" s="13"/>
       <c r="J30" s="13"/>
@@ -5394,8 +5394,8 @@
       <c r="F31" s="13"/>
       <c r="G31" s="13"/>
       <c r="H31" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I31" s="13"/>
       <c r="J31" s="13"/>
@@ -5438,8 +5438,8 @@
       <c r="F32" s="13"/>
       <c r="G32" s="13"/>
       <c r="H32" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I32" s="13"/>
       <c r="J32" s="13"/>
@@ -5482,8 +5482,8 @@
       <c r="F33" s="13"/>
       <c r="G33" s="13"/>
       <c r="H33" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I33" s="13"/>
       <c r="J33" s="13"/>
@@ -5526,8 +5526,8 @@
       <c r="F34" s="13"/>
       <c r="G34" s="13"/>
       <c r="H34" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I34" s="13"/>
       <c r="J34" s="13"/>
@@ -5570,8 +5570,8 @@
       <c r="F35" s="13"/>
       <c r="G35" s="13"/>
       <c r="H35" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I35" s="13"/>
       <c r="J35" s="13"/>
@@ -5614,8 +5614,8 @@
       <c r="F36" s="13"/>
       <c r="G36" s="13"/>
       <c r="H36" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I36" s="13"/>
       <c r="J36" s="13"/>
@@ -5658,8 +5658,8 @@
       <c r="F37" s="13"/>
       <c r="G37" s="13"/>
       <c r="H37" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I37" s="13"/>
       <c r="J37" s="13"/>
@@ -5702,8 +5702,8 @@
       <c r="F38" s="13"/>
       <c r="G38" s="13"/>
       <c r="H38" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I38" s="13"/>
       <c r="J38" s="13"/>
@@ -5746,8 +5746,8 @@
       <c r="F39" s="13"/>
       <c r="G39" s="13"/>
       <c r="H39" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I39" s="13"/>
       <c r="J39" s="13"/>
@@ -5790,8 +5790,8 @@
       <c r="F40" s="13"/>
       <c r="G40" s="13"/>
       <c r="H40" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I40" s="13"/>
       <c r="J40" s="13"/>
@@ -5834,8 +5834,8 @@
       <c r="F41" s="13"/>
       <c r="G41" s="13"/>
       <c r="H41" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I41" s="13"/>
       <c r="J41" s="13"/>
@@ -5878,8 +5878,8 @@
       <c r="F42" s="13"/>
       <c r="G42" s="13"/>
       <c r="H42" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I42" s="13"/>
       <c r="J42" s="13"/>
@@ -5922,8 +5922,8 @@
       <c r="F43" s="13"/>
       <c r="G43" s="13"/>
       <c r="H43" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I43" s="13"/>
       <c r="J43" s="13"/>
@@ -5966,8 +5966,8 @@
       <c r="F44" s="13"/>
       <c r="G44" s="13"/>
       <c r="H44" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I44" s="13"/>
       <c r="J44" s="13"/>
@@ -6010,8 +6010,8 @@
       <c r="F45" s="13"/>
       <c r="G45" s="13"/>
       <c r="H45" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I45" s="13"/>
       <c r="J45" s="13"/>
@@ -6054,8 +6054,8 @@
       <c r="F46" s="13"/>
       <c r="G46" s="13"/>
       <c r="H46" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I46" s="13"/>
       <c r="J46" s="13"/>
@@ -6098,8 +6098,8 @@
       <c r="F47" s="13"/>
       <c r="G47" s="13"/>
       <c r="H47" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I47" s="13"/>
       <c r="J47" s="13"/>
@@ -6142,8 +6142,8 @@
       <c r="F48" s="13"/>
       <c r="G48" s="13"/>
       <c r="H48" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I48" s="13"/>
       <c r="J48" s="13"/>
@@ -6186,8 +6186,8 @@
       <c r="F49" s="13"/>
       <c r="G49" s="13"/>
       <c r="H49" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I49" s="13"/>
       <c r="J49" s="13"/>
@@ -6230,8 +6230,8 @@
       <c r="F50" s="13"/>
       <c r="G50" s="13"/>
       <c r="H50" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I50" s="13"/>
       <c r="J50" s="13"/>
@@ -6274,8 +6274,8 @@
       <c r="F51" s="13"/>
       <c r="G51" s="13"/>
       <c r="H51" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I51" s="13"/>
       <c r="J51" s="13"/>
@@ -6318,8 +6318,8 @@
       <c r="F52" s="13"/>
       <c r="G52" s="13"/>
       <c r="H52" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I52" s="13"/>
       <c r="J52" s="13"/>
@@ -6362,8 +6362,8 @@
       <c r="F53" s="13"/>
       <c r="G53" s="13"/>
       <c r="H53" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I53" s="13"/>
       <c r="J53" s="13"/>
@@ -6406,8 +6406,8 @@
       <c r="F54" s="13"/>
       <c r="G54" s="13"/>
       <c r="H54" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I54" s="13"/>
       <c r="J54" s="13"/>
@@ -6450,8 +6450,8 @@
       <c r="F55" s="13"/>
       <c r="G55" s="13"/>
       <c r="H55" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I55" s="13"/>
       <c r="J55" s="13"/>
@@ -6494,8 +6494,8 @@
       <c r="F56" s="13"/>
       <c r="G56" s="13"/>
       <c r="H56" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I56" s="13"/>
       <c r="J56" s="13"/>
@@ -6538,8 +6538,8 @@
       <c r="F57" s="13"/>
       <c r="G57" s="13"/>
       <c r="H57" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I57" s="13"/>
       <c r="J57" s="13"/>
@@ -6582,8 +6582,8 @@
       <c r="F58" s="13"/>
       <c r="G58" s="13"/>
       <c r="H58" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I58" s="13"/>
       <c r="J58" s="13"/>
@@ -6626,8 +6626,8 @@
       <c r="F59" s="13"/>
       <c r="G59" s="13"/>
       <c r="H59" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I59" s="13"/>
       <c r="J59" s="13"/>
@@ -6670,8 +6670,8 @@
       <c r="F60" s="13"/>
       <c r="G60" s="13"/>
       <c r="H60" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I60" s="13"/>
       <c r="J60" s="13"/>
@@ -6714,8 +6714,8 @@
       <c r="F61" s="13"/>
       <c r="G61" s="13"/>
       <c r="H61" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I61" s="13"/>
       <c r="J61" s="13"/>
@@ -6758,8 +6758,8 @@
       <c r="F62" s="13"/>
       <c r="G62" s="13"/>
       <c r="H62" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I62" s="13"/>
       <c r="J62" s="13"/>
@@ -6802,8 +6802,8 @@
       <c r="F63" s="13"/>
       <c r="G63" s="13"/>
       <c r="H63" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I63" s="13"/>
       <c r="J63" s="13"/>
@@ -6846,8 +6846,8 @@
       <c r="F64" s="13"/>
       <c r="G64" s="13"/>
       <c r="H64" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I64" s="13"/>
       <c r="J64" s="13"/>
@@ -6890,8 +6890,8 @@
       <c r="F65" s="13"/>
       <c r="G65" s="13"/>
       <c r="H65" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I65" s="13"/>
       <c r="J65" s="13"/>
@@ -6934,8 +6934,8 @@
       <c r="F66" s="13"/>
       <c r="G66" s="13"/>
       <c r="H66" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I66" s="13"/>
       <c r="J66" s="13"/>
@@ -6978,8 +6978,8 @@
       <c r="F67" s="13"/>
       <c r="G67" s="13"/>
       <c r="H67" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I67" s="13"/>
       <c r="J67" s="13"/>
@@ -7022,8 +7022,8 @@
       <c r="F68" s="13"/>
       <c r="G68" s="13"/>
       <c r="H68" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I68" s="13"/>
       <c r="J68" s="13"/>
@@ -7066,8 +7066,8 @@
       <c r="F69" s="13"/>
       <c r="G69" s="13"/>
       <c r="H69" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I69" s="13"/>
       <c r="J69" s="13"/>
@@ -7110,8 +7110,8 @@
       <c r="F70" s="13"/>
       <c r="G70" s="13"/>
       <c r="H70" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I70" s="13"/>
       <c r="J70" s="13"/>
@@ -7154,8 +7154,8 @@
       <c r="F71" s="13"/>
       <c r="G71" s="13"/>
       <c r="H71" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I71" s="13"/>
       <c r="J71" s="13"/>
@@ -7198,8 +7198,8 @@
       <c r="F72" s="13"/>
       <c r="G72" s="13"/>
       <c r="H72" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I72" s="13"/>
       <c r="J72" s="13"/>
@@ -7242,8 +7242,8 @@
       <c r="F73" s="13"/>
       <c r="G73" s="13"/>
       <c r="H73" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I73" s="13"/>
       <c r="J73" s="13"/>
@@ -7286,8 +7286,8 @@
       <c r="F74" s="13"/>
       <c r="G74" s="13"/>
       <c r="H74" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I74" s="13"/>
       <c r="J74" s="13"/>
@@ -7330,8 +7330,8 @@
       <c r="F75" s="13"/>
       <c r="G75" s="13"/>
       <c r="H75" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" ref="H75:H138" si="2">L75&amp;"có hình dáng dạng "&amp;M75&amp;" chất liệu "&amp;N75&amp;" thành phần hóa chất: "&amp;O75&amp;" có kích thước "&amp;P75&amp;" dùng để "&amp;R75&amp;" cho "&amp;Q75</f>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I75" s="13"/>
       <c r="J75" s="13"/>
@@ -7375,7 +7375,7 @@
       <c r="G76" s="13"/>
       <c r="H76" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I76" s="13"/>
       <c r="J76" s="13"/>
@@ -7419,7 +7419,7 @@
       <c r="G77" s="13"/>
       <c r="H77" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I77" s="13"/>
       <c r="J77" s="13"/>
@@ -7463,7 +7463,7 @@
       <c r="G78" s="13"/>
       <c r="H78" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I78" s="13"/>
       <c r="J78" s="13"/>
@@ -7507,7 +7507,7 @@
       <c r="G79" s="13"/>
       <c r="H79" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I79" s="13"/>
       <c r="J79" s="13"/>
@@ -7551,7 +7551,7 @@
       <c r="G80" s="13"/>
       <c r="H80" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I80" s="13"/>
       <c r="J80" s="13"/>
@@ -7595,7 +7595,7 @@
       <c r="G81" s="13"/>
       <c r="H81" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I81" s="13"/>
       <c r="J81" s="13"/>
@@ -7639,7 +7639,7 @@
       <c r="G82" s="13"/>
       <c r="H82" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I82" s="13"/>
       <c r="J82" s="13"/>
@@ -7683,7 +7683,7 @@
       <c r="G83" s="13"/>
       <c r="H83" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I83" s="13"/>
       <c r="J83" s="13"/>
@@ -7727,7 +7727,7 @@
       <c r="G84" s="13"/>
       <c r="H84" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I84" s="13"/>
       <c r="J84" s="13"/>
@@ -7771,7 +7771,7 @@
       <c r="G85" s="13"/>
       <c r="H85" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I85" s="13"/>
       <c r="J85" s="13"/>
@@ -7815,7 +7815,7 @@
       <c r="G86" s="13"/>
       <c r="H86" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I86" s="13"/>
       <c r="J86" s="13"/>
@@ -7859,7 +7859,7 @@
       <c r="G87" s="13"/>
       <c r="H87" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I87" s="13"/>
       <c r="J87" s="13"/>
@@ -7903,7 +7903,7 @@
       <c r="G88" s="13"/>
       <c r="H88" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I88" s="13"/>
       <c r="J88" s="13"/>
@@ -7947,7 +7947,7 @@
       <c r="G89" s="13"/>
       <c r="H89" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I89" s="13"/>
       <c r="J89" s="13"/>
@@ -7991,7 +7991,7 @@
       <c r="G90" s="13"/>
       <c r="H90" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I90" s="13"/>
       <c r="J90" s="13"/>
@@ -8035,7 +8035,7 @@
       <c r="G91" s="13"/>
       <c r="H91" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I91" s="13"/>
       <c r="J91" s="13"/>
@@ -8079,7 +8079,7 @@
       <c r="G92" s="13"/>
       <c r="H92" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I92" s="13"/>
       <c r="J92" s="13"/>
@@ -8123,7 +8123,7 @@
       <c r="G93" s="13"/>
       <c r="H93" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I93" s="13"/>
       <c r="J93" s="13"/>
@@ -8166,8 +8166,8 @@
       <c r="F94" s="13"/>
       <c r="G94" s="13"/>
       <c r="H94" s="12" t="str">
-        <f t="shared" ref="H94:H157" si="3">M94&amp;" "&amp;N94&amp;" "&amp;O94&amp;""&amp;P94&amp;" "&amp;Q94&amp;" "&amp;R94</f>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I94" s="13"/>
       <c r="J94" s="13"/>
@@ -8210,8 +8210,8 @@
       <c r="F95" s="13"/>
       <c r="G95" s="13"/>
       <c r="H95" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I95" s="13"/>
       <c r="J95" s="13"/>
@@ -8254,8 +8254,8 @@
       <c r="F96" s="13"/>
       <c r="G96" s="13"/>
       <c r="H96" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I96" s="13"/>
       <c r="J96" s="13"/>
@@ -8298,8 +8298,8 @@
       <c r="F97" s="13"/>
       <c r="G97" s="13"/>
       <c r="H97" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I97" s="13"/>
       <c r="J97" s="13"/>
@@ -8342,8 +8342,8 @@
       <c r="F98" s="13"/>
       <c r="G98" s="13"/>
       <c r="H98" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I98" s="13"/>
       <c r="J98" s="13"/>
@@ -8386,8 +8386,8 @@
       <c r="F99" s="13"/>
       <c r="G99" s="13"/>
       <c r="H99" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I99" s="13"/>
       <c r="J99" s="13"/>
@@ -8430,8 +8430,8 @@
       <c r="F100" s="13"/>
       <c r="G100" s="13"/>
       <c r="H100" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I100" s="13"/>
       <c r="J100" s="13"/>
@@ -8474,8 +8474,8 @@
       <c r="F101" s="13"/>
       <c r="G101" s="13"/>
       <c r="H101" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I101" s="13"/>
       <c r="J101" s="13"/>
@@ -8518,8 +8518,8 @@
       <c r="F102" s="13"/>
       <c r="G102" s="13"/>
       <c r="H102" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I102" s="13"/>
       <c r="J102" s="13"/>
@@ -8562,8 +8562,8 @@
       <c r="F103" s="13"/>
       <c r="G103" s="13"/>
       <c r="H103" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I103" s="13"/>
       <c r="J103" s="13"/>
@@ -8606,8 +8606,8 @@
       <c r="F104" s="13"/>
       <c r="G104" s="13"/>
       <c r="H104" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I104" s="13"/>
       <c r="J104" s="13"/>
@@ -8650,8 +8650,8 @@
       <c r="F105" s="13"/>
       <c r="G105" s="13"/>
       <c r="H105" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I105" s="13"/>
       <c r="J105" s="13"/>
@@ -8694,8 +8694,8 @@
       <c r="F106" s="13"/>
       <c r="G106" s="13"/>
       <c r="H106" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I106" s="13"/>
       <c r="J106" s="13"/>
@@ -8738,8 +8738,8 @@
       <c r="F107" s="13"/>
       <c r="G107" s="13"/>
       <c r="H107" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I107" s="13"/>
       <c r="J107" s="13"/>
@@ -8782,8 +8782,8 @@
       <c r="F108" s="13"/>
       <c r="G108" s="13"/>
       <c r="H108" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I108" s="13"/>
       <c r="J108" s="13"/>
@@ -8826,8 +8826,8 @@
       <c r="F109" s="13"/>
       <c r="G109" s="13"/>
       <c r="H109" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I109" s="13"/>
       <c r="J109" s="13"/>
@@ -8870,8 +8870,8 @@
       <c r="F110" s="13"/>
       <c r="G110" s="13"/>
       <c r="H110" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I110" s="13"/>
       <c r="J110" s="13"/>
@@ -8914,8 +8914,8 @@
       <c r="F111" s="13"/>
       <c r="G111" s="13"/>
       <c r="H111" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I111" s="13"/>
       <c r="J111" s="13"/>
@@ -8958,8 +8958,8 @@
       <c r="F112" s="13"/>
       <c r="G112" s="13"/>
       <c r="H112" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I112" s="13"/>
       <c r="J112" s="13"/>
@@ -9002,8 +9002,8 @@
       <c r="F113" s="13"/>
       <c r="G113" s="13"/>
       <c r="H113" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I113" s="13"/>
       <c r="J113" s="13"/>
@@ -9046,8 +9046,8 @@
       <c r="F114" s="13"/>
       <c r="G114" s="13"/>
       <c r="H114" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I114" s="13"/>
       <c r="J114" s="13"/>
@@ -9090,8 +9090,8 @@
       <c r="F115" s="13"/>
       <c r="G115" s="13"/>
       <c r="H115" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I115" s="13"/>
       <c r="J115" s="13"/>
@@ -9134,8 +9134,8 @@
       <c r="F116" s="13"/>
       <c r="G116" s="13"/>
       <c r="H116" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I116" s="13"/>
       <c r="J116" s="13"/>
@@ -9178,8 +9178,8 @@
       <c r="F117" s="13"/>
       <c r="G117" s="13"/>
       <c r="H117" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I117" s="13"/>
       <c r="J117" s="13"/>
@@ -9222,8 +9222,8 @@
       <c r="F118" s="13"/>
       <c r="G118" s="13"/>
       <c r="H118" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I118" s="13"/>
       <c r="J118" s="13"/>
@@ -9266,8 +9266,8 @@
       <c r="F119" s="13"/>
       <c r="G119" s="13"/>
       <c r="H119" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I119" s="13"/>
       <c r="J119" s="13"/>
@@ -9310,8 +9310,8 @@
       <c r="F120" s="13"/>
       <c r="G120" s="13"/>
       <c r="H120" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I120" s="13"/>
       <c r="J120" s="13"/>
@@ -9354,8 +9354,8 @@
       <c r="F121" s="13"/>
       <c r="G121" s="13"/>
       <c r="H121" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I121" s="13"/>
       <c r="J121" s="13"/>
@@ -9398,8 +9398,8 @@
       <c r="F122" s="13"/>
       <c r="G122" s="13"/>
       <c r="H122" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I122" s="13"/>
       <c r="J122" s="13"/>
@@ -9442,8 +9442,8 @@
       <c r="F123" s="13"/>
       <c r="G123" s="13"/>
       <c r="H123" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I123" s="13"/>
       <c r="J123" s="13"/>
@@ -9486,8 +9486,8 @@
       <c r="F124" s="13"/>
       <c r="G124" s="13"/>
       <c r="H124" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I124" s="13"/>
       <c r="J124" s="13"/>
@@ -9530,8 +9530,8 @@
       <c r="F125" s="13"/>
       <c r="G125" s="13"/>
       <c r="H125" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I125" s="13"/>
       <c r="J125" s="13"/>
@@ -9574,8 +9574,8 @@
       <c r="F126" s="13"/>
       <c r="G126" s="13"/>
       <c r="H126" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I126" s="13"/>
       <c r="J126" s="13"/>
@@ -9618,8 +9618,8 @@
       <c r="F127" s="13"/>
       <c r="G127" s="13"/>
       <c r="H127" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I127" s="13"/>
       <c r="J127" s="13"/>
@@ -9662,8 +9662,8 @@
       <c r="F128" s="13"/>
       <c r="G128" s="13"/>
       <c r="H128" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I128" s="13"/>
       <c r="J128" s="13"/>
@@ -9706,8 +9706,8 @@
       <c r="F129" s="13"/>
       <c r="G129" s="13"/>
       <c r="H129" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I129" s="13"/>
       <c r="J129" s="13"/>
@@ -9750,8 +9750,8 @@
       <c r="F130" s="13"/>
       <c r="G130" s="13"/>
       <c r="H130" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I130" s="13"/>
       <c r="J130" s="13"/>
@@ -9794,8 +9794,8 @@
       <c r="F131" s="13"/>
       <c r="G131" s="13"/>
       <c r="H131" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I131" s="13"/>
       <c r="J131" s="13"/>
@@ -9838,8 +9838,8 @@
       <c r="F132" s="13"/>
       <c r="G132" s="13"/>
       <c r="H132" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I132" s="13"/>
       <c r="J132" s="13"/>
@@ -9882,8 +9882,8 @@
       <c r="F133" s="13"/>
       <c r="G133" s="13"/>
       <c r="H133" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I133" s="13"/>
       <c r="J133" s="13"/>
@@ -9926,8 +9926,8 @@
       <c r="F134" s="13"/>
       <c r="G134" s="13"/>
       <c r="H134" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I134" s="13"/>
       <c r="J134" s="13"/>
@@ -9970,8 +9970,8 @@
       <c r="F135" s="13"/>
       <c r="G135" s="13"/>
       <c r="H135" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I135" s="13"/>
       <c r="J135" s="13"/>
@@ -10014,8 +10014,8 @@
       <c r="F136" s="13"/>
       <c r="G136" s="13"/>
       <c r="H136" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I136" s="13"/>
       <c r="J136" s="13"/>
@@ -10058,8 +10058,8 @@
       <c r="F137" s="13"/>
       <c r="G137" s="13"/>
       <c r="H137" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I137" s="13"/>
       <c r="J137" s="13"/>
@@ -10102,8 +10102,8 @@
       <c r="F138" s="13"/>
       <c r="G138" s="13"/>
       <c r="H138" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I138" s="13"/>
       <c r="J138" s="13"/>
@@ -10146,8 +10146,8 @@
       <c r="F139" s="13"/>
       <c r="G139" s="13"/>
       <c r="H139" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" ref="H139:H202" si="3">L139&amp;"có hình dáng dạng "&amp;M139&amp;" chất liệu "&amp;N139&amp;" thành phần hóa chất: "&amp;O139&amp;" có kích thước "&amp;P139&amp;" dùng để "&amp;R139&amp;" cho "&amp;Q139</f>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I139" s="13"/>
       <c r="J139" s="13"/>
@@ -10191,7 +10191,7 @@
       <c r="G140" s="13"/>
       <c r="H140" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I140" s="13"/>
       <c r="J140" s="13"/>
@@ -10235,7 +10235,7 @@
       <c r="G141" s="13"/>
       <c r="H141" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I141" s="13"/>
       <c r="J141" s="13"/>
@@ -10279,7 +10279,7 @@
       <c r="G142" s="13"/>
       <c r="H142" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I142" s="13"/>
       <c r="J142" s="13"/>
@@ -10323,7 +10323,7 @@
       <c r="G143" s="13"/>
       <c r="H143" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I143" s="13"/>
       <c r="J143" s="13"/>
@@ -10367,7 +10367,7 @@
       <c r="G144" s="13"/>
       <c r="H144" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I144" s="13"/>
       <c r="J144" s="13"/>
@@ -10411,7 +10411,7 @@
       <c r="G145" s="13"/>
       <c r="H145" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I145" s="13"/>
       <c r="J145" s="13"/>
@@ -10455,7 +10455,7 @@
       <c r="G146" s="13"/>
       <c r="H146" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I146" s="13"/>
       <c r="J146" s="13"/>
@@ -10499,7 +10499,7 @@
       <c r="G147" s="13"/>
       <c r="H147" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I147" s="13"/>
       <c r="J147" s="13"/>
@@ -10543,7 +10543,7 @@
       <c r="G148" s="13"/>
       <c r="H148" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I148" s="13"/>
       <c r="J148" s="13"/>
@@ -10587,7 +10587,7 @@
       <c r="G149" s="13"/>
       <c r="H149" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I149" s="13"/>
       <c r="J149" s="13"/>
@@ -10631,7 +10631,7 @@
       <c r="G150" s="13"/>
       <c r="H150" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I150" s="13"/>
       <c r="J150" s="13"/>
@@ -10675,7 +10675,7 @@
       <c r="G151" s="13"/>
       <c r="H151" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I151" s="13"/>
       <c r="J151" s="13"/>
@@ -10719,7 +10719,7 @@
       <c r="G152" s="13"/>
       <c r="H152" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I152" s="13"/>
       <c r="J152" s="13"/>
@@ -10763,7 +10763,7 @@
       <c r="G153" s="13"/>
       <c r="H153" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I153" s="13"/>
       <c r="J153" s="13"/>
@@ -10807,7 +10807,7 @@
       <c r="G154" s="13"/>
       <c r="H154" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I154" s="13"/>
       <c r="J154" s="13"/>
@@ -10851,7 +10851,7 @@
       <c r="G155" s="13"/>
       <c r="H155" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I155" s="13"/>
       <c r="J155" s="13"/>
@@ -10895,7 +10895,7 @@
       <c r="G156" s="13"/>
       <c r="H156" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I156" s="13"/>
       <c r="J156" s="13"/>
@@ -10939,7 +10939,7 @@
       <c r="G157" s="13"/>
       <c r="H157" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I157" s="13"/>
       <c r="J157" s="13"/>
@@ -10982,8 +10982,8 @@
       <c r="F158" s="13"/>
       <c r="G158" s="13"/>
       <c r="H158" s="12" t="str">
-        <f t="shared" ref="H158:H221" si="4">M158&amp;" "&amp;N158&amp;" "&amp;O158&amp;""&amp;P158&amp;" "&amp;Q158&amp;" "&amp;R158</f>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I158" s="13"/>
       <c r="J158" s="13"/>
@@ -11026,8 +11026,8 @@
       <c r="F159" s="13"/>
       <c r="G159" s="13"/>
       <c r="H159" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I159" s="13"/>
       <c r="J159" s="13"/>
@@ -11070,8 +11070,8 @@
       <c r="F160" s="13"/>
       <c r="G160" s="13"/>
       <c r="H160" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I160" s="13"/>
       <c r="J160" s="13"/>
@@ -11114,8 +11114,8 @@
       <c r="F161" s="13"/>
       <c r="G161" s="13"/>
       <c r="H161" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I161" s="13"/>
       <c r="J161" s="13"/>
@@ -11158,8 +11158,8 @@
       <c r="F162" s="13"/>
       <c r="G162" s="13"/>
       <c r="H162" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I162" s="13"/>
       <c r="J162" s="13"/>
@@ -11202,8 +11202,8 @@
       <c r="F163" s="13"/>
       <c r="G163" s="13"/>
       <c r="H163" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I163" s="13"/>
       <c r="J163" s="13"/>
@@ -11246,8 +11246,8 @@
       <c r="F164" s="13"/>
       <c r="G164" s="13"/>
       <c r="H164" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I164" s="13"/>
       <c r="J164" s="13"/>
@@ -11290,8 +11290,8 @@
       <c r="F165" s="13"/>
       <c r="G165" s="13"/>
       <c r="H165" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I165" s="13"/>
       <c r="J165" s="13"/>
@@ -11334,8 +11334,8 @@
       <c r="F166" s="13"/>
       <c r="G166" s="13"/>
       <c r="H166" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I166" s="13"/>
       <c r="J166" s="13"/>
@@ -11378,8 +11378,8 @@
       <c r="F167" s="13"/>
       <c r="G167" s="13"/>
       <c r="H167" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I167" s="13"/>
       <c r="J167" s="13"/>
@@ -11422,8 +11422,8 @@
       <c r="F168" s="13"/>
       <c r="G168" s="13"/>
       <c r="H168" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I168" s="13"/>
       <c r="J168" s="13"/>
@@ -11466,8 +11466,8 @@
       <c r="F169" s="13"/>
       <c r="G169" s="13"/>
       <c r="H169" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I169" s="13"/>
       <c r="J169" s="13"/>
@@ -11510,8 +11510,8 @@
       <c r="F170" s="13"/>
       <c r="G170" s="13"/>
       <c r="H170" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I170" s="13"/>
       <c r="J170" s="13"/>
@@ -11554,8 +11554,8 @@
       <c r="F171" s="13"/>
       <c r="G171" s="13"/>
       <c r="H171" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I171" s="13"/>
       <c r="J171" s="13"/>
@@ -11598,8 +11598,8 @@
       <c r="F172" s="13"/>
       <c r="G172" s="13"/>
       <c r="H172" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I172" s="13"/>
       <c r="J172" s="13"/>
@@ -11642,8 +11642,8 @@
       <c r="F173" s="13"/>
       <c r="G173" s="13"/>
       <c r="H173" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I173" s="13"/>
       <c r="J173" s="13"/>
@@ -11686,8 +11686,8 @@
       <c r="F174" s="13"/>
       <c r="G174" s="13"/>
       <c r="H174" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I174" s="13"/>
       <c r="J174" s="13"/>
@@ -11730,8 +11730,8 @@
       <c r="F175" s="13"/>
       <c r="G175" s="13"/>
       <c r="H175" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I175" s="13"/>
       <c r="J175" s="13"/>
@@ -11774,8 +11774,8 @@
       <c r="F176" s="13"/>
       <c r="G176" s="13"/>
       <c r="H176" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I176" s="13"/>
       <c r="J176" s="13"/>
@@ -11818,8 +11818,8 @@
       <c r="F177" s="13"/>
       <c r="G177" s="13"/>
       <c r="H177" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I177" s="13"/>
       <c r="J177" s="13"/>
@@ -11862,8 +11862,8 @@
       <c r="F178" s="13"/>
       <c r="G178" s="13"/>
       <c r="H178" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I178" s="13"/>
       <c r="J178" s="13"/>
@@ -11906,8 +11906,8 @@
       <c r="F179" s="13"/>
       <c r="G179" s="13"/>
       <c r="H179" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I179" s="13"/>
       <c r="J179" s="13"/>
@@ -11950,8 +11950,8 @@
       <c r="F180" s="13"/>
       <c r="G180" s="13"/>
       <c r="H180" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I180" s="13"/>
       <c r="J180" s="13"/>
@@ -11994,8 +11994,8 @@
       <c r="F181" s="13"/>
       <c r="G181" s="13"/>
       <c r="H181" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I181" s="13"/>
       <c r="J181" s="13"/>
@@ -12038,8 +12038,8 @@
       <c r="F182" s="13"/>
       <c r="G182" s="13"/>
       <c r="H182" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I182" s="13"/>
       <c r="J182" s="13"/>
@@ -12082,8 +12082,8 @@
       <c r="F183" s="13"/>
       <c r="G183" s="13"/>
       <c r="H183" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I183" s="13"/>
       <c r="J183" s="13"/>
@@ -12126,8 +12126,8 @@
       <c r="F184" s="13"/>
       <c r="G184" s="13"/>
       <c r="H184" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I184" s="13"/>
       <c r="J184" s="13"/>
@@ -12170,8 +12170,8 @@
       <c r="F185" s="13"/>
       <c r="G185" s="13"/>
       <c r="H185" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I185" s="13"/>
       <c r="J185" s="13"/>
@@ -12214,8 +12214,8 @@
       <c r="F186" s="13"/>
       <c r="G186" s="13"/>
       <c r="H186" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I186" s="13"/>
       <c r="J186" s="13"/>
@@ -12258,8 +12258,8 @@
       <c r="F187" s="13"/>
       <c r="G187" s="13"/>
       <c r="H187" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I187" s="13"/>
       <c r="J187" s="13"/>
@@ -12302,8 +12302,8 @@
       <c r="F188" s="13"/>
       <c r="G188" s="13"/>
       <c r="H188" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I188" s="13"/>
       <c r="J188" s="13"/>
@@ -12346,8 +12346,8 @@
       <c r="F189" s="13"/>
       <c r="G189" s="13"/>
       <c r="H189" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I189" s="13"/>
       <c r="J189" s="13"/>
@@ -12390,8 +12390,8 @@
       <c r="F190" s="13"/>
       <c r="G190" s="13"/>
       <c r="H190" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I190" s="13"/>
       <c r="J190" s="13"/>
@@ -12434,8 +12434,8 @@
       <c r="F191" s="13"/>
       <c r="G191" s="13"/>
       <c r="H191" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I191" s="13"/>
       <c r="J191" s="13"/>
@@ -12478,8 +12478,8 @@
       <c r="F192" s="13"/>
       <c r="G192" s="13"/>
       <c r="H192" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I192" s="13"/>
       <c r="J192" s="13"/>
@@ -12522,8 +12522,8 @@
       <c r="F193" s="13"/>
       <c r="G193" s="13"/>
       <c r="H193" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I193" s="13"/>
       <c r="J193" s="13"/>
@@ -12566,8 +12566,8 @@
       <c r="F194" s="13"/>
       <c r="G194" s="13"/>
       <c r="H194" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I194" s="13"/>
       <c r="J194" s="13"/>
@@ -12610,8 +12610,8 @@
       <c r="F195" s="13"/>
       <c r="G195" s="13"/>
       <c r="H195" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I195" s="13"/>
       <c r="J195" s="13"/>
@@ -12654,8 +12654,8 @@
       <c r="F196" s="13"/>
       <c r="G196" s="13"/>
       <c r="H196" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I196" s="13"/>
       <c r="J196" s="13"/>
@@ -12698,8 +12698,8 @@
       <c r="F197" s="13"/>
       <c r="G197" s="13"/>
       <c r="H197" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I197" s="13"/>
       <c r="J197" s="13"/>
@@ -12742,8 +12742,8 @@
       <c r="F198" s="13"/>
       <c r="G198" s="13"/>
       <c r="H198" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I198" s="13"/>
       <c r="J198" s="13"/>
@@ -12786,8 +12786,8 @@
       <c r="F199" s="13"/>
       <c r="G199" s="13"/>
       <c r="H199" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I199" s="13"/>
       <c r="J199" s="13"/>
@@ -12830,8 +12830,8 @@
       <c r="F200" s="13"/>
       <c r="G200" s="13"/>
       <c r="H200" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I200" s="13"/>
       <c r="J200" s="13"/>
@@ -12874,8 +12874,8 @@
       <c r="F201" s="13"/>
       <c r="G201" s="13"/>
       <c r="H201" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I201" s="13"/>
       <c r="J201" s="13"/>
@@ -12918,8 +12918,8 @@
       <c r="F202" s="13"/>
       <c r="G202" s="13"/>
       <c r="H202" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="3"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I202" s="13"/>
       <c r="J202" s="13"/>
@@ -12962,8 +12962,8 @@
       <c r="F203" s="13"/>
       <c r="G203" s="13"/>
       <c r="H203" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" ref="H203:H266" si="4">L203&amp;"có hình dáng dạng "&amp;M203&amp;" chất liệu "&amp;N203&amp;" thành phần hóa chất: "&amp;O203&amp;" có kích thước "&amp;P203&amp;" dùng để "&amp;R203&amp;" cho "&amp;Q203</f>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I203" s="13"/>
       <c r="J203" s="13"/>
@@ -13007,7 +13007,7 @@
       <c r="G204" s="13"/>
       <c r="H204" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I204" s="13"/>
       <c r="J204" s="13"/>
@@ -13051,7 +13051,7 @@
       <c r="G205" s="13"/>
       <c r="H205" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I205" s="13"/>
       <c r="J205" s="13"/>
@@ -13095,7 +13095,7 @@
       <c r="G206" s="13"/>
       <c r="H206" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I206" s="13"/>
       <c r="J206" s="13"/>
@@ -13139,7 +13139,7 @@
       <c r="G207" s="13"/>
       <c r="H207" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I207" s="13"/>
       <c r="J207" s="13"/>
@@ -13183,7 +13183,7 @@
       <c r="G208" s="13"/>
       <c r="H208" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I208" s="13"/>
       <c r="J208" s="13"/>
@@ -13227,7 +13227,7 @@
       <c r="G209" s="13"/>
       <c r="H209" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I209" s="13"/>
       <c r="J209" s="13"/>
@@ -13271,7 +13271,7 @@
       <c r="G210" s="13"/>
       <c r="H210" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I210" s="13"/>
       <c r="J210" s="13"/>
@@ -13315,7 +13315,7 @@
       <c r="G211" s="13"/>
       <c r="H211" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I211" s="13"/>
       <c r="J211" s="13"/>
@@ -13359,7 +13359,7 @@
       <c r="G212" s="13"/>
       <c r="H212" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I212" s="13"/>
       <c r="J212" s="13"/>
@@ -13403,7 +13403,7 @@
       <c r="G213" s="13"/>
       <c r="H213" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I213" s="13"/>
       <c r="J213" s="13"/>
@@ -13447,7 +13447,7 @@
       <c r="G214" s="13"/>
       <c r="H214" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I214" s="13"/>
       <c r="J214" s="13"/>
@@ -13491,7 +13491,7 @@
       <c r="G215" s="13"/>
       <c r="H215" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I215" s="13"/>
       <c r="J215" s="13"/>
@@ -13535,7 +13535,7 @@
       <c r="G216" s="13"/>
       <c r="H216" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I216" s="13"/>
       <c r="J216" s="13"/>
@@ -13579,7 +13579,7 @@
       <c r="G217" s="13"/>
       <c r="H217" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I217" s="13"/>
       <c r="J217" s="13"/>
@@ -13623,7 +13623,7 @@
       <c r="G218" s="13"/>
       <c r="H218" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I218" s="13"/>
       <c r="J218" s="13"/>
@@ -13667,7 +13667,7 @@
       <c r="G219" s="13"/>
       <c r="H219" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I219" s="13"/>
       <c r="J219" s="13"/>
@@ -13711,7 +13711,7 @@
       <c r="G220" s="13"/>
       <c r="H220" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I220" s="13"/>
       <c r="J220" s="13"/>
@@ -13755,7 +13755,7 @@
       <c r="G221" s="13"/>
       <c r="H221" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I221" s="13"/>
       <c r="J221" s="13"/>
@@ -13798,8 +13798,8 @@
       <c r="F222" s="13"/>
       <c r="G222" s="13"/>
       <c r="H222" s="12" t="str">
-        <f t="shared" ref="H222:H285" si="5">M222&amp;" "&amp;N222&amp;" "&amp;O222&amp;""&amp;P222&amp;" "&amp;Q222&amp;" "&amp;R222</f>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I222" s="13"/>
       <c r="J222" s="13"/>
@@ -13842,8 +13842,8 @@
       <c r="F223" s="13"/>
       <c r="G223" s="13"/>
       <c r="H223" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I223" s="13"/>
       <c r="J223" s="13"/>
@@ -13886,8 +13886,8 @@
       <c r="F224" s="13"/>
       <c r="G224" s="13"/>
       <c r="H224" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I224" s="13"/>
       <c r="J224" s="13"/>
@@ -13930,8 +13930,8 @@
       <c r="F225" s="13"/>
       <c r="G225" s="13"/>
       <c r="H225" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I225" s="13"/>
       <c r="J225" s="13"/>
@@ -13974,8 +13974,8 @@
       <c r="F226" s="13"/>
       <c r="G226" s="13"/>
       <c r="H226" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I226" s="13"/>
       <c r="J226" s="13"/>
@@ -14018,8 +14018,8 @@
       <c r="F227" s="13"/>
       <c r="G227" s="13"/>
       <c r="H227" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I227" s="13"/>
       <c r="J227" s="13"/>
@@ -14062,8 +14062,8 @@
       <c r="F228" s="13"/>
       <c r="G228" s="13"/>
       <c r="H228" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I228" s="13"/>
       <c r="J228" s="13"/>
@@ -14106,8 +14106,8 @@
       <c r="F229" s="13"/>
       <c r="G229" s="13"/>
       <c r="H229" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I229" s="13"/>
       <c r="J229" s="13"/>
@@ -14150,8 +14150,8 @@
       <c r="F230" s="13"/>
       <c r="G230" s="13"/>
       <c r="H230" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I230" s="13"/>
       <c r="J230" s="13"/>
@@ -14194,8 +14194,8 @@
       <c r="F231" s="13"/>
       <c r="G231" s="13"/>
       <c r="H231" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I231" s="13"/>
       <c r="J231" s="13"/>
@@ -14238,8 +14238,8 @@
       <c r="F232" s="13"/>
       <c r="G232" s="13"/>
       <c r="H232" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I232" s="13"/>
       <c r="J232" s="13"/>
@@ -14282,8 +14282,8 @@
       <c r="F233" s="13"/>
       <c r="G233" s="13"/>
       <c r="H233" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I233" s="13"/>
       <c r="J233" s="13"/>
@@ -14326,8 +14326,8 @@
       <c r="F234" s="13"/>
       <c r="G234" s="13"/>
       <c r="H234" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I234" s="13"/>
       <c r="J234" s="13"/>
@@ -14370,8 +14370,8 @@
       <c r="F235" s="13"/>
       <c r="G235" s="13"/>
       <c r="H235" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I235" s="13"/>
       <c r="J235" s="13"/>
@@ -14414,8 +14414,8 @@
       <c r="F236" s="13"/>
       <c r="G236" s="13"/>
       <c r="H236" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I236" s="13"/>
       <c r="J236" s="13"/>
@@ -14458,8 +14458,8 @@
       <c r="F237" s="13"/>
       <c r="G237" s="13"/>
       <c r="H237" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I237" s="13"/>
       <c r="J237" s="13"/>
@@ -14502,8 +14502,8 @@
       <c r="F238" s="13"/>
       <c r="G238" s="13"/>
       <c r="H238" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I238" s="13"/>
       <c r="J238" s="13"/>
@@ -14546,8 +14546,8 @@
       <c r="F239" s="13"/>
       <c r="G239" s="13"/>
       <c r="H239" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I239" s="13"/>
       <c r="J239" s="13"/>
@@ -14590,8 +14590,8 @@
       <c r="F240" s="13"/>
       <c r="G240" s="13"/>
       <c r="H240" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I240" s="13"/>
       <c r="J240" s="13"/>
@@ -14634,8 +14634,8 @@
       <c r="F241" s="13"/>
       <c r="G241" s="13"/>
       <c r="H241" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I241" s="13"/>
       <c r="J241" s="13"/>
@@ -14678,8 +14678,8 @@
       <c r="F242" s="13"/>
       <c r="G242" s="13"/>
       <c r="H242" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I242" s="13"/>
       <c r="J242" s="13"/>
@@ -14722,8 +14722,8 @@
       <c r="F243" s="13"/>
       <c r="G243" s="13"/>
       <c r="H243" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I243" s="13"/>
       <c r="J243" s="13"/>
@@ -14766,8 +14766,8 @@
       <c r="F244" s="13"/>
       <c r="G244" s="13"/>
       <c r="H244" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I244" s="13"/>
       <c r="J244" s="13"/>
@@ -14810,8 +14810,8 @@
       <c r="F245" s="13"/>
       <c r="G245" s="13"/>
       <c r="H245" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I245" s="13"/>
       <c r="J245" s="13"/>
@@ -14854,8 +14854,8 @@
       <c r="F246" s="13"/>
       <c r="G246" s="13"/>
       <c r="H246" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I246" s="13"/>
       <c r="J246" s="13"/>
@@ -14898,8 +14898,8 @@
       <c r="F247" s="13"/>
       <c r="G247" s="13"/>
       <c r="H247" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I247" s="13"/>
       <c r="J247" s="13"/>
@@ -14942,8 +14942,8 @@
       <c r="F248" s="13"/>
       <c r="G248" s="13"/>
       <c r="H248" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I248" s="13"/>
       <c r="J248" s="13"/>
@@ -14986,8 +14986,8 @@
       <c r="F249" s="13"/>
       <c r="G249" s="13"/>
       <c r="H249" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I249" s="13"/>
       <c r="J249" s="13"/>
@@ -15030,8 +15030,8 @@
       <c r="F250" s="13"/>
       <c r="G250" s="13"/>
       <c r="H250" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I250" s="13"/>
       <c r="J250" s="13"/>
@@ -15074,8 +15074,8 @@
       <c r="F251" s="13"/>
       <c r="G251" s="13"/>
       <c r="H251" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I251" s="13"/>
       <c r="J251" s="13"/>
@@ -15118,8 +15118,8 @@
       <c r="F252" s="13"/>
       <c r="G252" s="13"/>
       <c r="H252" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I252" s="13"/>
       <c r="J252" s="13"/>
@@ -15162,8 +15162,8 @@
       <c r="F253" s="13"/>
       <c r="G253" s="13"/>
       <c r="H253" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I253" s="13"/>
       <c r="J253" s="13"/>
@@ -15206,8 +15206,8 @@
       <c r="F254" s="13"/>
       <c r="G254" s="13"/>
       <c r="H254" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I254" s="13"/>
       <c r="J254" s="13"/>
@@ -15250,8 +15250,8 @@
       <c r="F255" s="13"/>
       <c r="G255" s="13"/>
       <c r="H255" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I255" s="13"/>
       <c r="J255" s="13"/>
@@ -15294,8 +15294,8 @@
       <c r="F256" s="13"/>
       <c r="G256" s="13"/>
       <c r="H256" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I256" s="13"/>
       <c r="J256" s="13"/>
@@ -15338,8 +15338,8 @@
       <c r="F257" s="13"/>
       <c r="G257" s="13"/>
       <c r="H257" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I257" s="13"/>
       <c r="J257" s="13"/>
@@ -15382,8 +15382,8 @@
       <c r="F258" s="13"/>
       <c r="G258" s="13"/>
       <c r="H258" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I258" s="13"/>
       <c r="J258" s="13"/>
@@ -15426,8 +15426,8 @@
       <c r="F259" s="13"/>
       <c r="G259" s="13"/>
       <c r="H259" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I259" s="13"/>
       <c r="J259" s="13"/>
@@ -15470,8 +15470,8 @@
       <c r="F260" s="13"/>
       <c r="G260" s="13"/>
       <c r="H260" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I260" s="13"/>
       <c r="J260" s="13"/>
@@ -15514,8 +15514,8 @@
       <c r="F261" s="13"/>
       <c r="G261" s="13"/>
       <c r="H261" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I261" s="13"/>
       <c r="J261" s="13"/>
@@ -15558,8 +15558,8 @@
       <c r="F262" s="13"/>
       <c r="G262" s="13"/>
       <c r="H262" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I262" s="13"/>
       <c r="J262" s="13"/>
@@ -15602,8 +15602,8 @@
       <c r="F263" s="13"/>
       <c r="G263" s="13"/>
       <c r="H263" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I263" s="13"/>
       <c r="J263" s="13"/>
@@ -15646,8 +15646,8 @@
       <c r="F264" s="13"/>
       <c r="G264" s="13"/>
       <c r="H264" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I264" s="13"/>
       <c r="J264" s="13"/>
@@ -15690,8 +15690,8 @@
       <c r="F265" s="13"/>
       <c r="G265" s="13"/>
       <c r="H265" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I265" s="13"/>
       <c r="J265" s="13"/>
@@ -15734,8 +15734,8 @@
       <c r="F266" s="13"/>
       <c r="G266" s="13"/>
       <c r="H266" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="4"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I266" s="13"/>
       <c r="J266" s="13"/>
@@ -15778,8 +15778,8 @@
       <c r="F267" s="13"/>
       <c r="G267" s="13"/>
       <c r="H267" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" ref="H267:H330" si="5">L267&amp;"có hình dáng dạng "&amp;M267&amp;" chất liệu "&amp;N267&amp;" thành phần hóa chất: "&amp;O267&amp;" có kích thước "&amp;P267&amp;" dùng để "&amp;R267&amp;" cho "&amp;Q267</f>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I267" s="13"/>
       <c r="J267" s="13"/>
@@ -15823,7 +15823,7 @@
       <c r="G268" s="13"/>
       <c r="H268" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I268" s="13"/>
       <c r="J268" s="13"/>
@@ -15867,7 +15867,7 @@
       <c r="G269" s="13"/>
       <c r="H269" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I269" s="13"/>
       <c r="J269" s="13"/>
@@ -15911,7 +15911,7 @@
       <c r="G270" s="13"/>
       <c r="H270" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I270" s="13"/>
       <c r="J270" s="13"/>
@@ -15955,7 +15955,7 @@
       <c r="G271" s="13"/>
       <c r="H271" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I271" s="13"/>
       <c r="J271" s="13"/>
@@ -15999,7 +15999,7 @@
       <c r="G272" s="13"/>
       <c r="H272" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I272" s="13"/>
       <c r="J272" s="13"/>
@@ -16043,7 +16043,7 @@
       <c r="G273" s="13"/>
       <c r="H273" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I273" s="13"/>
       <c r="J273" s="13"/>
@@ -16087,7 +16087,7 @@
       <c r="G274" s="13"/>
       <c r="H274" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I274" s="13"/>
       <c r="J274" s="13"/>
@@ -16131,7 +16131,7 @@
       <c r="G275" s="13"/>
       <c r="H275" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I275" s="13"/>
       <c r="J275" s="13"/>
@@ -16175,7 +16175,7 @@
       <c r="G276" s="13"/>
       <c r="H276" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I276" s="13"/>
       <c r="J276" s="13"/>
@@ -16219,7 +16219,7 @@
       <c r="G277" s="13"/>
       <c r="H277" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I277" s="13"/>
       <c r="J277" s="13"/>
@@ -16263,7 +16263,7 @@
       <c r="G278" s="13"/>
       <c r="H278" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I278" s="13"/>
       <c r="J278" s="13"/>
@@ -16307,7 +16307,7 @@
       <c r="G279" s="13"/>
       <c r="H279" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I279" s="13"/>
       <c r="J279" s="13"/>
@@ -16351,7 +16351,7 @@
       <c r="G280" s="13"/>
       <c r="H280" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I280" s="13"/>
       <c r="J280" s="13"/>
@@ -16395,7 +16395,7 @@
       <c r="G281" s="13"/>
       <c r="H281" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I281" s="13"/>
       <c r="J281" s="13"/>
@@ -16439,7 +16439,7 @@
       <c r="G282" s="13"/>
       <c r="H282" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I282" s="13"/>
       <c r="J282" s="13"/>
@@ -16483,7 +16483,7 @@
       <c r="G283" s="13"/>
       <c r="H283" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I283" s="13"/>
       <c r="J283" s="13"/>
@@ -16527,7 +16527,7 @@
       <c r="G284" s="13"/>
       <c r="H284" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I284" s="13"/>
       <c r="J284" s="13"/>
@@ -16571,7 +16571,7 @@
       <c r="G285" s="13"/>
       <c r="H285" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I285" s="13"/>
       <c r="J285" s="13"/>
@@ -16614,8 +16614,8 @@
       <c r="F286" s="13"/>
       <c r="G286" s="13"/>
       <c r="H286" s="12" t="str">
-        <f t="shared" ref="H286:H349" si="6">M286&amp;" "&amp;N286&amp;" "&amp;O286&amp;""&amp;P286&amp;" "&amp;Q286&amp;" "&amp;R286</f>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I286" s="13"/>
       <c r="J286" s="13"/>
@@ -16658,8 +16658,8 @@
       <c r="F287" s="13"/>
       <c r="G287" s="13"/>
       <c r="H287" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I287" s="13"/>
       <c r="J287" s="13"/>
@@ -16702,8 +16702,8 @@
       <c r="F288" s="13"/>
       <c r="G288" s="13"/>
       <c r="H288" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I288" s="13"/>
       <c r="J288" s="13"/>
@@ -16746,8 +16746,8 @@
       <c r="F289" s="13"/>
       <c r="G289" s="13"/>
       <c r="H289" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I289" s="13"/>
       <c r="J289" s="13"/>
@@ -16790,8 +16790,8 @@
       <c r="F290" s="13"/>
       <c r="G290" s="13"/>
       <c r="H290" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I290" s="13"/>
       <c r="J290" s="13"/>
@@ -16834,8 +16834,8 @@
       <c r="F291" s="13"/>
       <c r="G291" s="13"/>
       <c r="H291" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I291" s="13"/>
       <c r="J291" s="13"/>
@@ -16878,8 +16878,8 @@
       <c r="F292" s="13"/>
       <c r="G292" s="13"/>
       <c r="H292" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I292" s="13"/>
       <c r="J292" s="13"/>
@@ -16922,8 +16922,8 @@
       <c r="F293" s="13"/>
       <c r="G293" s="13"/>
       <c r="H293" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I293" s="13"/>
       <c r="J293" s="13"/>
@@ -16966,8 +16966,8 @@
       <c r="F294" s="13"/>
       <c r="G294" s="13"/>
       <c r="H294" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I294" s="13"/>
       <c r="J294" s="13"/>
@@ -17010,8 +17010,8 @@
       <c r="F295" s="13"/>
       <c r="G295" s="13"/>
       <c r="H295" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I295" s="13"/>
       <c r="J295" s="13"/>
@@ -17054,8 +17054,8 @@
       <c r="F296" s="13"/>
       <c r="G296" s="13"/>
       <c r="H296" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I296" s="13"/>
       <c r="J296" s="13"/>
@@ -17098,8 +17098,8 @@
       <c r="F297" s="13"/>
       <c r="G297" s="13"/>
       <c r="H297" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I297" s="13"/>
       <c r="J297" s="13"/>
@@ -17142,8 +17142,8 @@
       <c r="F298" s="13"/>
       <c r="G298" s="13"/>
       <c r="H298" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I298" s="13"/>
       <c r="J298" s="13"/>
@@ -17186,8 +17186,8 @@
       <c r="F299" s="13"/>
       <c r="G299" s="13"/>
       <c r="H299" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I299" s="13"/>
       <c r="J299" s="13"/>
@@ -17230,8 +17230,8 @@
       <c r="F300" s="13"/>
       <c r="G300" s="13"/>
       <c r="H300" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I300" s="13"/>
       <c r="J300" s="13"/>
@@ -17274,8 +17274,8 @@
       <c r="F301" s="13"/>
       <c r="G301" s="13"/>
       <c r="H301" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I301" s="13"/>
       <c r="J301" s="13"/>
@@ -17318,8 +17318,8 @@
       <c r="F302" s="13"/>
       <c r="G302" s="13"/>
       <c r="H302" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I302" s="13"/>
       <c r="J302" s="13"/>
@@ -17362,8 +17362,8 @@
       <c r="F303" s="13"/>
       <c r="G303" s="13"/>
       <c r="H303" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I303" s="13"/>
       <c r="J303" s="13"/>
@@ -17406,8 +17406,8 @@
       <c r="F304" s="13"/>
       <c r="G304" s="13"/>
       <c r="H304" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I304" s="13"/>
       <c r="J304" s="13"/>
@@ -17450,8 +17450,8 @@
       <c r="F305" s="13"/>
       <c r="G305" s="13"/>
       <c r="H305" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I305" s="13"/>
       <c r="J305" s="13"/>
@@ -17494,8 +17494,8 @@
       <c r="F306" s="13"/>
       <c r="G306" s="13"/>
       <c r="H306" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I306" s="13"/>
       <c r="J306" s="13"/>
@@ -17538,8 +17538,8 @@
       <c r="F307" s="13"/>
       <c r="G307" s="13"/>
       <c r="H307" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I307" s="13"/>
       <c r="J307" s="13"/>
@@ -17582,8 +17582,8 @@
       <c r="F308" s="13"/>
       <c r="G308" s="13"/>
       <c r="H308" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I308" s="13"/>
       <c r="J308" s="13"/>
@@ -17626,8 +17626,8 @@
       <c r="F309" s="13"/>
       <c r="G309" s="13"/>
       <c r="H309" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I309" s="13"/>
       <c r="J309" s="13"/>
@@ -17670,8 +17670,8 @@
       <c r="F310" s="13"/>
       <c r="G310" s="13"/>
       <c r="H310" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I310" s="13"/>
       <c r="J310" s="13"/>
@@ -17714,8 +17714,8 @@
       <c r="F311" s="13"/>
       <c r="G311" s="13"/>
       <c r="H311" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I311" s="13"/>
       <c r="J311" s="13"/>
@@ -17758,8 +17758,8 @@
       <c r="F312" s="13"/>
       <c r="G312" s="13"/>
       <c r="H312" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I312" s="13"/>
       <c r="J312" s="13"/>
@@ -17802,8 +17802,8 @@
       <c r="F313" s="13"/>
       <c r="G313" s="13"/>
       <c r="H313" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I313" s="13"/>
       <c r="J313" s="13"/>
@@ -17846,8 +17846,8 @@
       <c r="F314" s="13"/>
       <c r="G314" s="13"/>
       <c r="H314" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I314" s="13"/>
       <c r="J314" s="13"/>
@@ -17890,8 +17890,8 @@
       <c r="F315" s="13"/>
       <c r="G315" s="13"/>
       <c r="H315" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I315" s="13"/>
       <c r="J315" s="13"/>
@@ -17934,8 +17934,8 @@
       <c r="F316" s="13"/>
       <c r="G316" s="13"/>
       <c r="H316" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I316" s="13"/>
       <c r="J316" s="13"/>
@@ -17978,8 +17978,8 @@
       <c r="F317" s="13"/>
       <c r="G317" s="13"/>
       <c r="H317" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I317" s="13"/>
       <c r="J317" s="13"/>
@@ -18022,8 +18022,8 @@
       <c r="F318" s="13"/>
       <c r="G318" s="13"/>
       <c r="H318" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I318" s="13"/>
       <c r="J318" s="13"/>
@@ -18066,8 +18066,8 @@
       <c r="F319" s="13"/>
       <c r="G319" s="13"/>
       <c r="H319" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I319" s="13"/>
       <c r="J319" s="13"/>
@@ -18110,8 +18110,8 @@
       <c r="F320" s="13"/>
       <c r="G320" s="13"/>
       <c r="H320" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I320" s="13"/>
       <c r="J320" s="13"/>
@@ -18154,8 +18154,8 @@
       <c r="F321" s="13"/>
       <c r="G321" s="13"/>
       <c r="H321" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I321" s="13"/>
       <c r="J321" s="13"/>
@@ -18198,8 +18198,8 @@
       <c r="F322" s="13"/>
       <c r="G322" s="13"/>
       <c r="H322" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I322" s="13"/>
       <c r="J322" s="13"/>
@@ -18242,8 +18242,8 @@
       <c r="F323" s="13"/>
       <c r="G323" s="13"/>
       <c r="H323" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I323" s="13"/>
       <c r="J323" s="13"/>
@@ -18286,8 +18286,8 @@
       <c r="F324" s="13"/>
       <c r="G324" s="13"/>
       <c r="H324" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I324" s="13"/>
       <c r="J324" s="13"/>
@@ -18330,8 +18330,8 @@
       <c r="F325" s="13"/>
       <c r="G325" s="13"/>
       <c r="H325" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I325" s="13"/>
       <c r="J325" s="13"/>
@@ -18374,8 +18374,8 @@
       <c r="F326" s="13"/>
       <c r="G326" s="13"/>
       <c r="H326" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I326" s="13"/>
       <c r="J326" s="13"/>
@@ -18418,8 +18418,8 @@
       <c r="F327" s="13"/>
       <c r="G327" s="13"/>
       <c r="H327" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I327" s="13"/>
       <c r="J327" s="13"/>
@@ -18462,8 +18462,8 @@
       <c r="F328" s="13"/>
       <c r="G328" s="13"/>
       <c r="H328" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I328" s="13"/>
       <c r="J328" s="13"/>
@@ -18506,8 +18506,8 @@
       <c r="F329" s="13"/>
       <c r="G329" s="13"/>
       <c r="H329" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I329" s="13"/>
       <c r="J329" s="13"/>
@@ -18550,8 +18550,8 @@
       <c r="F330" s="13"/>
       <c r="G330" s="13"/>
       <c r="H330" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="5"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I330" s="13"/>
       <c r="J330" s="13"/>
@@ -18594,8 +18594,8 @@
       <c r="F331" s="13"/>
       <c r="G331" s="13"/>
       <c r="H331" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" ref="H331:H394" si="6">L331&amp;"có hình dáng dạng "&amp;M331&amp;" chất liệu "&amp;N331&amp;" thành phần hóa chất: "&amp;O331&amp;" có kích thước "&amp;P331&amp;" dùng để "&amp;R331&amp;" cho "&amp;Q331</f>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I331" s="13"/>
       <c r="J331" s="13"/>
@@ -18639,7 +18639,7 @@
       <c r="G332" s="13"/>
       <c r="H332" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I332" s="13"/>
       <c r="J332" s="13"/>
@@ -18683,7 +18683,7 @@
       <c r="G333" s="13"/>
       <c r="H333" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I333" s="13"/>
       <c r="J333" s="13"/>
@@ -18727,7 +18727,7 @@
       <c r="G334" s="13"/>
       <c r="H334" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I334" s="13"/>
       <c r="J334" s="13"/>
@@ -18771,7 +18771,7 @@
       <c r="G335" s="13"/>
       <c r="H335" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I335" s="13"/>
       <c r="J335" s="13"/>
@@ -18815,7 +18815,7 @@
       <c r="G336" s="13"/>
       <c r="H336" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I336" s="13"/>
       <c r="J336" s="13"/>
@@ -18859,7 +18859,7 @@
       <c r="G337" s="13"/>
       <c r="H337" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I337" s="13"/>
       <c r="J337" s="13"/>
@@ -18903,7 +18903,7 @@
       <c r="G338" s="13"/>
       <c r="H338" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I338" s="13"/>
       <c r="J338" s="13"/>
@@ -18947,7 +18947,7 @@
       <c r="G339" s="13"/>
       <c r="H339" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I339" s="13"/>
       <c r="J339" s="13"/>
@@ -18991,7 +18991,7 @@
       <c r="G340" s="13"/>
       <c r="H340" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I340" s="13"/>
       <c r="J340" s="13"/>
@@ -19035,7 +19035,7 @@
       <c r="G341" s="13"/>
       <c r="H341" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I341" s="13"/>
       <c r="J341" s="13"/>
@@ -19079,7 +19079,7 @@
       <c r="G342" s="13"/>
       <c r="H342" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I342" s="13"/>
       <c r="J342" s="13"/>
@@ -19123,7 +19123,7 @@
       <c r="G343" s="13"/>
       <c r="H343" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I343" s="13"/>
       <c r="J343" s="13"/>
@@ -19167,7 +19167,7 @@
       <c r="G344" s="13"/>
       <c r="H344" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I344" s="13"/>
       <c r="J344" s="13"/>
@@ -19211,7 +19211,7 @@
       <c r="G345" s="13"/>
       <c r="H345" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I345" s="13"/>
       <c r="J345" s="13"/>
@@ -19255,7 +19255,7 @@
       <c r="G346" s="13"/>
       <c r="H346" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I346" s="13"/>
       <c r="J346" s="13"/>
@@ -19299,7 +19299,7 @@
       <c r="G347" s="13"/>
       <c r="H347" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I347" s="13"/>
       <c r="J347" s="13"/>
@@ -19343,7 +19343,7 @@
       <c r="G348" s="13"/>
       <c r="H348" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I348" s="13"/>
       <c r="J348" s="13"/>
@@ -19387,7 +19387,7 @@
       <c r="G349" s="13"/>
       <c r="H349" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I349" s="13"/>
       <c r="J349" s="13"/>
@@ -19430,8 +19430,8 @@
       <c r="F350" s="13"/>
       <c r="G350" s="13"/>
       <c r="H350" s="12" t="str">
-        <f t="shared" ref="H350:H413" si="7">M350&amp;" "&amp;N350&amp;" "&amp;O350&amp;""&amp;P350&amp;" "&amp;Q350&amp;" "&amp;R350</f>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I350" s="13"/>
       <c r="J350" s="13"/>
@@ -19474,8 +19474,8 @@
       <c r="F351" s="13"/>
       <c r="G351" s="13"/>
       <c r="H351" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I351" s="13"/>
       <c r="J351" s="13"/>
@@ -19518,8 +19518,8 @@
       <c r="F352" s="13"/>
       <c r="G352" s="13"/>
       <c r="H352" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I352" s="13"/>
       <c r="J352" s="13"/>
@@ -19562,8 +19562,8 @@
       <c r="F353" s="13"/>
       <c r="G353" s="13"/>
       <c r="H353" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I353" s="13"/>
       <c r="J353" s="13"/>
@@ -19606,8 +19606,8 @@
       <c r="F354" s="13"/>
       <c r="G354" s="13"/>
       <c r="H354" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I354" s="13"/>
       <c r="J354" s="13"/>
@@ -19650,8 +19650,8 @@
       <c r="F355" s="13"/>
       <c r="G355" s="13"/>
       <c r="H355" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I355" s="13"/>
       <c r="J355" s="13"/>
@@ -19694,8 +19694,8 @@
       <c r="F356" s="13"/>
       <c r="G356" s="13"/>
       <c r="H356" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I356" s="13"/>
       <c r="J356" s="13"/>
@@ -19738,8 +19738,8 @@
       <c r="F357" s="13"/>
       <c r="G357" s="13"/>
       <c r="H357" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I357" s="13"/>
       <c r="J357" s="13"/>
@@ -19782,8 +19782,8 @@
       <c r="F358" s="13"/>
       <c r="G358" s="13"/>
       <c r="H358" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I358" s="13"/>
       <c r="J358" s="13"/>
@@ -19826,8 +19826,8 @@
       <c r="F359" s="13"/>
       <c r="G359" s="13"/>
       <c r="H359" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I359" s="13"/>
       <c r="J359" s="13"/>
@@ -19870,8 +19870,8 @@
       <c r="F360" s="13"/>
       <c r="G360" s="13"/>
       <c r="H360" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I360" s="13"/>
       <c r="J360" s="13"/>
@@ -19914,8 +19914,8 @@
       <c r="F361" s="13"/>
       <c r="G361" s="13"/>
       <c r="H361" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I361" s="13"/>
       <c r="J361" s="13"/>
@@ -19958,8 +19958,8 @@
       <c r="F362" s="13"/>
       <c r="G362" s="13"/>
       <c r="H362" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I362" s="13"/>
       <c r="J362" s="13"/>
@@ -20002,8 +20002,8 @@
       <c r="F363" s="13"/>
       <c r="G363" s="13"/>
       <c r="H363" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I363" s="13"/>
       <c r="J363" s="13"/>
@@ -20046,8 +20046,8 @@
       <c r="F364" s="13"/>
       <c r="G364" s="13"/>
       <c r="H364" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I364" s="13"/>
       <c r="J364" s="13"/>
@@ -20090,8 +20090,8 @@
       <c r="F365" s="13"/>
       <c r="G365" s="13"/>
       <c r="H365" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I365" s="13"/>
       <c r="J365" s="13"/>
@@ -20134,8 +20134,8 @@
       <c r="F366" s="13"/>
       <c r="G366" s="13"/>
       <c r="H366" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I366" s="13"/>
       <c r="J366" s="13"/>
@@ -20178,8 +20178,8 @@
       <c r="F367" s="13"/>
       <c r="G367" s="13"/>
       <c r="H367" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I367" s="13"/>
       <c r="J367" s="13"/>
@@ -20222,8 +20222,8 @@
       <c r="F368" s="13"/>
       <c r="G368" s="13"/>
       <c r="H368" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I368" s="13"/>
       <c r="J368" s="13"/>
@@ -20266,8 +20266,8 @@
       <c r="F369" s="13"/>
       <c r="G369" s="13"/>
       <c r="H369" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I369" s="13"/>
       <c r="J369" s="13"/>
@@ -20310,8 +20310,8 @@
       <c r="F370" s="13"/>
       <c r="G370" s="13"/>
       <c r="H370" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I370" s="13"/>
       <c r="J370" s="13"/>
@@ -20354,8 +20354,8 @@
       <c r="F371" s="13"/>
       <c r="G371" s="13"/>
       <c r="H371" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I371" s="13"/>
       <c r="J371" s="13"/>
@@ -20398,8 +20398,8 @@
       <c r="F372" s="13"/>
       <c r="G372" s="13"/>
       <c r="H372" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I372" s="13"/>
       <c r="J372" s="13"/>
@@ -20442,8 +20442,8 @@
       <c r="F373" s="13"/>
       <c r="G373" s="13"/>
       <c r="H373" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I373" s="13"/>
       <c r="J373" s="13"/>
@@ -20486,8 +20486,8 @@
       <c r="F374" s="13"/>
       <c r="G374" s="13"/>
       <c r="H374" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I374" s="13"/>
       <c r="J374" s="13"/>
@@ -20530,8 +20530,8 @@
       <c r="F375" s="13"/>
       <c r="G375" s="13"/>
       <c r="H375" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I375" s="13"/>
       <c r="J375" s="13"/>
@@ -20574,8 +20574,8 @@
       <c r="F376" s="13"/>
       <c r="G376" s="13"/>
       <c r="H376" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I376" s="13"/>
       <c r="J376" s="13"/>
@@ -20618,8 +20618,8 @@
       <c r="F377" s="13"/>
       <c r="G377" s="13"/>
       <c r="H377" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I377" s="13"/>
       <c r="J377" s="13"/>
@@ -20662,8 +20662,8 @@
       <c r="F378" s="13"/>
       <c r="G378" s="13"/>
       <c r="H378" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I378" s="13"/>
       <c r="J378" s="13"/>
@@ -20706,8 +20706,8 @@
       <c r="F379" s="13"/>
       <c r="G379" s="13"/>
       <c r="H379" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I379" s="13"/>
       <c r="J379" s="13"/>
@@ -20750,8 +20750,8 @@
       <c r="F380" s="13"/>
       <c r="G380" s="13"/>
       <c r="H380" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I380" s="13"/>
       <c r="J380" s="13"/>
@@ -20794,8 +20794,8 @@
       <c r="F381" s="13"/>
       <c r="G381" s="13"/>
       <c r="H381" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I381" s="13"/>
       <c r="J381" s="13"/>
@@ -20838,8 +20838,8 @@
       <c r="F382" s="13"/>
       <c r="G382" s="13"/>
       <c r="H382" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I382" s="13"/>
       <c r="J382" s="13"/>
@@ -20882,8 +20882,8 @@
       <c r="F383" s="13"/>
       <c r="G383" s="13"/>
       <c r="H383" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I383" s="13"/>
       <c r="J383" s="13"/>
@@ -20926,8 +20926,8 @@
       <c r="F384" s="13"/>
       <c r="G384" s="13"/>
       <c r="H384" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I384" s="13"/>
       <c r="J384" s="13"/>
@@ -20970,8 +20970,8 @@
       <c r="F385" s="13"/>
       <c r="G385" s="13"/>
       <c r="H385" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I385" s="13"/>
       <c r="J385" s="13"/>
@@ -21014,8 +21014,8 @@
       <c r="F386" s="13"/>
       <c r="G386" s="13"/>
       <c r="H386" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I386" s="13"/>
       <c r="J386" s="13"/>
@@ -21058,8 +21058,8 @@
       <c r="F387" s="13"/>
       <c r="G387" s="13"/>
       <c r="H387" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I387" s="13"/>
       <c r="J387" s="13"/>
@@ -21102,8 +21102,8 @@
       <c r="F388" s="13"/>
       <c r="G388" s="13"/>
       <c r="H388" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I388" s="13"/>
       <c r="J388" s="13"/>
@@ -21146,8 +21146,8 @@
       <c r="F389" s="13"/>
       <c r="G389" s="13"/>
       <c r="H389" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I389" s="13"/>
       <c r="J389" s="13"/>
@@ -21190,8 +21190,8 @@
       <c r="F390" s="13"/>
       <c r="G390" s="13"/>
       <c r="H390" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I390" s="13"/>
       <c r="J390" s="13"/>
@@ -21234,8 +21234,8 @@
       <c r="F391" s="13"/>
       <c r="G391" s="13"/>
       <c r="H391" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I391" s="13"/>
       <c r="J391" s="13"/>
@@ -21278,8 +21278,8 @@
       <c r="F392" s="13"/>
       <c r="G392" s="13"/>
       <c r="H392" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I392" s="13"/>
       <c r="J392" s="13"/>
@@ -21322,8 +21322,8 @@
       <c r="F393" s="13"/>
       <c r="G393" s="13"/>
       <c r="H393" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I393" s="13"/>
       <c r="J393" s="13"/>
@@ -21366,8 +21366,8 @@
       <c r="F394" s="13"/>
       <c r="G394" s="13"/>
       <c r="H394" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="6"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I394" s="13"/>
       <c r="J394" s="13"/>
@@ -21410,8 +21410,8 @@
       <c r="F395" s="13"/>
       <c r="G395" s="13"/>
       <c r="H395" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" ref="H395:H458" si="7">L395&amp;"có hình dáng dạng "&amp;M395&amp;" chất liệu "&amp;N395&amp;" thành phần hóa chất: "&amp;O395&amp;" có kích thước "&amp;P395&amp;" dùng để "&amp;R395&amp;" cho "&amp;Q395</f>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I395" s="13"/>
       <c r="J395" s="13"/>
@@ -21455,7 +21455,7 @@
       <c r="G396" s="13"/>
       <c r="H396" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I396" s="13"/>
       <c r="J396" s="13"/>
@@ -21499,7 +21499,7 @@
       <c r="G397" s="13"/>
       <c r="H397" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I397" s="13"/>
       <c r="J397" s="13"/>
@@ -21543,7 +21543,7 @@
       <c r="G398" s="13"/>
       <c r="H398" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I398" s="13"/>
       <c r="J398" s="13"/>
@@ -21587,7 +21587,7 @@
       <c r="G399" s="13"/>
       <c r="H399" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I399" s="13"/>
       <c r="J399" s="13"/>
@@ -21631,7 +21631,7 @@
       <c r="G400" s="13"/>
       <c r="H400" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I400" s="13"/>
       <c r="J400" s="13"/>
@@ -21675,7 +21675,7 @@
       <c r="G401" s="13"/>
       <c r="H401" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I401" s="13"/>
       <c r="J401" s="13"/>
@@ -21719,7 +21719,7 @@
       <c r="G402" s="13"/>
       <c r="H402" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I402" s="13"/>
       <c r="J402" s="13"/>
@@ -21763,7 +21763,7 @@
       <c r="G403" s="13"/>
       <c r="H403" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I403" s="13"/>
       <c r="J403" s="13"/>
@@ -21807,7 +21807,7 @@
       <c r="G404" s="13"/>
       <c r="H404" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I404" s="13"/>
       <c r="J404" s="13"/>
@@ -21851,7 +21851,7 @@
       <c r="G405" s="13"/>
       <c r="H405" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I405" s="13"/>
       <c r="J405" s="13"/>
@@ -21895,7 +21895,7 @@
       <c r="G406" s="13"/>
       <c r="H406" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I406" s="13"/>
       <c r="J406" s="13"/>
@@ -21939,7 +21939,7 @@
       <c r="G407" s="13"/>
       <c r="H407" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I407" s="13"/>
       <c r="J407" s="13"/>
@@ -21983,7 +21983,7 @@
       <c r="G408" s="13"/>
       <c r="H408" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I408" s="13"/>
       <c r="J408" s="13"/>
@@ -22027,7 +22027,7 @@
       <c r="G409" s="13"/>
       <c r="H409" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I409" s="13"/>
       <c r="J409" s="13"/>
@@ -22071,7 +22071,7 @@
       <c r="G410" s="13"/>
       <c r="H410" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I410" s="13"/>
       <c r="J410" s="13"/>
@@ -22115,7 +22115,7 @@
       <c r="G411" s="13"/>
       <c r="H411" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I411" s="13"/>
       <c r="J411" s="13"/>
@@ -22159,7 +22159,7 @@
       <c r="G412" s="13"/>
       <c r="H412" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I412" s="13"/>
       <c r="J412" s="13"/>
@@ -22203,7 +22203,7 @@
       <c r="G413" s="13"/>
       <c r="H413" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I413" s="13"/>
       <c r="J413" s="13"/>
@@ -22246,8 +22246,8 @@
       <c r="F414" s="13"/>
       <c r="G414" s="13"/>
       <c r="H414" s="12" t="str">
-        <f t="shared" ref="H414:H477" si="8">M414&amp;" "&amp;N414&amp;" "&amp;O414&amp;""&amp;P414&amp;" "&amp;Q414&amp;" "&amp;R414</f>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I414" s="13"/>
       <c r="J414" s="13"/>
@@ -22290,8 +22290,8 @@
       <c r="F415" s="13"/>
       <c r="G415" s="13"/>
       <c r="H415" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I415" s="13"/>
       <c r="J415" s="13"/>
@@ -22334,8 +22334,8 @@
       <c r="F416" s="13"/>
       <c r="G416" s="13"/>
       <c r="H416" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I416" s="13"/>
       <c r="J416" s="13"/>
@@ -22378,8 +22378,8 @@
       <c r="F417" s="13"/>
       <c r="G417" s="13"/>
       <c r="H417" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I417" s="13"/>
       <c r="J417" s="13"/>
@@ -22422,8 +22422,8 @@
       <c r="F418" s="13"/>
       <c r="G418" s="13"/>
       <c r="H418" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I418" s="13"/>
       <c r="J418" s="13"/>
@@ -22466,8 +22466,8 @@
       <c r="F419" s="13"/>
       <c r="G419" s="13"/>
       <c r="H419" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I419" s="13"/>
       <c r="J419" s="13"/>
@@ -22510,8 +22510,8 @@
       <c r="F420" s="13"/>
       <c r="G420" s="13"/>
       <c r="H420" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I420" s="13"/>
       <c r="J420" s="13"/>
@@ -22554,8 +22554,8 @@
       <c r="F421" s="13"/>
       <c r="G421" s="13"/>
       <c r="H421" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I421" s="13"/>
       <c r="J421" s="13"/>
@@ -22598,8 +22598,8 @@
       <c r="F422" s="13"/>
       <c r="G422" s="13"/>
       <c r="H422" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I422" s="13"/>
       <c r="J422" s="13"/>
@@ -22642,8 +22642,8 @@
       <c r="F423" s="13"/>
       <c r="G423" s="13"/>
       <c r="H423" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I423" s="13"/>
       <c r="J423" s="13"/>
@@ -22686,8 +22686,8 @@
       <c r="F424" s="13"/>
       <c r="G424" s="13"/>
       <c r="H424" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I424" s="13"/>
       <c r="J424" s="13"/>
@@ -22730,8 +22730,8 @@
       <c r="F425" s="13"/>
       <c r="G425" s="13"/>
       <c r="H425" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I425" s="13"/>
       <c r="J425" s="13"/>
@@ -22774,8 +22774,8 @@
       <c r="F426" s="13"/>
       <c r="G426" s="13"/>
       <c r="H426" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I426" s="13"/>
       <c r="J426" s="13"/>
@@ -22818,8 +22818,8 @@
       <c r="F427" s="13"/>
       <c r="G427" s="13"/>
       <c r="H427" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I427" s="13"/>
       <c r="J427" s="13"/>
@@ -22862,8 +22862,8 @@
       <c r="F428" s="13"/>
       <c r="G428" s="13"/>
       <c r="H428" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I428" s="13"/>
       <c r="J428" s="13"/>
@@ -22906,8 +22906,8 @@
       <c r="F429" s="13"/>
       <c r="G429" s="13"/>
       <c r="H429" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I429" s="13"/>
       <c r="J429" s="13"/>
@@ -22950,8 +22950,8 @@
       <c r="F430" s="13"/>
       <c r="G430" s="13"/>
       <c r="H430" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I430" s="13"/>
       <c r="J430" s="13"/>
@@ -22994,8 +22994,8 @@
       <c r="F431" s="13"/>
       <c r="G431" s="13"/>
       <c r="H431" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I431" s="13"/>
       <c r="J431" s="13"/>
@@ -23038,8 +23038,8 @@
       <c r="F432" s="13"/>
       <c r="G432" s="13"/>
       <c r="H432" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I432" s="13"/>
       <c r="J432" s="13"/>
@@ -23082,8 +23082,8 @@
       <c r="F433" s="13"/>
       <c r="G433" s="13"/>
       <c r="H433" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I433" s="13"/>
       <c r="J433" s="13"/>
@@ -23126,8 +23126,8 @@
       <c r="F434" s="13"/>
       <c r="G434" s="13"/>
       <c r="H434" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I434" s="13"/>
       <c r="J434" s="13"/>
@@ -23170,8 +23170,8 @@
       <c r="F435" s="13"/>
       <c r="G435" s="13"/>
       <c r="H435" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I435" s="13"/>
       <c r="J435" s="13"/>
@@ -23214,8 +23214,8 @@
       <c r="F436" s="13"/>
       <c r="G436" s="13"/>
       <c r="H436" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I436" s="13"/>
       <c r="J436" s="13"/>
@@ -23258,8 +23258,8 @@
       <c r="F437" s="13"/>
       <c r="G437" s="13"/>
       <c r="H437" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I437" s="13"/>
       <c r="J437" s="13"/>
@@ -23302,8 +23302,8 @@
       <c r="F438" s="13"/>
       <c r="G438" s="13"/>
       <c r="H438" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I438" s="13"/>
       <c r="J438" s="13"/>
@@ -23346,8 +23346,8 @@
       <c r="F439" s="13"/>
       <c r="G439" s="13"/>
       <c r="H439" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I439" s="13"/>
       <c r="J439" s="13"/>
@@ -23390,8 +23390,8 @@
       <c r="F440" s="13"/>
       <c r="G440" s="13"/>
       <c r="H440" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I440" s="13"/>
       <c r="J440" s="13"/>
@@ -23434,8 +23434,8 @@
       <c r="F441" s="13"/>
       <c r="G441" s="13"/>
       <c r="H441" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I441" s="13"/>
       <c r="J441" s="13"/>
@@ -23478,8 +23478,8 @@
       <c r="F442" s="13"/>
       <c r="G442" s="13"/>
       <c r="H442" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I442" s="13"/>
       <c r="J442" s="13"/>
@@ -23522,8 +23522,8 @@
       <c r="F443" s="13"/>
       <c r="G443" s="13"/>
       <c r="H443" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I443" s="13"/>
       <c r="J443" s="13"/>
@@ -23566,8 +23566,8 @@
       <c r="F444" s="13"/>
       <c r="G444" s="13"/>
       <c r="H444" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I444" s="13"/>
       <c r="J444" s="13"/>
@@ -23610,8 +23610,8 @@
       <c r="F445" s="13"/>
       <c r="G445" s="13"/>
       <c r="H445" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I445" s="13"/>
       <c r="J445" s="13"/>
@@ -23654,8 +23654,8 @@
       <c r="F446" s="13"/>
       <c r="G446" s="13"/>
       <c r="H446" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I446" s="13"/>
       <c r="J446" s="13"/>
@@ -23698,8 +23698,8 @@
       <c r="F447" s="13"/>
       <c r="G447" s="13"/>
       <c r="H447" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I447" s="13"/>
       <c r="J447" s="13"/>
@@ -23742,8 +23742,8 @@
       <c r="F448" s="13"/>
       <c r="G448" s="13"/>
       <c r="H448" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I448" s="13"/>
       <c r="J448" s="13"/>
@@ -23786,8 +23786,8 @@
       <c r="F449" s="13"/>
       <c r="G449" s="13"/>
       <c r="H449" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I449" s="13"/>
       <c r="J449" s="13"/>
@@ -23830,8 +23830,8 @@
       <c r="F450" s="13"/>
       <c r="G450" s="13"/>
       <c r="H450" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I450" s="13"/>
       <c r="J450" s="13"/>
@@ -23874,8 +23874,8 @@
       <c r="F451" s="13"/>
       <c r="G451" s="13"/>
       <c r="H451" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I451" s="13"/>
       <c r="J451" s="13"/>
@@ -23918,8 +23918,8 @@
       <c r="F452" s="13"/>
       <c r="G452" s="13"/>
       <c r="H452" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I452" s="13"/>
       <c r="J452" s="13"/>
@@ -23962,8 +23962,8 @@
       <c r="F453" s="13"/>
       <c r="G453" s="13"/>
       <c r="H453" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I453" s="13"/>
       <c r="J453" s="13"/>
@@ -24006,8 +24006,8 @@
       <c r="F454" s="13"/>
       <c r="G454" s="13"/>
       <c r="H454" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I454" s="13"/>
       <c r="J454" s="13"/>
@@ -24050,8 +24050,8 @@
       <c r="F455" s="13"/>
       <c r="G455" s="13"/>
       <c r="H455" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I455" s="13"/>
       <c r="J455" s="13"/>
@@ -24094,8 +24094,8 @@
       <c r="F456" s="13"/>
       <c r="G456" s="13"/>
       <c r="H456" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I456" s="13"/>
       <c r="J456" s="13"/>
@@ -24138,8 +24138,8 @@
       <c r="F457" s="13"/>
       <c r="G457" s="13"/>
       <c r="H457" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I457" s="13"/>
       <c r="J457" s="13"/>
@@ -24182,8 +24182,8 @@
       <c r="F458" s="13"/>
       <c r="G458" s="13"/>
       <c r="H458" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="7"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I458" s="13"/>
       <c r="J458" s="13"/>
@@ -24226,8 +24226,8 @@
       <c r="F459" s="13"/>
       <c r="G459" s="13"/>
       <c r="H459" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" ref="H459:H522" si="8">L459&amp;"có hình dáng dạng "&amp;M459&amp;" chất liệu "&amp;N459&amp;" thành phần hóa chất: "&amp;O459&amp;" có kích thước "&amp;P459&amp;" dùng để "&amp;R459&amp;" cho "&amp;Q459</f>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I459" s="13"/>
       <c r="J459" s="13"/>
@@ -24271,7 +24271,7 @@
       <c r="G460" s="13"/>
       <c r="H460" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I460" s="13"/>
       <c r="J460" s="13"/>
@@ -24315,7 +24315,7 @@
       <c r="G461" s="13"/>
       <c r="H461" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I461" s="13"/>
       <c r="J461" s="13"/>
@@ -24359,7 +24359,7 @@
       <c r="G462" s="13"/>
       <c r="H462" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I462" s="13"/>
       <c r="J462" s="13"/>
@@ -24403,7 +24403,7 @@
       <c r="G463" s="13"/>
       <c r="H463" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I463" s="13"/>
       <c r="J463" s="13"/>
@@ -24447,7 +24447,7 @@
       <c r="G464" s="13"/>
       <c r="H464" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I464" s="13"/>
       <c r="J464" s="13"/>
@@ -24491,7 +24491,7 @@
       <c r="G465" s="13"/>
       <c r="H465" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I465" s="13"/>
       <c r="J465" s="13"/>
@@ -24535,7 +24535,7 @@
       <c r="G466" s="13"/>
       <c r="H466" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I466" s="13"/>
       <c r="J466" s="13"/>
@@ -24579,7 +24579,7 @@
       <c r="G467" s="13"/>
       <c r="H467" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I467" s="13"/>
       <c r="J467" s="13"/>
@@ -24623,7 +24623,7 @@
       <c r="G468" s="13"/>
       <c r="H468" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I468" s="13"/>
       <c r="J468" s="13"/>
@@ -24667,7 +24667,7 @@
       <c r="G469" s="13"/>
       <c r="H469" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I469" s="13"/>
       <c r="J469" s="13"/>
@@ -24711,7 +24711,7 @@
       <c r="G470" s="13"/>
       <c r="H470" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I470" s="13"/>
       <c r="J470" s="13"/>
@@ -24755,7 +24755,7 @@
       <c r="G471" s="13"/>
       <c r="H471" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I471" s="13"/>
       <c r="J471" s="13"/>
@@ -24799,7 +24799,7 @@
       <c r="G472" s="13"/>
       <c r="H472" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I472" s="13"/>
       <c r="J472" s="13"/>
@@ -24843,7 +24843,7 @@
       <c r="G473" s="13"/>
       <c r="H473" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I473" s="13"/>
       <c r="J473" s="13"/>
@@ -24887,7 +24887,7 @@
       <c r="G474" s="13"/>
       <c r="H474" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I474" s="13"/>
       <c r="J474" s="13"/>
@@ -24931,7 +24931,7 @@
       <c r="G475" s="13"/>
       <c r="H475" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I475" s="13"/>
       <c r="J475" s="13"/>
@@ -24975,7 +24975,7 @@
       <c r="G476" s="13"/>
       <c r="H476" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I476" s="13"/>
       <c r="J476" s="13"/>
@@ -25019,7 +25019,7 @@
       <c r="G477" s="13"/>
       <c r="H477" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I477" s="13"/>
       <c r="J477" s="13"/>
@@ -25062,8 +25062,8 @@
       <c r="F478" s="13"/>
       <c r="G478" s="13"/>
       <c r="H478" s="12" t="str">
-        <f t="shared" ref="H478:H541" si="9">M478&amp;" "&amp;N478&amp;" "&amp;O478&amp;""&amp;P478&amp;" "&amp;Q478&amp;" "&amp;R478</f>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I478" s="13"/>
       <c r="J478" s="13"/>
@@ -25106,8 +25106,8 @@
       <c r="F479" s="13"/>
       <c r="G479" s="13"/>
       <c r="H479" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I479" s="13"/>
       <c r="J479" s="13"/>
@@ -25150,8 +25150,8 @@
       <c r="F480" s="13"/>
       <c r="G480" s="13"/>
       <c r="H480" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I480" s="13"/>
       <c r="J480" s="13"/>
@@ -25194,8 +25194,8 @@
       <c r="F481" s="13"/>
       <c r="G481" s="13"/>
       <c r="H481" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I481" s="13"/>
       <c r="J481" s="13"/>
@@ -25238,8 +25238,8 @@
       <c r="F482" s="13"/>
       <c r="G482" s="13"/>
       <c r="H482" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I482" s="13"/>
       <c r="J482" s="13"/>
@@ -25282,8 +25282,8 @@
       <c r="F483" s="13"/>
       <c r="G483" s="13"/>
       <c r="H483" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I483" s="13"/>
       <c r="J483" s="13"/>
@@ -25326,8 +25326,8 @@
       <c r="F484" s="13"/>
       <c r="G484" s="13"/>
       <c r="H484" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I484" s="13"/>
       <c r="J484" s="13"/>
@@ -25370,8 +25370,8 @@
       <c r="F485" s="13"/>
       <c r="G485" s="13"/>
       <c r="H485" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I485" s="13"/>
       <c r="J485" s="13"/>
@@ -25414,8 +25414,8 @@
       <c r="F486" s="13"/>
       <c r="G486" s="13"/>
       <c r="H486" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I486" s="13"/>
       <c r="J486" s="13"/>
@@ -25458,8 +25458,8 @@
       <c r="F487" s="13"/>
       <c r="G487" s="13"/>
       <c r="H487" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I487" s="13"/>
       <c r="J487" s="13"/>
@@ -25502,8 +25502,8 @@
       <c r="F488" s="13"/>
       <c r="G488" s="13"/>
       <c r="H488" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I488" s="13"/>
       <c r="J488" s="13"/>
@@ -25546,8 +25546,8 @@
       <c r="F489" s="13"/>
       <c r="G489" s="13"/>
       <c r="H489" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I489" s="13"/>
       <c r="J489" s="13"/>
@@ -25590,8 +25590,8 @@
       <c r="F490" s="13"/>
       <c r="G490" s="13"/>
       <c r="H490" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I490" s="13"/>
       <c r="J490" s="13"/>
@@ -25634,8 +25634,8 @@
       <c r="F491" s="13"/>
       <c r="G491" s="13"/>
       <c r="H491" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I491" s="13"/>
       <c r="J491" s="13"/>
@@ -25678,8 +25678,8 @@
       <c r="F492" s="13"/>
       <c r="G492" s="13"/>
       <c r="H492" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I492" s="13"/>
       <c r="J492" s="13"/>
@@ -25722,8 +25722,8 @@
       <c r="F493" s="13"/>
       <c r="G493" s="13"/>
       <c r="H493" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I493" s="13"/>
       <c r="J493" s="13"/>
@@ -25766,8 +25766,8 @@
       <c r="F494" s="13"/>
       <c r="G494" s="13"/>
       <c r="H494" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I494" s="13"/>
       <c r="J494" s="13"/>
@@ -25810,8 +25810,8 @@
       <c r="F495" s="13"/>
       <c r="G495" s="13"/>
       <c r="H495" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I495" s="13"/>
       <c r="J495" s="13"/>
@@ -25854,8 +25854,8 @@
       <c r="F496" s="13"/>
       <c r="G496" s="13"/>
       <c r="H496" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I496" s="13"/>
       <c r="J496" s="13"/>
@@ -25898,8 +25898,8 @@
       <c r="F497" s="13"/>
       <c r="G497" s="13"/>
       <c r="H497" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I497" s="13"/>
       <c r="J497" s="13"/>
@@ -25942,8 +25942,8 @@
       <c r="F498" s="13"/>
       <c r="G498" s="13"/>
       <c r="H498" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I498" s="13"/>
       <c r="J498" s="13"/>
@@ -25986,8 +25986,8 @@
       <c r="F499" s="13"/>
       <c r="G499" s="13"/>
       <c r="H499" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I499" s="13"/>
       <c r="J499" s="13"/>
@@ -26030,8 +26030,8 @@
       <c r="F500" s="13"/>
       <c r="G500" s="13"/>
       <c r="H500" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I500" s="13"/>
       <c r="J500" s="13"/>
@@ -26074,8 +26074,8 @@
       <c r="F501" s="13"/>
       <c r="G501" s="13"/>
       <c r="H501" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I501" s="13"/>
       <c r="J501" s="13"/>
@@ -26118,8 +26118,8 @@
       <c r="F502" s="13"/>
       <c r="G502" s="13"/>
       <c r="H502" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I502" s="13"/>
       <c r="J502" s="13"/>
@@ -26162,8 +26162,8 @@
       <c r="F503" s="13"/>
       <c r="G503" s="13"/>
       <c r="H503" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I503" s="13"/>
       <c r="J503" s="13"/>
@@ -26206,8 +26206,8 @@
       <c r="F504" s="13"/>
       <c r="G504" s="13"/>
       <c r="H504" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I504" s="13"/>
       <c r="J504" s="13"/>
@@ -26250,8 +26250,8 @@
       <c r="F505" s="13"/>
       <c r="G505" s="13"/>
       <c r="H505" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I505" s="13"/>
       <c r="J505" s="13"/>
@@ -26294,8 +26294,8 @@
       <c r="F506" s="13"/>
       <c r="G506" s="13"/>
       <c r="H506" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I506" s="13"/>
       <c r="J506" s="13"/>
@@ -26338,8 +26338,8 @@
       <c r="F507" s="13"/>
       <c r="G507" s="13"/>
       <c r="H507" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I507" s="13"/>
       <c r="J507" s="13"/>
@@ -26382,8 +26382,8 @@
       <c r="F508" s="13"/>
       <c r="G508" s="13"/>
       <c r="H508" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I508" s="13"/>
       <c r="J508" s="13"/>
@@ -26426,8 +26426,8 @@
       <c r="F509" s="13"/>
       <c r="G509" s="13"/>
       <c r="H509" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I509" s="13"/>
       <c r="J509" s="13"/>
@@ -26470,8 +26470,8 @@
       <c r="F510" s="13"/>
       <c r="G510" s="13"/>
       <c r="H510" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I510" s="13"/>
       <c r="J510" s="13"/>
@@ -26514,8 +26514,8 @@
       <c r="F511" s="13"/>
       <c r="G511" s="13"/>
       <c r="H511" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I511" s="13"/>
       <c r="J511" s="13"/>
@@ -26558,8 +26558,8 @@
       <c r="F512" s="13"/>
       <c r="G512" s="13"/>
       <c r="H512" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I512" s="13"/>
       <c r="J512" s="13"/>
@@ -26602,8 +26602,8 @@
       <c r="F513" s="13"/>
       <c r="G513" s="13"/>
       <c r="H513" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I513" s="13"/>
       <c r="J513" s="13"/>
@@ -26646,8 +26646,8 @@
       <c r="F514" s="13"/>
       <c r="G514" s="13"/>
       <c r="H514" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I514" s="13"/>
       <c r="J514" s="13"/>
@@ -26690,8 +26690,8 @@
       <c r="F515" s="13"/>
       <c r="G515" s="13"/>
       <c r="H515" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I515" s="13"/>
       <c r="J515" s="13"/>
@@ -26734,8 +26734,8 @@
       <c r="F516" s="13"/>
       <c r="G516" s="13"/>
       <c r="H516" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I516" s="13"/>
       <c r="J516" s="13"/>
@@ -26778,8 +26778,8 @@
       <c r="F517" s="13"/>
       <c r="G517" s="13"/>
       <c r="H517" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I517" s="13"/>
       <c r="J517" s="13"/>
@@ -26822,8 +26822,8 @@
       <c r="F518" s="13"/>
       <c r="G518" s="13"/>
       <c r="H518" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I518" s="13"/>
       <c r="J518" s="13"/>
@@ -26866,8 +26866,8 @@
       <c r="F519" s="13"/>
       <c r="G519" s="13"/>
       <c r="H519" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I519" s="13"/>
       <c r="J519" s="13"/>
@@ -26910,8 +26910,8 @@
       <c r="F520" s="13"/>
       <c r="G520" s="13"/>
       <c r="H520" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I520" s="13"/>
       <c r="J520" s="13"/>
@@ -26954,8 +26954,8 @@
       <c r="F521" s="13"/>
       <c r="G521" s="13"/>
       <c r="H521" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I521" s="13"/>
       <c r="J521" s="13"/>
@@ -26998,8 +26998,8 @@
       <c r="F522" s="13"/>
       <c r="G522" s="13"/>
       <c r="H522" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="8"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I522" s="13"/>
       <c r="J522" s="13"/>
@@ -27042,8 +27042,8 @@
       <c r="F523" s="13"/>
       <c r="G523" s="13"/>
       <c r="H523" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" ref="H523:H569" si="9">L523&amp;"có hình dáng dạng "&amp;M523&amp;" chất liệu "&amp;N523&amp;" thành phần hóa chất: "&amp;O523&amp;" có kích thước "&amp;P523&amp;" dùng để "&amp;R523&amp;" cho "&amp;Q523</f>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I523" s="13"/>
       <c r="J523" s="13"/>
@@ -27087,7 +27087,7 @@
       <c r="G524" s="13"/>
       <c r="H524" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I524" s="13"/>
       <c r="J524" s="13"/>
@@ -27131,7 +27131,7 @@
       <c r="G525" s="13"/>
       <c r="H525" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I525" s="13"/>
       <c r="J525" s="13"/>
@@ -27175,7 +27175,7 @@
       <c r="G526" s="13"/>
       <c r="H526" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I526" s="13"/>
       <c r="J526" s="13"/>
@@ -27219,7 +27219,7 @@
       <c r="G527" s="13"/>
       <c r="H527" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I527" s="13"/>
       <c r="J527" s="13"/>
@@ -27263,7 +27263,7 @@
       <c r="G528" s="13"/>
       <c r="H528" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I528" s="13"/>
       <c r="J528" s="13"/>
@@ -27307,7 +27307,7 @@
       <c r="G529" s="13"/>
       <c r="H529" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I529" s="13"/>
       <c r="J529" s="13"/>
@@ -27351,7 +27351,7 @@
       <c r="G530" s="13"/>
       <c r="H530" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I530" s="13"/>
       <c r="J530" s="13"/>
@@ -27395,7 +27395,7 @@
       <c r="G531" s="13"/>
       <c r="H531" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I531" s="13"/>
       <c r="J531" s="13"/>
@@ -27439,7 +27439,7 @@
       <c r="G532" s="13"/>
       <c r="H532" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I532" s="13"/>
       <c r="J532" s="13"/>
@@ -27483,7 +27483,7 @@
       <c r="G533" s="13"/>
       <c r="H533" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I533" s="13"/>
       <c r="J533" s="13"/>
@@ -27527,7 +27527,7 @@
       <c r="G534" s="13"/>
       <c r="H534" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I534" s="13"/>
       <c r="J534" s="13"/>
@@ -27571,7 +27571,7 @@
       <c r="G535" s="13"/>
       <c r="H535" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I535" s="13"/>
       <c r="J535" s="13"/>
@@ -27615,7 +27615,7 @@
       <c r="G536" s="13"/>
       <c r="H536" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I536" s="13"/>
       <c r="J536" s="13"/>
@@ -27659,7 +27659,7 @@
       <c r="G537" s="13"/>
       <c r="H537" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I537" s="13"/>
       <c r="J537" s="13"/>
@@ -27703,7 +27703,7 @@
       <c r="G538" s="13"/>
       <c r="H538" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I538" s="13"/>
       <c r="J538" s="13"/>
@@ -27747,7 +27747,7 @@
       <c r="G539" s="13"/>
       <c r="H539" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I539" s="13"/>
       <c r="J539" s="13"/>
@@ -27791,7 +27791,7 @@
       <c r="G540" s="13"/>
       <c r="H540" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I540" s="13"/>
       <c r="J540" s="13"/>
@@ -27835,7 +27835,7 @@
       <c r="G541" s="13"/>
       <c r="H541" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">    </v>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I541" s="13"/>
       <c r="J541" s="13"/>
@@ -27878,8 +27878,8 @@
       <c r="F542" s="13"/>
       <c r="G542" s="13"/>
       <c r="H542" s="12" t="str">
-        <f t="shared" ref="H542:H569" si="10">M542&amp;" "&amp;N542&amp;" "&amp;O542&amp;""&amp;P542&amp;" "&amp;Q542&amp;" "&amp;R542</f>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I542" s="13"/>
       <c r="J542" s="13"/>
@@ -27922,8 +27922,8 @@
       <c r="F543" s="13"/>
       <c r="G543" s="13"/>
       <c r="H543" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I543" s="13"/>
       <c r="J543" s="13"/>
@@ -27966,8 +27966,8 @@
       <c r="F544" s="13"/>
       <c r="G544" s="13"/>
       <c r="H544" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I544" s="13"/>
       <c r="J544" s="13"/>
@@ -28010,8 +28010,8 @@
       <c r="F545" s="13"/>
       <c r="G545" s="13"/>
       <c r="H545" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I545" s="13"/>
       <c r="J545" s="13"/>
@@ -28054,8 +28054,8 @@
       <c r="F546" s="13"/>
       <c r="G546" s="13"/>
       <c r="H546" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I546" s="13"/>
       <c r="J546" s="13"/>
@@ -28098,8 +28098,8 @@
       <c r="F547" s="13"/>
       <c r="G547" s="13"/>
       <c r="H547" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I547" s="13"/>
       <c r="J547" s="13"/>
@@ -28142,8 +28142,8 @@
       <c r="F548" s="13"/>
       <c r="G548" s="13"/>
       <c r="H548" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I548" s="13"/>
       <c r="J548" s="13"/>
@@ -28186,8 +28186,8 @@
       <c r="F549" s="13"/>
       <c r="G549" s="13"/>
       <c r="H549" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I549" s="13"/>
       <c r="J549" s="13"/>
@@ -28230,8 +28230,8 @@
       <c r="F550" s="13"/>
       <c r="G550" s="13"/>
       <c r="H550" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I550" s="13"/>
       <c r="J550" s="13"/>
@@ -28274,8 +28274,8 @@
       <c r="F551" s="13"/>
       <c r="G551" s="13"/>
       <c r="H551" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I551" s="13"/>
       <c r="J551" s="13"/>
@@ -28318,8 +28318,8 @@
       <c r="F552" s="13"/>
       <c r="G552" s="13"/>
       <c r="H552" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I552" s="13"/>
       <c r="J552" s="13"/>
@@ -28362,8 +28362,8 @@
       <c r="F553" s="13"/>
       <c r="G553" s="13"/>
       <c r="H553" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I553" s="13"/>
       <c r="J553" s="13"/>
@@ -28406,8 +28406,8 @@
       <c r="F554" s="13"/>
       <c r="G554" s="13"/>
       <c r="H554" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I554" s="13"/>
       <c r="J554" s="13"/>
@@ -28450,8 +28450,8 @@
       <c r="F555" s="13"/>
       <c r="G555" s="13"/>
       <c r="H555" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I555" s="13"/>
       <c r="J555" s="13"/>
@@ -28494,8 +28494,8 @@
       <c r="F556" s="13"/>
       <c r="G556" s="13"/>
       <c r="H556" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I556" s="13"/>
       <c r="J556" s="13"/>
@@ -28538,8 +28538,8 @@
       <c r="F557" s="13"/>
       <c r="G557" s="13"/>
       <c r="H557" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I557" s="13"/>
       <c r="J557" s="13"/>
@@ -28582,8 +28582,8 @@
       <c r="F558" s="13"/>
       <c r="G558" s="13"/>
       <c r="H558" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I558" s="13"/>
       <c r="J558" s="13"/>
@@ -28626,8 +28626,8 @@
       <c r="F559" s="13"/>
       <c r="G559" s="13"/>
       <c r="H559" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I559" s="13"/>
       <c r="J559" s="13"/>
@@ -28670,8 +28670,8 @@
       <c r="F560" s="13"/>
       <c r="G560" s="13"/>
       <c r="H560" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I560" s="13"/>
       <c r="J560" s="13"/>
@@ -28714,8 +28714,8 @@
       <c r="F561" s="13"/>
       <c r="G561" s="13"/>
       <c r="H561" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I561" s="13"/>
       <c r="J561" s="13"/>
@@ -28758,8 +28758,8 @@
       <c r="F562" s="13"/>
       <c r="G562" s="13"/>
       <c r="H562" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I562" s="13"/>
       <c r="J562" s="13"/>
@@ -28802,8 +28802,8 @@
       <c r="F563" s="13"/>
       <c r="G563" s="13"/>
       <c r="H563" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I563" s="13"/>
       <c r="J563" s="13"/>
@@ -28846,8 +28846,8 @@
       <c r="F564" s="13"/>
       <c r="G564" s="13"/>
       <c r="H564" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I564" s="13"/>
       <c r="J564" s="13"/>
@@ -28890,8 +28890,8 @@
       <c r="F565" s="13"/>
       <c r="G565" s="13"/>
       <c r="H565" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I565" s="13"/>
       <c r="J565" s="13"/>
@@ -28934,8 +28934,8 @@
       <c r="F566" s="13"/>
       <c r="G566" s="13"/>
       <c r="H566" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I566" s="13"/>
       <c r="J566" s="13"/>
@@ -28978,8 +28978,8 @@
       <c r="F567" s="13"/>
       <c r="G567" s="13"/>
       <c r="H567" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I567" s="13"/>
       <c r="J567" s="13"/>
@@ -29022,8 +29022,8 @@
       <c r="F568" s="13"/>
       <c r="G568" s="13"/>
       <c r="H568" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I568" s="13"/>
       <c r="J568" s="13"/>
@@ -29066,8 +29066,8 @@
       <c r="F569" s="13"/>
       <c r="G569" s="13"/>
       <c r="H569" s="12" t="str">
-        <f t="shared" si="10"/>
-        <v xml:space="preserve">    </v>
+        <f t="shared" si="9"/>
+        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
       </c>
       <c r="I569" s="13"/>
       <c r="J569" s="13"/>
@@ -29098,6 +29098,23 @@
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="B4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="X8:X9"/>
     <mergeCell ref="AE8:AE9"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="AF8:AF9"/>
@@ -29114,23 +29131,6 @@
     <mergeCell ref="Z8:Z9"/>
     <mergeCell ref="AA8:AA9"/>
     <mergeCell ref="AB8:AB9"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="X8:X9"/>
-    <mergeCell ref="B4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="A6:I6"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA10:AA569" xr:uid="{A48AEAD6-16A7-419C-9ADE-A3A1D0E68BC1}">
@@ -29193,11 +29193,11 @@
       </c>
     </row>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
       <c r="E2" s="20" t="s">
         <v>209</v>
       </c>
@@ -29207,11 +29207,11 @@
       <c r="G2" s="21"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="59" t="s">
         <v>201</v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
       <c r="E3" s="20" t="s">
         <v>209</v>
       </c>
@@ -29226,10 +29226,10 @@
       <c r="B4" s="29">
         <v>1</v>
       </c>
-      <c r="C4" s="56" t="s">
+      <c r="C4" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="57"/>
+      <c r="D4" s="56"/>
       <c r="E4" s="20" t="s">
         <v>204</v>
       </c>
@@ -29242,10 +29242,10 @@
       <c r="B5" s="29">
         <v>2</v>
       </c>
-      <c r="C5" s="51" t="s">
+      <c r="C5" s="57" t="s">
         <v>215</v>
       </c>
-      <c r="D5" s="52"/>
+      <c r="D5" s="58"/>
       <c r="E5" s="20" t="s">
         <v>204</v>
       </c>
@@ -29257,10 +29257,10 @@
       <c r="B6" s="29">
         <v>3</v>
       </c>
-      <c r="C6" s="51" t="s">
+      <c r="C6" s="57" t="s">
         <v>216</v>
       </c>
-      <c r="D6" s="52"/>
+      <c r="D6" s="58"/>
       <c r="E6" s="20" t="s">
         <v>209</v>
       </c>
@@ -29275,10 +29275,10 @@
       <c r="B7" s="29">
         <v>4</v>
       </c>
-      <c r="C7" s="51" t="s">
+      <c r="C7" s="57" t="s">
         <v>217</v>
       </c>
-      <c r="D7" s="52"/>
+      <c r="D7" s="58"/>
       <c r="E7" s="20" t="s">
         <v>209</v>
       </c>
@@ -29293,10 +29293,10 @@
       <c r="B8" s="29">
         <v>5</v>
       </c>
-      <c r="C8" s="51" t="s">
+      <c r="C8" s="57" t="s">
         <v>218</v>
       </c>
-      <c r="D8" s="52"/>
+      <c r="D8" s="58"/>
       <c r="E8" s="20" t="s">
         <v>206</v>
       </c>
@@ -29311,10 +29311,10 @@
       <c r="B9" s="29">
         <v>6</v>
       </c>
-      <c r="C9" s="51" t="s">
+      <c r="C9" s="57" t="s">
         <v>219</v>
       </c>
-      <c r="D9" s="52"/>
+      <c r="D9" s="58"/>
       <c r="E9" s="20" t="s">
         <v>204</v>
       </c>
@@ -29329,10 +29329,10 @@
       <c r="B10" s="29">
         <v>7</v>
       </c>
-      <c r="C10" s="51" t="s">
+      <c r="C10" s="57" t="s">
         <v>220</v>
       </c>
-      <c r="D10" s="52"/>
+      <c r="D10" s="58"/>
       <c r="E10" s="20" t="s">
         <v>209</v>
       </c>
@@ -29347,10 +29347,10 @@
       <c r="B11" s="29">
         <v>8</v>
       </c>
-      <c r="C11" s="51" t="s">
+      <c r="C11" s="57" t="s">
         <v>222</v>
       </c>
-      <c r="D11" s="52"/>
+      <c r="D11" s="58"/>
       <c r="E11" s="20" t="s">
         <v>209</v>
       </c>
@@ -29365,10 +29365,10 @@
       <c r="B12" s="29">
         <v>9</v>
       </c>
-      <c r="C12" s="51" t="s">
+      <c r="C12" s="57" t="s">
         <v>223</v>
       </c>
-      <c r="D12" s="52"/>
+      <c r="D12" s="58"/>
       <c r="E12" s="20" t="s">
         <v>209</v>
       </c>
@@ -29381,10 +29381,10 @@
       <c r="B13" s="29">
         <v>10</v>
       </c>
-      <c r="C13" s="51" t="s">
+      <c r="C13" s="57" t="s">
         <v>221</v>
       </c>
-      <c r="D13" s="52"/>
+      <c r="D13" s="58"/>
       <c r="E13" s="20" t="s">
         <v>204</v>
       </c>
@@ -29397,10 +29397,10 @@
       <c r="B14" s="29">
         <v>11</v>
       </c>
-      <c r="C14" s="51" t="s">
+      <c r="C14" s="57" t="s">
         <v>224</v>
       </c>
-      <c r="D14" s="52"/>
+      <c r="D14" s="58"/>
       <c r="E14" s="20" t="s">
         <v>204</v>
       </c>
@@ -29413,10 +29413,10 @@
       <c r="B15" s="29">
         <v>12</v>
       </c>
-      <c r="C15" s="51" t="s">
+      <c r="C15" s="57" t="s">
         <v>225</v>
       </c>
-      <c r="D15" s="52"/>
+      <c r="D15" s="58"/>
       <c r="E15" s="20" t="s">
         <v>209</v>
       </c>
@@ -29428,11 +29428,11 @@
       </c>
     </row>
     <row r="16" spans="2:7" ht="72" x14ac:dyDescent="0.25">
-      <c r="B16" s="54">
+      <c r="B16" s="60">
         <f>B15+1</f>
         <v>13</v>
       </c>
-      <c r="C16" s="55" t="s">
+      <c r="C16" s="54" t="s">
         <v>231</v>
       </c>
       <c r="D16" s="30" t="s">
@@ -29449,8 +29449,8 @@
       </c>
     </row>
     <row r="17" spans="2:7" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="54"/>
-      <c r="C17" s="55"/>
+      <c r="B17" s="60"/>
+      <c r="C17" s="54"/>
       <c r="D17" s="30" t="s">
         <v>227</v>
       </c>
@@ -29465,8 +29465,8 @@
       </c>
     </row>
     <row r="18" spans="2:7" ht="72" x14ac:dyDescent="0.25">
-      <c r="B18" s="54"/>
-      <c r="C18" s="55"/>
+      <c r="B18" s="60"/>
+      <c r="C18" s="54"/>
       <c r="D18" s="30" t="s">
         <v>228</v>
       </c>
@@ -29481,8 +29481,8 @@
       </c>
     </row>
     <row r="19" spans="2:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="B19" s="54"/>
-      <c r="C19" s="55"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="54"/>
       <c r="D19" s="30" t="s">
         <v>229</v>
       </c>
@@ -29497,8 +29497,8 @@
       </c>
     </row>
     <row r="20" spans="2:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="B20" s="54"/>
-      <c r="C20" s="55"/>
+      <c r="B20" s="60"/>
+      <c r="C20" s="54"/>
       <c r="D20" s="30" t="s">
         <v>230</v>
       </c>
@@ -29513,8 +29513,8 @@
       </c>
     </row>
     <row r="21" spans="2:7" ht="48" x14ac:dyDescent="0.25">
-      <c r="B21" s="54"/>
-      <c r="C21" s="55"/>
+      <c r="B21" s="60"/>
+      <c r="C21" s="54"/>
       <c r="D21" s="30" t="s">
         <v>234</v>
       </c>
@@ -29532,10 +29532,10 @@
       <c r="B22" s="31">
         <v>14</v>
       </c>
-      <c r="C22" s="51" t="s">
+      <c r="C22" s="57" t="s">
         <v>235</v>
       </c>
-      <c r="D22" s="52"/>
+      <c r="D22" s="58"/>
       <c r="E22" s="20" t="s">
         <v>206</v>
       </c>
@@ -29551,10 +29551,10 @@
         <f t="shared" ref="B23:B35" si="0">B22+1</f>
         <v>15</v>
       </c>
-      <c r="C23" s="51" t="s">
+      <c r="C23" s="57" t="s">
         <v>236</v>
       </c>
-      <c r="D23" s="52"/>
+      <c r="D23" s="58"/>
       <c r="E23" s="20" t="s">
         <v>206</v>
       </c>
@@ -29570,10 +29570,10 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C24" s="51" t="s">
+      <c r="C24" s="57" t="s">
         <v>232</v>
       </c>
-      <c r="D24" s="52"/>
+      <c r="D24" s="58"/>
       <c r="E24" s="20" t="s">
         <v>206</v>
       </c>
@@ -29589,10 +29589,10 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C25" s="51" t="s">
+      <c r="C25" s="57" t="s">
         <v>233</v>
       </c>
-      <c r="D25" s="52"/>
+      <c r="D25" s="58"/>
       <c r="E25" s="20" t="s">
         <v>206</v>
       </c>
@@ -29608,10 +29608,10 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C26" s="51" t="s">
+      <c r="C26" s="57" t="s">
         <v>237</v>
       </c>
-      <c r="D26" s="52"/>
+      <c r="D26" s="58"/>
       <c r="E26" s="20" t="s">
         <v>211</v>
       </c>
@@ -29627,10 +29627,10 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C27" s="51" t="s">
+      <c r="C27" s="57" t="s">
         <v>238</v>
       </c>
-      <c r="D27" s="52"/>
+      <c r="D27" s="58"/>
       <c r="E27" s="20" t="s">
         <v>209</v>
       </c>
@@ -29646,10 +29646,10 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C28" s="51" t="s">
+      <c r="C28" s="57" t="s">
         <v>239</v>
       </c>
-      <c r="D28" s="52"/>
+      <c r="D28" s="58"/>
       <c r="E28" s="20" t="s">
         <v>209</v>
       </c>
@@ -29665,10 +29665,10 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C29" s="51" t="s">
+      <c r="C29" s="57" t="s">
         <v>240</v>
       </c>
-      <c r="D29" s="52"/>
+      <c r="D29" s="58"/>
       <c r="E29" s="20" t="s">
         <v>209</v>
       </c>
@@ -29684,10 +29684,10 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C30" s="51" t="s">
+      <c r="C30" s="57" t="s">
         <v>241</v>
       </c>
-      <c r="D30" s="52"/>
+      <c r="D30" s="58"/>
       <c r="E30" s="20" t="s">
         <v>204</v>
       </c>
@@ -29703,10 +29703,10 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C31" s="51" t="s">
+      <c r="C31" s="57" t="s">
         <v>242</v>
       </c>
-      <c r="D31" s="52"/>
+      <c r="D31" s="58"/>
       <c r="E31" s="20" t="s">
         <v>204</v>
       </c>
@@ -29722,10 +29722,10 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C32" s="51" t="s">
+      <c r="C32" s="57" t="s">
         <v>243</v>
       </c>
-      <c r="D32" s="52"/>
+      <c r="D32" s="58"/>
       <c r="E32" s="20" t="s">
         <v>204</v>
       </c>
@@ -29739,10 +29739,10 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C33" s="51" t="s">
+      <c r="C33" s="57" t="s">
         <v>244</v>
       </c>
-      <c r="D33" s="52"/>
+      <c r="D33" s="58"/>
       <c r="E33" s="20" t="s">
         <v>204</v>
       </c>
@@ -29758,10 +29758,10 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C34" s="55" t="s">
+      <c r="C34" s="54" t="s">
         <v>245</v>
       </c>
-      <c r="D34" s="55"/>
+      <c r="D34" s="54"/>
       <c r="E34" s="20" t="s">
         <v>206</v>
       </c>
@@ -29777,10 +29777,10 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C35" s="55" t="s">
+      <c r="C35" s="54" t="s">
         <v>246</v>
       </c>
-      <c r="D35" s="55"/>
+      <c r="D35" s="54"/>
       <c r="E35" s="20" t="s">
         <v>206</v>
       </c>
@@ -29794,6 +29794,20 @@
   </sheetData>
   <autoFilter ref="B1:H35" xr:uid="{9A62EE61-DA4A-4471-B605-47242F0A4DEA}"/>
   <mergeCells count="30">
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B16:B21"/>
+    <mergeCell ref="C16:C21"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="C4:D4"/>
@@ -29810,20 +29824,6 @@
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="B16:B21"/>
-    <mergeCell ref="C16:C21"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -29858,7 +29858,7 @@
       <c r="B2" s="17" t="s">
         <v>451</v>
       </c>
-      <c r="D2" s="59" t="s">
+      <c r="D2" s="35" t="s">
         <v>642</v>
       </c>
     </row>
@@ -29869,7 +29869,7 @@
       <c r="B3" s="17" t="s">
         <v>452</v>
       </c>
-      <c r="D3" s="59" t="s">
+      <c r="D3" s="35" t="s">
         <v>643</v>
       </c>
     </row>
@@ -29880,7 +29880,7 @@
       <c r="B4" s="17" t="s">
         <v>453</v>
       </c>
-      <c r="D4" s="59" t="s">
+      <c r="D4" s="35" t="s">
         <v>644</v>
       </c>
     </row>
@@ -29891,7 +29891,7 @@
       <c r="B5" s="17" t="s">
         <v>454</v>
       </c>
-      <c r="D5" s="59" t="s">
+      <c r="D5" s="35" t="s">
         <v>645</v>
       </c>
     </row>
@@ -29902,7 +29902,7 @@
       <c r="B6" s="17" t="s">
         <v>455</v>
       </c>
-      <c r="D6" s="59" t="s">
+      <c r="D6" s="35" t="s">
         <v>646</v>
       </c>
     </row>
@@ -29913,7 +29913,7 @@
       <c r="B7" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="59" t="s">
+      <c r="D7" s="35" t="s">
         <v>647</v>
       </c>
     </row>
@@ -29924,7 +29924,7 @@
       <c r="B8" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="60" t="s">
+      <c r="D8" s="36" t="s">
         <v>648</v>
       </c>
     </row>
@@ -29935,7 +29935,7 @@
       <c r="B9" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="60" t="s">
+      <c r="D9" s="36" t="s">
         <v>649</v>
       </c>
     </row>
@@ -29946,7 +29946,7 @@
       <c r="B10" s="17" t="s">
         <v>456</v>
       </c>
-      <c r="D10" s="59" t="s">
+      <c r="D10" s="35" t="s">
         <v>650</v>
       </c>
     </row>
@@ -29957,7 +29957,7 @@
       <c r="B11" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="60" t="s">
+      <c r="D11" s="36" t="s">
         <v>651</v>
       </c>
     </row>
@@ -29968,7 +29968,7 @@
       <c r="B12" s="17" t="s">
         <v>457</v>
       </c>
-      <c r="D12" s="59" t="s">
+      <c r="D12" s="35" t="s">
         <v>652</v>
       </c>
     </row>
@@ -29979,7 +29979,7 @@
       <c r="B13" s="17" t="s">
         <v>458</v>
       </c>
-      <c r="D13" s="59" t="s">
+      <c r="D13" s="35" t="s">
         <v>653</v>
       </c>
     </row>
@@ -29990,7 +29990,7 @@
       <c r="B14" s="17" t="s">
         <v>459</v>
       </c>
-      <c r="D14" s="59" t="s">
+      <c r="D14" s="35" t="s">
         <v>654</v>
       </c>
     </row>
@@ -30001,7 +30001,7 @@
       <c r="B15" s="17" t="s">
         <v>460</v>
       </c>
-      <c r="D15" s="59" t="s">
+      <c r="D15" s="35" t="s">
         <v>655</v>
       </c>
     </row>
@@ -30012,7 +30012,7 @@
       <c r="B16" s="17" t="s">
         <v>461</v>
       </c>
-      <c r="D16" s="59" t="s">
+      <c r="D16" s="35" t="s">
         <v>656</v>
       </c>
     </row>
@@ -30023,7 +30023,7 @@
       <c r="B17" s="17" t="s">
         <v>462</v>
       </c>
-      <c r="D17" s="59" t="s">
+      <c r="D17" s="35" t="s">
         <v>657</v>
       </c>
     </row>
@@ -30034,7 +30034,7 @@
       <c r="B18" s="17" t="s">
         <v>463</v>
       </c>
-      <c r="D18" s="59" t="s">
+      <c r="D18" s="35" t="s">
         <v>658</v>
       </c>
     </row>
@@ -30045,7 +30045,7 @@
       <c r="B19" s="17" t="s">
         <v>464</v>
       </c>
-      <c r="D19" s="60" t="s">
+      <c r="D19" s="36" t="s">
         <v>659</v>
       </c>
     </row>
@@ -30056,7 +30056,7 @@
       <c r="B20" s="17" t="s">
         <v>465</v>
       </c>
-      <c r="D20" s="60" t="s">
+      <c r="D20" s="36" t="s">
         <v>660</v>
       </c>
     </row>
@@ -30067,7 +30067,7 @@
       <c r="B21" s="17" t="s">
         <v>466</v>
       </c>
-      <c r="D21" s="60" t="s">
+      <c r="D21" s="36" t="s">
         <v>661</v>
       </c>
     </row>
@@ -30078,7 +30078,7 @@
       <c r="B22" s="17" t="s">
         <v>467</v>
       </c>
-      <c r="D22" s="59" t="s">
+      <c r="D22" s="35" t="s">
         <v>662</v>
       </c>
     </row>
@@ -30089,7 +30089,7 @@
       <c r="B23" s="17" t="s">
         <v>468</v>
       </c>
-      <c r="D23" s="60" t="s">
+      <c r="D23" s="36" t="s">
         <v>663</v>
       </c>
     </row>
@@ -30100,7 +30100,7 @@
       <c r="B24" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="59" t="s">
+      <c r="D24" s="35" t="s">
         <v>664</v>
       </c>
     </row>
@@ -30111,7 +30111,7 @@
       <c r="B25" s="17" t="s">
         <v>469</v>
       </c>
-      <c r="D25" s="60" t="s">
+      <c r="D25" s="36" t="s">
         <v>665</v>
       </c>
     </row>
@@ -30122,7 +30122,7 @@
       <c r="B26" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="D26" s="60" t="s">
+      <c r="D26" s="36" t="s">
         <v>666</v>
       </c>
     </row>
@@ -30133,7 +30133,7 @@
       <c r="B27" s="17" t="s">
         <v>470</v>
       </c>
-      <c r="D27" s="59" t="s">
+      <c r="D27" s="35" t="s">
         <v>667</v>
       </c>
     </row>
@@ -30144,7 +30144,7 @@
       <c r="B28" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D28" s="59" t="s">
+      <c r="D28" s="35" t="s">
         <v>668</v>
       </c>
     </row>
@@ -30155,7 +30155,7 @@
       <c r="B29" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D29" s="60" t="s">
+      <c r="D29" s="36" t="s">
         <v>669</v>
       </c>
     </row>
@@ -30166,7 +30166,7 @@
       <c r="B30" s="17" t="s">
         <v>471</v>
       </c>
-      <c r="D30" s="60" t="s">
+      <c r="D30" s="36" t="s">
         <v>670</v>
       </c>
     </row>
@@ -30177,7 +30177,7 @@
       <c r="B31" s="17" t="s">
         <v>472</v>
       </c>
-      <c r="D31" s="59" t="s">
+      <c r="D31" s="35" t="s">
         <v>671</v>
       </c>
     </row>
@@ -30188,7 +30188,7 @@
       <c r="B32" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="D32" s="59" t="s">
+      <c r="D32" s="35" t="s">
         <v>672</v>
       </c>
     </row>
@@ -30199,7 +30199,7 @@
       <c r="B33" s="17" t="s">
         <v>473</v>
       </c>
-      <c r="D33" s="59" t="s">
+      <c r="D33" s="35" t="s">
         <v>673</v>
       </c>
     </row>
@@ -30210,7 +30210,7 @@
       <c r="B34" s="17" t="s">
         <v>474</v>
       </c>
-      <c r="D34" s="59" t="s">
+      <c r="D34" s="35" t="s">
         <v>674</v>
       </c>
     </row>
@@ -30221,7 +30221,7 @@
       <c r="B35" s="17" t="s">
         <v>475</v>
       </c>
-      <c r="D35" s="59" t="s">
+      <c r="D35" s="35" t="s">
         <v>675</v>
       </c>
     </row>
@@ -30232,7 +30232,7 @@
       <c r="B36" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D36" s="59" t="s">
+      <c r="D36" s="35" t="s">
         <v>676</v>
       </c>
     </row>
@@ -30243,7 +30243,7 @@
       <c r="B37" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D37" s="59" t="s">
+      <c r="D37" s="35" t="s">
         <v>677</v>
       </c>
     </row>
@@ -30254,7 +30254,7 @@
       <c r="B38" s="17" t="s">
         <v>476</v>
       </c>
-      <c r="D38" s="60" t="s">
+      <c r="D38" s="36" t="s">
         <v>678</v>
       </c>
     </row>
@@ -30265,7 +30265,7 @@
       <c r="B39" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D39" s="59" t="s">
+      <c r="D39" s="35" t="s">
         <v>679</v>
       </c>
     </row>
@@ -30276,7 +30276,7 @@
       <c r="B40" s="17" t="s">
         <v>477</v>
       </c>
-      <c r="D40" s="59" t="s">
+      <c r="D40" s="35" t="s">
         <v>680</v>
       </c>
     </row>
@@ -30287,7 +30287,7 @@
       <c r="B41" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D41" s="59" t="s">
+      <c r="D41" s="35" t="s">
         <v>681</v>
       </c>
     </row>
@@ -30298,7 +30298,7 @@
       <c r="B42" s="17" t="s">
         <v>478</v>
       </c>
-      <c r="D42" s="59" t="s">
+      <c r="D42" s="35" t="s">
         <v>682</v>
       </c>
     </row>
@@ -30309,7 +30309,7 @@
       <c r="B43" s="17" t="s">
         <v>479</v>
       </c>
-      <c r="D43" s="59" t="s">
+      <c r="D43" s="35" t="s">
         <v>683</v>
       </c>
     </row>
@@ -30320,7 +30320,7 @@
       <c r="B44" s="17" t="s">
         <v>480</v>
       </c>
-      <c r="D44" s="59" t="s">
+      <c r="D44" s="35" t="s">
         <v>684</v>
       </c>
     </row>
@@ -30331,7 +30331,7 @@
       <c r="B45" s="17" t="s">
         <v>481</v>
       </c>
-      <c r="D45" s="59" t="s">
+      <c r="D45" s="35" t="s">
         <v>685</v>
       </c>
     </row>
@@ -30342,7 +30342,7 @@
       <c r="B46" s="17" t="s">
         <v>482</v>
       </c>
-      <c r="D46" s="59" t="s">
+      <c r="D46" s="35" t="s">
         <v>686</v>
       </c>
     </row>
@@ -30353,7 +30353,7 @@
       <c r="B47" s="17" t="s">
         <v>483</v>
       </c>
-      <c r="D47" s="59" t="s">
+      <c r="D47" s="35" t="s">
         <v>687</v>
       </c>
     </row>
@@ -30364,7 +30364,7 @@
       <c r="B48" s="17" t="s">
         <v>484</v>
       </c>
-      <c r="D48" s="59" t="s">
+      <c r="D48" s="35" t="s">
         <v>688</v>
       </c>
     </row>
@@ -30375,7 +30375,7 @@
       <c r="B49" s="17" t="s">
         <v>485</v>
       </c>
-      <c r="D49" s="59" t="s">
+      <c r="D49" s="35" t="s">
         <v>689</v>
       </c>
     </row>
@@ -30386,7 +30386,7 @@
       <c r="B50" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="D50" s="59" t="s">
+      <c r="D50" s="35" t="s">
         <v>690</v>
       </c>
     </row>
@@ -30397,7 +30397,7 @@
       <c r="B51" s="17" t="s">
         <v>486</v>
       </c>
-      <c r="D51" s="59" t="s">
+      <c r="D51" s="35" t="s">
         <v>691</v>
       </c>
     </row>
@@ -30408,7 +30408,7 @@
       <c r="B52" s="17" t="s">
         <v>487</v>
       </c>
-      <c r="D52" s="59" t="s">
+      <c r="D52" s="35" t="s">
         <v>692</v>
       </c>
     </row>
@@ -30419,7 +30419,7 @@
       <c r="B53" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D53" s="59" t="s">
+      <c r="D53" s="35" t="s">
         <v>693</v>
       </c>
     </row>
@@ -30430,7 +30430,7 @@
       <c r="B54" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="D54" s="60" t="s">
+      <c r="D54" s="36" t="s">
         <v>694</v>
       </c>
     </row>
@@ -30441,7 +30441,7 @@
       <c r="B55" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="D55" s="60" t="s">
+      <c r="D55" s="36" t="s">
         <v>695</v>
       </c>
     </row>
@@ -30452,7 +30452,7 @@
       <c r="B56" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="D56" s="60" t="s">
+      <c r="D56" s="36" t="s">
         <v>696</v>
       </c>
     </row>
@@ -30463,7 +30463,7 @@
       <c r="B57" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="D57" s="59" t="s">
+      <c r="D57" s="35" t="s">
         <v>697</v>
       </c>
     </row>
@@ -30474,7 +30474,7 @@
       <c r="B58" s="17" t="s">
         <v>488</v>
       </c>
-      <c r="D58" s="59" t="s">
+      <c r="D58" s="35" t="s">
         <v>698</v>
       </c>
     </row>
@@ -30485,7 +30485,7 @@
       <c r="B59" s="17" t="s">
         <v>489</v>
       </c>
-      <c r="D59" s="60" t="s">
+      <c r="D59" s="36" t="s">
         <v>699</v>
       </c>
     </row>
@@ -30496,7 +30496,7 @@
       <c r="B60" s="17" t="s">
         <v>490</v>
       </c>
-      <c r="D60" s="59" t="s">
+      <c r="D60" s="35" t="s">
         <v>700</v>
       </c>
     </row>
@@ -30507,7 +30507,7 @@
       <c r="B61" s="17" t="s">
         <v>491</v>
       </c>
-      <c r="D61" s="59" t="s">
+      <c r="D61" s="35" t="s">
         <v>701</v>
       </c>
     </row>
@@ -30518,7 +30518,7 @@
       <c r="B62" s="17" t="s">
         <v>492</v>
       </c>
-      <c r="D62" s="59" t="s">
+      <c r="D62" s="35" t="s">
         <v>702</v>
       </c>
     </row>
@@ -30529,7 +30529,7 @@
       <c r="B63" s="17" t="s">
         <v>493</v>
       </c>
-      <c r="D63" s="59" t="s">
+      <c r="D63" s="35" t="s">
         <v>703</v>
       </c>
     </row>
@@ -30540,7 +30540,7 @@
       <c r="B64" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D64" s="59" t="s">
+      <c r="D64" s="35" t="s">
         <v>704</v>
       </c>
     </row>
@@ -30551,7 +30551,7 @@
       <c r="B65" s="17" t="s">
         <v>494</v>
       </c>
-      <c r="D65" s="59" t="s">
+      <c r="D65" s="35" t="s">
         <v>705</v>
       </c>
     </row>
@@ -30562,7 +30562,7 @@
       <c r="B66" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D66" s="59" t="s">
+      <c r="D66" s="35" t="s">
         <v>706</v>
       </c>
     </row>
@@ -30573,7 +30573,7 @@
       <c r="B67" s="17" t="s">
         <v>495</v>
       </c>
-      <c r="D67" s="60" t="s">
+      <c r="D67" s="36" t="s">
         <v>707</v>
       </c>
     </row>
@@ -30584,7 +30584,7 @@
       <c r="B68" s="17" t="s">
         <v>496</v>
       </c>
-      <c r="D68" s="60" t="s">
+      <c r="D68" s="36" t="s">
         <v>708</v>
       </c>
     </row>
@@ -30595,7 +30595,7 @@
       <c r="B69" s="17" t="s">
         <v>497</v>
       </c>
-      <c r="D69" s="59" t="s">
+      <c r="D69" s="35" t="s">
         <v>709</v>
       </c>
     </row>
@@ -30606,7 +30606,7 @@
       <c r="B70" s="17" t="s">
         <v>498</v>
       </c>
-      <c r="D70" s="60" t="s">
+      <c r="D70" s="36" t="s">
         <v>710</v>
       </c>
     </row>
@@ -30617,7 +30617,7 @@
       <c r="B71" s="17" t="s">
         <v>499</v>
       </c>
-      <c r="D71" s="59" t="s">
+      <c r="D71" s="35" t="s">
         <v>711</v>
       </c>
     </row>
@@ -30628,7 +30628,7 @@
       <c r="B72" s="17" t="s">
         <v>500</v>
       </c>
-      <c r="D72" s="59" t="s">
+      <c r="D72" s="35" t="s">
         <v>712</v>
       </c>
     </row>
@@ -30639,7 +30639,7 @@
       <c r="B73" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D73" s="59" t="s">
+      <c r="D73" s="35" t="s">
         <v>713</v>
       </c>
     </row>
@@ -30650,7 +30650,7 @@
       <c r="B74" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D74" s="59" t="s">
+      <c r="D74" s="35" t="s">
         <v>714</v>
       </c>
     </row>
@@ -30661,7 +30661,7 @@
       <c r="B75" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D75" s="59" t="s">
+      <c r="D75" s="35" t="s">
         <v>715</v>
       </c>
     </row>
@@ -30672,7 +30672,7 @@
       <c r="B76" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="D76" s="59" t="s">
+      <c r="D76" s="35" t="s">
         <v>716</v>
       </c>
     </row>
@@ -30683,7 +30683,7 @@
       <c r="B77" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="D77" s="59" t="s">
+      <c r="D77" s="35" t="s">
         <v>717</v>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       <c r="B78" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="D78" s="59" t="s">
+      <c r="D78" s="35" t="s">
         <v>718</v>
       </c>
     </row>
@@ -30705,7 +30705,7 @@
       <c r="B79" s="17" t="s">
         <v>501</v>
       </c>
-      <c r="D79" s="59" t="s">
+      <c r="D79" s="35" t="s">
         <v>719</v>
       </c>
     </row>
@@ -30716,7 +30716,7 @@
       <c r="B80" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="D80" s="59" t="s">
+      <c r="D80" s="35" t="s">
         <v>720</v>
       </c>
     </row>
@@ -30727,7 +30727,7 @@
       <c r="B81" s="17" t="s">
         <v>502</v>
       </c>
-      <c r="D81" s="59" t="s">
+      <c r="D81" s="35" t="s">
         <v>721</v>
       </c>
     </row>
@@ -30738,7 +30738,7 @@
       <c r="B82" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="D82" s="60" t="s">
+      <c r="D82" s="36" t="s">
         <v>722</v>
       </c>
     </row>
@@ -30749,7 +30749,7 @@
       <c r="B83" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="D83" s="59" t="s">
+      <c r="D83" s="35" t="s">
         <v>723</v>
       </c>
     </row>
@@ -30760,7 +30760,7 @@
       <c r="B84" s="17" t="s">
         <v>503</v>
       </c>
-      <c r="D84" s="59" t="s">
+      <c r="D84" s="35" t="s">
         <v>724</v>
       </c>
     </row>
@@ -30771,7 +30771,7 @@
       <c r="B85" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="D85" s="59" t="s">
+      <c r="D85" s="35" t="s">
         <v>725</v>
       </c>
     </row>
@@ -30782,7 +30782,7 @@
       <c r="B86" s="17" t="s">
         <v>504</v>
       </c>
-      <c r="D86" s="60" t="s">
+      <c r="D86" s="36" t="s">
         <v>726</v>
       </c>
     </row>
@@ -30793,7 +30793,7 @@
       <c r="B87" s="17" t="s">
         <v>505</v>
       </c>
-      <c r="D87" s="59" t="s">
+      <c r="D87" s="35" t="s">
         <v>727</v>
       </c>
     </row>
@@ -30804,7 +30804,7 @@
       <c r="B88" s="17" t="s">
         <v>506</v>
       </c>
-      <c r="D88" s="59" t="s">
+      <c r="D88" s="35" t="s">
         <v>728</v>
       </c>
     </row>
@@ -30815,7 +30815,7 @@
       <c r="B89" s="17" t="s">
         <v>507</v>
       </c>
-      <c r="D89" s="59" t="s">
+      <c r="D89" s="35" t="s">
         <v>729</v>
       </c>
     </row>
@@ -30826,7 +30826,7 @@
       <c r="B90" s="17" t="s">
         <v>508</v>
       </c>
-      <c r="D90" s="59" t="s">
+      <c r="D90" s="35" t="s">
         <v>730</v>
       </c>
     </row>
@@ -30837,7 +30837,7 @@
       <c r="B91" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="D91" s="59" t="s">
+      <c r="D91" s="35" t="s">
         <v>731</v>
       </c>
     </row>
@@ -30848,7 +30848,7 @@
       <c r="B92" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="D92" s="59" t="s">
+      <c r="D92" s="35" t="s">
         <v>732</v>
       </c>
     </row>
@@ -30859,7 +30859,7 @@
       <c r="B93" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="D93" s="59" t="s">
+      <c r="D93" s="35" t="s">
         <v>733</v>
       </c>
     </row>
@@ -30870,7 +30870,7 @@
       <c r="B94" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D94" s="59" t="s">
+      <c r="D94" s="35" t="s">
         <v>734</v>
       </c>
     </row>
@@ -30881,7 +30881,7 @@
       <c r="B95" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="D95" s="59" t="s">
+      <c r="D95" s="35" t="s">
         <v>735</v>
       </c>
     </row>
@@ -30892,7 +30892,7 @@
       <c r="B96" s="17" t="s">
         <v>509</v>
       </c>
-      <c r="D96" s="60" t="s">
+      <c r="D96" s="36" t="s">
         <v>736</v>
       </c>
     </row>
@@ -30903,7 +30903,7 @@
       <c r="B97" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D97" s="59" t="s">
+      <c r="D97" s="35" t="s">
         <v>737</v>
       </c>
     </row>
@@ -30914,7 +30914,7 @@
       <c r="B98" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D98" s="59" t="s">
+      <c r="D98" s="35" t="s">
         <v>738</v>
       </c>
     </row>
@@ -30925,7 +30925,7 @@
       <c r="B99" s="17" t="s">
         <v>510</v>
       </c>
-      <c r="D99" s="59" t="s">
+      <c r="D99" s="35" t="s">
         <v>739</v>
       </c>
     </row>
@@ -30936,7 +30936,7 @@
       <c r="B100" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="D100" s="59" t="s">
+      <c r="D100" s="35" t="s">
         <v>740</v>
       </c>
     </row>
@@ -30947,7 +30947,7 @@
       <c r="B101" s="17" t="s">
         <v>511</v>
       </c>
-      <c r="D101" s="59" t="s">
+      <c r="D101" s="35" t="s">
         <v>741</v>
       </c>
     </row>
@@ -30958,7 +30958,7 @@
       <c r="B102" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D102" s="59" t="s">
+      <c r="D102" s="35" t="s">
         <v>742</v>
       </c>
     </row>
@@ -30969,7 +30969,7 @@
       <c r="B103" s="17" t="s">
         <v>512</v>
       </c>
-      <c r="D103" s="59" t="s">
+      <c r="D103" s="35" t="s">
         <v>743</v>
       </c>
     </row>
@@ -30980,7 +30980,7 @@
       <c r="B104" s="17" t="s">
         <v>513</v>
       </c>
-      <c r="D104" s="59" t="s">
+      <c r="D104" s="35" t="s">
         <v>744</v>
       </c>
     </row>
@@ -30991,7 +30991,7 @@
       <c r="B105" s="17" t="s">
         <v>514</v>
       </c>
-      <c r="D105" s="60" t="s">
+      <c r="D105" s="36" t="s">
         <v>745</v>
       </c>
     </row>
@@ -31002,7 +31002,7 @@
       <c r="B106" s="17" t="s">
         <v>515</v>
       </c>
-      <c r="D106" s="60" t="s">
+      <c r="D106" s="36" t="s">
         <v>746</v>
       </c>
     </row>
@@ -31013,7 +31013,7 @@
       <c r="B107" s="17" t="s">
         <v>516</v>
       </c>
-      <c r="D107" s="59" t="s">
+      <c r="D107" s="35" t="s">
         <v>747</v>
       </c>
     </row>
@@ -31035,7 +31035,7 @@
       <c r="B109" s="17" t="s">
         <v>516</v>
       </c>
-      <c r="D109" s="61" t="s">
+      <c r="D109" s="37" t="s">
         <v>749</v>
       </c>
     </row>
@@ -31068,7 +31068,7 @@
       <c r="B112" s="17" t="s">
         <v>520</v>
       </c>
-      <c r="D112" s="59" t="s">
+      <c r="D112" s="35" t="s">
         <v>752</v>
       </c>
     </row>
@@ -32818,12 +32818,12 @@
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
       <c r="G2" s="4" t="s">
         <v>1</v>
       </c>

--- a/wwwroot/template/TemPlateQuote.xlsx
+++ b/wwwroot/template/TemPlateQuote.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\khanhmf\Cost Managerment\wwwroot\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89289C90-24B2-4FE4-AB08-F35F0C2D49E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D24112-D211-467D-AC3A-8F6AF1A67275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F4BD22E2-5202-4BAA-B608-770E176E4E09}"/>
   </bookViews>
@@ -2436,9 +2436,6 @@
     <t xml:space="preserve"> Molding engineering </t>
   </si>
   <si>
-    <t xml:space="preserve">Molding PP-ME </t>
-  </si>
-  <si>
     <t>Kiban</t>
   </si>
   <si>
@@ -3241,6 +3238,9 @@
   </si>
   <si>
     <t>Pallet</t>
+  </si>
+  <si>
+    <t>Molding MPE-ME</t>
   </si>
 </sst>
 </file>
@@ -4470,8 +4470,8 @@
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
       <c r="H10" s="12" t="str">
-        <f>L10&amp;"có hình dáng dạng "&amp;M10&amp;" chất liệu "&amp;N10&amp;" thành phần hóa chất: "&amp;O10&amp;" có kích thước "&amp;P10&amp;" dùng để "&amp;R10&amp;" cho "&amp;Q10</f>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <f>IF(B10="","",L10&amp;"có hình dáng dạng "&amp;M10&amp;" chất liệu "&amp;N10&amp;" thành phần hóa chất: "&amp;O10&amp;" có kích thước "&amp;P10&amp;" dùng để "&amp;R10&amp;" cho "&amp;Q10)</f>
+        <v/>
       </c>
       <c r="I10" s="13"/>
       <c r="J10" s="13"/>
@@ -4514,8 +4514,8 @@
       <c r="F11" s="13"/>
       <c r="G11" s="13"/>
       <c r="H11" s="12" t="str">
-        <f t="shared" ref="H11:H74" si="1">L11&amp;"có hình dáng dạng "&amp;M11&amp;" chất liệu "&amp;N11&amp;" thành phần hóa chất: "&amp;O11&amp;" có kích thước "&amp;P11&amp;" dùng để "&amp;R11&amp;" cho "&amp;Q11</f>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <f>IF(B11="","",L11&amp;"có hình dáng dạng "&amp;M11&amp;" chất liệu "&amp;N11&amp;" thành phần hóa chất: "&amp;O11&amp;" có kích thước "&amp;P11&amp;" dùng để "&amp;R11&amp;" cho "&amp;Q11)</f>
+        <v/>
       </c>
       <c r="I11" s="13"/>
       <c r="J11" s="13"/>
@@ -4558,8 +4558,8 @@
       <c r="F12" s="13"/>
       <c r="G12" s="13"/>
       <c r="H12" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <f>IF(B12="","",L12&amp;"có hình dáng dạng "&amp;M12&amp;" chất liệu "&amp;N12&amp;" thành phần hóa chất: "&amp;O12&amp;" có kích thước "&amp;P12&amp;" dùng để "&amp;R12&amp;" cho "&amp;Q12)</f>
+        <v/>
       </c>
       <c r="I12" s="13"/>
       <c r="J12" s="13"/>
@@ -4602,8 +4602,8 @@
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
       <c r="H13" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <f t="shared" ref="H13:H76" si="1">IF(B13="","",L13&amp;"có hình dáng dạng "&amp;M13&amp;" chất liệu "&amp;N13&amp;" thành phần hóa chất: "&amp;O13&amp;" có kích thước "&amp;P13&amp;" dùng để "&amp;R13&amp;" cho "&amp;Q13)</f>
+        <v/>
       </c>
       <c r="I13" s="13"/>
       <c r="J13" s="13"/>
@@ -4647,7 +4647,7 @@
       <c r="G14" s="13"/>
       <c r="H14" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I14" s="13"/>
       <c r="J14" s="13"/>
@@ -4691,7 +4691,7 @@
       <c r="G15" s="13"/>
       <c r="H15" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I15" s="13"/>
       <c r="J15" s="13"/>
@@ -4735,7 +4735,7 @@
       <c r="G16" s="13"/>
       <c r="H16" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I16" s="13"/>
       <c r="J16" s="13"/>
@@ -4779,7 +4779,7 @@
       <c r="G17" s="13"/>
       <c r="H17" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I17" s="13"/>
       <c r="J17" s="13"/>
@@ -4823,7 +4823,7 @@
       <c r="G18" s="13"/>
       <c r="H18" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I18" s="13"/>
       <c r="J18" s="13"/>
@@ -4867,7 +4867,7 @@
       <c r="G19" s="13"/>
       <c r="H19" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I19" s="13"/>
       <c r="J19" s="13"/>
@@ -4911,7 +4911,7 @@
       <c r="G20" s="13"/>
       <c r="H20" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I20" s="13"/>
       <c r="J20" s="13"/>
@@ -4955,7 +4955,7 @@
       <c r="G21" s="13"/>
       <c r="H21" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I21" s="13"/>
       <c r="J21" s="13"/>
@@ -4999,7 +4999,7 @@
       <c r="G22" s="13"/>
       <c r="H22" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I22" s="13"/>
       <c r="J22" s="13"/>
@@ -5043,7 +5043,7 @@
       <c r="G23" s="13"/>
       <c r="H23" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I23" s="13"/>
       <c r="J23" s="13"/>
@@ -5087,7 +5087,7 @@
       <c r="G24" s="13"/>
       <c r="H24" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I24" s="13"/>
       <c r="J24" s="13"/>
@@ -5131,7 +5131,7 @@
       <c r="G25" s="13"/>
       <c r="H25" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I25" s="13"/>
       <c r="J25" s="13"/>
@@ -5175,7 +5175,7 @@
       <c r="G26" s="13"/>
       <c r="H26" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I26" s="13"/>
       <c r="J26" s="13"/>
@@ -5219,7 +5219,7 @@
       <c r="G27" s="13"/>
       <c r="H27" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I27" s="13"/>
       <c r="J27" s="13"/>
@@ -5263,7 +5263,7 @@
       <c r="G28" s="13"/>
       <c r="H28" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I28" s="13"/>
       <c r="J28" s="13"/>
@@ -5307,7 +5307,7 @@
       <c r="G29" s="13"/>
       <c r="H29" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I29" s="13"/>
       <c r="J29" s="13"/>
@@ -5351,7 +5351,7 @@
       <c r="G30" s="13"/>
       <c r="H30" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I30" s="13"/>
       <c r="J30" s="13"/>
@@ -5395,7 +5395,7 @@
       <c r="G31" s="13"/>
       <c r="H31" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I31" s="13"/>
       <c r="J31" s="13"/>
@@ -5439,7 +5439,7 @@
       <c r="G32" s="13"/>
       <c r="H32" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I32" s="13"/>
       <c r="J32" s="13"/>
@@ -5483,7 +5483,7 @@
       <c r="G33" s="13"/>
       <c r="H33" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I33" s="13"/>
       <c r="J33" s="13"/>
@@ -5527,7 +5527,7 @@
       <c r="G34" s="13"/>
       <c r="H34" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I34" s="13"/>
       <c r="J34" s="13"/>
@@ -5571,7 +5571,7 @@
       <c r="G35" s="13"/>
       <c r="H35" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I35" s="13"/>
       <c r="J35" s="13"/>
@@ -5615,7 +5615,7 @@
       <c r="G36" s="13"/>
       <c r="H36" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I36" s="13"/>
       <c r="J36" s="13"/>
@@ -5659,7 +5659,7 @@
       <c r="G37" s="13"/>
       <c r="H37" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I37" s="13"/>
       <c r="J37" s="13"/>
@@ -5703,7 +5703,7 @@
       <c r="G38" s="13"/>
       <c r="H38" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I38" s="13"/>
       <c r="J38" s="13"/>
@@ -5747,7 +5747,7 @@
       <c r="G39" s="13"/>
       <c r="H39" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I39" s="13"/>
       <c r="J39" s="13"/>
@@ -5791,7 +5791,7 @@
       <c r="G40" s="13"/>
       <c r="H40" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I40" s="13"/>
       <c r="J40" s="13"/>
@@ -5835,7 +5835,7 @@
       <c r="G41" s="13"/>
       <c r="H41" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I41" s="13"/>
       <c r="J41" s="13"/>
@@ -5879,7 +5879,7 @@
       <c r="G42" s="13"/>
       <c r="H42" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I42" s="13"/>
       <c r="J42" s="13"/>
@@ -5923,7 +5923,7 @@
       <c r="G43" s="13"/>
       <c r="H43" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I43" s="13"/>
       <c r="J43" s="13"/>
@@ -5967,7 +5967,7 @@
       <c r="G44" s="13"/>
       <c r="H44" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I44" s="13"/>
       <c r="J44" s="13"/>
@@ -6011,7 +6011,7 @@
       <c r="G45" s="13"/>
       <c r="H45" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I45" s="13"/>
       <c r="J45" s="13"/>
@@ -6055,7 +6055,7 @@
       <c r="G46" s="13"/>
       <c r="H46" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I46" s="13"/>
       <c r="J46" s="13"/>
@@ -6099,7 +6099,7 @@
       <c r="G47" s="13"/>
       <c r="H47" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I47" s="13"/>
       <c r="J47" s="13"/>
@@ -6143,7 +6143,7 @@
       <c r="G48" s="13"/>
       <c r="H48" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I48" s="13"/>
       <c r="J48" s="13"/>
@@ -6187,7 +6187,7 @@
       <c r="G49" s="13"/>
       <c r="H49" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I49" s="13"/>
       <c r="J49" s="13"/>
@@ -6231,7 +6231,7 @@
       <c r="G50" s="13"/>
       <c r="H50" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I50" s="13"/>
       <c r="J50" s="13"/>
@@ -6275,7 +6275,7 @@
       <c r="G51" s="13"/>
       <c r="H51" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I51" s="13"/>
       <c r="J51" s="13"/>
@@ -6319,7 +6319,7 @@
       <c r="G52" s="13"/>
       <c r="H52" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I52" s="13"/>
       <c r="J52" s="13"/>
@@ -6363,7 +6363,7 @@
       <c r="G53" s="13"/>
       <c r="H53" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I53" s="13"/>
       <c r="J53" s="13"/>
@@ -6407,7 +6407,7 @@
       <c r="G54" s="13"/>
       <c r="H54" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I54" s="13"/>
       <c r="J54" s="13"/>
@@ -6451,7 +6451,7 @@
       <c r="G55" s="13"/>
       <c r="H55" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I55" s="13"/>
       <c r="J55" s="13"/>
@@ -6495,7 +6495,7 @@
       <c r="G56" s="13"/>
       <c r="H56" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I56" s="13"/>
       <c r="J56" s="13"/>
@@ -6539,7 +6539,7 @@
       <c r="G57" s="13"/>
       <c r="H57" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I57" s="13"/>
       <c r="J57" s="13"/>
@@ -6583,7 +6583,7 @@
       <c r="G58" s="13"/>
       <c r="H58" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I58" s="13"/>
       <c r="J58" s="13"/>
@@ -6627,7 +6627,7 @@
       <c r="G59" s="13"/>
       <c r="H59" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I59" s="13"/>
       <c r="J59" s="13"/>
@@ -6671,7 +6671,7 @@
       <c r="G60" s="13"/>
       <c r="H60" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I60" s="13"/>
       <c r="J60" s="13"/>
@@ -6715,7 +6715,7 @@
       <c r="G61" s="13"/>
       <c r="H61" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I61" s="13"/>
       <c r="J61" s="13"/>
@@ -6759,7 +6759,7 @@
       <c r="G62" s="13"/>
       <c r="H62" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I62" s="13"/>
       <c r="J62" s="13"/>
@@ -6803,7 +6803,7 @@
       <c r="G63" s="13"/>
       <c r="H63" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I63" s="13"/>
       <c r="J63" s="13"/>
@@ -6847,7 +6847,7 @@
       <c r="G64" s="13"/>
       <c r="H64" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I64" s="13"/>
       <c r="J64" s="13"/>
@@ -6891,7 +6891,7 @@
       <c r="G65" s="13"/>
       <c r="H65" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I65" s="13"/>
       <c r="J65" s="13"/>
@@ -6935,7 +6935,7 @@
       <c r="G66" s="13"/>
       <c r="H66" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I66" s="13"/>
       <c r="J66" s="13"/>
@@ -6979,7 +6979,7 @@
       <c r="G67" s="13"/>
       <c r="H67" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I67" s="13"/>
       <c r="J67" s="13"/>
@@ -7023,7 +7023,7 @@
       <c r="G68" s="13"/>
       <c r="H68" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I68" s="13"/>
       <c r="J68" s="13"/>
@@ -7067,7 +7067,7 @@
       <c r="G69" s="13"/>
       <c r="H69" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I69" s="13"/>
       <c r="J69" s="13"/>
@@ -7111,7 +7111,7 @@
       <c r="G70" s="13"/>
       <c r="H70" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I70" s="13"/>
       <c r="J70" s="13"/>
@@ -7155,7 +7155,7 @@
       <c r="G71" s="13"/>
       <c r="H71" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I71" s="13"/>
       <c r="J71" s="13"/>
@@ -7199,7 +7199,7 @@
       <c r="G72" s="13"/>
       <c r="H72" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I72" s="13"/>
       <c r="J72" s="13"/>
@@ -7243,7 +7243,7 @@
       <c r="G73" s="13"/>
       <c r="H73" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I73" s="13"/>
       <c r="J73" s="13"/>
@@ -7287,7 +7287,7 @@
       <c r="G74" s="13"/>
       <c r="H74" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I74" s="13"/>
       <c r="J74" s="13"/>
@@ -7330,8 +7330,8 @@
       <c r="F75" s="13"/>
       <c r="G75" s="13"/>
       <c r="H75" s="12" t="str">
-        <f t="shared" ref="H75:H138" si="2">L75&amp;"có hình dáng dạng "&amp;M75&amp;" chất liệu "&amp;N75&amp;" thành phần hóa chất: "&amp;O75&amp;" có kích thước "&amp;P75&amp;" dùng để "&amp;R75&amp;" cho "&amp;Q75</f>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="I75" s="13"/>
       <c r="J75" s="13"/>
@@ -7374,8 +7374,8 @@
       <c r="F76" s="13"/>
       <c r="G76" s="13"/>
       <c r="H76" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="I76" s="13"/>
       <c r="J76" s="13"/>
@@ -7418,8 +7418,8 @@
       <c r="F77" s="13"/>
       <c r="G77" s="13"/>
       <c r="H77" s="12" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <f t="shared" ref="H77:H140" si="2">IF(B77="","",L77&amp;"có hình dáng dạng "&amp;M77&amp;" chất liệu "&amp;N77&amp;" thành phần hóa chất: "&amp;O77&amp;" có kích thước "&amp;P77&amp;" dùng để "&amp;R77&amp;" cho "&amp;Q77)</f>
+        <v/>
       </c>
       <c r="I77" s="13"/>
       <c r="J77" s="13"/>
@@ -7463,7 +7463,7 @@
       <c r="G78" s="13"/>
       <c r="H78" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I78" s="13"/>
       <c r="J78" s="13"/>
@@ -7507,7 +7507,7 @@
       <c r="G79" s="13"/>
       <c r="H79" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I79" s="13"/>
       <c r="J79" s="13"/>
@@ -7551,7 +7551,7 @@
       <c r="G80" s="13"/>
       <c r="H80" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I80" s="13"/>
       <c r="J80" s="13"/>
@@ -7595,7 +7595,7 @@
       <c r="G81" s="13"/>
       <c r="H81" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I81" s="13"/>
       <c r="J81" s="13"/>
@@ -7639,7 +7639,7 @@
       <c r="G82" s="13"/>
       <c r="H82" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I82" s="13"/>
       <c r="J82" s="13"/>
@@ -7683,7 +7683,7 @@
       <c r="G83" s="13"/>
       <c r="H83" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I83" s="13"/>
       <c r="J83" s="13"/>
@@ -7727,7 +7727,7 @@
       <c r="G84" s="13"/>
       <c r="H84" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I84" s="13"/>
       <c r="J84" s="13"/>
@@ -7771,7 +7771,7 @@
       <c r="G85" s="13"/>
       <c r="H85" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I85" s="13"/>
       <c r="J85" s="13"/>
@@ -7815,7 +7815,7 @@
       <c r="G86" s="13"/>
       <c r="H86" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I86" s="13"/>
       <c r="J86" s="13"/>
@@ -7859,7 +7859,7 @@
       <c r="G87" s="13"/>
       <c r="H87" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I87" s="13"/>
       <c r="J87" s="13"/>
@@ -7903,7 +7903,7 @@
       <c r="G88" s="13"/>
       <c r="H88" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I88" s="13"/>
       <c r="J88" s="13"/>
@@ -7947,7 +7947,7 @@
       <c r="G89" s="13"/>
       <c r="H89" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I89" s="13"/>
       <c r="J89" s="13"/>
@@ -7991,7 +7991,7 @@
       <c r="G90" s="13"/>
       <c r="H90" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I90" s="13"/>
       <c r="J90" s="13"/>
@@ -8035,7 +8035,7 @@
       <c r="G91" s="13"/>
       <c r="H91" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I91" s="13"/>
       <c r="J91" s="13"/>
@@ -8079,7 +8079,7 @@
       <c r="G92" s="13"/>
       <c r="H92" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I92" s="13"/>
       <c r="J92" s="13"/>
@@ -8123,7 +8123,7 @@
       <c r="G93" s="13"/>
       <c r="H93" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I93" s="13"/>
       <c r="J93" s="13"/>
@@ -8167,7 +8167,7 @@
       <c r="G94" s="13"/>
       <c r="H94" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I94" s="13"/>
       <c r="J94" s="13"/>
@@ -8211,7 +8211,7 @@
       <c r="G95" s="13"/>
       <c r="H95" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I95" s="13"/>
       <c r="J95" s="13"/>
@@ -8255,7 +8255,7 @@
       <c r="G96" s="13"/>
       <c r="H96" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I96" s="13"/>
       <c r="J96" s="13"/>
@@ -8299,7 +8299,7 @@
       <c r="G97" s="13"/>
       <c r="H97" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I97" s="13"/>
       <c r="J97" s="13"/>
@@ -8343,7 +8343,7 @@
       <c r="G98" s="13"/>
       <c r="H98" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I98" s="13"/>
       <c r="J98" s="13"/>
@@ -8387,7 +8387,7 @@
       <c r="G99" s="13"/>
       <c r="H99" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I99" s="13"/>
       <c r="J99" s="13"/>
@@ -8431,7 +8431,7 @@
       <c r="G100" s="13"/>
       <c r="H100" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I100" s="13"/>
       <c r="J100" s="13"/>
@@ -8475,7 +8475,7 @@
       <c r="G101" s="13"/>
       <c r="H101" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I101" s="13"/>
       <c r="J101" s="13"/>
@@ -8519,7 +8519,7 @@
       <c r="G102" s="13"/>
       <c r="H102" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I102" s="13"/>
       <c r="J102" s="13"/>
@@ -8563,7 +8563,7 @@
       <c r="G103" s="13"/>
       <c r="H103" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I103" s="13"/>
       <c r="J103" s="13"/>
@@ -8607,7 +8607,7 @@
       <c r="G104" s="13"/>
       <c r="H104" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I104" s="13"/>
       <c r="J104" s="13"/>
@@ -8651,7 +8651,7 @@
       <c r="G105" s="13"/>
       <c r="H105" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I105" s="13"/>
       <c r="J105" s="13"/>
@@ -8695,7 +8695,7 @@
       <c r="G106" s="13"/>
       <c r="H106" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I106" s="13"/>
       <c r="J106" s="13"/>
@@ -8739,7 +8739,7 @@
       <c r="G107" s="13"/>
       <c r="H107" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I107" s="13"/>
       <c r="J107" s="13"/>
@@ -8783,7 +8783,7 @@
       <c r="G108" s="13"/>
       <c r="H108" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I108" s="13"/>
       <c r="J108" s="13"/>
@@ -8827,7 +8827,7 @@
       <c r="G109" s="13"/>
       <c r="H109" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I109" s="13"/>
       <c r="J109" s="13"/>
@@ -8871,7 +8871,7 @@
       <c r="G110" s="13"/>
       <c r="H110" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I110" s="13"/>
       <c r="J110" s="13"/>
@@ -8915,7 +8915,7 @@
       <c r="G111" s="13"/>
       <c r="H111" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I111" s="13"/>
       <c r="J111" s="13"/>
@@ -8959,7 +8959,7 @@
       <c r="G112" s="13"/>
       <c r="H112" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I112" s="13"/>
       <c r="J112" s="13"/>
@@ -9003,7 +9003,7 @@
       <c r="G113" s="13"/>
       <c r="H113" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I113" s="13"/>
       <c r="J113" s="13"/>
@@ -9047,7 +9047,7 @@
       <c r="G114" s="13"/>
       <c r="H114" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I114" s="13"/>
       <c r="J114" s="13"/>
@@ -9091,7 +9091,7 @@
       <c r="G115" s="13"/>
       <c r="H115" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I115" s="13"/>
       <c r="J115" s="13"/>
@@ -9135,7 +9135,7 @@
       <c r="G116" s="13"/>
       <c r="H116" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I116" s="13"/>
       <c r="J116" s="13"/>
@@ -9179,7 +9179,7 @@
       <c r="G117" s="13"/>
       <c r="H117" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I117" s="13"/>
       <c r="J117" s="13"/>
@@ -9223,7 +9223,7 @@
       <c r="G118" s="13"/>
       <c r="H118" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I118" s="13"/>
       <c r="J118" s="13"/>
@@ -9267,7 +9267,7 @@
       <c r="G119" s="13"/>
       <c r="H119" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I119" s="13"/>
       <c r="J119" s="13"/>
@@ -9311,7 +9311,7 @@
       <c r="G120" s="13"/>
       <c r="H120" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I120" s="13"/>
       <c r="J120" s="13"/>
@@ -9355,7 +9355,7 @@
       <c r="G121" s="13"/>
       <c r="H121" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I121" s="13"/>
       <c r="J121" s="13"/>
@@ -9399,7 +9399,7 @@
       <c r="G122" s="13"/>
       <c r="H122" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I122" s="13"/>
       <c r="J122" s="13"/>
@@ -9443,7 +9443,7 @@
       <c r="G123" s="13"/>
       <c r="H123" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I123" s="13"/>
       <c r="J123" s="13"/>
@@ -9487,7 +9487,7 @@
       <c r="G124" s="13"/>
       <c r="H124" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I124" s="13"/>
       <c r="J124" s="13"/>
@@ -9531,7 +9531,7 @@
       <c r="G125" s="13"/>
       <c r="H125" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I125" s="13"/>
       <c r="J125" s="13"/>
@@ -9575,7 +9575,7 @@
       <c r="G126" s="13"/>
       <c r="H126" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I126" s="13"/>
       <c r="J126" s="13"/>
@@ -9619,7 +9619,7 @@
       <c r="G127" s="13"/>
       <c r="H127" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I127" s="13"/>
       <c r="J127" s="13"/>
@@ -9663,7 +9663,7 @@
       <c r="G128" s="13"/>
       <c r="H128" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I128" s="13"/>
       <c r="J128" s="13"/>
@@ -9707,7 +9707,7 @@
       <c r="G129" s="13"/>
       <c r="H129" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I129" s="13"/>
       <c r="J129" s="13"/>
@@ -9751,7 +9751,7 @@
       <c r="G130" s="13"/>
       <c r="H130" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I130" s="13"/>
       <c r="J130" s="13"/>
@@ -9795,7 +9795,7 @@
       <c r="G131" s="13"/>
       <c r="H131" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I131" s="13"/>
       <c r="J131" s="13"/>
@@ -9839,7 +9839,7 @@
       <c r="G132" s="13"/>
       <c r="H132" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I132" s="13"/>
       <c r="J132" s="13"/>
@@ -9883,7 +9883,7 @@
       <c r="G133" s="13"/>
       <c r="H133" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I133" s="13"/>
       <c r="J133" s="13"/>
@@ -9927,7 +9927,7 @@
       <c r="G134" s="13"/>
       <c r="H134" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I134" s="13"/>
       <c r="J134" s="13"/>
@@ -9971,7 +9971,7 @@
       <c r="G135" s="13"/>
       <c r="H135" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I135" s="13"/>
       <c r="J135" s="13"/>
@@ -10015,7 +10015,7 @@
       <c r="G136" s="13"/>
       <c r="H136" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I136" s="13"/>
       <c r="J136" s="13"/>
@@ -10059,7 +10059,7 @@
       <c r="G137" s="13"/>
       <c r="H137" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I137" s="13"/>
       <c r="J137" s="13"/>
@@ -10103,7 +10103,7 @@
       <c r="G138" s="13"/>
       <c r="H138" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I138" s="13"/>
       <c r="J138" s="13"/>
@@ -10146,8 +10146,8 @@
       <c r="F139" s="13"/>
       <c r="G139" s="13"/>
       <c r="H139" s="12" t="str">
-        <f t="shared" ref="H139:H202" si="3">L139&amp;"có hình dáng dạng "&amp;M139&amp;" chất liệu "&amp;N139&amp;" thành phần hóa chất: "&amp;O139&amp;" có kích thước "&amp;P139&amp;" dùng để "&amp;R139&amp;" cho "&amp;Q139</f>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="I139" s="13"/>
       <c r="J139" s="13"/>
@@ -10190,8 +10190,8 @@
       <c r="F140" s="13"/>
       <c r="G140" s="13"/>
       <c r="H140" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <f t="shared" si="2"/>
+        <v/>
       </c>
       <c r="I140" s="13"/>
       <c r="J140" s="13"/>
@@ -10234,8 +10234,8 @@
       <c r="F141" s="13"/>
       <c r="G141" s="13"/>
       <c r="H141" s="12" t="str">
-        <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <f t="shared" ref="H141:H204" si="3">IF(B141="","",L141&amp;"có hình dáng dạng "&amp;M141&amp;" chất liệu "&amp;N141&amp;" thành phần hóa chất: "&amp;O141&amp;" có kích thước "&amp;P141&amp;" dùng để "&amp;R141&amp;" cho "&amp;Q141)</f>
+        <v/>
       </c>
       <c r="I141" s="13"/>
       <c r="J141" s="13"/>
@@ -10279,7 +10279,7 @@
       <c r="G142" s="13"/>
       <c r="H142" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I142" s="13"/>
       <c r="J142" s="13"/>
@@ -10323,7 +10323,7 @@
       <c r="G143" s="13"/>
       <c r="H143" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I143" s="13"/>
       <c r="J143" s="13"/>
@@ -10367,7 +10367,7 @@
       <c r="G144" s="13"/>
       <c r="H144" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I144" s="13"/>
       <c r="J144" s="13"/>
@@ -10411,7 +10411,7 @@
       <c r="G145" s="13"/>
       <c r="H145" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I145" s="13"/>
       <c r="J145" s="13"/>
@@ -10455,7 +10455,7 @@
       <c r="G146" s="13"/>
       <c r="H146" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I146" s="13"/>
       <c r="J146" s="13"/>
@@ -10499,7 +10499,7 @@
       <c r="G147" s="13"/>
       <c r="H147" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I147" s="13"/>
       <c r="J147" s="13"/>
@@ -10543,7 +10543,7 @@
       <c r="G148" s="13"/>
       <c r="H148" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I148" s="13"/>
       <c r="J148" s="13"/>
@@ -10587,7 +10587,7 @@
       <c r="G149" s="13"/>
       <c r="H149" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I149" s="13"/>
       <c r="J149" s="13"/>
@@ -10631,7 +10631,7 @@
       <c r="G150" s="13"/>
       <c r="H150" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I150" s="13"/>
       <c r="J150" s="13"/>
@@ -10675,7 +10675,7 @@
       <c r="G151" s="13"/>
       <c r="H151" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I151" s="13"/>
       <c r="J151" s="13"/>
@@ -10719,7 +10719,7 @@
       <c r="G152" s="13"/>
       <c r="H152" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I152" s="13"/>
       <c r="J152" s="13"/>
@@ -10763,7 +10763,7 @@
       <c r="G153" s="13"/>
       <c r="H153" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I153" s="13"/>
       <c r="J153" s="13"/>
@@ -10807,7 +10807,7 @@
       <c r="G154" s="13"/>
       <c r="H154" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I154" s="13"/>
       <c r="J154" s="13"/>
@@ -10851,7 +10851,7 @@
       <c r="G155" s="13"/>
       <c r="H155" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I155" s="13"/>
       <c r="J155" s="13"/>
@@ -10895,7 +10895,7 @@
       <c r="G156" s="13"/>
       <c r="H156" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I156" s="13"/>
       <c r="J156" s="13"/>
@@ -10939,7 +10939,7 @@
       <c r="G157" s="13"/>
       <c r="H157" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I157" s="13"/>
       <c r="J157" s="13"/>
@@ -10983,7 +10983,7 @@
       <c r="G158" s="13"/>
       <c r="H158" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I158" s="13"/>
       <c r="J158" s="13"/>
@@ -11027,7 +11027,7 @@
       <c r="G159" s="13"/>
       <c r="H159" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I159" s="13"/>
       <c r="J159" s="13"/>
@@ -11071,7 +11071,7 @@
       <c r="G160" s="13"/>
       <c r="H160" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I160" s="13"/>
       <c r="J160" s="13"/>
@@ -11115,7 +11115,7 @@
       <c r="G161" s="13"/>
       <c r="H161" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I161" s="13"/>
       <c r="J161" s="13"/>
@@ -11159,7 +11159,7 @@
       <c r="G162" s="13"/>
       <c r="H162" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I162" s="13"/>
       <c r="J162" s="13"/>
@@ -11203,7 +11203,7 @@
       <c r="G163" s="13"/>
       <c r="H163" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I163" s="13"/>
       <c r="J163" s="13"/>
@@ -11247,7 +11247,7 @@
       <c r="G164" s="13"/>
       <c r="H164" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I164" s="13"/>
       <c r="J164" s="13"/>
@@ -11291,7 +11291,7 @@
       <c r="G165" s="13"/>
       <c r="H165" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I165" s="13"/>
       <c r="J165" s="13"/>
@@ -11335,7 +11335,7 @@
       <c r="G166" s="13"/>
       <c r="H166" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I166" s="13"/>
       <c r="J166" s="13"/>
@@ -11379,7 +11379,7 @@
       <c r="G167" s="13"/>
       <c r="H167" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I167" s="13"/>
       <c r="J167" s="13"/>
@@ -11423,7 +11423,7 @@
       <c r="G168" s="13"/>
       <c r="H168" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I168" s="13"/>
       <c r="J168" s="13"/>
@@ -11467,7 +11467,7 @@
       <c r="G169" s="13"/>
       <c r="H169" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I169" s="13"/>
       <c r="J169" s="13"/>
@@ -11511,7 +11511,7 @@
       <c r="G170" s="13"/>
       <c r="H170" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I170" s="13"/>
       <c r="J170" s="13"/>
@@ -11555,7 +11555,7 @@
       <c r="G171" s="13"/>
       <c r="H171" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I171" s="13"/>
       <c r="J171" s="13"/>
@@ -11599,7 +11599,7 @@
       <c r="G172" s="13"/>
       <c r="H172" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I172" s="13"/>
       <c r="J172" s="13"/>
@@ -11643,7 +11643,7 @@
       <c r="G173" s="13"/>
       <c r="H173" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I173" s="13"/>
       <c r="J173" s="13"/>
@@ -11687,7 +11687,7 @@
       <c r="G174" s="13"/>
       <c r="H174" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I174" s="13"/>
       <c r="J174" s="13"/>
@@ -11731,7 +11731,7 @@
       <c r="G175" s="13"/>
       <c r="H175" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I175" s="13"/>
       <c r="J175" s="13"/>
@@ -11775,7 +11775,7 @@
       <c r="G176" s="13"/>
       <c r="H176" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I176" s="13"/>
       <c r="J176" s="13"/>
@@ -11819,7 +11819,7 @@
       <c r="G177" s="13"/>
       <c r="H177" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I177" s="13"/>
       <c r="J177" s="13"/>
@@ -11863,7 +11863,7 @@
       <c r="G178" s="13"/>
       <c r="H178" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I178" s="13"/>
       <c r="J178" s="13"/>
@@ -11907,7 +11907,7 @@
       <c r="G179" s="13"/>
       <c r="H179" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I179" s="13"/>
       <c r="J179" s="13"/>
@@ -11951,7 +11951,7 @@
       <c r="G180" s="13"/>
       <c r="H180" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I180" s="13"/>
       <c r="J180" s="13"/>
@@ -11995,7 +11995,7 @@
       <c r="G181" s="13"/>
       <c r="H181" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I181" s="13"/>
       <c r="J181" s="13"/>
@@ -12039,7 +12039,7 @@
       <c r="G182" s="13"/>
       <c r="H182" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I182" s="13"/>
       <c r="J182" s="13"/>
@@ -12083,7 +12083,7 @@
       <c r="G183" s="13"/>
       <c r="H183" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I183" s="13"/>
       <c r="J183" s="13"/>
@@ -12127,7 +12127,7 @@
       <c r="G184" s="13"/>
       <c r="H184" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I184" s="13"/>
       <c r="J184" s="13"/>
@@ -12171,7 +12171,7 @@
       <c r="G185" s="13"/>
       <c r="H185" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I185" s="13"/>
       <c r="J185" s="13"/>
@@ -12215,7 +12215,7 @@
       <c r="G186" s="13"/>
       <c r="H186" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I186" s="13"/>
       <c r="J186" s="13"/>
@@ -12259,7 +12259,7 @@
       <c r="G187" s="13"/>
       <c r="H187" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I187" s="13"/>
       <c r="J187" s="13"/>
@@ -12303,7 +12303,7 @@
       <c r="G188" s="13"/>
       <c r="H188" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I188" s="13"/>
       <c r="J188" s="13"/>
@@ -12347,7 +12347,7 @@
       <c r="G189" s="13"/>
       <c r="H189" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I189" s="13"/>
       <c r="J189" s="13"/>
@@ -12391,7 +12391,7 @@
       <c r="G190" s="13"/>
       <c r="H190" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I190" s="13"/>
       <c r="J190" s="13"/>
@@ -12435,7 +12435,7 @@
       <c r="G191" s="13"/>
       <c r="H191" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I191" s="13"/>
       <c r="J191" s="13"/>
@@ -12479,7 +12479,7 @@
       <c r="G192" s="13"/>
       <c r="H192" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I192" s="13"/>
       <c r="J192" s="13"/>
@@ -12523,7 +12523,7 @@
       <c r="G193" s="13"/>
       <c r="H193" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I193" s="13"/>
       <c r="J193" s="13"/>
@@ -12567,7 +12567,7 @@
       <c r="G194" s="13"/>
       <c r="H194" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I194" s="13"/>
       <c r="J194" s="13"/>
@@ -12611,7 +12611,7 @@
       <c r="G195" s="13"/>
       <c r="H195" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I195" s="13"/>
       <c r="J195" s="13"/>
@@ -12655,7 +12655,7 @@
       <c r="G196" s="13"/>
       <c r="H196" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I196" s="13"/>
       <c r="J196" s="13"/>
@@ -12699,7 +12699,7 @@
       <c r="G197" s="13"/>
       <c r="H197" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I197" s="13"/>
       <c r="J197" s="13"/>
@@ -12743,7 +12743,7 @@
       <c r="G198" s="13"/>
       <c r="H198" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I198" s="13"/>
       <c r="J198" s="13"/>
@@ -12787,7 +12787,7 @@
       <c r="G199" s="13"/>
       <c r="H199" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I199" s="13"/>
       <c r="J199" s="13"/>
@@ -12831,7 +12831,7 @@
       <c r="G200" s="13"/>
       <c r="H200" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I200" s="13"/>
       <c r="J200" s="13"/>
@@ -12875,7 +12875,7 @@
       <c r="G201" s="13"/>
       <c r="H201" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I201" s="13"/>
       <c r="J201" s="13"/>
@@ -12919,7 +12919,7 @@
       <c r="G202" s="13"/>
       <c r="H202" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I202" s="13"/>
       <c r="J202" s="13"/>
@@ -12962,8 +12962,8 @@
       <c r="F203" s="13"/>
       <c r="G203" s="13"/>
       <c r="H203" s="12" t="str">
-        <f t="shared" ref="H203:H266" si="4">L203&amp;"có hình dáng dạng "&amp;M203&amp;" chất liệu "&amp;N203&amp;" thành phần hóa chất: "&amp;O203&amp;" có kích thước "&amp;P203&amp;" dùng để "&amp;R203&amp;" cho "&amp;Q203</f>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="I203" s="13"/>
       <c r="J203" s="13"/>
@@ -13006,8 +13006,8 @@
       <c r="F204" s="13"/>
       <c r="G204" s="13"/>
       <c r="H204" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="I204" s="13"/>
       <c r="J204" s="13"/>
@@ -13050,8 +13050,8 @@
       <c r="F205" s="13"/>
       <c r="G205" s="13"/>
       <c r="H205" s="12" t="str">
-        <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <f t="shared" ref="H205:H268" si="4">IF(B205="","",L205&amp;"có hình dáng dạng "&amp;M205&amp;" chất liệu "&amp;N205&amp;" thành phần hóa chất: "&amp;O205&amp;" có kích thước "&amp;P205&amp;" dùng để "&amp;R205&amp;" cho "&amp;Q205)</f>
+        <v/>
       </c>
       <c r="I205" s="13"/>
       <c r="J205" s="13"/>
@@ -13095,7 +13095,7 @@
       <c r="G206" s="13"/>
       <c r="H206" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I206" s="13"/>
       <c r="J206" s="13"/>
@@ -13139,7 +13139,7 @@
       <c r="G207" s="13"/>
       <c r="H207" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I207" s="13"/>
       <c r="J207" s="13"/>
@@ -13183,7 +13183,7 @@
       <c r="G208" s="13"/>
       <c r="H208" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I208" s="13"/>
       <c r="J208" s="13"/>
@@ -13227,7 +13227,7 @@
       <c r="G209" s="13"/>
       <c r="H209" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I209" s="13"/>
       <c r="J209" s="13"/>
@@ -13271,7 +13271,7 @@
       <c r="G210" s="13"/>
       <c r="H210" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I210" s="13"/>
       <c r="J210" s="13"/>
@@ -13315,7 +13315,7 @@
       <c r="G211" s="13"/>
       <c r="H211" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I211" s="13"/>
       <c r="J211" s="13"/>
@@ -13359,7 +13359,7 @@
       <c r="G212" s="13"/>
       <c r="H212" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I212" s="13"/>
       <c r="J212" s="13"/>
@@ -13403,7 +13403,7 @@
       <c r="G213" s="13"/>
       <c r="H213" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I213" s="13"/>
       <c r="J213" s="13"/>
@@ -13447,7 +13447,7 @@
       <c r="G214" s="13"/>
       <c r="H214" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I214" s="13"/>
       <c r="J214" s="13"/>
@@ -13491,7 +13491,7 @@
       <c r="G215" s="13"/>
       <c r="H215" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I215" s="13"/>
       <c r="J215" s="13"/>
@@ -13535,7 +13535,7 @@
       <c r="G216" s="13"/>
       <c r="H216" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I216" s="13"/>
       <c r="J216" s="13"/>
@@ -13579,7 +13579,7 @@
       <c r="G217" s="13"/>
       <c r="H217" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I217" s="13"/>
       <c r="J217" s="13"/>
@@ -13623,7 +13623,7 @@
       <c r="G218" s="13"/>
       <c r="H218" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I218" s="13"/>
       <c r="J218" s="13"/>
@@ -13667,7 +13667,7 @@
       <c r="G219" s="13"/>
       <c r="H219" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I219" s="13"/>
       <c r="J219" s="13"/>
@@ -13711,7 +13711,7 @@
       <c r="G220" s="13"/>
       <c r="H220" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I220" s="13"/>
       <c r="J220" s="13"/>
@@ -13755,7 +13755,7 @@
       <c r="G221" s="13"/>
       <c r="H221" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I221" s="13"/>
       <c r="J221" s="13"/>
@@ -13799,7 +13799,7 @@
       <c r="G222" s="13"/>
       <c r="H222" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I222" s="13"/>
       <c r="J222" s="13"/>
@@ -13843,7 +13843,7 @@
       <c r="G223" s="13"/>
       <c r="H223" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I223" s="13"/>
       <c r="J223" s="13"/>
@@ -13887,7 +13887,7 @@
       <c r="G224" s="13"/>
       <c r="H224" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I224" s="13"/>
       <c r="J224" s="13"/>
@@ -13931,7 +13931,7 @@
       <c r="G225" s="13"/>
       <c r="H225" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I225" s="13"/>
       <c r="J225" s="13"/>
@@ -13975,7 +13975,7 @@
       <c r="G226" s="13"/>
       <c r="H226" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I226" s="13"/>
       <c r="J226" s="13"/>
@@ -14019,7 +14019,7 @@
       <c r="G227" s="13"/>
       <c r="H227" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I227" s="13"/>
       <c r="J227" s="13"/>
@@ -14063,7 +14063,7 @@
       <c r="G228" s="13"/>
       <c r="H228" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I228" s="13"/>
       <c r="J228" s="13"/>
@@ -14107,7 +14107,7 @@
       <c r="G229" s="13"/>
       <c r="H229" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I229" s="13"/>
       <c r="J229" s="13"/>
@@ -14151,7 +14151,7 @@
       <c r="G230" s="13"/>
       <c r="H230" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I230" s="13"/>
       <c r="J230" s="13"/>
@@ -14195,7 +14195,7 @@
       <c r="G231" s="13"/>
       <c r="H231" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I231" s="13"/>
       <c r="J231" s="13"/>
@@ -14239,7 +14239,7 @@
       <c r="G232" s="13"/>
       <c r="H232" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I232" s="13"/>
       <c r="J232" s="13"/>
@@ -14283,7 +14283,7 @@
       <c r="G233" s="13"/>
       <c r="H233" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I233" s="13"/>
       <c r="J233" s="13"/>
@@ -14327,7 +14327,7 @@
       <c r="G234" s="13"/>
       <c r="H234" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I234" s="13"/>
       <c r="J234" s="13"/>
@@ -14371,7 +14371,7 @@
       <c r="G235" s="13"/>
       <c r="H235" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I235" s="13"/>
       <c r="J235" s="13"/>
@@ -14415,7 +14415,7 @@
       <c r="G236" s="13"/>
       <c r="H236" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I236" s="13"/>
       <c r="J236" s="13"/>
@@ -14459,7 +14459,7 @@
       <c r="G237" s="13"/>
       <c r="H237" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I237" s="13"/>
       <c r="J237" s="13"/>
@@ -14503,7 +14503,7 @@
       <c r="G238" s="13"/>
       <c r="H238" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I238" s="13"/>
       <c r="J238" s="13"/>
@@ -14547,7 +14547,7 @@
       <c r="G239" s="13"/>
       <c r="H239" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I239" s="13"/>
       <c r="J239" s="13"/>
@@ -14591,7 +14591,7 @@
       <c r="G240" s="13"/>
       <c r="H240" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I240" s="13"/>
       <c r="J240" s="13"/>
@@ -14635,7 +14635,7 @@
       <c r="G241" s="13"/>
       <c r="H241" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I241" s="13"/>
       <c r="J241" s="13"/>
@@ -14679,7 +14679,7 @@
       <c r="G242" s="13"/>
       <c r="H242" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I242" s="13"/>
       <c r="J242" s="13"/>
@@ -14723,7 +14723,7 @@
       <c r="G243" s="13"/>
       <c r="H243" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I243" s="13"/>
       <c r="J243" s="13"/>
@@ -14767,7 +14767,7 @@
       <c r="G244" s="13"/>
       <c r="H244" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I244" s="13"/>
       <c r="J244" s="13"/>
@@ -14811,7 +14811,7 @@
       <c r="G245" s="13"/>
       <c r="H245" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I245" s="13"/>
       <c r="J245" s="13"/>
@@ -14855,7 +14855,7 @@
       <c r="G246" s="13"/>
       <c r="H246" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I246" s="13"/>
       <c r="J246" s="13"/>
@@ -14899,7 +14899,7 @@
       <c r="G247" s="13"/>
       <c r="H247" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I247" s="13"/>
       <c r="J247" s="13"/>
@@ -14943,7 +14943,7 @@
       <c r="G248" s="13"/>
       <c r="H248" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I248" s="13"/>
       <c r="J248" s="13"/>
@@ -14987,7 +14987,7 @@
       <c r="G249" s="13"/>
       <c r="H249" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I249" s="13"/>
       <c r="J249" s="13"/>
@@ -15031,7 +15031,7 @@
       <c r="G250" s="13"/>
       <c r="H250" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I250" s="13"/>
       <c r="J250" s="13"/>
@@ -15075,7 +15075,7 @@
       <c r="G251" s="13"/>
       <c r="H251" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I251" s="13"/>
       <c r="J251" s="13"/>
@@ -15119,7 +15119,7 @@
       <c r="G252" s="13"/>
       <c r="H252" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I252" s="13"/>
       <c r="J252" s="13"/>
@@ -15163,7 +15163,7 @@
       <c r="G253" s="13"/>
       <c r="H253" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I253" s="13"/>
       <c r="J253" s="13"/>
@@ -15207,7 +15207,7 @@
       <c r="G254" s="13"/>
       <c r="H254" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I254" s="13"/>
       <c r="J254" s="13"/>
@@ -15251,7 +15251,7 @@
       <c r="G255" s="13"/>
       <c r="H255" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I255" s="13"/>
       <c r="J255" s="13"/>
@@ -15295,7 +15295,7 @@
       <c r="G256" s="13"/>
       <c r="H256" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I256" s="13"/>
       <c r="J256" s="13"/>
@@ -15339,7 +15339,7 @@
       <c r="G257" s="13"/>
       <c r="H257" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I257" s="13"/>
       <c r="J257" s="13"/>
@@ -15383,7 +15383,7 @@
       <c r="G258" s="13"/>
       <c r="H258" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I258" s="13"/>
       <c r="J258" s="13"/>
@@ -15427,7 +15427,7 @@
       <c r="G259" s="13"/>
       <c r="H259" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I259" s="13"/>
       <c r="J259" s="13"/>
@@ -15471,7 +15471,7 @@
       <c r="G260" s="13"/>
       <c r="H260" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I260" s="13"/>
       <c r="J260" s="13"/>
@@ -15515,7 +15515,7 @@
       <c r="G261" s="13"/>
       <c r="H261" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I261" s="13"/>
       <c r="J261" s="13"/>
@@ -15559,7 +15559,7 @@
       <c r="G262" s="13"/>
       <c r="H262" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I262" s="13"/>
       <c r="J262" s="13"/>
@@ -15603,7 +15603,7 @@
       <c r="G263" s="13"/>
       <c r="H263" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I263" s="13"/>
       <c r="J263" s="13"/>
@@ -15647,7 +15647,7 @@
       <c r="G264" s="13"/>
       <c r="H264" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I264" s="13"/>
       <c r="J264" s="13"/>
@@ -15691,7 +15691,7 @@
       <c r="G265" s="13"/>
       <c r="H265" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I265" s="13"/>
       <c r="J265" s="13"/>
@@ -15735,7 +15735,7 @@
       <c r="G266" s="13"/>
       <c r="H266" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I266" s="13"/>
       <c r="J266" s="13"/>
@@ -15778,8 +15778,8 @@
       <c r="F267" s="13"/>
       <c r="G267" s="13"/>
       <c r="H267" s="12" t="str">
-        <f t="shared" ref="H267:H330" si="5">L267&amp;"có hình dáng dạng "&amp;M267&amp;" chất liệu "&amp;N267&amp;" thành phần hóa chất: "&amp;O267&amp;" có kích thước "&amp;P267&amp;" dùng để "&amp;R267&amp;" cho "&amp;Q267</f>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="I267" s="13"/>
       <c r="J267" s="13"/>
@@ -15822,8 +15822,8 @@
       <c r="F268" s="13"/>
       <c r="G268" s="13"/>
       <c r="H268" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <f t="shared" si="4"/>
+        <v/>
       </c>
       <c r="I268" s="13"/>
       <c r="J268" s="13"/>
@@ -15866,8 +15866,8 @@
       <c r="F269" s="13"/>
       <c r="G269" s="13"/>
       <c r="H269" s="12" t="str">
-        <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <f t="shared" ref="H269:H332" si="5">IF(B269="","",L269&amp;"có hình dáng dạng "&amp;M269&amp;" chất liệu "&amp;N269&amp;" thành phần hóa chất: "&amp;O269&amp;" có kích thước "&amp;P269&amp;" dùng để "&amp;R269&amp;" cho "&amp;Q269)</f>
+        <v/>
       </c>
       <c r="I269" s="13"/>
       <c r="J269" s="13"/>
@@ -15911,7 +15911,7 @@
       <c r="G270" s="13"/>
       <c r="H270" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I270" s="13"/>
       <c r="J270" s="13"/>
@@ -15955,7 +15955,7 @@
       <c r="G271" s="13"/>
       <c r="H271" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I271" s="13"/>
       <c r="J271" s="13"/>
@@ -15999,7 +15999,7 @@
       <c r="G272" s="13"/>
       <c r="H272" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I272" s="13"/>
       <c r="J272" s="13"/>
@@ -16043,7 +16043,7 @@
       <c r="G273" s="13"/>
       <c r="H273" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I273" s="13"/>
       <c r="J273" s="13"/>
@@ -16087,7 +16087,7 @@
       <c r="G274" s="13"/>
       <c r="H274" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I274" s="13"/>
       <c r="J274" s="13"/>
@@ -16131,7 +16131,7 @@
       <c r="G275" s="13"/>
       <c r="H275" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I275" s="13"/>
       <c r="J275" s="13"/>
@@ -16175,7 +16175,7 @@
       <c r="G276" s="13"/>
       <c r="H276" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I276" s="13"/>
       <c r="J276" s="13"/>
@@ -16219,7 +16219,7 @@
       <c r="G277" s="13"/>
       <c r="H277" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I277" s="13"/>
       <c r="J277" s="13"/>
@@ -16263,7 +16263,7 @@
       <c r="G278" s="13"/>
       <c r="H278" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I278" s="13"/>
       <c r="J278" s="13"/>
@@ -16307,7 +16307,7 @@
       <c r="G279" s="13"/>
       <c r="H279" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I279" s="13"/>
       <c r="J279" s="13"/>
@@ -16351,7 +16351,7 @@
       <c r="G280" s="13"/>
       <c r="H280" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I280" s="13"/>
       <c r="J280" s="13"/>
@@ -16395,7 +16395,7 @@
       <c r="G281" s="13"/>
       <c r="H281" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I281" s="13"/>
       <c r="J281" s="13"/>
@@ -16439,7 +16439,7 @@
       <c r="G282" s="13"/>
       <c r="H282" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I282" s="13"/>
       <c r="J282" s="13"/>
@@ -16483,7 +16483,7 @@
       <c r="G283" s="13"/>
       <c r="H283" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I283" s="13"/>
       <c r="J283" s="13"/>
@@ -16527,7 +16527,7 @@
       <c r="G284" s="13"/>
       <c r="H284" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I284" s="13"/>
       <c r="J284" s="13"/>
@@ -16571,7 +16571,7 @@
       <c r="G285" s="13"/>
       <c r="H285" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I285" s="13"/>
       <c r="J285" s="13"/>
@@ -16615,7 +16615,7 @@
       <c r="G286" s="13"/>
       <c r="H286" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I286" s="13"/>
       <c r="J286" s="13"/>
@@ -16659,7 +16659,7 @@
       <c r="G287" s="13"/>
       <c r="H287" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I287" s="13"/>
       <c r="J287" s="13"/>
@@ -16703,7 +16703,7 @@
       <c r="G288" s="13"/>
       <c r="H288" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I288" s="13"/>
       <c r="J288" s="13"/>
@@ -16747,7 +16747,7 @@
       <c r="G289" s="13"/>
       <c r="H289" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I289" s="13"/>
       <c r="J289" s="13"/>
@@ -16791,7 +16791,7 @@
       <c r="G290" s="13"/>
       <c r="H290" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I290" s="13"/>
       <c r="J290" s="13"/>
@@ -16835,7 +16835,7 @@
       <c r="G291" s="13"/>
       <c r="H291" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I291" s="13"/>
       <c r="J291" s="13"/>
@@ -16879,7 +16879,7 @@
       <c r="G292" s="13"/>
       <c r="H292" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I292" s="13"/>
       <c r="J292" s="13"/>
@@ -16923,7 +16923,7 @@
       <c r="G293" s="13"/>
       <c r="H293" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I293" s="13"/>
       <c r="J293" s="13"/>
@@ -16967,7 +16967,7 @@
       <c r="G294" s="13"/>
       <c r="H294" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I294" s="13"/>
       <c r="J294" s="13"/>
@@ -17011,7 +17011,7 @@
       <c r="G295" s="13"/>
       <c r="H295" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I295" s="13"/>
       <c r="J295" s="13"/>
@@ -17055,7 +17055,7 @@
       <c r="G296" s="13"/>
       <c r="H296" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I296" s="13"/>
       <c r="J296" s="13"/>
@@ -17099,7 +17099,7 @@
       <c r="G297" s="13"/>
       <c r="H297" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I297" s="13"/>
       <c r="J297" s="13"/>
@@ -17143,7 +17143,7 @@
       <c r="G298" s="13"/>
       <c r="H298" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I298" s="13"/>
       <c r="J298" s="13"/>
@@ -17187,7 +17187,7 @@
       <c r="G299" s="13"/>
       <c r="H299" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I299" s="13"/>
       <c r="J299" s="13"/>
@@ -17231,7 +17231,7 @@
       <c r="G300" s="13"/>
       <c r="H300" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I300" s="13"/>
       <c r="J300" s="13"/>
@@ -17275,7 +17275,7 @@
       <c r="G301" s="13"/>
       <c r="H301" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I301" s="13"/>
       <c r="J301" s="13"/>
@@ -17319,7 +17319,7 @@
       <c r="G302" s="13"/>
       <c r="H302" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I302" s="13"/>
       <c r="J302" s="13"/>
@@ -17363,7 +17363,7 @@
       <c r="G303" s="13"/>
       <c r="H303" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I303" s="13"/>
       <c r="J303" s="13"/>
@@ -17407,7 +17407,7 @@
       <c r="G304" s="13"/>
       <c r="H304" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I304" s="13"/>
       <c r="J304" s="13"/>
@@ -17451,7 +17451,7 @@
       <c r="G305" s="13"/>
       <c r="H305" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I305" s="13"/>
       <c r="J305" s="13"/>
@@ -17495,7 +17495,7 @@
       <c r="G306" s="13"/>
       <c r="H306" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I306" s="13"/>
       <c r="J306" s="13"/>
@@ -17539,7 +17539,7 @@
       <c r="G307" s="13"/>
       <c r="H307" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I307" s="13"/>
       <c r="J307" s="13"/>
@@ -17583,7 +17583,7 @@
       <c r="G308" s="13"/>
       <c r="H308" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I308" s="13"/>
       <c r="J308" s="13"/>
@@ -17627,7 +17627,7 @@
       <c r="G309" s="13"/>
       <c r="H309" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I309" s="13"/>
       <c r="J309" s="13"/>
@@ -17671,7 +17671,7 @@
       <c r="G310" s="13"/>
       <c r="H310" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I310" s="13"/>
       <c r="J310" s="13"/>
@@ -17715,7 +17715,7 @@
       <c r="G311" s="13"/>
       <c r="H311" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I311" s="13"/>
       <c r="J311" s="13"/>
@@ -17759,7 +17759,7 @@
       <c r="G312" s="13"/>
       <c r="H312" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I312" s="13"/>
       <c r="J312" s="13"/>
@@ -17803,7 +17803,7 @@
       <c r="G313" s="13"/>
       <c r="H313" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I313" s="13"/>
       <c r="J313" s="13"/>
@@ -17847,7 +17847,7 @@
       <c r="G314" s="13"/>
       <c r="H314" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I314" s="13"/>
       <c r="J314" s="13"/>
@@ -17891,7 +17891,7 @@
       <c r="G315" s="13"/>
       <c r="H315" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I315" s="13"/>
       <c r="J315" s="13"/>
@@ -17935,7 +17935,7 @@
       <c r="G316" s="13"/>
       <c r="H316" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I316" s="13"/>
       <c r="J316" s="13"/>
@@ -17979,7 +17979,7 @@
       <c r="G317" s="13"/>
       <c r="H317" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I317" s="13"/>
       <c r="J317" s="13"/>
@@ -18023,7 +18023,7 @@
       <c r="G318" s="13"/>
       <c r="H318" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I318" s="13"/>
       <c r="J318" s="13"/>
@@ -18067,7 +18067,7 @@
       <c r="G319" s="13"/>
       <c r="H319" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I319" s="13"/>
       <c r="J319" s="13"/>
@@ -18111,7 +18111,7 @@
       <c r="G320" s="13"/>
       <c r="H320" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I320" s="13"/>
       <c r="J320" s="13"/>
@@ -18155,7 +18155,7 @@
       <c r="G321" s="13"/>
       <c r="H321" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I321" s="13"/>
       <c r="J321" s="13"/>
@@ -18199,7 +18199,7 @@
       <c r="G322" s="13"/>
       <c r="H322" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I322" s="13"/>
       <c r="J322" s="13"/>
@@ -18243,7 +18243,7 @@
       <c r="G323" s="13"/>
       <c r="H323" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I323" s="13"/>
       <c r="J323" s="13"/>
@@ -18287,7 +18287,7 @@
       <c r="G324" s="13"/>
       <c r="H324" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I324" s="13"/>
       <c r="J324" s="13"/>
@@ -18331,7 +18331,7 @@
       <c r="G325" s="13"/>
       <c r="H325" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I325" s="13"/>
       <c r="J325" s="13"/>
@@ -18375,7 +18375,7 @@
       <c r="G326" s="13"/>
       <c r="H326" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I326" s="13"/>
       <c r="J326" s="13"/>
@@ -18419,7 +18419,7 @@
       <c r="G327" s="13"/>
       <c r="H327" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I327" s="13"/>
       <c r="J327" s="13"/>
@@ -18463,7 +18463,7 @@
       <c r="G328" s="13"/>
       <c r="H328" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I328" s="13"/>
       <c r="J328" s="13"/>
@@ -18507,7 +18507,7 @@
       <c r="G329" s="13"/>
       <c r="H329" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I329" s="13"/>
       <c r="J329" s="13"/>
@@ -18551,7 +18551,7 @@
       <c r="G330" s="13"/>
       <c r="H330" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I330" s="13"/>
       <c r="J330" s="13"/>
@@ -18594,8 +18594,8 @@
       <c r="F331" s="13"/>
       <c r="G331" s="13"/>
       <c r="H331" s="12" t="str">
-        <f t="shared" ref="H331:H394" si="6">L331&amp;"có hình dáng dạng "&amp;M331&amp;" chất liệu "&amp;N331&amp;" thành phần hóa chất: "&amp;O331&amp;" có kích thước "&amp;P331&amp;" dùng để "&amp;R331&amp;" cho "&amp;Q331</f>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="I331" s="13"/>
       <c r="J331" s="13"/>
@@ -18638,8 +18638,8 @@
       <c r="F332" s="13"/>
       <c r="G332" s="13"/>
       <c r="H332" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <f t="shared" si="5"/>
+        <v/>
       </c>
       <c r="I332" s="13"/>
       <c r="J332" s="13"/>
@@ -18682,8 +18682,8 @@
       <c r="F333" s="13"/>
       <c r="G333" s="13"/>
       <c r="H333" s="12" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <f t="shared" ref="H333:H396" si="6">IF(B333="","",L333&amp;"có hình dáng dạng "&amp;M333&amp;" chất liệu "&amp;N333&amp;" thành phần hóa chất: "&amp;O333&amp;" có kích thước "&amp;P333&amp;" dùng để "&amp;R333&amp;" cho "&amp;Q333)</f>
+        <v/>
       </c>
       <c r="I333" s="13"/>
       <c r="J333" s="13"/>
@@ -18727,7 +18727,7 @@
       <c r="G334" s="13"/>
       <c r="H334" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I334" s="13"/>
       <c r="J334" s="13"/>
@@ -18771,7 +18771,7 @@
       <c r="G335" s="13"/>
       <c r="H335" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I335" s="13"/>
       <c r="J335" s="13"/>
@@ -18815,7 +18815,7 @@
       <c r="G336" s="13"/>
       <c r="H336" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I336" s="13"/>
       <c r="J336" s="13"/>
@@ -18859,7 +18859,7 @@
       <c r="G337" s="13"/>
       <c r="H337" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I337" s="13"/>
       <c r="J337" s="13"/>
@@ -18903,7 +18903,7 @@
       <c r="G338" s="13"/>
       <c r="H338" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I338" s="13"/>
       <c r="J338" s="13"/>
@@ -18947,7 +18947,7 @@
       <c r="G339" s="13"/>
       <c r="H339" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I339" s="13"/>
       <c r="J339" s="13"/>
@@ -18991,7 +18991,7 @@
       <c r="G340" s="13"/>
       <c r="H340" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I340" s="13"/>
       <c r="J340" s="13"/>
@@ -19035,7 +19035,7 @@
       <c r="G341" s="13"/>
       <c r="H341" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I341" s="13"/>
       <c r="J341" s="13"/>
@@ -19079,7 +19079,7 @@
       <c r="G342" s="13"/>
       <c r="H342" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I342" s="13"/>
       <c r="J342" s="13"/>
@@ -19123,7 +19123,7 @@
       <c r="G343" s="13"/>
       <c r="H343" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I343" s="13"/>
       <c r="J343" s="13"/>
@@ -19167,7 +19167,7 @@
       <c r="G344" s="13"/>
       <c r="H344" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I344" s="13"/>
       <c r="J344" s="13"/>
@@ -19211,7 +19211,7 @@
       <c r="G345" s="13"/>
       <c r="H345" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I345" s="13"/>
       <c r="J345" s="13"/>
@@ -19255,7 +19255,7 @@
       <c r="G346" s="13"/>
       <c r="H346" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I346" s="13"/>
       <c r="J346" s="13"/>
@@ -19299,7 +19299,7 @@
       <c r="G347" s="13"/>
       <c r="H347" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I347" s="13"/>
       <c r="J347" s="13"/>
@@ -19343,7 +19343,7 @@
       <c r="G348" s="13"/>
       <c r="H348" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I348" s="13"/>
       <c r="J348" s="13"/>
@@ -19387,7 +19387,7 @@
       <c r="G349" s="13"/>
       <c r="H349" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I349" s="13"/>
       <c r="J349" s="13"/>
@@ -19431,7 +19431,7 @@
       <c r="G350" s="13"/>
       <c r="H350" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I350" s="13"/>
       <c r="J350" s="13"/>
@@ -19475,7 +19475,7 @@
       <c r="G351" s="13"/>
       <c r="H351" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I351" s="13"/>
       <c r="J351" s="13"/>
@@ -19519,7 +19519,7 @@
       <c r="G352" s="13"/>
       <c r="H352" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I352" s="13"/>
       <c r="J352" s="13"/>
@@ -19563,7 +19563,7 @@
       <c r="G353" s="13"/>
       <c r="H353" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I353" s="13"/>
       <c r="J353" s="13"/>
@@ -19607,7 +19607,7 @@
       <c r="G354" s="13"/>
       <c r="H354" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I354" s="13"/>
       <c r="J354" s="13"/>
@@ -19651,7 +19651,7 @@
       <c r="G355" s="13"/>
       <c r="H355" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I355" s="13"/>
       <c r="J355" s="13"/>
@@ -19695,7 +19695,7 @@
       <c r="G356" s="13"/>
       <c r="H356" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I356" s="13"/>
       <c r="J356" s="13"/>
@@ -19739,7 +19739,7 @@
       <c r="G357" s="13"/>
       <c r="H357" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I357" s="13"/>
       <c r="J357" s="13"/>
@@ -19783,7 +19783,7 @@
       <c r="G358" s="13"/>
       <c r="H358" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I358" s="13"/>
       <c r="J358" s="13"/>
@@ -19827,7 +19827,7 @@
       <c r="G359" s="13"/>
       <c r="H359" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I359" s="13"/>
       <c r="J359" s="13"/>
@@ -19871,7 +19871,7 @@
       <c r="G360" s="13"/>
       <c r="H360" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I360" s="13"/>
       <c r="J360" s="13"/>
@@ -19915,7 +19915,7 @@
       <c r="G361" s="13"/>
       <c r="H361" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I361" s="13"/>
       <c r="J361" s="13"/>
@@ -19959,7 +19959,7 @@
       <c r="G362" s="13"/>
       <c r="H362" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I362" s="13"/>
       <c r="J362" s="13"/>
@@ -20003,7 +20003,7 @@
       <c r="G363" s="13"/>
       <c r="H363" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I363" s="13"/>
       <c r="J363" s="13"/>
@@ -20047,7 +20047,7 @@
       <c r="G364" s="13"/>
       <c r="H364" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I364" s="13"/>
       <c r="J364" s="13"/>
@@ -20091,7 +20091,7 @@
       <c r="G365" s="13"/>
       <c r="H365" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I365" s="13"/>
       <c r="J365" s="13"/>
@@ -20135,7 +20135,7 @@
       <c r="G366" s="13"/>
       <c r="H366" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I366" s="13"/>
       <c r="J366" s="13"/>
@@ -20179,7 +20179,7 @@
       <c r="G367" s="13"/>
       <c r="H367" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I367" s="13"/>
       <c r="J367" s="13"/>
@@ -20223,7 +20223,7 @@
       <c r="G368" s="13"/>
       <c r="H368" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I368" s="13"/>
       <c r="J368" s="13"/>
@@ -20267,7 +20267,7 @@
       <c r="G369" s="13"/>
       <c r="H369" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I369" s="13"/>
       <c r="J369" s="13"/>
@@ -20311,7 +20311,7 @@
       <c r="G370" s="13"/>
       <c r="H370" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I370" s="13"/>
       <c r="J370" s="13"/>
@@ -20355,7 +20355,7 @@
       <c r="G371" s="13"/>
       <c r="H371" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I371" s="13"/>
       <c r="J371" s="13"/>
@@ -20399,7 +20399,7 @@
       <c r="G372" s="13"/>
       <c r="H372" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I372" s="13"/>
       <c r="J372" s="13"/>
@@ -20443,7 +20443,7 @@
       <c r="G373" s="13"/>
       <c r="H373" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I373" s="13"/>
       <c r="J373" s="13"/>
@@ -20487,7 +20487,7 @@
       <c r="G374" s="13"/>
       <c r="H374" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I374" s="13"/>
       <c r="J374" s="13"/>
@@ -20531,7 +20531,7 @@
       <c r="G375" s="13"/>
       <c r="H375" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I375" s="13"/>
       <c r="J375" s="13"/>
@@ -20575,7 +20575,7 @@
       <c r="G376" s="13"/>
       <c r="H376" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I376" s="13"/>
       <c r="J376" s="13"/>
@@ -20619,7 +20619,7 @@
       <c r="G377" s="13"/>
       <c r="H377" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I377" s="13"/>
       <c r="J377" s="13"/>
@@ -20663,7 +20663,7 @@
       <c r="G378" s="13"/>
       <c r="H378" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I378" s="13"/>
       <c r="J378" s="13"/>
@@ -20707,7 +20707,7 @@
       <c r="G379" s="13"/>
       <c r="H379" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I379" s="13"/>
       <c r="J379" s="13"/>
@@ -20751,7 +20751,7 @@
       <c r="G380" s="13"/>
       <c r="H380" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I380" s="13"/>
       <c r="J380" s="13"/>
@@ -20795,7 +20795,7 @@
       <c r="G381" s="13"/>
       <c r="H381" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I381" s="13"/>
       <c r="J381" s="13"/>
@@ -20839,7 +20839,7 @@
       <c r="G382" s="13"/>
       <c r="H382" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I382" s="13"/>
       <c r="J382" s="13"/>
@@ -20883,7 +20883,7 @@
       <c r="G383" s="13"/>
       <c r="H383" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I383" s="13"/>
       <c r="J383" s="13"/>
@@ -20927,7 +20927,7 @@
       <c r="G384" s="13"/>
       <c r="H384" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I384" s="13"/>
       <c r="J384" s="13"/>
@@ -20971,7 +20971,7 @@
       <c r="G385" s="13"/>
       <c r="H385" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I385" s="13"/>
       <c r="J385" s="13"/>
@@ -21015,7 +21015,7 @@
       <c r="G386" s="13"/>
       <c r="H386" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I386" s="13"/>
       <c r="J386" s="13"/>
@@ -21059,7 +21059,7 @@
       <c r="G387" s="13"/>
       <c r="H387" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I387" s="13"/>
       <c r="J387" s="13"/>
@@ -21103,7 +21103,7 @@
       <c r="G388" s="13"/>
       <c r="H388" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I388" s="13"/>
       <c r="J388" s="13"/>
@@ -21147,7 +21147,7 @@
       <c r="G389" s="13"/>
       <c r="H389" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I389" s="13"/>
       <c r="J389" s="13"/>
@@ -21191,7 +21191,7 @@
       <c r="G390" s="13"/>
       <c r="H390" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I390" s="13"/>
       <c r="J390" s="13"/>
@@ -21235,7 +21235,7 @@
       <c r="G391" s="13"/>
       <c r="H391" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I391" s="13"/>
       <c r="J391" s="13"/>
@@ -21279,7 +21279,7 @@
       <c r="G392" s="13"/>
       <c r="H392" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I392" s="13"/>
       <c r="J392" s="13"/>
@@ -21323,7 +21323,7 @@
       <c r="G393" s="13"/>
       <c r="H393" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I393" s="13"/>
       <c r="J393" s="13"/>
@@ -21367,7 +21367,7 @@
       <c r="G394" s="13"/>
       <c r="H394" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I394" s="13"/>
       <c r="J394" s="13"/>
@@ -21410,8 +21410,8 @@
       <c r="F395" s="13"/>
       <c r="G395" s="13"/>
       <c r="H395" s="12" t="str">
-        <f t="shared" ref="H395:H458" si="7">L395&amp;"có hình dáng dạng "&amp;M395&amp;" chất liệu "&amp;N395&amp;" thành phần hóa chất: "&amp;O395&amp;" có kích thước "&amp;P395&amp;" dùng để "&amp;R395&amp;" cho "&amp;Q395</f>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="I395" s="13"/>
       <c r="J395" s="13"/>
@@ -21454,8 +21454,8 @@
       <c r="F396" s="13"/>
       <c r="G396" s="13"/>
       <c r="H396" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="I396" s="13"/>
       <c r="J396" s="13"/>
@@ -21498,8 +21498,8 @@
       <c r="F397" s="13"/>
       <c r="G397" s="13"/>
       <c r="H397" s="12" t="str">
-        <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <f t="shared" ref="H397:H460" si="7">IF(B397="","",L397&amp;"có hình dáng dạng "&amp;M397&amp;" chất liệu "&amp;N397&amp;" thành phần hóa chất: "&amp;O397&amp;" có kích thước "&amp;P397&amp;" dùng để "&amp;R397&amp;" cho "&amp;Q397)</f>
+        <v/>
       </c>
       <c r="I397" s="13"/>
       <c r="J397" s="13"/>
@@ -21543,7 +21543,7 @@
       <c r="G398" s="13"/>
       <c r="H398" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I398" s="13"/>
       <c r="J398" s="13"/>
@@ -21587,7 +21587,7 @@
       <c r="G399" s="13"/>
       <c r="H399" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I399" s="13"/>
       <c r="J399" s="13"/>
@@ -21631,7 +21631,7 @@
       <c r="G400" s="13"/>
       <c r="H400" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I400" s="13"/>
       <c r="J400" s="13"/>
@@ -21675,7 +21675,7 @@
       <c r="G401" s="13"/>
       <c r="H401" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I401" s="13"/>
       <c r="J401" s="13"/>
@@ -21719,7 +21719,7 @@
       <c r="G402" s="13"/>
       <c r="H402" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I402" s="13"/>
       <c r="J402" s="13"/>
@@ -21763,7 +21763,7 @@
       <c r="G403" s="13"/>
       <c r="H403" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I403" s="13"/>
       <c r="J403" s="13"/>
@@ -21807,7 +21807,7 @@
       <c r="G404" s="13"/>
       <c r="H404" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I404" s="13"/>
       <c r="J404" s="13"/>
@@ -21851,7 +21851,7 @@
       <c r="G405" s="13"/>
       <c r="H405" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I405" s="13"/>
       <c r="J405" s="13"/>
@@ -21895,7 +21895,7 @@
       <c r="G406" s="13"/>
       <c r="H406" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I406" s="13"/>
       <c r="J406" s="13"/>
@@ -21939,7 +21939,7 @@
       <c r="G407" s="13"/>
       <c r="H407" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I407" s="13"/>
       <c r="J407" s="13"/>
@@ -21983,7 +21983,7 @@
       <c r="G408" s="13"/>
       <c r="H408" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I408" s="13"/>
       <c r="J408" s="13"/>
@@ -22027,7 +22027,7 @@
       <c r="G409" s="13"/>
       <c r="H409" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I409" s="13"/>
       <c r="J409" s="13"/>
@@ -22071,7 +22071,7 @@
       <c r="G410" s="13"/>
       <c r="H410" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I410" s="13"/>
       <c r="J410" s="13"/>
@@ -22115,7 +22115,7 @@
       <c r="G411" s="13"/>
       <c r="H411" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I411" s="13"/>
       <c r="J411" s="13"/>
@@ -22159,7 +22159,7 @@
       <c r="G412" s="13"/>
       <c r="H412" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I412" s="13"/>
       <c r="J412" s="13"/>
@@ -22203,7 +22203,7 @@
       <c r="G413" s="13"/>
       <c r="H413" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I413" s="13"/>
       <c r="J413" s="13"/>
@@ -22247,7 +22247,7 @@
       <c r="G414" s="13"/>
       <c r="H414" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I414" s="13"/>
       <c r="J414" s="13"/>
@@ -22291,7 +22291,7 @@
       <c r="G415" s="13"/>
       <c r="H415" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I415" s="13"/>
       <c r="J415" s="13"/>
@@ -22335,7 +22335,7 @@
       <c r="G416" s="13"/>
       <c r="H416" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I416" s="13"/>
       <c r="J416" s="13"/>
@@ -22379,7 +22379,7 @@
       <c r="G417" s="13"/>
       <c r="H417" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I417" s="13"/>
       <c r="J417" s="13"/>
@@ -22423,7 +22423,7 @@
       <c r="G418" s="13"/>
       <c r="H418" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I418" s="13"/>
       <c r="J418" s="13"/>
@@ -22467,7 +22467,7 @@
       <c r="G419" s="13"/>
       <c r="H419" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I419" s="13"/>
       <c r="J419" s="13"/>
@@ -22511,7 +22511,7 @@
       <c r="G420" s="13"/>
       <c r="H420" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I420" s="13"/>
       <c r="J420" s="13"/>
@@ -22555,7 +22555,7 @@
       <c r="G421" s="13"/>
       <c r="H421" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I421" s="13"/>
       <c r="J421" s="13"/>
@@ -22599,7 +22599,7 @@
       <c r="G422" s="13"/>
       <c r="H422" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I422" s="13"/>
       <c r="J422" s="13"/>
@@ -22643,7 +22643,7 @@
       <c r="G423" s="13"/>
       <c r="H423" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I423" s="13"/>
       <c r="J423" s="13"/>
@@ -22687,7 +22687,7 @@
       <c r="G424" s="13"/>
       <c r="H424" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I424" s="13"/>
       <c r="J424" s="13"/>
@@ -22731,7 +22731,7 @@
       <c r="G425" s="13"/>
       <c r="H425" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I425" s="13"/>
       <c r="J425" s="13"/>
@@ -22775,7 +22775,7 @@
       <c r="G426" s="13"/>
       <c r="H426" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I426" s="13"/>
       <c r="J426" s="13"/>
@@ -22819,7 +22819,7 @@
       <c r="G427" s="13"/>
       <c r="H427" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I427" s="13"/>
       <c r="J427" s="13"/>
@@ -22863,7 +22863,7 @@
       <c r="G428" s="13"/>
       <c r="H428" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I428" s="13"/>
       <c r="J428" s="13"/>
@@ -22907,7 +22907,7 @@
       <c r="G429" s="13"/>
       <c r="H429" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I429" s="13"/>
       <c r="J429" s="13"/>
@@ -22951,7 +22951,7 @@
       <c r="G430" s="13"/>
       <c r="H430" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I430" s="13"/>
       <c r="J430" s="13"/>
@@ -22995,7 +22995,7 @@
       <c r="G431" s="13"/>
       <c r="H431" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I431" s="13"/>
       <c r="J431" s="13"/>
@@ -23039,7 +23039,7 @@
       <c r="G432" s="13"/>
       <c r="H432" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I432" s="13"/>
       <c r="J432" s="13"/>
@@ -23083,7 +23083,7 @@
       <c r="G433" s="13"/>
       <c r="H433" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I433" s="13"/>
       <c r="J433" s="13"/>
@@ -23127,7 +23127,7 @@
       <c r="G434" s="13"/>
       <c r="H434" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I434" s="13"/>
       <c r="J434" s="13"/>
@@ -23171,7 +23171,7 @@
       <c r="G435" s="13"/>
       <c r="H435" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I435" s="13"/>
       <c r="J435" s="13"/>
@@ -23215,7 +23215,7 @@
       <c r="G436" s="13"/>
       <c r="H436" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I436" s="13"/>
       <c r="J436" s="13"/>
@@ -23259,7 +23259,7 @@
       <c r="G437" s="13"/>
       <c r="H437" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I437" s="13"/>
       <c r="J437" s="13"/>
@@ -23303,7 +23303,7 @@
       <c r="G438" s="13"/>
       <c r="H438" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I438" s="13"/>
       <c r="J438" s="13"/>
@@ -23347,7 +23347,7 @@
       <c r="G439" s="13"/>
       <c r="H439" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I439" s="13"/>
       <c r="J439" s="13"/>
@@ -23391,7 +23391,7 @@
       <c r="G440" s="13"/>
       <c r="H440" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I440" s="13"/>
       <c r="J440" s="13"/>
@@ -23435,7 +23435,7 @@
       <c r="G441" s="13"/>
       <c r="H441" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I441" s="13"/>
       <c r="J441" s="13"/>
@@ -23479,7 +23479,7 @@
       <c r="G442" s="13"/>
       <c r="H442" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I442" s="13"/>
       <c r="J442" s="13"/>
@@ -23523,7 +23523,7 @@
       <c r="G443" s="13"/>
       <c r="H443" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I443" s="13"/>
       <c r="J443" s="13"/>
@@ -23567,7 +23567,7 @@
       <c r="G444" s="13"/>
       <c r="H444" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I444" s="13"/>
       <c r="J444" s="13"/>
@@ -23611,7 +23611,7 @@
       <c r="G445" s="13"/>
       <c r="H445" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I445" s="13"/>
       <c r="J445" s="13"/>
@@ -23655,7 +23655,7 @@
       <c r="G446" s="13"/>
       <c r="H446" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I446" s="13"/>
       <c r="J446" s="13"/>
@@ -23699,7 +23699,7 @@
       <c r="G447" s="13"/>
       <c r="H447" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I447" s="13"/>
       <c r="J447" s="13"/>
@@ -23743,7 +23743,7 @@
       <c r="G448" s="13"/>
       <c r="H448" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I448" s="13"/>
       <c r="J448" s="13"/>
@@ -23787,7 +23787,7 @@
       <c r="G449" s="13"/>
       <c r="H449" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I449" s="13"/>
       <c r="J449" s="13"/>
@@ -23831,7 +23831,7 @@
       <c r="G450" s="13"/>
       <c r="H450" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I450" s="13"/>
       <c r="J450" s="13"/>
@@ -23875,7 +23875,7 @@
       <c r="G451" s="13"/>
       <c r="H451" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I451" s="13"/>
       <c r="J451" s="13"/>
@@ -23919,7 +23919,7 @@
       <c r="G452" s="13"/>
       <c r="H452" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I452" s="13"/>
       <c r="J452" s="13"/>
@@ -23963,7 +23963,7 @@
       <c r="G453" s="13"/>
       <c r="H453" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I453" s="13"/>
       <c r="J453" s="13"/>
@@ -24007,7 +24007,7 @@
       <c r="G454" s="13"/>
       <c r="H454" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I454" s="13"/>
       <c r="J454" s="13"/>
@@ -24051,7 +24051,7 @@
       <c r="G455" s="13"/>
       <c r="H455" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I455" s="13"/>
       <c r="J455" s="13"/>
@@ -24095,7 +24095,7 @@
       <c r="G456" s="13"/>
       <c r="H456" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I456" s="13"/>
       <c r="J456" s="13"/>
@@ -24139,7 +24139,7 @@
       <c r="G457" s="13"/>
       <c r="H457" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I457" s="13"/>
       <c r="J457" s="13"/>
@@ -24183,7 +24183,7 @@
       <c r="G458" s="13"/>
       <c r="H458" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I458" s="13"/>
       <c r="J458" s="13"/>
@@ -24226,8 +24226,8 @@
       <c r="F459" s="13"/>
       <c r="G459" s="13"/>
       <c r="H459" s="12" t="str">
-        <f t="shared" ref="H459:H522" si="8">L459&amp;"có hình dáng dạng "&amp;M459&amp;" chất liệu "&amp;N459&amp;" thành phần hóa chất: "&amp;O459&amp;" có kích thước "&amp;P459&amp;" dùng để "&amp;R459&amp;" cho "&amp;Q459</f>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="I459" s="13"/>
       <c r="J459" s="13"/>
@@ -24270,8 +24270,8 @@
       <c r="F460" s="13"/>
       <c r="G460" s="13"/>
       <c r="H460" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="I460" s="13"/>
       <c r="J460" s="13"/>
@@ -24314,8 +24314,8 @@
       <c r="F461" s="13"/>
       <c r="G461" s="13"/>
       <c r="H461" s="12" t="str">
-        <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <f t="shared" ref="H461:H524" si="8">IF(B461="","",L461&amp;"có hình dáng dạng "&amp;M461&amp;" chất liệu "&amp;N461&amp;" thành phần hóa chất: "&amp;O461&amp;" có kích thước "&amp;P461&amp;" dùng để "&amp;R461&amp;" cho "&amp;Q461)</f>
+        <v/>
       </c>
       <c r="I461" s="13"/>
       <c r="J461" s="13"/>
@@ -24359,7 +24359,7 @@
       <c r="G462" s="13"/>
       <c r="H462" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I462" s="13"/>
       <c r="J462" s="13"/>
@@ -24403,7 +24403,7 @@
       <c r="G463" s="13"/>
       <c r="H463" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I463" s="13"/>
       <c r="J463" s="13"/>
@@ -24447,7 +24447,7 @@
       <c r="G464" s="13"/>
       <c r="H464" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I464" s="13"/>
       <c r="J464" s="13"/>
@@ -24491,7 +24491,7 @@
       <c r="G465" s="13"/>
       <c r="H465" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I465" s="13"/>
       <c r="J465" s="13"/>
@@ -24535,7 +24535,7 @@
       <c r="G466" s="13"/>
       <c r="H466" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I466" s="13"/>
       <c r="J466" s="13"/>
@@ -24579,7 +24579,7 @@
       <c r="G467" s="13"/>
       <c r="H467" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I467" s="13"/>
       <c r="J467" s="13"/>
@@ -24623,7 +24623,7 @@
       <c r="G468" s="13"/>
       <c r="H468" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I468" s="13"/>
       <c r="J468" s="13"/>
@@ -24667,7 +24667,7 @@
       <c r="G469" s="13"/>
       <c r="H469" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I469" s="13"/>
       <c r="J469" s="13"/>
@@ -24711,7 +24711,7 @@
       <c r="G470" s="13"/>
       <c r="H470" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I470" s="13"/>
       <c r="J470" s="13"/>
@@ -24755,7 +24755,7 @@
       <c r="G471" s="13"/>
       <c r="H471" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I471" s="13"/>
       <c r="J471" s="13"/>
@@ -24799,7 +24799,7 @@
       <c r="G472" s="13"/>
       <c r="H472" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I472" s="13"/>
       <c r="J472" s="13"/>
@@ -24843,7 +24843,7 @@
       <c r="G473" s="13"/>
       <c r="H473" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I473" s="13"/>
       <c r="J473" s="13"/>
@@ -24887,7 +24887,7 @@
       <c r="G474" s="13"/>
       <c r="H474" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I474" s="13"/>
       <c r="J474" s="13"/>
@@ -24931,7 +24931,7 @@
       <c r="G475" s="13"/>
       <c r="H475" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I475" s="13"/>
       <c r="J475" s="13"/>
@@ -24975,7 +24975,7 @@
       <c r="G476" s="13"/>
       <c r="H476" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I476" s="13"/>
       <c r="J476" s="13"/>
@@ -25019,7 +25019,7 @@
       <c r="G477" s="13"/>
       <c r="H477" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I477" s="13"/>
       <c r="J477" s="13"/>
@@ -25063,7 +25063,7 @@
       <c r="G478" s="13"/>
       <c r="H478" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I478" s="13"/>
       <c r="J478" s="13"/>
@@ -25107,7 +25107,7 @@
       <c r="G479" s="13"/>
       <c r="H479" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I479" s="13"/>
       <c r="J479" s="13"/>
@@ -25151,7 +25151,7 @@
       <c r="G480" s="13"/>
       <c r="H480" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I480" s="13"/>
       <c r="J480" s="13"/>
@@ -25195,7 +25195,7 @@
       <c r="G481" s="13"/>
       <c r="H481" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I481" s="13"/>
       <c r="J481" s="13"/>
@@ -25239,7 +25239,7 @@
       <c r="G482" s="13"/>
       <c r="H482" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I482" s="13"/>
       <c r="J482" s="13"/>
@@ -25283,7 +25283,7 @@
       <c r="G483" s="13"/>
       <c r="H483" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I483" s="13"/>
       <c r="J483" s="13"/>
@@ -25327,7 +25327,7 @@
       <c r="G484" s="13"/>
       <c r="H484" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I484" s="13"/>
       <c r="J484" s="13"/>
@@ -25371,7 +25371,7 @@
       <c r="G485" s="13"/>
       <c r="H485" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I485" s="13"/>
       <c r="J485" s="13"/>
@@ -25415,7 +25415,7 @@
       <c r="G486" s="13"/>
       <c r="H486" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I486" s="13"/>
       <c r="J486" s="13"/>
@@ -25459,7 +25459,7 @@
       <c r="G487" s="13"/>
       <c r="H487" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I487" s="13"/>
       <c r="J487" s="13"/>
@@ -25503,7 +25503,7 @@
       <c r="G488" s="13"/>
       <c r="H488" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I488" s="13"/>
       <c r="J488" s="13"/>
@@ -25547,7 +25547,7 @@
       <c r="G489" s="13"/>
       <c r="H489" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I489" s="13"/>
       <c r="J489" s="13"/>
@@ -25591,7 +25591,7 @@
       <c r="G490" s="13"/>
       <c r="H490" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I490" s="13"/>
       <c r="J490" s="13"/>
@@ -25635,7 +25635,7 @@
       <c r="G491" s="13"/>
       <c r="H491" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I491" s="13"/>
       <c r="J491" s="13"/>
@@ -25679,7 +25679,7 @@
       <c r="G492" s="13"/>
       <c r="H492" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I492" s="13"/>
       <c r="J492" s="13"/>
@@ -25723,7 +25723,7 @@
       <c r="G493" s="13"/>
       <c r="H493" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I493" s="13"/>
       <c r="J493" s="13"/>
@@ -25767,7 +25767,7 @@
       <c r="G494" s="13"/>
       <c r="H494" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I494" s="13"/>
       <c r="J494" s="13"/>
@@ -25811,7 +25811,7 @@
       <c r="G495" s="13"/>
       <c r="H495" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I495" s="13"/>
       <c r="J495" s="13"/>
@@ -25855,7 +25855,7 @@
       <c r="G496" s="13"/>
       <c r="H496" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I496" s="13"/>
       <c r="J496" s="13"/>
@@ -25899,7 +25899,7 @@
       <c r="G497" s="13"/>
       <c r="H497" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I497" s="13"/>
       <c r="J497" s="13"/>
@@ -25943,7 +25943,7 @@
       <c r="G498" s="13"/>
       <c r="H498" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I498" s="13"/>
       <c r="J498" s="13"/>
@@ -25987,7 +25987,7 @@
       <c r="G499" s="13"/>
       <c r="H499" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I499" s="13"/>
       <c r="J499" s="13"/>
@@ -26031,7 +26031,7 @@
       <c r="G500" s="13"/>
       <c r="H500" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I500" s="13"/>
       <c r="J500" s="13"/>
@@ -26075,7 +26075,7 @@
       <c r="G501" s="13"/>
       <c r="H501" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I501" s="13"/>
       <c r="J501" s="13"/>
@@ -26119,7 +26119,7 @@
       <c r="G502" s="13"/>
       <c r="H502" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I502" s="13"/>
       <c r="J502" s="13"/>
@@ -26163,7 +26163,7 @@
       <c r="G503" s="13"/>
       <c r="H503" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I503" s="13"/>
       <c r="J503" s="13"/>
@@ -26207,7 +26207,7 @@
       <c r="G504" s="13"/>
       <c r="H504" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I504" s="13"/>
       <c r="J504" s="13"/>
@@ -26251,7 +26251,7 @@
       <c r="G505" s="13"/>
       <c r="H505" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I505" s="13"/>
       <c r="J505" s="13"/>
@@ -26295,7 +26295,7 @@
       <c r="G506" s="13"/>
       <c r="H506" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I506" s="13"/>
       <c r="J506" s="13"/>
@@ -26339,7 +26339,7 @@
       <c r="G507" s="13"/>
       <c r="H507" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I507" s="13"/>
       <c r="J507" s="13"/>
@@ -26383,7 +26383,7 @@
       <c r="G508" s="13"/>
       <c r="H508" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I508" s="13"/>
       <c r="J508" s="13"/>
@@ -26427,7 +26427,7 @@
       <c r="G509" s="13"/>
       <c r="H509" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I509" s="13"/>
       <c r="J509" s="13"/>
@@ -26471,7 +26471,7 @@
       <c r="G510" s="13"/>
       <c r="H510" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I510" s="13"/>
       <c r="J510" s="13"/>
@@ -26515,7 +26515,7 @@
       <c r="G511" s="13"/>
       <c r="H511" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I511" s="13"/>
       <c r="J511" s="13"/>
@@ -26559,7 +26559,7 @@
       <c r="G512" s="13"/>
       <c r="H512" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I512" s="13"/>
       <c r="J512" s="13"/>
@@ -26603,7 +26603,7 @@
       <c r="G513" s="13"/>
       <c r="H513" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I513" s="13"/>
       <c r="J513" s="13"/>
@@ -26647,7 +26647,7 @@
       <c r="G514" s="13"/>
       <c r="H514" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I514" s="13"/>
       <c r="J514" s="13"/>
@@ -26691,7 +26691,7 @@
       <c r="G515" s="13"/>
       <c r="H515" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I515" s="13"/>
       <c r="J515" s="13"/>
@@ -26735,7 +26735,7 @@
       <c r="G516" s="13"/>
       <c r="H516" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I516" s="13"/>
       <c r="J516" s="13"/>
@@ -26779,7 +26779,7 @@
       <c r="G517" s="13"/>
       <c r="H517" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I517" s="13"/>
       <c r="J517" s="13"/>
@@ -26823,7 +26823,7 @@
       <c r="G518" s="13"/>
       <c r="H518" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I518" s="13"/>
       <c r="J518" s="13"/>
@@ -26867,7 +26867,7 @@
       <c r="G519" s="13"/>
       <c r="H519" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I519" s="13"/>
       <c r="J519" s="13"/>
@@ -26911,7 +26911,7 @@
       <c r="G520" s="13"/>
       <c r="H520" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I520" s="13"/>
       <c r="J520" s="13"/>
@@ -26955,7 +26955,7 @@
       <c r="G521" s="13"/>
       <c r="H521" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I521" s="13"/>
       <c r="J521" s="13"/>
@@ -26999,7 +26999,7 @@
       <c r="G522" s="13"/>
       <c r="H522" s="12" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I522" s="13"/>
       <c r="J522" s="13"/>
@@ -27042,8 +27042,8 @@
       <c r="F523" s="13"/>
       <c r="G523" s="13"/>
       <c r="H523" s="12" t="str">
-        <f t="shared" ref="H523:H569" si="9">L523&amp;"có hình dáng dạng "&amp;M523&amp;" chất liệu "&amp;N523&amp;" thành phần hóa chất: "&amp;O523&amp;" có kích thước "&amp;P523&amp;" dùng để "&amp;R523&amp;" cho "&amp;Q523</f>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <f t="shared" si="8"/>
+        <v/>
       </c>
       <c r="I523" s="13"/>
       <c r="J523" s="13"/>
@@ -27086,8 +27086,8 @@
       <c r="F524" s="13"/>
       <c r="G524" s="13"/>
       <c r="H524" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <f t="shared" si="8"/>
+        <v/>
       </c>
       <c r="I524" s="13"/>
       <c r="J524" s="13"/>
@@ -27130,8 +27130,8 @@
       <c r="F525" s="13"/>
       <c r="G525" s="13"/>
       <c r="H525" s="12" t="str">
-        <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <f t="shared" ref="H525:H569" si="9">IF(B525="","",L525&amp;"có hình dáng dạng "&amp;M525&amp;" chất liệu "&amp;N525&amp;" thành phần hóa chất: "&amp;O525&amp;" có kích thước "&amp;P525&amp;" dùng để "&amp;R525&amp;" cho "&amp;Q525)</f>
+        <v/>
       </c>
       <c r="I525" s="13"/>
       <c r="J525" s="13"/>
@@ -27175,7 +27175,7 @@
       <c r="G526" s="13"/>
       <c r="H526" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I526" s="13"/>
       <c r="J526" s="13"/>
@@ -27219,7 +27219,7 @@
       <c r="G527" s="13"/>
       <c r="H527" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I527" s="13"/>
       <c r="J527" s="13"/>
@@ -27263,7 +27263,7 @@
       <c r="G528" s="13"/>
       <c r="H528" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I528" s="13"/>
       <c r="J528" s="13"/>
@@ -27307,7 +27307,7 @@
       <c r="G529" s="13"/>
       <c r="H529" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I529" s="13"/>
       <c r="J529" s="13"/>
@@ -27351,7 +27351,7 @@
       <c r="G530" s="13"/>
       <c r="H530" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I530" s="13"/>
       <c r="J530" s="13"/>
@@ -27395,7 +27395,7 @@
       <c r="G531" s="13"/>
       <c r="H531" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I531" s="13"/>
       <c r="J531" s="13"/>
@@ -27439,7 +27439,7 @@
       <c r="G532" s="13"/>
       <c r="H532" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I532" s="13"/>
       <c r="J532" s="13"/>
@@ -27483,7 +27483,7 @@
       <c r="G533" s="13"/>
       <c r="H533" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I533" s="13"/>
       <c r="J533" s="13"/>
@@ -27527,7 +27527,7 @@
       <c r="G534" s="13"/>
       <c r="H534" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I534" s="13"/>
       <c r="J534" s="13"/>
@@ -27571,7 +27571,7 @@
       <c r="G535" s="13"/>
       <c r="H535" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I535" s="13"/>
       <c r="J535" s="13"/>
@@ -27615,7 +27615,7 @@
       <c r="G536" s="13"/>
       <c r="H536" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I536" s="13"/>
       <c r="J536" s="13"/>
@@ -27659,7 +27659,7 @@
       <c r="G537" s="13"/>
       <c r="H537" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I537" s="13"/>
       <c r="J537" s="13"/>
@@ -27703,7 +27703,7 @@
       <c r="G538" s="13"/>
       <c r="H538" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I538" s="13"/>
       <c r="J538" s="13"/>
@@ -27747,7 +27747,7 @@
       <c r="G539" s="13"/>
       <c r="H539" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I539" s="13"/>
       <c r="J539" s="13"/>
@@ -27791,7 +27791,7 @@
       <c r="G540" s="13"/>
       <c r="H540" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I540" s="13"/>
       <c r="J540" s="13"/>
@@ -27835,7 +27835,7 @@
       <c r="G541" s="13"/>
       <c r="H541" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I541" s="13"/>
       <c r="J541" s="13"/>
@@ -27879,7 +27879,7 @@
       <c r="G542" s="13"/>
       <c r="H542" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I542" s="13"/>
       <c r="J542" s="13"/>
@@ -27923,7 +27923,7 @@
       <c r="G543" s="13"/>
       <c r="H543" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I543" s="13"/>
       <c r="J543" s="13"/>
@@ -27967,7 +27967,7 @@
       <c r="G544" s="13"/>
       <c r="H544" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I544" s="13"/>
       <c r="J544" s="13"/>
@@ -28011,7 +28011,7 @@
       <c r="G545" s="13"/>
       <c r="H545" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I545" s="13"/>
       <c r="J545" s="13"/>
@@ -28055,7 +28055,7 @@
       <c r="G546" s="13"/>
       <c r="H546" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I546" s="13"/>
       <c r="J546" s="13"/>
@@ -28099,7 +28099,7 @@
       <c r="G547" s="13"/>
       <c r="H547" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I547" s="13"/>
       <c r="J547" s="13"/>
@@ -28143,7 +28143,7 @@
       <c r="G548" s="13"/>
       <c r="H548" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I548" s="13"/>
       <c r="J548" s="13"/>
@@ -28187,7 +28187,7 @@
       <c r="G549" s="13"/>
       <c r="H549" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I549" s="13"/>
       <c r="J549" s="13"/>
@@ -28231,7 +28231,7 @@
       <c r="G550" s="13"/>
       <c r="H550" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I550" s="13"/>
       <c r="J550" s="13"/>
@@ -28275,7 +28275,7 @@
       <c r="G551" s="13"/>
       <c r="H551" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I551" s="13"/>
       <c r="J551" s="13"/>
@@ -28319,7 +28319,7 @@
       <c r="G552" s="13"/>
       <c r="H552" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I552" s="13"/>
       <c r="J552" s="13"/>
@@ -28363,7 +28363,7 @@
       <c r="G553" s="13"/>
       <c r="H553" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I553" s="13"/>
       <c r="J553" s="13"/>
@@ -28407,7 +28407,7 @@
       <c r="G554" s="13"/>
       <c r="H554" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I554" s="13"/>
       <c r="J554" s="13"/>
@@ -28451,7 +28451,7 @@
       <c r="G555" s="13"/>
       <c r="H555" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I555" s="13"/>
       <c r="J555" s="13"/>
@@ -28495,7 +28495,7 @@
       <c r="G556" s="13"/>
       <c r="H556" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I556" s="13"/>
       <c r="J556" s="13"/>
@@ -28539,7 +28539,7 @@
       <c r="G557" s="13"/>
       <c r="H557" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I557" s="13"/>
       <c r="J557" s="13"/>
@@ -28583,7 +28583,7 @@
       <c r="G558" s="13"/>
       <c r="H558" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I558" s="13"/>
       <c r="J558" s="13"/>
@@ -28627,7 +28627,7 @@
       <c r="G559" s="13"/>
       <c r="H559" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I559" s="13"/>
       <c r="J559" s="13"/>
@@ -28671,7 +28671,7 @@
       <c r="G560" s="13"/>
       <c r="H560" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I560" s="13"/>
       <c r="J560" s="13"/>
@@ -28715,7 +28715,7 @@
       <c r="G561" s="13"/>
       <c r="H561" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I561" s="13"/>
       <c r="J561" s="13"/>
@@ -28759,7 +28759,7 @@
       <c r="G562" s="13"/>
       <c r="H562" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I562" s="13"/>
       <c r="J562" s="13"/>
@@ -28803,7 +28803,7 @@
       <c r="G563" s="13"/>
       <c r="H563" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I563" s="13"/>
       <c r="J563" s="13"/>
@@ -28847,7 +28847,7 @@
       <c r="G564" s="13"/>
       <c r="H564" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I564" s="13"/>
       <c r="J564" s="13"/>
@@ -28891,7 +28891,7 @@
       <c r="G565" s="13"/>
       <c r="H565" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I565" s="13"/>
       <c r="J565" s="13"/>
@@ -28935,7 +28935,7 @@
       <c r="G566" s="13"/>
       <c r="H566" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I566" s="13"/>
       <c r="J566" s="13"/>
@@ -28979,7 +28979,7 @@
       <c r="G567" s="13"/>
       <c r="H567" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I567" s="13"/>
       <c r="J567" s="13"/>
@@ -29023,7 +29023,7 @@
       <c r="G568" s="13"/>
       <c r="H568" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I568" s="13"/>
       <c r="J568" s="13"/>
@@ -29067,7 +29067,7 @@
       <c r="G569" s="13"/>
       <c r="H569" s="12" t="str">
         <f t="shared" si="9"/>
-        <v xml:space="preserve">có hình dáng dạng  chất liệu  thành phần hóa chất:  có kích thước  dùng để  cho </v>
+        <v/>
       </c>
       <c r="I569" s="13"/>
       <c r="J569" s="13"/>
@@ -29848,7 +29848,7 @@
         <v>203</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -29859,7 +29859,7 @@
         <v>451</v>
       </c>
       <c r="D2" s="35" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -29870,7 +29870,7 @@
         <v>452</v>
       </c>
       <c r="D3" s="35" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -29881,7 +29881,7 @@
         <v>453</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -29892,7 +29892,7 @@
         <v>454</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -29903,7 +29903,7 @@
         <v>455</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -29914,7 +29914,7 @@
         <v>10</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
@@ -29925,7 +29925,7 @@
         <v>11</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
@@ -29936,7 +29936,7 @@
         <v>12</v>
       </c>
       <c r="D9" s="36" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -29947,7 +29947,7 @@
         <v>456</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
@@ -29958,7 +29958,7 @@
         <v>13</v>
       </c>
       <c r="D11" s="36" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -29969,7 +29969,7 @@
         <v>457</v>
       </c>
       <c r="D12" s="35" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -29980,7 +29980,7 @@
         <v>458</v>
       </c>
       <c r="D13" s="35" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -29991,7 +29991,7 @@
         <v>459</v>
       </c>
       <c r="D14" s="35" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30002,7 +30002,7 @@
         <v>460</v>
       </c>
       <c r="D15" s="35" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30013,7 +30013,7 @@
         <v>461</v>
       </c>
       <c r="D16" s="35" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30024,7 +30024,7 @@
         <v>462</v>
       </c>
       <c r="D17" s="35" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30035,7 +30035,7 @@
         <v>463</v>
       </c>
       <c r="D18" s="35" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
@@ -30046,7 +30046,7 @@
         <v>464</v>
       </c>
       <c r="D19" s="36" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
@@ -30057,7 +30057,7 @@
         <v>465</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
@@ -30068,7 +30068,7 @@
         <v>466</v>
       </c>
       <c r="D21" s="36" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30079,7 +30079,7 @@
         <v>467</v>
       </c>
       <c r="D22" s="35" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
@@ -30090,7 +30090,7 @@
         <v>468</v>
       </c>
       <c r="D23" s="36" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30101,7 +30101,7 @@
         <v>15</v>
       </c>
       <c r="D24" s="35" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
@@ -30112,7 +30112,7 @@
         <v>469</v>
       </c>
       <c r="D25" s="36" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
@@ -30123,7 +30123,7 @@
         <v>16</v>
       </c>
       <c r="D26" s="36" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30134,7 +30134,7 @@
         <v>470</v>
       </c>
       <c r="D27" s="35" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30145,7 +30145,7 @@
         <v>17</v>
       </c>
       <c r="D28" s="35" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
@@ -30156,7 +30156,7 @@
         <v>18</v>
       </c>
       <c r="D29" s="36" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
@@ -30167,7 +30167,7 @@
         <v>471</v>
       </c>
       <c r="D30" s="36" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30178,7 +30178,7 @@
         <v>472</v>
       </c>
       <c r="D31" s="35" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30189,7 +30189,7 @@
         <v>19</v>
       </c>
       <c r="D32" s="35" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30200,7 +30200,7 @@
         <v>473</v>
       </c>
       <c r="D33" s="35" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30211,7 +30211,7 @@
         <v>474</v>
       </c>
       <c r="D34" s="35" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30222,7 +30222,7 @@
         <v>475</v>
       </c>
       <c r="D35" s="35" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30233,7 +30233,7 @@
         <v>20</v>
       </c>
       <c r="D36" s="35" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30244,7 +30244,7 @@
         <v>21</v>
       </c>
       <c r="D37" s="35" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
@@ -30255,7 +30255,7 @@
         <v>476</v>
       </c>
       <c r="D38" s="36" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30266,7 +30266,7 @@
         <v>22</v>
       </c>
       <c r="D39" s="35" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30277,7 +30277,7 @@
         <v>477</v>
       </c>
       <c r="D40" s="35" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30288,7 +30288,7 @@
         <v>23</v>
       </c>
       <c r="D41" s="35" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30299,7 +30299,7 @@
         <v>478</v>
       </c>
       <c r="D42" s="35" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30310,7 +30310,7 @@
         <v>479</v>
       </c>
       <c r="D43" s="35" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30321,7 +30321,7 @@
         <v>480</v>
       </c>
       <c r="D44" s="35" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30332,7 +30332,7 @@
         <v>481</v>
       </c>
       <c r="D45" s="35" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30343,7 +30343,7 @@
         <v>482</v>
       </c>
       <c r="D46" s="35" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30354,7 +30354,7 @@
         <v>483</v>
       </c>
       <c r="D47" s="35" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30362,10 +30362,10 @@
         <v>5170</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>484</v>
+        <v>752</v>
       </c>
       <c r="D48" s="35" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30373,10 +30373,10 @@
         <v>5180</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D49" s="35" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30387,7 +30387,7 @@
         <v>24</v>
       </c>
       <c r="D50" s="35" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30395,10 +30395,10 @@
         <v>5220</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D51" s="35" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30406,10 +30406,10 @@
         <v>6110</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D52" s="35" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30420,7 +30420,7 @@
         <v>25</v>
       </c>
       <c r="D53" s="35" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
@@ -30431,7 +30431,7 @@
         <v>26</v>
       </c>
       <c r="D54" s="36" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
@@ -30442,7 +30442,7 @@
         <v>27</v>
       </c>
       <c r="D55" s="36" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
@@ -30453,7 +30453,7 @@
         <v>28</v>
       </c>
       <c r="D56" s="36" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30464,7 +30464,7 @@
         <v>29</v>
       </c>
       <c r="D57" s="35" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30472,10 +30472,10 @@
         <v>270</v>
       </c>
       <c r="B58" s="17" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D58" s="35" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
@@ -30483,10 +30483,10 @@
         <v>271</v>
       </c>
       <c r="B59" s="17" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D59" s="36" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30494,10 +30494,10 @@
         <v>272</v>
       </c>
       <c r="B60" s="17" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D60" s="35" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30505,10 +30505,10 @@
         <v>273</v>
       </c>
       <c r="B61" s="17" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D61" s="35" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30516,10 +30516,10 @@
         <v>274</v>
       </c>
       <c r="B62" s="17" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D62" s="35" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30527,10 +30527,10 @@
         <v>275</v>
       </c>
       <c r="B63" s="17" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D63" s="35" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30541,7 +30541,7 @@
         <v>31</v>
       </c>
       <c r="D64" s="35" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30549,10 +30549,10 @@
         <v>32</v>
       </c>
       <c r="B65" s="17" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D65" s="35" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30563,7 +30563,7 @@
         <v>34</v>
       </c>
       <c r="D66" s="35" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
@@ -30571,10 +30571,10 @@
         <v>276</v>
       </c>
       <c r="B67" s="17" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D67" s="36" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
@@ -30582,10 +30582,10 @@
         <v>277</v>
       </c>
       <c r="B68" s="17" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D68" s="36" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30593,10 +30593,10 @@
         <v>278</v>
       </c>
       <c r="B69" s="17" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D69" s="35" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
@@ -30604,10 +30604,10 @@
         <v>35</v>
       </c>
       <c r="B70" s="17" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D70" s="36" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30615,10 +30615,10 @@
         <v>36</v>
       </c>
       <c r="B71" s="17" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D71" s="35" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30626,10 +30626,10 @@
         <v>279</v>
       </c>
       <c r="B72" s="17" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D72" s="35" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30640,7 +30640,7 @@
         <v>39</v>
       </c>
       <c r="D73" s="35" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30651,7 +30651,7 @@
         <v>41</v>
       </c>
       <c r="D74" s="35" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30662,7 +30662,7 @@
         <v>43</v>
       </c>
       <c r="D75" s="35" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30673,7 +30673,7 @@
         <v>45</v>
       </c>
       <c r="D76" s="35" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30684,7 +30684,7 @@
         <v>47</v>
       </c>
       <c r="D77" s="35" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30695,7 +30695,7 @@
         <v>49</v>
       </c>
       <c r="D78" s="35" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30703,10 +30703,10 @@
         <v>50</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D79" s="35" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30717,7 +30717,7 @@
         <v>52</v>
       </c>
       <c r="D80" s="35" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30725,10 +30725,10 @@
         <v>280</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D81" s="35" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
@@ -30739,7 +30739,7 @@
         <v>54</v>
       </c>
       <c r="D82" s="36" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30750,7 +30750,7 @@
         <v>54</v>
       </c>
       <c r="D83" s="35" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30758,10 +30758,10 @@
         <v>281</v>
       </c>
       <c r="B84" s="17" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D84" s="35" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30772,7 +30772,7 @@
         <v>57</v>
       </c>
       <c r="D85" s="35" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
@@ -30780,10 +30780,10 @@
         <v>282</v>
       </c>
       <c r="B86" s="17" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D86" s="36" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30791,10 +30791,10 @@
         <v>59</v>
       </c>
       <c r="B87" s="17" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D87" s="35" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30802,10 +30802,10 @@
         <v>283</v>
       </c>
       <c r="B88" s="17" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D88" s="35" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30813,10 +30813,10 @@
         <v>284</v>
       </c>
       <c r="B89" s="17" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D89" s="35" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30824,10 +30824,10 @@
         <v>285</v>
       </c>
       <c r="B90" s="17" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D90" s="35" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30838,7 +30838,7 @@
         <v>62</v>
       </c>
       <c r="D91" s="35" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30849,7 +30849,7 @@
         <v>64</v>
       </c>
       <c r="D92" s="35" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30860,7 +30860,7 @@
         <v>66</v>
       </c>
       <c r="D93" s="35" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30871,7 +30871,7 @@
         <v>68</v>
       </c>
       <c r="D94" s="35" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30882,7 +30882,7 @@
         <v>70</v>
       </c>
       <c r="D95" s="35" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
@@ -30890,10 +30890,10 @@
         <v>71</v>
       </c>
       <c r="B96" s="17" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D96" s="36" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30904,7 +30904,7 @@
         <v>73</v>
       </c>
       <c r="D97" s="35" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30915,7 +30915,7 @@
         <v>63</v>
       </c>
       <c r="D98" s="35" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30923,10 +30923,10 @@
         <v>287</v>
       </c>
       <c r="B99" s="17" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D99" s="35" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30937,7 +30937,7 @@
         <v>72</v>
       </c>
       <c r="D100" s="35" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30945,10 +30945,10 @@
         <v>289</v>
       </c>
       <c r="B101" s="17" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D101" s="35" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30959,7 +30959,7 @@
         <v>33</v>
       </c>
       <c r="D102" s="35" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30967,10 +30967,10 @@
         <v>291</v>
       </c>
       <c r="B103" s="17" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D103" s="35" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -30978,10 +30978,10 @@
         <v>292</v>
       </c>
       <c r="B104" s="17" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D104" s="35" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
@@ -30989,10 +30989,10 @@
         <v>293</v>
       </c>
       <c r="B105" s="17" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D105" s="36" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
@@ -31000,10 +31000,10 @@
         <v>294</v>
       </c>
       <c r="B106" s="17" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D106" s="36" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -31011,10 +31011,10 @@
         <v>295</v>
       </c>
       <c r="B107" s="17" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D107" s="35" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="15" x14ac:dyDescent="0.25">
@@ -31022,10 +31022,10 @@
         <v>296</v>
       </c>
       <c r="B108" s="17" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D108" s="32" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
@@ -31033,10 +31033,10 @@
         <v>297</v>
       </c>
       <c r="B109" s="17" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="D109" s="37" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="15" x14ac:dyDescent="0.25">
@@ -31044,10 +31044,10 @@
         <v>298</v>
       </c>
       <c r="B110" s="17" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D110" s="32" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="15" x14ac:dyDescent="0.25">
@@ -31055,10 +31055,10 @@
         <v>299</v>
       </c>
       <c r="B111" s="17" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D111" s="32" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -31066,10 +31066,10 @@
         <v>300</v>
       </c>
       <c r="B112" s="17" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D112" s="35" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.2">
@@ -31093,7 +31093,7 @@
         <v>303</v>
       </c>
       <c r="B115" s="17" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.2">
@@ -31101,7 +31101,7 @@
         <v>304</v>
       </c>
       <c r="B116" s="17" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.2">
@@ -31109,7 +31109,7 @@
         <v>305</v>
       </c>
       <c r="B117" s="17" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.2">
@@ -31117,7 +31117,7 @@
         <v>306</v>
       </c>
       <c r="B118" s="17" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.2">
@@ -31125,7 +31125,7 @@
         <v>307</v>
       </c>
       <c r="B119" s="17" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.2">
@@ -31133,7 +31133,7 @@
         <v>308</v>
       </c>
       <c r="B120" s="17" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
@@ -31141,7 +31141,7 @@
         <v>309</v>
       </c>
       <c r="B121" s="17" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.2">
@@ -31157,7 +31157,7 @@
         <v>311</v>
       </c>
       <c r="B123" s="17" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.2">
@@ -31165,7 +31165,7 @@
         <v>312</v>
       </c>
       <c r="B124" s="17" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.2">
@@ -31173,7 +31173,7 @@
         <v>313</v>
       </c>
       <c r="B125" s="17" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.2">
@@ -31197,7 +31197,7 @@
         <v>316</v>
       </c>
       <c r="B128" s="17" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.2">
@@ -31205,7 +31205,7 @@
         <v>317</v>
       </c>
       <c r="B129" s="17" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.2">
@@ -31213,7 +31213,7 @@
         <v>318</v>
       </c>
       <c r="B130" s="17" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.2">
@@ -31221,7 +31221,7 @@
         <v>319</v>
       </c>
       <c r="B131" s="17" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.2">
@@ -31229,7 +31229,7 @@
         <v>320</v>
       </c>
       <c r="B132" s="17" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.2">
@@ -31237,7 +31237,7 @@
         <v>321</v>
       </c>
       <c r="B133" s="17" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.2">
@@ -31245,7 +31245,7 @@
         <v>322</v>
       </c>
       <c r="B134" s="17" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.2">
@@ -31253,7 +31253,7 @@
         <v>323</v>
       </c>
       <c r="B135" s="17" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.2">
@@ -31261,7 +31261,7 @@
         <v>324</v>
       </c>
       <c r="B136" s="17" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.2">
@@ -31269,7 +31269,7 @@
         <v>325</v>
       </c>
       <c r="B137" s="17" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.2">
@@ -31277,7 +31277,7 @@
         <v>326</v>
       </c>
       <c r="B138" s="17" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.2">
@@ -31285,7 +31285,7 @@
         <v>327</v>
       </c>
       <c r="B139" s="17" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.2">
@@ -31293,7 +31293,7 @@
         <v>328</v>
       </c>
       <c r="B140" s="17" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.2">
@@ -31301,7 +31301,7 @@
         <v>329</v>
       </c>
       <c r="B141" s="17" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.2">
@@ -31309,7 +31309,7 @@
         <v>330</v>
       </c>
       <c r="B142" s="17" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
@@ -31317,7 +31317,7 @@
         <v>331</v>
       </c>
       <c r="B143" s="17" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.2">
@@ -31325,7 +31325,7 @@
         <v>332</v>
       </c>
       <c r="B144" s="17" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.2">
@@ -31333,7 +31333,7 @@
         <v>333</v>
       </c>
       <c r="B145" s="17" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.2">
@@ -31341,7 +31341,7 @@
         <v>334</v>
       </c>
       <c r="B146" s="17" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.2">
@@ -31349,7 +31349,7 @@
         <v>335</v>
       </c>
       <c r="B147" s="17" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.2">
@@ -31357,7 +31357,7 @@
         <v>336</v>
       </c>
       <c r="B148" s="17" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.2">
@@ -31365,7 +31365,7 @@
         <v>337</v>
       </c>
       <c r="B149" s="17" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.2">
@@ -31381,7 +31381,7 @@
         <v>339</v>
       </c>
       <c r="B151" s="17" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.2">
@@ -31389,7 +31389,7 @@
         <v>340</v>
       </c>
       <c r="B152" s="17" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.2">
@@ -31397,7 +31397,7 @@
         <v>341</v>
       </c>
       <c r="B153" s="17" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.2">
@@ -31405,7 +31405,7 @@
         <v>342</v>
       </c>
       <c r="B154" s="17" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.2">
@@ -31413,7 +31413,7 @@
         <v>343</v>
       </c>
       <c r="B155" s="17" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.2">
@@ -31421,7 +31421,7 @@
         <v>344</v>
       </c>
       <c r="B156" s="17" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.2">
@@ -31429,7 +31429,7 @@
         <v>345</v>
       </c>
       <c r="B157" s="17" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.2">
@@ -31445,7 +31445,7 @@
         <v>347</v>
       </c>
       <c r="B159" s="17" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.2">
@@ -31469,7 +31469,7 @@
         <v>350</v>
       </c>
       <c r="B162" s="17" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.2">
@@ -31477,7 +31477,7 @@
         <v>351</v>
       </c>
       <c r="B163" s="17" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.2">
@@ -31493,7 +31493,7 @@
         <v>353</v>
       </c>
       <c r="B165" s="17" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.2">
@@ -31501,7 +31501,7 @@
         <v>354</v>
       </c>
       <c r="B166" s="17" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.2">
@@ -31525,7 +31525,7 @@
         <v>357</v>
       </c>
       <c r="B169" s="17" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.2">
@@ -31533,7 +31533,7 @@
         <v>358</v>
       </c>
       <c r="B170" s="17" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.2">
@@ -31541,7 +31541,7 @@
         <v>359</v>
       </c>
       <c r="B171" s="17" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.2">
@@ -31549,7 +31549,7 @@
         <v>360</v>
       </c>
       <c r="B172" s="17" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.2">
@@ -31557,7 +31557,7 @@
         <v>361</v>
       </c>
       <c r="B173" s="17" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.2">
@@ -31565,7 +31565,7 @@
         <v>362</v>
       </c>
       <c r="B174" s="17" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.2">
@@ -31581,7 +31581,7 @@
         <v>364</v>
       </c>
       <c r="B176" s="17" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.2">
@@ -31589,7 +31589,7 @@
         <v>365</v>
       </c>
       <c r="B177" s="17" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.2">
@@ -31597,7 +31597,7 @@
         <v>366</v>
       </c>
       <c r="B178" s="17" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.2">
@@ -31613,7 +31613,7 @@
         <v>368</v>
       </c>
       <c r="B180" s="17" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.2">
@@ -31621,7 +31621,7 @@
         <v>369</v>
       </c>
       <c r="B181" s="17" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.2">
@@ -31669,7 +31669,7 @@
         <v>375</v>
       </c>
       <c r="B187" s="17" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
@@ -31677,7 +31677,7 @@
         <v>376</v>
       </c>
       <c r="B188" s="17" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
@@ -31685,7 +31685,7 @@
         <v>377</v>
       </c>
       <c r="B189" s="17" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.2">
@@ -31693,7 +31693,7 @@
         <v>378</v>
       </c>
       <c r="B190" s="17" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.2">
@@ -31701,7 +31701,7 @@
         <v>379</v>
       </c>
       <c r="B191" s="17" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.2">
@@ -31717,7 +31717,7 @@
         <v>381</v>
       </c>
       <c r="B193" s="17" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.2">
@@ -31725,7 +31725,7 @@
         <v>382</v>
       </c>
       <c r="B194" s="17" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
@@ -31733,7 +31733,7 @@
         <v>383</v>
       </c>
       <c r="B195" s="17" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
@@ -31741,7 +31741,7 @@
         <v>384</v>
       </c>
       <c r="B196" s="17" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
@@ -31757,7 +31757,7 @@
         <v>386</v>
       </c>
       <c r="B198" s="17" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.2">
@@ -31765,7 +31765,7 @@
         <v>387</v>
       </c>
       <c r="B199" s="17" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.2">
@@ -31773,7 +31773,7 @@
         <v>388</v>
       </c>
       <c r="B200" s="17" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.2">
@@ -31781,7 +31781,7 @@
         <v>389</v>
       </c>
       <c r="B201" s="17" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.2">
@@ -31789,7 +31789,7 @@
         <v>390</v>
       </c>
       <c r="B202" s="17" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.2">
@@ -31797,7 +31797,7 @@
         <v>391</v>
       </c>
       <c r="B203" s="17" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.2">
@@ -31805,7 +31805,7 @@
         <v>392</v>
       </c>
       <c r="B204" s="17" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.2">
@@ -31813,7 +31813,7 @@
         <v>393</v>
       </c>
       <c r="B205" s="17" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.2">
@@ -31821,7 +31821,7 @@
         <v>394</v>
       </c>
       <c r="B206" s="17" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.2">
@@ -31829,7 +31829,7 @@
         <v>395</v>
       </c>
       <c r="B207" s="17" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.2">
@@ -31837,7 +31837,7 @@
         <v>396</v>
       </c>
       <c r="B208" s="17" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.2">
@@ -31845,7 +31845,7 @@
         <v>397</v>
       </c>
       <c r="B209" s="17" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
@@ -31861,7 +31861,7 @@
         <v>399</v>
       </c>
       <c r="B211" s="17" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.2">
@@ -31869,7 +31869,7 @@
         <v>400</v>
       </c>
       <c r="B212" s="17" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.2">
@@ -31893,7 +31893,7 @@
         <v>403</v>
       </c>
       <c r="B215" s="17" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.2">
@@ -31901,7 +31901,7 @@
         <v>404</v>
       </c>
       <c r="B216" s="17" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.2">
@@ -31909,7 +31909,7 @@
         <v>405</v>
       </c>
       <c r="B217" s="17" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.2">
@@ -31917,7 +31917,7 @@
         <v>406</v>
       </c>
       <c r="B218" s="17" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.2">
@@ -31925,7 +31925,7 @@
         <v>407</v>
       </c>
       <c r="B219" s="17" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.2">
@@ -31933,7 +31933,7 @@
         <v>408</v>
       </c>
       <c r="B220" s="17" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
@@ -31941,7 +31941,7 @@
         <v>409</v>
       </c>
       <c r="B221" s="17" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.2">
@@ -31949,7 +31949,7 @@
         <v>410</v>
       </c>
       <c r="B222" s="17" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.2">
@@ -31957,7 +31957,7 @@
         <v>411</v>
       </c>
       <c r="B223" s="17" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
@@ -31965,7 +31965,7 @@
         <v>412</v>
       </c>
       <c r="B224" s="17" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.2">
@@ -31973,7 +31973,7 @@
         <v>413</v>
       </c>
       <c r="B225" s="17" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.2">
@@ -31981,7 +31981,7 @@
         <v>414</v>
       </c>
       <c r="B226" s="17" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.2">
@@ -31989,7 +31989,7 @@
         <v>415</v>
       </c>
       <c r="B227" s="17" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.2">
@@ -31997,7 +31997,7 @@
         <v>416</v>
       </c>
       <c r="B228" s="17" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.2">
@@ -32021,7 +32021,7 @@
         <v>417</v>
       </c>
       <c r="B231" s="17" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.2">
@@ -32029,7 +32029,7 @@
         <v>418</v>
       </c>
       <c r="B232" s="17" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.2">
@@ -32037,7 +32037,7 @@
         <v>419</v>
       </c>
       <c r="B233" s="17" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.2">
@@ -32045,7 +32045,7 @@
         <v>420</v>
       </c>
       <c r="B234" s="17" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.2">
@@ -32053,7 +32053,7 @@
         <v>421</v>
       </c>
       <c r="B235" s="17" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.2">
@@ -32061,7 +32061,7 @@
         <v>422</v>
       </c>
       <c r="B236" s="17" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.2">
@@ -32069,7 +32069,7 @@
         <v>423</v>
       </c>
       <c r="B237" s="17" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.2">
@@ -32077,7 +32077,7 @@
         <v>424</v>
       </c>
       <c r="B238" s="17" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.2">
@@ -32085,7 +32085,7 @@
         <v>425</v>
       </c>
       <c r="B239" s="17" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.2">
@@ -32109,7 +32109,7 @@
         <v>426</v>
       </c>
       <c r="B242" s="17" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.2">
@@ -32117,7 +32117,7 @@
         <v>427</v>
       </c>
       <c r="B243" s="17" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.2">
@@ -32125,7 +32125,7 @@
         <v>428</v>
       </c>
       <c r="B244" s="17" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.2">
@@ -32133,7 +32133,7 @@
         <v>429</v>
       </c>
       <c r="B245" s="17" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.2">
@@ -32141,7 +32141,7 @@
         <v>430</v>
       </c>
       <c r="B246" s="17" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.2">
@@ -32149,7 +32149,7 @@
         <v>431</v>
       </c>
       <c r="B247" s="17" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.2">
@@ -32157,7 +32157,7 @@
         <v>432</v>
       </c>
       <c r="B248" s="17" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.2">
@@ -32165,7 +32165,7 @@
         <v>433</v>
       </c>
       <c r="B249" s="17" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.2">
@@ -32173,7 +32173,7 @@
         <v>434</v>
       </c>
       <c r="B250" s="17" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.2">
@@ -32213,7 +32213,7 @@
         <v>435</v>
       </c>
       <c r="B255" s="17" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.2">
@@ -32221,7 +32221,7 @@
         <v>436</v>
       </c>
       <c r="B256" s="17" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.2">
@@ -32237,7 +32237,7 @@
         <v>437</v>
       </c>
       <c r="B258" s="17" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.2">
@@ -32245,7 +32245,7 @@
         <v>438</v>
       </c>
       <c r="B259" s="17" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.2">
@@ -32253,7 +32253,7 @@
         <v>439</v>
       </c>
       <c r="B260" s="17" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.2">
@@ -32261,7 +32261,7 @@
         <v>440</v>
       </c>
       <c r="B261" s="17" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.2">
@@ -32269,7 +32269,7 @@
         <v>441</v>
       </c>
       <c r="B262" s="17" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.2">
@@ -32277,7 +32277,7 @@
         <v>442</v>
       </c>
       <c r="B263" s="17" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.2">
@@ -32285,7 +32285,7 @@
         <v>443</v>
       </c>
       <c r="B264" s="17" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.2">
@@ -32293,7 +32293,7 @@
         <v>444</v>
       </c>
       <c r="B265" s="17" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.2">
@@ -32301,7 +32301,7 @@
         <v>445</v>
       </c>
       <c r="B266" s="17" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.2">
@@ -32309,7 +32309,7 @@
         <v>446</v>
       </c>
       <c r="B267" s="17" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.2">
@@ -32557,7 +32557,7 @@
         <v>151</v>
       </c>
       <c r="B298" s="17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.2">
@@ -32733,7 +32733,7 @@
         <v>447</v>
       </c>
       <c r="B320" s="17" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.2">
@@ -32741,7 +32741,7 @@
         <v>448</v>
       </c>
       <c r="B321" s="17" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.2">
@@ -32757,7 +32757,7 @@
         <v>196</v>
       </c>
       <c r="B323" s="17" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.2">
@@ -32781,7 +32781,7 @@
         <v>449</v>
       </c>
       <c r="B326" s="17" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.2">

--- a/wwwroot/template/TemPlateQuote.xlsx
+++ b/wwwroot/template/TemPlateQuote.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\khanhmf\Cost Managerment\wwwroot\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D24112-D211-467D-AC3A-8F6AF1A67275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28921A7A-4735-4D7B-902D-FD1C66E91630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F4BD22E2-5202-4BAA-B608-770E176E4E09}"/>
   </bookViews>
@@ -3579,13 +3579,34 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3607,24 +3628,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3634,18 +3646,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4123,18 +4123,18 @@
     </row>
     <row r="4" spans="1:32" ht="11.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9"/>
-      <c r="B4" s="49" t="s">
+      <c r="B4" s="38" t="s">
         <v>213</v>
       </c>
-      <c r="C4" s="49"/>
-      <c r="D4" s="50"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="39"/>
       <c r="E4" s="25"/>
       <c r="F4" s="25"/>
       <c r="G4" s="25"/>
-      <c r="H4" s="49" t="s">
+      <c r="H4" s="38" t="s">
         <v>214</v>
       </c>
-      <c r="I4" s="51"/>
+      <c r="I4" s="40"/>
       <c r="J4" s="9"/>
       <c r="K4" s="25"/>
       <c r="M4" s="9"/>
@@ -4156,14 +4156,14 @@
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="9"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="50"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="39"/>
       <c r="E5" s="25"/>
       <c r="F5" s="25"/>
       <c r="G5" s="25"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="51"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="40"/>
       <c r="J5" s="25"/>
       <c r="K5" s="25"/>
       <c r="L5" s="18"/>
@@ -4187,17 +4187,17 @@
       <c r="AD5" s="9"/>
     </row>
     <row r="6" spans="1:32" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="43" t="s">
         <v>264</v>
       </c>
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
       <c r="J6" s="18"/>
       <c r="K6" s="18"/>
       <c r="L6" s="18"/>
@@ -4257,15 +4257,15 @@
       <c r="L7" s="26">
         <v>12</v>
       </c>
-      <c r="M7" s="41">
+      <c r="M7" s="48">
         <f>L7+1</f>
         <v>13</v>
       </c>
-      <c r="N7" s="42"/>
-      <c r="O7" s="42"/>
-      <c r="P7" s="42"/>
-      <c r="Q7" s="42"/>
-      <c r="R7" s="43"/>
+      <c r="N7" s="49"/>
+      <c r="O7" s="49"/>
+      <c r="P7" s="49"/>
+      <c r="Q7" s="49"/>
+      <c r="R7" s="50"/>
       <c r="S7" s="24">
         <v>14</v>
       </c>
@@ -4323,106 +4323,106 @@
       </c>
     </row>
     <row r="8" spans="1:32" s="7" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="47" t="s">
+      <c r="A8" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="41" t="s">
         <v>215</v>
       </c>
-      <c r="C8" s="39" t="s">
+      <c r="C8" s="41" t="s">
         <v>216</v>
       </c>
-      <c r="D8" s="39" t="s">
+      <c r="D8" s="41" t="s">
         <v>217</v>
       </c>
-      <c r="E8" s="39" t="s">
+      <c r="E8" s="41" t="s">
         <v>218</v>
       </c>
-      <c r="F8" s="39" t="s">
+      <c r="F8" s="41" t="s">
         <v>219</v>
       </c>
-      <c r="G8" s="39" t="s">
+      <c r="G8" s="41" t="s">
         <v>220</v>
       </c>
-      <c r="H8" s="39" t="s">
+      <c r="H8" s="41" t="s">
         <v>222</v>
       </c>
-      <c r="I8" s="39" t="s">
+      <c r="I8" s="41" t="s">
         <v>223</v>
       </c>
-      <c r="J8" s="39" t="s">
+      <c r="J8" s="41" t="s">
         <v>221</v>
       </c>
-      <c r="K8" s="39" t="s">
+      <c r="K8" s="41" t="s">
         <v>224</v>
       </c>
-      <c r="L8" s="39" t="s">
+      <c r="L8" s="41" t="s">
         <v>225</v>
       </c>
-      <c r="M8" s="44" t="s">
+      <c r="M8" s="51" t="s">
         <v>231</v>
       </c>
-      <c r="N8" s="45"/>
-      <c r="O8" s="45"/>
-      <c r="P8" s="45"/>
-      <c r="Q8" s="45"/>
-      <c r="R8" s="46"/>
-      <c r="S8" s="39" t="s">
+      <c r="N8" s="52"/>
+      <c r="O8" s="52"/>
+      <c r="P8" s="52"/>
+      <c r="Q8" s="52"/>
+      <c r="R8" s="53"/>
+      <c r="S8" s="41" t="s">
         <v>235</v>
       </c>
-      <c r="T8" s="39" t="s">
+      <c r="T8" s="41" t="s">
         <v>236</v>
       </c>
-      <c r="U8" s="39" t="s">
+      <c r="U8" s="41" t="s">
         <v>232</v>
       </c>
-      <c r="V8" s="39" t="s">
+      <c r="V8" s="41" t="s">
         <v>233</v>
       </c>
-      <c r="W8" s="39" t="s">
+      <c r="W8" s="41" t="s">
         <v>237</v>
       </c>
-      <c r="X8" s="39" t="s">
+      <c r="X8" s="41" t="s">
         <v>238</v>
       </c>
-      <c r="Y8" s="39" t="s">
+      <c r="Y8" s="41" t="s">
         <v>239</v>
       </c>
-      <c r="Z8" s="39" t="s">
+      <c r="Z8" s="41" t="s">
         <v>240</v>
       </c>
-      <c r="AA8" s="39" t="s">
+      <c r="AA8" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="AB8" s="39" t="s">
+      <c r="AB8" s="41" t="s">
         <v>242</v>
       </c>
-      <c r="AC8" s="39" t="s">
+      <c r="AC8" s="41" t="s">
         <v>243</v>
       </c>
-      <c r="AD8" s="39" t="s">
+      <c r="AD8" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="AE8" s="38" t="s">
+      <c r="AE8" s="47" t="s">
         <v>245</v>
       </c>
-      <c r="AF8" s="38" t="s">
+      <c r="AF8" s="47" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="9" spans="1:32" s="7" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A9" s="48"/>
-      <c r="B9" s="40"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="40"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="40"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="40"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="40"/>
+      <c r="A9" s="46"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="42"/>
+      <c r="L9" s="42"/>
       <c r="M9" s="19" t="s">
         <v>226</v>
       </c>
@@ -4441,20 +4441,20 @@
       <c r="R9" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="S9" s="40"/>
-      <c r="T9" s="40"/>
-      <c r="U9" s="40"/>
-      <c r="V9" s="40"/>
-      <c r="W9" s="40"/>
-      <c r="X9" s="40"/>
-      <c r="Y9" s="40"/>
-      <c r="Z9" s="40"/>
-      <c r="AA9" s="40"/>
-      <c r="AB9" s="40"/>
-      <c r="AC9" s="40"/>
-      <c r="AD9" s="40"/>
-      <c r="AE9" s="38"/>
-      <c r="AF9" s="38"/>
+      <c r="S9" s="42"/>
+      <c r="T9" s="42"/>
+      <c r="U9" s="42"/>
+      <c r="V9" s="42"/>
+      <c r="W9" s="42"/>
+      <c r="X9" s="42"/>
+      <c r="Y9" s="42"/>
+      <c r="Z9" s="42"/>
+      <c r="AA9" s="42"/>
+      <c r="AB9" s="42"/>
+      <c r="AC9" s="42"/>
+      <c r="AD9" s="42"/>
+      <c r="AE9" s="47"/>
+      <c r="AF9" s="47"/>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
@@ -29098,23 +29098,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="B4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="S8:S9"/>
-    <mergeCell ref="A6:I6"/>
-    <mergeCell ref="Y8:Y9"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="U8:U9"/>
-    <mergeCell ref="V8:V9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="X8:X9"/>
     <mergeCell ref="AE8:AE9"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="AF8:AF9"/>
@@ -29131,6 +29114,23 @@
     <mergeCell ref="Z8:Z9"/>
     <mergeCell ref="AA8:AA9"/>
     <mergeCell ref="AB8:AB9"/>
+    <mergeCell ref="Y8:Y9"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="X8:X9"/>
+    <mergeCell ref="B4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="S8:S9"/>
+    <mergeCell ref="A6:I6"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA10:AA569" xr:uid="{A48AEAD6-16A7-419C-9ADE-A3A1D0E68BC1}">
@@ -29193,11 +29193,11 @@
       </c>
     </row>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
       <c r="E2" s="20" t="s">
         <v>209</v>
       </c>
@@ -29207,11 +29207,11 @@
       <c r="G2" s="21"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="56" t="s">
         <v>201</v>
       </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
       <c r="E3" s="20" t="s">
         <v>209</v>
       </c>
@@ -29226,10 +29226,10 @@
       <c r="B4" s="29">
         <v>1</v>
       </c>
-      <c r="C4" s="55" t="s">
+      <c r="C4" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="56"/>
+      <c r="D4" s="60"/>
       <c r="E4" s="20" t="s">
         <v>204</v>
       </c>
@@ -29242,10 +29242,10 @@
       <c r="B5" s="29">
         <v>2</v>
       </c>
-      <c r="C5" s="57" t="s">
+      <c r="C5" s="54" t="s">
         <v>215</v>
       </c>
-      <c r="D5" s="58"/>
+      <c r="D5" s="55"/>
       <c r="E5" s="20" t="s">
         <v>204</v>
       </c>
@@ -29257,10 +29257,10 @@
       <c r="B6" s="29">
         <v>3</v>
       </c>
-      <c r="C6" s="57" t="s">
+      <c r="C6" s="54" t="s">
         <v>216</v>
       </c>
-      <c r="D6" s="58"/>
+      <c r="D6" s="55"/>
       <c r="E6" s="20" t="s">
         <v>209</v>
       </c>
@@ -29275,10 +29275,10 @@
       <c r="B7" s="29">
         <v>4</v>
       </c>
-      <c r="C7" s="57" t="s">
+      <c r="C7" s="54" t="s">
         <v>217</v>
       </c>
-      <c r="D7" s="58"/>
+      <c r="D7" s="55"/>
       <c r="E7" s="20" t="s">
         <v>209</v>
       </c>
@@ -29293,10 +29293,10 @@
       <c r="B8" s="29">
         <v>5</v>
       </c>
-      <c r="C8" s="57" t="s">
+      <c r="C8" s="54" t="s">
         <v>218</v>
       </c>
-      <c r="D8" s="58"/>
+      <c r="D8" s="55"/>
       <c r="E8" s="20" t="s">
         <v>206</v>
       </c>
@@ -29311,10 +29311,10 @@
       <c r="B9" s="29">
         <v>6</v>
       </c>
-      <c r="C9" s="57" t="s">
+      <c r="C9" s="54" t="s">
         <v>219</v>
       </c>
-      <c r="D9" s="58"/>
+      <c r="D9" s="55"/>
       <c r="E9" s="20" t="s">
         <v>204</v>
       </c>
@@ -29329,10 +29329,10 @@
       <c r="B10" s="29">
         <v>7</v>
       </c>
-      <c r="C10" s="57" t="s">
+      <c r="C10" s="54" t="s">
         <v>220</v>
       </c>
-      <c r="D10" s="58"/>
+      <c r="D10" s="55"/>
       <c r="E10" s="20" t="s">
         <v>209</v>
       </c>
@@ -29347,10 +29347,10 @@
       <c r="B11" s="29">
         <v>8</v>
       </c>
-      <c r="C11" s="57" t="s">
+      <c r="C11" s="54" t="s">
         <v>222</v>
       </c>
-      <c r="D11" s="58"/>
+      <c r="D11" s="55"/>
       <c r="E11" s="20" t="s">
         <v>209</v>
       </c>
@@ -29365,10 +29365,10 @@
       <c r="B12" s="29">
         <v>9</v>
       </c>
-      <c r="C12" s="57" t="s">
+      <c r="C12" s="54" t="s">
         <v>223</v>
       </c>
-      <c r="D12" s="58"/>
+      <c r="D12" s="55"/>
       <c r="E12" s="20" t="s">
         <v>209</v>
       </c>
@@ -29381,10 +29381,10 @@
       <c r="B13" s="29">
         <v>10</v>
       </c>
-      <c r="C13" s="57" t="s">
+      <c r="C13" s="54" t="s">
         <v>221</v>
       </c>
-      <c r="D13" s="58"/>
+      <c r="D13" s="55"/>
       <c r="E13" s="20" t="s">
         <v>204</v>
       </c>
@@ -29397,10 +29397,10 @@
       <c r="B14" s="29">
         <v>11</v>
       </c>
-      <c r="C14" s="57" t="s">
+      <c r="C14" s="54" t="s">
         <v>224</v>
       </c>
-      <c r="D14" s="58"/>
+      <c r="D14" s="55"/>
       <c r="E14" s="20" t="s">
         <v>204</v>
       </c>
@@ -29413,10 +29413,10 @@
       <c r="B15" s="29">
         <v>12</v>
       </c>
-      <c r="C15" s="57" t="s">
+      <c r="C15" s="54" t="s">
         <v>225</v>
       </c>
-      <c r="D15" s="58"/>
+      <c r="D15" s="55"/>
       <c r="E15" s="20" t="s">
         <v>209</v>
       </c>
@@ -29428,11 +29428,11 @@
       </c>
     </row>
     <row r="16" spans="2:7" ht="72" x14ac:dyDescent="0.25">
-      <c r="B16" s="60">
+      <c r="B16" s="57">
         <f>B15+1</f>
         <v>13</v>
       </c>
-      <c r="C16" s="54" t="s">
+      <c r="C16" s="58" t="s">
         <v>231</v>
       </c>
       <c r="D16" s="30" t="s">
@@ -29449,8 +29449,8 @@
       </c>
     </row>
     <row r="17" spans="2:7" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="60"/>
-      <c r="C17" s="54"/>
+      <c r="B17" s="57"/>
+      <c r="C17" s="58"/>
       <c r="D17" s="30" t="s">
         <v>227</v>
       </c>
@@ -29465,8 +29465,8 @@
       </c>
     </row>
     <row r="18" spans="2:7" ht="72" x14ac:dyDescent="0.25">
-      <c r="B18" s="60"/>
-      <c r="C18" s="54"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="58"/>
       <c r="D18" s="30" t="s">
         <v>228</v>
       </c>
@@ -29481,8 +29481,8 @@
       </c>
     </row>
     <row r="19" spans="2:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="B19" s="60"/>
-      <c r="C19" s="54"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="58"/>
       <c r="D19" s="30" t="s">
         <v>229</v>
       </c>
@@ -29497,8 +29497,8 @@
       </c>
     </row>
     <row r="20" spans="2:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="B20" s="60"/>
-      <c r="C20" s="54"/>
+      <c r="B20" s="57"/>
+      <c r="C20" s="58"/>
       <c r="D20" s="30" t="s">
         <v>230</v>
       </c>
@@ -29513,8 +29513,8 @@
       </c>
     </row>
     <row r="21" spans="2:7" ht="48" x14ac:dyDescent="0.25">
-      <c r="B21" s="60"/>
-      <c r="C21" s="54"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="58"/>
       <c r="D21" s="30" t="s">
         <v>234</v>
       </c>
@@ -29532,10 +29532,10 @@
       <c r="B22" s="31">
         <v>14</v>
       </c>
-      <c r="C22" s="57" t="s">
+      <c r="C22" s="54" t="s">
         <v>235</v>
       </c>
-      <c r="D22" s="58"/>
+      <c r="D22" s="55"/>
       <c r="E22" s="20" t="s">
         <v>206</v>
       </c>
@@ -29551,10 +29551,10 @@
         <f t="shared" ref="B23:B35" si="0">B22+1</f>
         <v>15</v>
       </c>
-      <c r="C23" s="57" t="s">
+      <c r="C23" s="54" t="s">
         <v>236</v>
       </c>
-      <c r="D23" s="58"/>
+      <c r="D23" s="55"/>
       <c r="E23" s="20" t="s">
         <v>206</v>
       </c>
@@ -29570,10 +29570,10 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C24" s="57" t="s">
+      <c r="C24" s="54" t="s">
         <v>232</v>
       </c>
-      <c r="D24" s="58"/>
+      <c r="D24" s="55"/>
       <c r="E24" s="20" t="s">
         <v>206</v>
       </c>
@@ -29589,10 +29589,10 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C25" s="57" t="s">
+      <c r="C25" s="54" t="s">
         <v>233</v>
       </c>
-      <c r="D25" s="58"/>
+      <c r="D25" s="55"/>
       <c r="E25" s="20" t="s">
         <v>206</v>
       </c>
@@ -29608,10 +29608,10 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C26" s="57" t="s">
+      <c r="C26" s="54" t="s">
         <v>237</v>
       </c>
-      <c r="D26" s="58"/>
+      <c r="D26" s="55"/>
       <c r="E26" s="20" t="s">
         <v>211</v>
       </c>
@@ -29627,10 +29627,10 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C27" s="57" t="s">
+      <c r="C27" s="54" t="s">
         <v>238</v>
       </c>
-      <c r="D27" s="58"/>
+      <c r="D27" s="55"/>
       <c r="E27" s="20" t="s">
         <v>209</v>
       </c>
@@ -29646,10 +29646,10 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C28" s="57" t="s">
+      <c r="C28" s="54" t="s">
         <v>239</v>
       </c>
-      <c r="D28" s="58"/>
+      <c r="D28" s="55"/>
       <c r="E28" s="20" t="s">
         <v>209</v>
       </c>
@@ -29665,10 +29665,10 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C29" s="57" t="s">
+      <c r="C29" s="54" t="s">
         <v>240</v>
       </c>
-      <c r="D29" s="58"/>
+      <c r="D29" s="55"/>
       <c r="E29" s="20" t="s">
         <v>209</v>
       </c>
@@ -29684,10 +29684,10 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C30" s="57" t="s">
+      <c r="C30" s="54" t="s">
         <v>241</v>
       </c>
-      <c r="D30" s="58"/>
+      <c r="D30" s="55"/>
       <c r="E30" s="20" t="s">
         <v>204</v>
       </c>
@@ -29703,10 +29703,10 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C31" s="57" t="s">
+      <c r="C31" s="54" t="s">
         <v>242</v>
       </c>
-      <c r="D31" s="58"/>
+      <c r="D31" s="55"/>
       <c r="E31" s="20" t="s">
         <v>204</v>
       </c>
@@ -29722,10 +29722,10 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C32" s="57" t="s">
+      <c r="C32" s="54" t="s">
         <v>243</v>
       </c>
-      <c r="D32" s="58"/>
+      <c r="D32" s="55"/>
       <c r="E32" s="20" t="s">
         <v>204</v>
       </c>
@@ -29739,10 +29739,10 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C33" s="57" t="s">
+      <c r="C33" s="54" t="s">
         <v>244</v>
       </c>
-      <c r="D33" s="58"/>
+      <c r="D33" s="55"/>
       <c r="E33" s="20" t="s">
         <v>204</v>
       </c>
@@ -29758,10 +29758,10 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C34" s="54" t="s">
+      <c r="C34" s="58" t="s">
         <v>245</v>
       </c>
-      <c r="D34" s="54"/>
+      <c r="D34" s="58"/>
       <c r="E34" s="20" t="s">
         <v>206</v>
       </c>
@@ -29777,10 +29777,10 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C35" s="54" t="s">
+      <c r="C35" s="58" t="s">
         <v>246</v>
       </c>
-      <c r="D35" s="54"/>
+      <c r="D35" s="58"/>
       <c r="E35" s="20" t="s">
         <v>206</v>
       </c>
@@ -29794,20 +29794,6 @@
   </sheetData>
   <autoFilter ref="B1:H35" xr:uid="{9A62EE61-DA4A-4471-B605-47242F0A4DEA}"/>
   <mergeCells count="30">
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="B16:B21"/>
-    <mergeCell ref="C16:C21"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="C4:D4"/>
@@ -29824,6 +29810,20 @@
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B16:B21"/>
+    <mergeCell ref="C16:C21"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
